--- a/src/data/AFCARS.xlsx
+++ b/src/data/AFCARS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="67">
   <si>
     <t>State</t>
   </si>
@@ -243,7 +243,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,6 +260,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -279,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -337,7 +343,15 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -672,7 +686,10 @@
         <v>0.4245024022</v>
       </c>
       <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
+      <c r="M3" s="7">
+        <f>SUM(C2:C53)</f>
+        <v>360536</v>
+      </c>
       <c r="N3" s="13"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
@@ -6506,2536 +6523,4572 @@
       </c>
     </row>
     <row r="158">
-      <c r="I158" s="19"/>
+      <c r="A158" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B158" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C158" s="3">
+        <v>2512.0</v>
+      </c>
+      <c r="D158" s="3">
+        <v>907.0</v>
+      </c>
+      <c r="E158" s="3">
+        <v>829.0</v>
+      </c>
+      <c r="F158" s="3">
+        <v>242.0</v>
+      </c>
+      <c r="G158" s="3">
+        <v>214.0</v>
+      </c>
+      <c r="H158" s="20">
+        <v>0.548</v>
+      </c>
+      <c r="J158" s="21"/>
     </row>
     <row r="159">
-      <c r="I159" s="19"/>
+      <c r="A159" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B159" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C159" s="3">
+        <v>5797.0</v>
+      </c>
+      <c r="D159" s="3">
+        <v>3602.0</v>
+      </c>
+      <c r="E159" s="3">
+        <v>924.0</v>
+      </c>
+      <c r="F159" s="3">
+        <v>352.0</v>
+      </c>
+      <c r="G159" s="3">
+        <v>611.0</v>
+      </c>
+      <c r="H159" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="J159" s="21"/>
     </row>
     <row r="160">
-      <c r="I160" s="19"/>
+      <c r="A160" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B160" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C160" s="3">
+        <v>3444.0</v>
+      </c>
+      <c r="D160" s="3">
+        <v>1546.0</v>
+      </c>
+      <c r="E160" s="3">
+        <v>823.0</v>
+      </c>
+      <c r="F160" s="3">
+        <v>126.0</v>
+      </c>
+      <c r="G160" s="3">
+        <v>698.0</v>
+      </c>
+      <c r="H160" s="20">
+        <v>0.383</v>
+      </c>
+      <c r="J160" s="21"/>
     </row>
     <row r="161">
-      <c r="I161" s="19"/>
+      <c r="A161" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C161" s="3">
+        <v>9058.0</v>
+      </c>
+      <c r="D161" s="3">
+        <v>2283.0</v>
+      </c>
+      <c r="E161" s="3">
+        <v>3792.0</v>
+      </c>
+      <c r="F161" s="3">
+        <v>1300.0</v>
+      </c>
+      <c r="G161" s="3">
+        <v>1719.0</v>
+      </c>
+      <c r="H161" s="20">
+        <v>0.464</v>
+      </c>
+      <c r="J161" s="21"/>
     </row>
     <row r="162">
-      <c r="I162" s="19"/>
+      <c r="A162" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B162" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C162" s="3">
+        <v>40305.0</v>
+      </c>
+      <c r="D162" s="3">
+        <v>20517.0</v>
+      </c>
+      <c r="E162" s="3">
+        <v>12356.0</v>
+      </c>
+      <c r="F162" s="3">
+        <v>6235.0</v>
+      </c>
+      <c r="G162" s="3">
+        <v>5923.0</v>
+      </c>
+      <c r="H162" s="20">
+        <v>0.479</v>
+      </c>
+      <c r="J162" s="21"/>
     </row>
     <row r="163">
-      <c r="I163" s="19"/>
+      <c r="A163" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B163" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C163" s="3">
+        <v>4158.0</v>
+      </c>
+      <c r="D163" s="3">
+        <v>1868.0</v>
+      </c>
+      <c r="E163" s="3">
+        <v>1164.0</v>
+      </c>
+      <c r="F163" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="G163" s="3">
+        <v>534.0</v>
+      </c>
+      <c r="H163" s="20">
+        <v>0.419</v>
+      </c>
+      <c r="J163" s="21"/>
     </row>
     <row r="164">
-      <c r="I164" s="19"/>
+      <c r="A164" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B164" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C164" s="3">
+        <v>3404.0</v>
+      </c>
+      <c r="D164" s="3">
+        <v>1315.0</v>
+      </c>
+      <c r="E164" s="3">
+        <v>1179.0</v>
+      </c>
+      <c r="F164" s="3">
+        <v>321.0</v>
+      </c>
+      <c r="G164" s="3">
+        <v>384.0</v>
+      </c>
+      <c r="H164" s="20">
+        <v>0.384</v>
+      </c>
+      <c r="J164" s="21"/>
     </row>
     <row r="165">
-      <c r="I165" s="19"/>
+      <c r="A165" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B165" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C165" s="3">
+        <v>545.0</v>
+      </c>
+      <c r="D165" s="3">
+        <v>286.0</v>
+      </c>
+      <c r="E165" s="3">
+        <v>118.0</v>
+      </c>
+      <c r="F165" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G165" s="3">
+        <v>63.0</v>
+      </c>
+      <c r="H165" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="J165" s="21"/>
     </row>
     <row r="166">
-      <c r="I166" s="19"/>
+      <c r="A166" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B166" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C166" s="3">
+        <v>535.0</v>
+      </c>
+      <c r="D166" s="3">
+        <v>325.0</v>
+      </c>
+      <c r="E166" s="3">
+        <v>68.0</v>
+      </c>
+      <c r="F166" s="3">
+        <v>61.0</v>
+      </c>
+      <c r="G166" s="3">
+        <v>91.0</v>
+      </c>
+      <c r="H166" s="20">
+        <v>0.327</v>
+      </c>
+      <c r="J166" s="21"/>
     </row>
     <row r="167">
-      <c r="I167" s="19"/>
+      <c r="A167" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B167" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C167" s="3">
+        <v>17453.0</v>
+      </c>
+      <c r="D167" s="3">
+        <v>7451.0</v>
+      </c>
+      <c r="E167" s="3">
+        <v>6319.0</v>
+      </c>
+      <c r="F167" s="3">
+        <v>870.0</v>
+      </c>
+      <c r="G167" s="3">
+        <v>4037.0</v>
+      </c>
+      <c r="H167" s="20">
+        <v>0.378</v>
+      </c>
+      <c r="J167" s="21"/>
     </row>
     <row r="168">
-      <c r="I168" s="19"/>
+      <c r="A168" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B168" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C168" s="3">
+        <v>11056.0</v>
+      </c>
+      <c r="D168" s="3">
+        <v>6819.0</v>
+      </c>
+      <c r="E168" s="3">
+        <v>2015.0</v>
+      </c>
+      <c r="F168" s="3">
+        <v>940.0</v>
+      </c>
+      <c r="G168" s="3">
+        <v>1247.0</v>
+      </c>
+      <c r="H168" s="20">
+        <v>0.415</v>
+      </c>
+      <c r="J168" s="21"/>
     </row>
     <row r="169">
-      <c r="I169" s="19"/>
+      <c r="A169" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B169" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C169" s="3">
+        <v>882.0</v>
+      </c>
+      <c r="D169" s="3">
+        <v>314.0</v>
+      </c>
+      <c r="E169" s="3">
+        <v>308.0</v>
+      </c>
+      <c r="F169" s="3">
+        <v>166.0</v>
+      </c>
+      <c r="G169" s="3">
+        <v>164.0</v>
+      </c>
+      <c r="H169" s="20">
+        <v>0.538</v>
+      </c>
+      <c r="J169" s="21"/>
     </row>
     <row r="170">
-      <c r="I170" s="19"/>
+      <c r="A170" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B170" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C170" s="3">
+        <v>3733.0</v>
+      </c>
+      <c r="D170" s="3">
+        <v>1383.0</v>
+      </c>
+      <c r="E170" s="3">
+        <v>1504.0</v>
+      </c>
+      <c r="F170" s="3">
+        <v>620.0</v>
+      </c>
+      <c r="G170" s="3">
+        <v>867.0</v>
+      </c>
+      <c r="H170" s="20">
+        <v>0.482</v>
+      </c>
+      <c r="J170" s="21"/>
     </row>
     <row r="171">
-      <c r="I171" s="19"/>
+      <c r="A171" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B171" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C171" s="3">
+        <v>1317.0</v>
+      </c>
+      <c r="D171" s="3">
+        <v>668.0</v>
+      </c>
+      <c r="E171" s="3">
+        <v>234.0</v>
+      </c>
+      <c r="F171" s="3">
+        <v>117.0</v>
+      </c>
+      <c r="G171" s="3">
+        <v>293.0</v>
+      </c>
+      <c r="H171" s="20">
+        <v>0.626</v>
+      </c>
+      <c r="J171" s="21"/>
     </row>
     <row r="172">
-      <c r="I172" s="19"/>
+      <c r="A172" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B172" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C172" s="3">
+        <v>18530.0</v>
+      </c>
+      <c r="D172" s="3">
+        <v>7547.0</v>
+      </c>
+      <c r="E172" s="3">
+        <v>8208.0</v>
+      </c>
+      <c r="F172" s="3">
+        <v>3039.0</v>
+      </c>
+      <c r="G172" s="3">
+        <v>2179.0</v>
+      </c>
+      <c r="H172" s="20">
+        <v>0.482</v>
+      </c>
+      <c r="J172" s="21"/>
     </row>
     <row r="173">
-      <c r="I173" s="19"/>
+      <c r="A173" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B173" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C173" s="3">
+        <v>11918.0</v>
+      </c>
+      <c r="D173" s="3">
+        <v>3546.0</v>
+      </c>
+      <c r="E173" s="3">
+        <v>5116.0</v>
+      </c>
+      <c r="F173" s="3">
+        <v>943.0</v>
+      </c>
+      <c r="G173" s="3">
+        <v>1557.0</v>
+      </c>
+      <c r="H173" s="20">
+        <v>0.547</v>
+      </c>
+      <c r="J173" s="21"/>
     </row>
     <row r="174">
-      <c r="I174" s="19"/>
+      <c r="A174" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B174" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C174" s="3">
+        <v>6203.0</v>
+      </c>
+      <c r="D174" s="3">
+        <v>2599.0</v>
+      </c>
+      <c r="E174" s="3">
+        <v>1967.0</v>
+      </c>
+      <c r="F174" s="3">
+        <v>1692.0</v>
+      </c>
+      <c r="G174" s="3">
+        <v>744.0</v>
+      </c>
+      <c r="H174" s="20">
+        <v>0.511</v>
+      </c>
+      <c r="J174" s="21"/>
     </row>
     <row r="175">
-      <c r="I175" s="19"/>
+      <c r="A175" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B175" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C175" s="3">
+        <v>7937.0</v>
+      </c>
+      <c r="D175" s="3">
+        <v>4516.0</v>
+      </c>
+      <c r="E175" s="3">
+        <v>1140.0</v>
+      </c>
+      <c r="F175" s="3">
+        <v>1516.0</v>
+      </c>
+      <c r="G175" s="3">
+        <v>1257.0</v>
+      </c>
+      <c r="H175" s="20">
+        <v>0.394</v>
+      </c>
+      <c r="J175" s="21"/>
     </row>
     <row r="176">
-      <c r="I176" s="19"/>
+      <c r="A176" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B176" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C176" s="3">
+        <v>4483.0</v>
+      </c>
+      <c r="D176" s="3">
+        <v>1949.0</v>
+      </c>
+      <c r="E176" s="3">
+        <v>1691.0</v>
+      </c>
+      <c r="F176" s="3">
+        <v>447.0</v>
+      </c>
+      <c r="G176" s="3">
+        <v>608.0</v>
+      </c>
+      <c r="H176" s="20">
+        <v>0.494</v>
+      </c>
+      <c r="J176" s="21"/>
     </row>
     <row r="177">
-      <c r="I177" s="19"/>
+      <c r="A177" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B177" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C177" s="3">
+        <v>8564.0</v>
+      </c>
+      <c r="D177" s="3">
+        <v>4757.0</v>
+      </c>
+      <c r="E177" s="3">
+        <v>146.0</v>
+      </c>
+      <c r="F177" s="3">
+        <v>1405.0</v>
+      </c>
+      <c r="G177" s="3">
+        <v>869.0</v>
+      </c>
+      <c r="H177" s="20">
+        <v>0.553</v>
+      </c>
+      <c r="J177" s="21"/>
     </row>
     <row r="178">
-      <c r="I178" s="19"/>
+      <c r="A178" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B178" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C178" s="3">
+        <v>3605.0</v>
+      </c>
+      <c r="D178" s="3">
+        <v>1494.0</v>
+      </c>
+      <c r="E178" s="3">
+        <v>839.0</v>
+      </c>
+      <c r="F178" s="3">
+        <v>172.0</v>
+      </c>
+      <c r="G178" s="3">
+        <v>333.0</v>
+      </c>
+      <c r="H178" s="20">
+        <v>0.343</v>
+      </c>
+      <c r="J178" s="21"/>
     </row>
     <row r="179">
-      <c r="I179" s="19"/>
+      <c r="A179" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B179" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C179" s="3">
+        <v>2469.0</v>
+      </c>
+      <c r="D179" s="3">
+        <v>993.0</v>
+      </c>
+      <c r="E179" s="3">
+        <v>882.0</v>
+      </c>
+      <c r="F179" s="3">
+        <v>223.0</v>
+      </c>
+      <c r="G179" s="3">
+        <v>385.0</v>
+      </c>
+      <c r="H179" s="20">
+        <v>0.448</v>
+      </c>
+      <c r="J179" s="21"/>
     </row>
     <row r="180">
-      <c r="I180" s="19"/>
+      <c r="A180" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B180" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C180" s="3">
+        <v>9593.0</v>
+      </c>
+      <c r="D180" s="3">
+        <v>2469.0</v>
+      </c>
+      <c r="E180" s="3">
+        <v>4667.0</v>
+      </c>
+      <c r="F180" s="3">
+        <v>1397.0</v>
+      </c>
+      <c r="G180" s="3">
+        <v>1426.0</v>
+      </c>
+      <c r="H180" s="20">
+        <v>0.361</v>
+      </c>
+      <c r="J180" s="21"/>
     </row>
     <row r="181">
-      <c r="I181" s="19"/>
+      <c r="A181" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B181" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C181" s="3">
+        <v>5851.0</v>
+      </c>
+      <c r="D181" s="3">
+        <v>1517.0</v>
+      </c>
+      <c r="E181" s="3">
+        <v>1941.0</v>
+      </c>
+      <c r="F181" s="3">
+        <v>865.0</v>
+      </c>
+      <c r="G181" s="3">
+        <v>693.0</v>
+      </c>
+      <c r="H181" s="20">
+        <v>0.547</v>
+      </c>
+      <c r="J181" s="21"/>
     </row>
     <row r="182">
-      <c r="I182" s="19"/>
+      <c r="A182" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B182" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C182" s="3">
+        <v>12673.0</v>
+      </c>
+      <c r="D182" s="3">
+        <v>2757.0</v>
+      </c>
+      <c r="E182" s="3">
+        <v>5004.0</v>
+      </c>
+      <c r="F182" s="3">
+        <v>367.0</v>
+      </c>
+      <c r="G182" s="3">
+        <v>1309.0</v>
+      </c>
+      <c r="H182" s="20">
+        <v>0.563</v>
+      </c>
+      <c r="J182" s="21"/>
     </row>
     <row r="183">
-      <c r="I183" s="19"/>
+      <c r="A183" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B183" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C183" s="3">
+        <v>3911.0</v>
+      </c>
+      <c r="D183" s="3">
+        <v>1558.0</v>
+      </c>
+      <c r="E183" s="3">
+        <v>1450.0</v>
+      </c>
+      <c r="F183" s="3">
+        <v>433.0</v>
+      </c>
+      <c r="G183" s="3">
+        <v>592.0</v>
+      </c>
+      <c r="H183" s="20">
+        <v>0.469</v>
+      </c>
+      <c r="J183" s="21"/>
     </row>
     <row r="184">
-      <c r="I184" s="19"/>
+      <c r="A184" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B184" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C184" s="3">
+        <v>2265.0</v>
+      </c>
+      <c r="D184" s="3">
+        <v>1577.0</v>
+      </c>
+      <c r="E184" s="3">
+        <v>116.0</v>
+      </c>
+      <c r="F184" s="3">
+        <v>255.0</v>
+      </c>
+      <c r="G184" s="3">
+        <v>264.0</v>
+      </c>
+      <c r="H184" s="20">
+        <v>0.559</v>
+      </c>
+      <c r="J184" s="21"/>
     </row>
     <row r="185">
-      <c r="I185" s="19"/>
+      <c r="A185" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B185" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C185" s="3">
+        <v>10774.0</v>
+      </c>
+      <c r="D185" s="3">
+        <v>5415.0</v>
+      </c>
+      <c r="E185" s="3">
+        <v>2454.0</v>
+      </c>
+      <c r="F185" s="3">
+        <v>1088.0</v>
+      </c>
+      <c r="G185" s="3">
+        <v>1205.0</v>
+      </c>
+      <c r="H185" s="20">
+        <v>0.323</v>
+      </c>
+      <c r="J185" s="21"/>
     </row>
     <row r="186">
-      <c r="I186" s="19"/>
+      <c r="A186" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B186" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C186" s="3">
+        <v>1237.0</v>
+      </c>
+      <c r="D186" s="3">
+        <v>636.0</v>
+      </c>
+      <c r="E186" s="3">
+        <v>304.0</v>
+      </c>
+      <c r="F186" s="3">
+        <v>319.0</v>
+      </c>
+      <c r="G186" s="3">
+        <v>238.0</v>
+      </c>
+      <c r="H186" s="20">
+        <v>0.476</v>
+      </c>
+      <c r="J186" s="21"/>
     </row>
     <row r="187">
-      <c r="I187" s="19"/>
+      <c r="A187" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B187" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C187" s="3">
+        <v>3743.0</v>
+      </c>
+      <c r="D187" s="3">
+        <v>1542.0</v>
+      </c>
+      <c r="E187" s="3">
+        <v>1112.0</v>
+      </c>
+      <c r="F187" s="3">
+        <v>259.0</v>
+      </c>
+      <c r="G187" s="3">
+        <v>485.0</v>
+      </c>
+      <c r="H187" s="20">
+        <v>0.509</v>
+      </c>
+      <c r="J187" s="21"/>
     </row>
     <row r="188">
-      <c r="I188" s="19"/>
+      <c r="A188" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B188" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C188" s="3">
+        <v>1164.0</v>
+      </c>
+      <c r="D188" s="3">
+        <v>511.0</v>
+      </c>
+      <c r="E188" s="3">
+        <v>278.0</v>
+      </c>
+      <c r="F188" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="G188" s="3">
+        <v>143.0</v>
+      </c>
+      <c r="H188" s="20">
+        <v>0.582</v>
+      </c>
+      <c r="J188" s="21"/>
     </row>
     <row r="189">
-      <c r="I189" s="19"/>
+      <c r="A189" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B189" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C189" s="3">
+        <v>2826.0</v>
+      </c>
+      <c r="D189" s="3">
+        <v>1419.0</v>
+      </c>
+      <c r="E189" s="3">
+        <v>1164.0</v>
+      </c>
+      <c r="F189" s="3">
+        <v>300.0</v>
+      </c>
+      <c r="G189" s="3">
+        <v>383.0</v>
+      </c>
+      <c r="H189" s="20">
+        <v>0.451</v>
+      </c>
+      <c r="J189" s="21"/>
     </row>
     <row r="190">
-      <c r="I190" s="19"/>
+      <c r="A190" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B190" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C190" s="3">
+        <v>2307.0</v>
+      </c>
+      <c r="D190" s="3">
+        <v>930.0</v>
+      </c>
+      <c r="E190" s="3">
+        <v>812.0</v>
+      </c>
+      <c r="F190" s="3">
+        <v>390.0</v>
+      </c>
+      <c r="G190" s="3">
+        <v>152.0</v>
+      </c>
+      <c r="H190" s="20">
+        <v>0.616</v>
+      </c>
+      <c r="J190" s="21"/>
     </row>
     <row r="191">
-      <c r="I191" s="19"/>
+      <c r="A191" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B191" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C191" s="3">
+        <v>4044.0</v>
+      </c>
+      <c r="D191" s="3">
+        <v>1609.0</v>
+      </c>
+      <c r="E191" s="3">
+        <v>1661.0</v>
+      </c>
+      <c r="F191" s="3">
+        <v>387.0</v>
+      </c>
+      <c r="G191" s="3">
+        <v>726.0</v>
+      </c>
+      <c r="H191" s="20">
+        <v>0.555</v>
+      </c>
+      <c r="J191" s="21"/>
     </row>
     <row r="192">
-      <c r="I192" s="19"/>
+      <c r="A192" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B192" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C192" s="3">
+        <v>14752.0</v>
+      </c>
+      <c r="D192" s="3">
+        <v>6360.0</v>
+      </c>
+      <c r="E192" s="3">
+        <v>5082.0</v>
+      </c>
+      <c r="F192" s="3">
+        <v>1073.0</v>
+      </c>
+      <c r="G192" s="3">
+        <v>1434.0</v>
+      </c>
+      <c r="H192" s="20">
+        <v>0.47</v>
+      </c>
+      <c r="J192" s="21"/>
     </row>
     <row r="193">
-      <c r="I193" s="19"/>
+      <c r="A193" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B193" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C193" s="3">
+        <v>15053.0</v>
+      </c>
+      <c r="D193" s="3">
+        <v>6786.0</v>
+      </c>
+      <c r="E193" s="3">
+        <v>3298.0</v>
+      </c>
+      <c r="F193" s="3">
+        <v>3794.0</v>
+      </c>
+      <c r="G193" s="3">
+        <v>1527.0</v>
+      </c>
+      <c r="H193" s="20">
+        <v>0.42</v>
+      </c>
+      <c r="J193" s="21"/>
     </row>
     <row r="194">
-      <c r="I194" s="19"/>
+      <c r="A194" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B194" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C194" s="3">
+        <v>6051.0</v>
+      </c>
+      <c r="D194" s="3">
+        <v>3067.0</v>
+      </c>
+      <c r="E194" s="3">
+        <v>1779.0</v>
+      </c>
+      <c r="F194" s="3">
+        <v>1289.0</v>
+      </c>
+      <c r="G194" s="3">
+        <v>1349.0</v>
+      </c>
+      <c r="H194" s="20">
+        <v>0.461</v>
+      </c>
+      <c r="J194" s="21"/>
     </row>
     <row r="195">
-      <c r="I195" s="19"/>
+      <c r="A195" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B195" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C195" s="3">
+        <v>4377.0</v>
+      </c>
+      <c r="D195" s="3">
+        <v>1829.0</v>
+      </c>
+      <c r="E195" s="3">
+        <v>1484.0</v>
+      </c>
+      <c r="F195" s="3">
+        <v>167.0</v>
+      </c>
+      <c r="G195" s="3">
+        <v>390.0</v>
+      </c>
+      <c r="H195" s="20">
+        <v>0.516</v>
+      </c>
+      <c r="J195" s="21"/>
     </row>
     <row r="196">
-      <c r="I196" s="19"/>
+      <c r="A196" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B196" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C196" s="3">
+        <v>11312.0</v>
+      </c>
+      <c r="D196" s="3">
+        <v>4616.0</v>
+      </c>
+      <c r="E196" s="3">
+        <v>2780.0</v>
+      </c>
+      <c r="F196" s="3">
+        <v>1346.0</v>
+      </c>
+      <c r="G196" s="3">
+        <v>1672.0</v>
+      </c>
+      <c r="H196" s="20">
+        <v>0.479</v>
+      </c>
+      <c r="J196" s="21"/>
     </row>
     <row r="197">
-      <c r="I197" s="19"/>
+      <c r="A197" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B197" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C197" s="3">
+        <v>2356.0</v>
+      </c>
+      <c r="D197" s="22"/>
+      <c r="E197" s="3">
+        <v>366.0</v>
+      </c>
+      <c r="F197" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="G197" s="3">
+        <v>34.0</v>
+      </c>
+      <c r="H197" s="20">
+        <v>0.522</v>
+      </c>
+      <c r="J197" s="21"/>
     </row>
     <row r="198">
-      <c r="I198" s="19"/>
+      <c r="A198" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B198" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C198" s="3">
+        <v>1692.0</v>
+      </c>
+      <c r="D198" s="3">
+        <v>483.0</v>
+      </c>
+      <c r="E198" s="3">
+        <v>459.0</v>
+      </c>
+      <c r="F198" s="3">
+        <v>46.0</v>
+      </c>
+      <c r="G198" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="H198" s="20">
+        <v>0.538</v>
+      </c>
+      <c r="J198" s="21"/>
     </row>
     <row r="199">
-      <c r="I199" s="19"/>
+      <c r="A199" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B199" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C199" s="3">
+        <v>3337.0</v>
+      </c>
+      <c r="D199" s="3">
+        <v>1883.0</v>
+      </c>
+      <c r="E199" s="3">
+        <v>821.0</v>
+      </c>
+      <c r="F199" s="3">
+        <v>718.0</v>
+      </c>
+      <c r="G199" s="3">
+        <v>562.0</v>
+      </c>
+      <c r="H199" s="20">
+        <v>0.452</v>
+      </c>
+      <c r="J199" s="21"/>
     </row>
     <row r="200">
-      <c r="I200" s="19"/>
+      <c r="A200" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B200" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C200" s="3">
+        <v>1685.0</v>
+      </c>
+      <c r="D200" s="3">
+        <v>871.0</v>
+      </c>
+      <c r="E200" s="3">
+        <v>447.0</v>
+      </c>
+      <c r="F200" s="3">
+        <v>473.0</v>
+      </c>
+      <c r="G200" s="3">
+        <v>260.0</v>
+      </c>
+      <c r="H200" s="20">
+        <v>0.471</v>
+      </c>
+      <c r="J200" s="21"/>
     </row>
     <row r="201">
-      <c r="I201" s="19"/>
+      <c r="A201" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B201" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C201" s="3">
+        <v>9123.0</v>
+      </c>
+      <c r="D201" s="3">
+        <v>1178.0</v>
+      </c>
+      <c r="E201" s="3">
+        <v>426.0</v>
+      </c>
+      <c r="F201" s="3">
+        <v>825.0</v>
+      </c>
+      <c r="G201" s="3">
+        <v>1165.0</v>
+      </c>
+      <c r="H201" s="20">
+        <v>0.434</v>
+      </c>
+      <c r="J201" s="21"/>
     </row>
     <row r="202">
-      <c r="I202" s="19"/>
+      <c r="A202" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B202" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C202" s="3">
+        <v>17225.0</v>
+      </c>
+      <c r="D202" s="3">
+        <v>7954.0</v>
+      </c>
+      <c r="E202" s="3">
+        <v>4986.0</v>
+      </c>
+      <c r="F202" s="3">
+        <v>3992.0</v>
+      </c>
+      <c r="G202" s="3">
+        <v>3075.0</v>
+      </c>
+      <c r="H202" s="20">
+        <v>0.39</v>
+      </c>
+      <c r="J202" s="21"/>
     </row>
     <row r="203">
-      <c r="I203" s="19"/>
+      <c r="A203" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B203" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C203" s="3">
+        <v>1706.0</v>
+      </c>
+      <c r="D203" s="3">
+        <v>805.0</v>
+      </c>
+      <c r="E203" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="F203" s="3">
+        <v>201.0</v>
+      </c>
+      <c r="G203" s="3">
+        <v>316.0</v>
+      </c>
+      <c r="H203" s="20">
+        <v>0.442</v>
+      </c>
+      <c r="J203" s="21"/>
     </row>
     <row r="204">
-      <c r="I204" s="19"/>
+      <c r="A204" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B204" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C204" s="3">
+        <v>5339.0</v>
+      </c>
+      <c r="D204" s="3">
+        <v>2870.0</v>
+      </c>
+      <c r="E204" s="3">
+        <v>542.0</v>
+      </c>
+      <c r="F204" s="3">
+        <v>978.0</v>
+      </c>
+      <c r="G204" s="3">
+        <v>571.0</v>
+      </c>
+      <c r="H204" s="20">
+        <v>0.285</v>
+      </c>
+      <c r="J204" s="21"/>
     </row>
     <row r="205">
-      <c r="I205" s="19"/>
+      <c r="A205" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B205" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C205" s="3">
+        <v>945.0</v>
+      </c>
+      <c r="D205" s="3">
+        <v>116.0</v>
+      </c>
+      <c r="E205" s="3">
+        <v>306.0</v>
+      </c>
+      <c r="F205" s="3">
+        <v>174.0</v>
+      </c>
+      <c r="G205" s="3">
+        <v>222.0</v>
+      </c>
+      <c r="H205" s="20">
+        <v>0.381</v>
+      </c>
+      <c r="J205" s="21"/>
     </row>
     <row r="206">
-      <c r="I206" s="19"/>
+      <c r="A206" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B206" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C206" s="3">
+        <v>6192.0</v>
+      </c>
+      <c r="D206" s="3">
+        <v>2070.0</v>
+      </c>
+      <c r="E206" s="3">
+        <v>2708.0</v>
+      </c>
+      <c r="F206" s="3">
+        <v>873.0</v>
+      </c>
+      <c r="G206" s="3">
+        <v>712.0</v>
+      </c>
+      <c r="H206" s="20">
+        <v>0.623</v>
+      </c>
+      <c r="J206" s="21"/>
     </row>
     <row r="207">
-      <c r="I207" s="19"/>
+      <c r="A207" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B207" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C207" s="3">
+        <v>6050.0</v>
+      </c>
+      <c r="D207" s="3">
+        <v>2849.0</v>
+      </c>
+      <c r="E207" s="3">
+        <v>2278.0</v>
+      </c>
+      <c r="F207" s="3">
+        <v>488.0</v>
+      </c>
+      <c r="G207" s="3">
+        <v>589.0</v>
+      </c>
+      <c r="H207" s="20">
+        <v>0.514</v>
+      </c>
+      <c r="J207" s="21"/>
     </row>
     <row r="208">
-      <c r="I208" s="19"/>
+      <c r="A208" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B208" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C208" s="3">
+        <v>6939.0</v>
+      </c>
+      <c r="D208" s="3">
+        <v>1923.0</v>
+      </c>
+      <c r="E208" s="3">
+        <v>3466.0</v>
+      </c>
+      <c r="F208" s="3">
+        <v>932.0</v>
+      </c>
+      <c r="G208" s="3">
+        <v>1064.0</v>
+      </c>
+      <c r="H208" s="20">
+        <v>0.472</v>
+      </c>
+      <c r="J208" s="21"/>
     </row>
     <row r="209">
-      <c r="I209" s="19"/>
+      <c r="A209" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B209" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="C209" s="3">
+        <v>625.0</v>
+      </c>
+      <c r="D209" s="3">
+        <v>97.0</v>
+      </c>
+      <c r="E209" s="3">
+        <v>97.0</v>
+      </c>
+      <c r="F209" s="22"/>
+      <c r="G209" s="3">
+        <v>84.0</v>
+      </c>
+      <c r="H209" s="20">
+        <v>0.717</v>
+      </c>
+      <c r="J209" s="21"/>
     </row>
     <row r="210">
-      <c r="I210" s="19"/>
+      <c r="A210" s="23"/>
+      <c r="I210" s="21"/>
     </row>
     <row r="211">
-      <c r="I211" s="19"/>
+      <c r="A211" s="23"/>
+      <c r="I211" s="21"/>
     </row>
     <row r="212">
-      <c r="I212" s="19"/>
+      <c r="A212" s="23"/>
+      <c r="I212" s="21"/>
     </row>
     <row r="213">
-      <c r="I213" s="19"/>
+      <c r="A213" s="23"/>
+      <c r="I213" s="21"/>
     </row>
     <row r="214">
-      <c r="I214" s="19"/>
+      <c r="A214" s="23"/>
+      <c r="I214" s="21"/>
     </row>
     <row r="215">
-      <c r="I215" s="19"/>
+      <c r="A215" s="23"/>
+      <c r="I215" s="21"/>
     </row>
     <row r="216">
-      <c r="I216" s="19"/>
+      <c r="A216" s="23"/>
+      <c r="I216" s="21"/>
     </row>
     <row r="217">
-      <c r="I217" s="19"/>
+      <c r="A217" s="23"/>
+      <c r="I217" s="21"/>
     </row>
     <row r="218">
-      <c r="I218" s="19"/>
+      <c r="A218" s="23"/>
+      <c r="I218" s="21"/>
     </row>
     <row r="219">
-      <c r="I219" s="19"/>
+      <c r="A219" s="23"/>
+      <c r="I219" s="21"/>
     </row>
     <row r="220">
-      <c r="I220" s="19"/>
+      <c r="A220" s="23"/>
+      <c r="I220" s="21"/>
     </row>
     <row r="221">
-      <c r="I221" s="19"/>
+      <c r="A221" s="23"/>
+      <c r="I221" s="21"/>
     </row>
     <row r="222">
-      <c r="I222" s="19"/>
+      <c r="A222" s="23"/>
+      <c r="I222" s="21"/>
     </row>
     <row r="223">
-      <c r="I223" s="19"/>
+      <c r="A223" s="23"/>
+      <c r="I223" s="21"/>
     </row>
     <row r="224">
-      <c r="I224" s="19"/>
+      <c r="A224" s="23"/>
+      <c r="I224" s="21"/>
     </row>
     <row r="225">
-      <c r="I225" s="19"/>
+      <c r="A225" s="23"/>
+      <c r="I225" s="21"/>
     </row>
     <row r="226">
-      <c r="I226" s="19"/>
+      <c r="A226" s="23"/>
+      <c r="I226" s="21"/>
     </row>
     <row r="227">
-      <c r="I227" s="19"/>
+      <c r="A227" s="23"/>
+      <c r="I227" s="21"/>
     </row>
     <row r="228">
-      <c r="I228" s="19"/>
+      <c r="A228" s="23"/>
+      <c r="I228" s="21"/>
     </row>
     <row r="229">
-      <c r="I229" s="19"/>
+      <c r="A229" s="23"/>
+      <c r="I229" s="21"/>
     </row>
     <row r="230">
-      <c r="I230" s="19"/>
+      <c r="A230" s="23"/>
+      <c r="I230" s="21"/>
     </row>
     <row r="231">
-      <c r="I231" s="19"/>
+      <c r="A231" s="23"/>
+      <c r="I231" s="21"/>
     </row>
     <row r="232">
-      <c r="I232" s="19"/>
+      <c r="A232" s="23"/>
+      <c r="I232" s="21"/>
     </row>
     <row r="233">
-      <c r="I233" s="19"/>
+      <c r="A233" s="23"/>
+      <c r="I233" s="21"/>
     </row>
     <row r="234">
-      <c r="I234" s="19"/>
+      <c r="A234" s="23"/>
+      <c r="I234" s="21"/>
     </row>
     <row r="235">
-      <c r="I235" s="19"/>
+      <c r="A235" s="23"/>
+      <c r="I235" s="21"/>
     </row>
     <row r="236">
-      <c r="I236" s="19"/>
+      <c r="A236" s="23"/>
+      <c r="I236" s="21"/>
     </row>
     <row r="237">
-      <c r="I237" s="19"/>
+      <c r="A237" s="23"/>
+      <c r="I237" s="21"/>
     </row>
     <row r="238">
-      <c r="I238" s="19"/>
+      <c r="A238" s="23"/>
+      <c r="I238" s="21"/>
     </row>
     <row r="239">
-      <c r="I239" s="19"/>
+      <c r="A239" s="23"/>
+      <c r="I239" s="21"/>
     </row>
     <row r="240">
-      <c r="I240" s="19"/>
+      <c r="A240" s="23"/>
+      <c r="I240" s="21"/>
     </row>
     <row r="241">
-      <c r="I241" s="19"/>
+      <c r="A241" s="23"/>
+      <c r="I241" s="21"/>
     </row>
     <row r="242">
-      <c r="I242" s="19"/>
+      <c r="A242" s="23"/>
+      <c r="I242" s="21"/>
     </row>
     <row r="243">
-      <c r="I243" s="19"/>
+      <c r="A243" s="23"/>
+      <c r="I243" s="21"/>
     </row>
     <row r="244">
-      <c r="I244" s="19"/>
+      <c r="A244" s="23"/>
+      <c r="I244" s="21"/>
     </row>
     <row r="245">
-      <c r="I245" s="19"/>
+      <c r="A245" s="23"/>
+      <c r="I245" s="21"/>
     </row>
     <row r="246">
-      <c r="I246" s="19"/>
+      <c r="A246" s="23"/>
+      <c r="I246" s="21"/>
     </row>
     <row r="247">
-      <c r="I247" s="19"/>
+      <c r="A247" s="23"/>
+      <c r="I247" s="21"/>
     </row>
     <row r="248">
-      <c r="I248" s="19"/>
+      <c r="A248" s="23"/>
+      <c r="I248" s="21"/>
     </row>
     <row r="249">
-      <c r="I249" s="19"/>
+      <c r="A249" s="23"/>
+      <c r="I249" s="21"/>
     </row>
     <row r="250">
-      <c r="I250" s="19"/>
+      <c r="A250" s="23"/>
+      <c r="I250" s="21"/>
     </row>
     <row r="251">
-      <c r="I251" s="19"/>
+      <c r="A251" s="23"/>
+      <c r="I251" s="21"/>
     </row>
     <row r="252">
-      <c r="I252" s="19"/>
+      <c r="A252" s="23"/>
+      <c r="I252" s="21"/>
     </row>
     <row r="253">
-      <c r="I253" s="19"/>
+      <c r="A253" s="23"/>
+      <c r="I253" s="21"/>
     </row>
     <row r="254">
-      <c r="I254" s="19"/>
+      <c r="A254" s="23"/>
+      <c r="I254" s="21"/>
     </row>
     <row r="255">
-      <c r="I255" s="19"/>
+      <c r="A255" s="23"/>
+      <c r="I255" s="21"/>
     </row>
     <row r="256">
-      <c r="I256" s="19"/>
+      <c r="A256" s="23"/>
+      <c r="I256" s="21"/>
     </row>
     <row r="257">
-      <c r="I257" s="19"/>
+      <c r="A257" s="23"/>
+      <c r="I257" s="21"/>
     </row>
     <row r="258">
-      <c r="I258" s="19"/>
+      <c r="A258" s="23"/>
+      <c r="I258" s="21"/>
     </row>
     <row r="259">
-      <c r="I259" s="19"/>
+      <c r="A259" s="23"/>
+      <c r="I259" s="21"/>
     </row>
     <row r="260">
-      <c r="I260" s="19"/>
+      <c r="A260" s="23"/>
+      <c r="I260" s="21"/>
     </row>
     <row r="261">
-      <c r="I261" s="19"/>
+      <c r="A261" s="23"/>
+      <c r="I261" s="21"/>
     </row>
     <row r="262">
-      <c r="I262" s="19"/>
+      <c r="A262" s="23"/>
+      <c r="I262" s="21"/>
     </row>
     <row r="263">
-      <c r="I263" s="19"/>
+      <c r="A263" s="23"/>
+      <c r="I263" s="21"/>
     </row>
     <row r="264">
-      <c r="I264" s="19"/>
+      <c r="A264" s="23"/>
+      <c r="I264" s="21"/>
     </row>
     <row r="265">
-      <c r="I265" s="19"/>
+      <c r="A265" s="23"/>
+      <c r="I265" s="21"/>
     </row>
     <row r="266">
-      <c r="I266" s="19"/>
+      <c r="A266" s="23"/>
+      <c r="I266" s="21"/>
     </row>
     <row r="267">
-      <c r="I267" s="19"/>
+      <c r="A267" s="23"/>
+      <c r="I267" s="21"/>
     </row>
     <row r="268">
-      <c r="I268" s="19"/>
+      <c r="A268" s="23"/>
+      <c r="I268" s="21"/>
     </row>
     <row r="269">
-      <c r="I269" s="19"/>
+      <c r="A269" s="23"/>
+      <c r="I269" s="21"/>
     </row>
     <row r="270">
-      <c r="I270" s="19"/>
+      <c r="A270" s="23"/>
+      <c r="I270" s="21"/>
     </row>
     <row r="271">
-      <c r="I271" s="19"/>
+      <c r="A271" s="23"/>
+      <c r="I271" s="21"/>
     </row>
     <row r="272">
-      <c r="I272" s="19"/>
+      <c r="A272" s="23"/>
+      <c r="I272" s="21"/>
     </row>
     <row r="273">
-      <c r="I273" s="19"/>
+      <c r="A273" s="23"/>
+      <c r="I273" s="21"/>
     </row>
     <row r="274">
-      <c r="I274" s="19"/>
+      <c r="A274" s="23"/>
+      <c r="I274" s="21"/>
     </row>
     <row r="275">
-      <c r="I275" s="19"/>
+      <c r="A275" s="23"/>
+      <c r="I275" s="21"/>
     </row>
     <row r="276">
-      <c r="I276" s="19"/>
+      <c r="A276" s="23"/>
+      <c r="I276" s="21"/>
     </row>
     <row r="277">
-      <c r="I277" s="19"/>
+      <c r="A277" s="23"/>
+      <c r="I277" s="21"/>
     </row>
     <row r="278">
-      <c r="I278" s="19"/>
+      <c r="A278" s="23"/>
+      <c r="I278" s="21"/>
     </row>
     <row r="279">
-      <c r="I279" s="19"/>
+      <c r="A279" s="23"/>
+      <c r="I279" s="21"/>
     </row>
     <row r="280">
-      <c r="I280" s="19"/>
+      <c r="A280" s="23"/>
+      <c r="I280" s="21"/>
     </row>
     <row r="281">
-      <c r="I281" s="19"/>
+      <c r="A281" s="23"/>
+      <c r="I281" s="21"/>
     </row>
     <row r="282">
-      <c r="I282" s="19"/>
+      <c r="A282" s="23"/>
+      <c r="I282" s="21"/>
     </row>
     <row r="283">
-      <c r="I283" s="19"/>
+      <c r="A283" s="23"/>
+      <c r="I283" s="21"/>
     </row>
     <row r="284">
-      <c r="I284" s="19"/>
+      <c r="A284" s="23"/>
+      <c r="I284" s="21"/>
     </row>
     <row r="285">
-      <c r="I285" s="19"/>
+      <c r="A285" s="23"/>
+      <c r="I285" s="21"/>
     </row>
     <row r="286">
-      <c r="I286" s="19"/>
+      <c r="A286" s="23"/>
+      <c r="I286" s="21"/>
     </row>
     <row r="287">
-      <c r="I287" s="19"/>
+      <c r="A287" s="23"/>
+      <c r="I287" s="21"/>
     </row>
     <row r="288">
-      <c r="I288" s="19"/>
+      <c r="A288" s="23"/>
+      <c r="I288" s="21"/>
     </row>
     <row r="289">
-      <c r="I289" s="19"/>
+      <c r="A289" s="23"/>
+      <c r="I289" s="21"/>
     </row>
     <row r="290">
-      <c r="I290" s="19"/>
+      <c r="A290" s="23"/>
+      <c r="I290" s="21"/>
     </row>
     <row r="291">
-      <c r="I291" s="19"/>
+      <c r="A291" s="23"/>
+      <c r="I291" s="21"/>
     </row>
     <row r="292">
-      <c r="I292" s="19"/>
+      <c r="A292" s="23"/>
+      <c r="I292" s="21"/>
     </row>
     <row r="293">
-      <c r="I293" s="19"/>
+      <c r="A293" s="23"/>
+      <c r="I293" s="21"/>
     </row>
     <row r="294">
-      <c r="I294" s="19"/>
+      <c r="A294" s="23"/>
+      <c r="I294" s="21"/>
     </row>
     <row r="295">
-      <c r="I295" s="19"/>
+      <c r="A295" s="23"/>
+      <c r="I295" s="21"/>
     </row>
     <row r="296">
-      <c r="I296" s="19"/>
+      <c r="A296" s="23"/>
+      <c r="I296" s="21"/>
     </row>
     <row r="297">
-      <c r="I297" s="19"/>
+      <c r="A297" s="23"/>
+      <c r="I297" s="21"/>
     </row>
     <row r="298">
-      <c r="I298" s="19"/>
+      <c r="A298" s="23"/>
+      <c r="I298" s="21"/>
     </row>
     <row r="299">
-      <c r="I299" s="19"/>
+      <c r="A299" s="23"/>
+      <c r="I299" s="21"/>
     </row>
     <row r="300">
-      <c r="I300" s="19"/>
+      <c r="A300" s="23"/>
+      <c r="I300" s="21"/>
     </row>
     <row r="301">
-      <c r="I301" s="19"/>
+      <c r="A301" s="23"/>
+      <c r="I301" s="21"/>
     </row>
     <row r="302">
-      <c r="I302" s="19"/>
+      <c r="A302" s="23"/>
+      <c r="I302" s="21"/>
     </row>
     <row r="303">
-      <c r="I303" s="19"/>
+      <c r="A303" s="23"/>
+      <c r="I303" s="21"/>
     </row>
     <row r="304">
-      <c r="I304" s="19"/>
+      <c r="A304" s="23"/>
+      <c r="I304" s="21"/>
     </row>
     <row r="305">
-      <c r="I305" s="19"/>
+      <c r="A305" s="23"/>
+      <c r="I305" s="21"/>
     </row>
     <row r="306">
-      <c r="I306" s="19"/>
+      <c r="A306" s="23"/>
+      <c r="I306" s="21"/>
     </row>
     <row r="307">
-      <c r="I307" s="19"/>
+      <c r="A307" s="23"/>
+      <c r="I307" s="21"/>
     </row>
     <row r="308">
-      <c r="I308" s="19"/>
+      <c r="A308" s="23"/>
+      <c r="I308" s="21"/>
     </row>
     <row r="309">
-      <c r="I309" s="19"/>
+      <c r="A309" s="23"/>
+      <c r="I309" s="21"/>
     </row>
     <row r="310">
-      <c r="I310" s="19"/>
+      <c r="A310" s="23"/>
+      <c r="I310" s="21"/>
     </row>
     <row r="311">
-      <c r="I311" s="19"/>
+      <c r="A311" s="23"/>
+      <c r="I311" s="21"/>
     </row>
     <row r="312">
-      <c r="I312" s="19"/>
+      <c r="A312" s="23"/>
+      <c r="I312" s="21"/>
     </row>
     <row r="313">
-      <c r="I313" s="19"/>
+      <c r="A313" s="23"/>
+      <c r="I313" s="21"/>
     </row>
     <row r="314">
-      <c r="I314" s="19"/>
+      <c r="A314" s="23"/>
+      <c r="I314" s="21"/>
     </row>
     <row r="315">
-      <c r="I315" s="19"/>
+      <c r="A315" s="23"/>
+      <c r="I315" s="21"/>
     </row>
     <row r="316">
-      <c r="I316" s="19"/>
+      <c r="A316" s="23"/>
+      <c r="I316" s="21"/>
     </row>
     <row r="317">
-      <c r="I317" s="19"/>
+      <c r="A317" s="23"/>
+      <c r="I317" s="21"/>
     </row>
     <row r="318">
-      <c r="I318" s="19"/>
+      <c r="A318" s="23"/>
+      <c r="I318" s="21"/>
     </row>
     <row r="319">
-      <c r="I319" s="19"/>
+      <c r="A319" s="23"/>
+      <c r="I319" s="21"/>
     </row>
     <row r="320">
-      <c r="I320" s="19"/>
+      <c r="A320" s="23"/>
+      <c r="I320" s="21"/>
     </row>
     <row r="321">
-      <c r="I321" s="19"/>
+      <c r="A321" s="23"/>
+      <c r="I321" s="21"/>
     </row>
     <row r="322">
-      <c r="I322" s="19"/>
+      <c r="A322" s="23"/>
+      <c r="I322" s="21"/>
     </row>
     <row r="323">
-      <c r="I323" s="19"/>
+      <c r="A323" s="23"/>
+      <c r="I323" s="21"/>
     </row>
     <row r="324">
-      <c r="I324" s="19"/>
+      <c r="A324" s="23"/>
+      <c r="I324" s="21"/>
     </row>
     <row r="325">
-      <c r="I325" s="19"/>
+      <c r="A325" s="23"/>
+      <c r="I325" s="21"/>
     </row>
     <row r="326">
-      <c r="I326" s="19"/>
+      <c r="A326" s="23"/>
+      <c r="I326" s="21"/>
     </row>
     <row r="327">
-      <c r="I327" s="19"/>
+      <c r="A327" s="23"/>
+      <c r="I327" s="21"/>
     </row>
     <row r="328">
-      <c r="I328" s="19"/>
+      <c r="A328" s="23"/>
+      <c r="I328" s="21"/>
     </row>
     <row r="329">
-      <c r="I329" s="19"/>
+      <c r="A329" s="23"/>
+      <c r="I329" s="21"/>
     </row>
     <row r="330">
-      <c r="I330" s="19"/>
+      <c r="A330" s="23"/>
+      <c r="I330" s="21"/>
     </row>
     <row r="331">
-      <c r="I331" s="19"/>
+      <c r="A331" s="23"/>
+      <c r="I331" s="21"/>
     </row>
     <row r="332">
-      <c r="I332" s="19"/>
+      <c r="A332" s="23"/>
+      <c r="I332" s="21"/>
     </row>
     <row r="333">
-      <c r="I333" s="19"/>
+      <c r="A333" s="23"/>
+      <c r="I333" s="21"/>
     </row>
     <row r="334">
-      <c r="I334" s="19"/>
+      <c r="A334" s="23"/>
+      <c r="I334" s="21"/>
     </row>
     <row r="335">
-      <c r="I335" s="19"/>
+      <c r="A335" s="23"/>
+      <c r="I335" s="21"/>
     </row>
     <row r="336">
-      <c r="I336" s="19"/>
+      <c r="A336" s="23"/>
+      <c r="I336" s="21"/>
     </row>
     <row r="337">
-      <c r="I337" s="19"/>
+      <c r="A337" s="23"/>
+      <c r="I337" s="21"/>
     </row>
     <row r="338">
-      <c r="I338" s="19"/>
+      <c r="A338" s="23"/>
+      <c r="I338" s="21"/>
     </row>
     <row r="339">
-      <c r="I339" s="19"/>
+      <c r="A339" s="23"/>
+      <c r="I339" s="21"/>
     </row>
     <row r="340">
-      <c r="I340" s="19"/>
+      <c r="A340" s="23"/>
+      <c r="I340" s="21"/>
     </row>
     <row r="341">
-      <c r="I341" s="19"/>
+      <c r="A341" s="23"/>
+      <c r="I341" s="21"/>
     </row>
     <row r="342">
-      <c r="I342" s="19"/>
+      <c r="A342" s="23"/>
+      <c r="I342" s="21"/>
     </row>
     <row r="343">
-      <c r="I343" s="19"/>
+      <c r="A343" s="23"/>
+      <c r="I343" s="21"/>
     </row>
     <row r="344">
-      <c r="I344" s="19"/>
+      <c r="A344" s="23"/>
+      <c r="I344" s="21"/>
     </row>
     <row r="345">
-      <c r="I345" s="19"/>
+      <c r="A345" s="23"/>
+      <c r="I345" s="21"/>
     </row>
     <row r="346">
-      <c r="I346" s="19"/>
+      <c r="A346" s="23"/>
+      <c r="I346" s="21"/>
     </row>
     <row r="347">
-      <c r="I347" s="19"/>
+      <c r="A347" s="23"/>
+      <c r="I347" s="21"/>
     </row>
     <row r="348">
-      <c r="I348" s="19"/>
+      <c r="A348" s="23"/>
+      <c r="I348" s="21"/>
     </row>
     <row r="349">
-      <c r="I349" s="19"/>
+      <c r="A349" s="23"/>
+      <c r="I349" s="21"/>
     </row>
     <row r="350">
-      <c r="I350" s="19"/>
+      <c r="A350" s="23"/>
+      <c r="I350" s="21"/>
     </row>
     <row r="351">
-      <c r="I351" s="19"/>
+      <c r="A351" s="23"/>
+      <c r="I351" s="21"/>
     </row>
     <row r="352">
-      <c r="I352" s="19"/>
+      <c r="A352" s="23"/>
+      <c r="I352" s="21"/>
     </row>
     <row r="353">
-      <c r="I353" s="19"/>
+      <c r="A353" s="23"/>
+      <c r="I353" s="21"/>
     </row>
     <row r="354">
-      <c r="I354" s="19"/>
+      <c r="A354" s="23"/>
+      <c r="I354" s="21"/>
     </row>
     <row r="355">
-      <c r="I355" s="19"/>
+      <c r="A355" s="23"/>
+      <c r="I355" s="21"/>
     </row>
     <row r="356">
-      <c r="I356" s="19"/>
+      <c r="A356" s="23"/>
+      <c r="I356" s="21"/>
     </row>
     <row r="357">
-      <c r="I357" s="19"/>
+      <c r="A357" s="23"/>
+      <c r="I357" s="21"/>
     </row>
     <row r="358">
-      <c r="I358" s="19"/>
+      <c r="A358" s="23"/>
+      <c r="I358" s="21"/>
     </row>
     <row r="359">
-      <c r="I359" s="19"/>
+      <c r="A359" s="23"/>
+      <c r="I359" s="21"/>
     </row>
     <row r="360">
-      <c r="I360" s="19"/>
+      <c r="A360" s="23"/>
+      <c r="I360" s="21"/>
     </row>
     <row r="361">
-      <c r="I361" s="19"/>
+      <c r="A361" s="23"/>
+      <c r="I361" s="21"/>
     </row>
     <row r="362">
-      <c r="I362" s="19"/>
+      <c r="A362" s="23"/>
+      <c r="I362" s="21"/>
     </row>
     <row r="363">
-      <c r="I363" s="19"/>
+      <c r="A363" s="23"/>
+      <c r="I363" s="21"/>
     </row>
     <row r="364">
-      <c r="I364" s="19"/>
+      <c r="A364" s="23"/>
+      <c r="I364" s="21"/>
     </row>
     <row r="365">
-      <c r="I365" s="19"/>
+      <c r="A365" s="23"/>
+      <c r="I365" s="21"/>
     </row>
     <row r="366">
-      <c r="I366" s="19"/>
+      <c r="A366" s="23"/>
+      <c r="I366" s="21"/>
     </row>
     <row r="367">
-      <c r="I367" s="19"/>
+      <c r="A367" s="23"/>
+      <c r="I367" s="21"/>
     </row>
     <row r="368">
-      <c r="I368" s="19"/>
+      <c r="A368" s="23"/>
+      <c r="I368" s="21"/>
     </row>
     <row r="369">
-      <c r="I369" s="19"/>
+      <c r="A369" s="23"/>
+      <c r="I369" s="21"/>
     </row>
     <row r="370">
-      <c r="I370" s="19"/>
+      <c r="A370" s="23"/>
+      <c r="I370" s="21"/>
     </row>
     <row r="371">
-      <c r="I371" s="19"/>
+      <c r="A371" s="23"/>
+      <c r="I371" s="21"/>
     </row>
     <row r="372">
-      <c r="I372" s="19"/>
+      <c r="A372" s="23"/>
+      <c r="I372" s="21"/>
     </row>
     <row r="373">
-      <c r="I373" s="19"/>
+      <c r="A373" s="23"/>
+      <c r="I373" s="21"/>
     </row>
     <row r="374">
-      <c r="I374" s="19"/>
+      <c r="A374" s="23"/>
+      <c r="I374" s="21"/>
     </row>
     <row r="375">
-      <c r="I375" s="19"/>
+      <c r="A375" s="23"/>
+      <c r="I375" s="21"/>
     </row>
     <row r="376">
-      <c r="I376" s="19"/>
+      <c r="A376" s="23"/>
+      <c r="I376" s="21"/>
     </row>
     <row r="377">
-      <c r="I377" s="19"/>
+      <c r="A377" s="23"/>
+      <c r="I377" s="21"/>
     </row>
     <row r="378">
-      <c r="I378" s="19"/>
+      <c r="A378" s="23"/>
+      <c r="I378" s="21"/>
     </row>
     <row r="379">
-      <c r="I379" s="19"/>
+      <c r="A379" s="23"/>
+      <c r="I379" s="21"/>
     </row>
     <row r="380">
-      <c r="I380" s="19"/>
+      <c r="A380" s="23"/>
+      <c r="I380" s="21"/>
     </row>
     <row r="381">
-      <c r="I381" s="19"/>
+      <c r="A381" s="23"/>
+      <c r="I381" s="21"/>
     </row>
     <row r="382">
-      <c r="I382" s="19"/>
+      <c r="A382" s="23"/>
+      <c r="I382" s="21"/>
     </row>
     <row r="383">
-      <c r="I383" s="19"/>
+      <c r="A383" s="23"/>
+      <c r="I383" s="21"/>
     </row>
     <row r="384">
-      <c r="I384" s="19"/>
+      <c r="A384" s="23"/>
+      <c r="I384" s="21"/>
     </row>
     <row r="385">
-      <c r="I385" s="19"/>
+      <c r="A385" s="23"/>
+      <c r="I385" s="21"/>
     </row>
     <row r="386">
-      <c r="I386" s="19"/>
+      <c r="A386" s="23"/>
+      <c r="I386" s="21"/>
     </row>
     <row r="387">
-      <c r="I387" s="19"/>
+      <c r="A387" s="23"/>
+      <c r="I387" s="21"/>
     </row>
     <row r="388">
-      <c r="I388" s="19"/>
+      <c r="A388" s="23"/>
+      <c r="I388" s="21"/>
     </row>
     <row r="389">
-      <c r="I389" s="19"/>
+      <c r="A389" s="23"/>
+      <c r="I389" s="21"/>
     </row>
     <row r="390">
-      <c r="I390" s="19"/>
+      <c r="A390" s="23"/>
+      <c r="I390" s="21"/>
     </row>
     <row r="391">
-      <c r="I391" s="19"/>
+      <c r="A391" s="23"/>
+      <c r="I391" s="21"/>
     </row>
     <row r="392">
-      <c r="I392" s="19"/>
+      <c r="A392" s="23"/>
+      <c r="I392" s="21"/>
     </row>
     <row r="393">
-      <c r="I393" s="19"/>
+      <c r="A393" s="23"/>
+      <c r="I393" s="21"/>
     </row>
     <row r="394">
-      <c r="I394" s="19"/>
+      <c r="A394" s="23"/>
+      <c r="I394" s="21"/>
     </row>
     <row r="395">
-      <c r="I395" s="19"/>
+      <c r="A395" s="23"/>
+      <c r="I395" s="21"/>
     </row>
     <row r="396">
-      <c r="I396" s="19"/>
+      <c r="A396" s="23"/>
+      <c r="I396" s="21"/>
     </row>
     <row r="397">
-      <c r="I397" s="19"/>
+      <c r="A397" s="23"/>
+      <c r="I397" s="21"/>
     </row>
     <row r="398">
-      <c r="I398" s="19"/>
+      <c r="A398" s="23"/>
+      <c r="I398" s="21"/>
     </row>
     <row r="399">
-      <c r="I399" s="19"/>
+      <c r="A399" s="23"/>
+      <c r="I399" s="21"/>
     </row>
     <row r="400">
-      <c r="I400" s="19"/>
+      <c r="A400" s="23"/>
+      <c r="I400" s="21"/>
     </row>
     <row r="401">
-      <c r="I401" s="19"/>
+      <c r="A401" s="23"/>
+      <c r="I401" s="21"/>
     </row>
     <row r="402">
-      <c r="I402" s="19"/>
+      <c r="A402" s="23"/>
+      <c r="I402" s="21"/>
     </row>
     <row r="403">
-      <c r="I403" s="19"/>
+      <c r="A403" s="23"/>
+      <c r="I403" s="21"/>
     </row>
     <row r="404">
-      <c r="I404" s="19"/>
+      <c r="A404" s="23"/>
+      <c r="I404" s="21"/>
     </row>
     <row r="405">
-      <c r="I405" s="19"/>
+      <c r="A405" s="23"/>
+      <c r="I405" s="21"/>
     </row>
     <row r="406">
-      <c r="I406" s="19"/>
+      <c r="A406" s="23"/>
+      <c r="I406" s="21"/>
     </row>
     <row r="407">
-      <c r="I407" s="19"/>
+      <c r="A407" s="23"/>
+      <c r="I407" s="21"/>
     </row>
     <row r="408">
-      <c r="I408" s="19"/>
+      <c r="A408" s="23"/>
+      <c r="I408" s="21"/>
     </row>
     <row r="409">
-      <c r="I409" s="19"/>
+      <c r="A409" s="23"/>
+      <c r="I409" s="21"/>
     </row>
     <row r="410">
-      <c r="I410" s="19"/>
+      <c r="A410" s="23"/>
+      <c r="I410" s="21"/>
     </row>
     <row r="411">
-      <c r="I411" s="19"/>
+      <c r="A411" s="23"/>
+      <c r="I411" s="21"/>
     </row>
     <row r="412">
-      <c r="I412" s="19"/>
+      <c r="A412" s="23"/>
+      <c r="I412" s="21"/>
     </row>
     <row r="413">
-      <c r="I413" s="19"/>
+      <c r="A413" s="23"/>
+      <c r="I413" s="21"/>
     </row>
     <row r="414">
-      <c r="I414" s="19"/>
+      <c r="A414" s="23"/>
+      <c r="I414" s="21"/>
     </row>
     <row r="415">
-      <c r="I415" s="19"/>
+      <c r="A415" s="23"/>
+      <c r="I415" s="21"/>
     </row>
     <row r="416">
-      <c r="I416" s="19"/>
+      <c r="A416" s="23"/>
+      <c r="I416" s="21"/>
     </row>
     <row r="417">
-      <c r="I417" s="19"/>
+      <c r="A417" s="23"/>
+      <c r="I417" s="21"/>
     </row>
     <row r="418">
-      <c r="I418" s="19"/>
+      <c r="A418" s="23"/>
+      <c r="I418" s="21"/>
     </row>
     <row r="419">
-      <c r="I419" s="19"/>
+      <c r="A419" s="23"/>
+      <c r="I419" s="21"/>
     </row>
     <row r="420">
-      <c r="I420" s="19"/>
+      <c r="A420" s="23"/>
+      <c r="I420" s="21"/>
     </row>
     <row r="421">
-      <c r="I421" s="19"/>
+      <c r="A421" s="23"/>
+      <c r="I421" s="21"/>
     </row>
     <row r="422">
-      <c r="I422" s="19"/>
+      <c r="A422" s="23"/>
+      <c r="I422" s="21"/>
     </row>
     <row r="423">
-      <c r="I423" s="19"/>
+      <c r="A423" s="23"/>
+      <c r="I423" s="21"/>
     </row>
     <row r="424">
-      <c r="I424" s="19"/>
+      <c r="A424" s="23"/>
+      <c r="I424" s="21"/>
     </row>
     <row r="425">
-      <c r="I425" s="19"/>
+      <c r="A425" s="23"/>
+      <c r="I425" s="21"/>
     </row>
     <row r="426">
-      <c r="I426" s="19"/>
+      <c r="A426" s="23"/>
+      <c r="I426" s="21"/>
     </row>
     <row r="427">
-      <c r="I427" s="19"/>
+      <c r="A427" s="23"/>
+      <c r="I427" s="21"/>
     </row>
     <row r="428">
-      <c r="I428" s="19"/>
+      <c r="A428" s="23"/>
+      <c r="I428" s="21"/>
     </row>
     <row r="429">
-      <c r="I429" s="19"/>
+      <c r="A429" s="23"/>
+      <c r="I429" s="21"/>
     </row>
     <row r="430">
-      <c r="I430" s="19"/>
+      <c r="A430" s="23"/>
+      <c r="I430" s="21"/>
     </row>
     <row r="431">
-      <c r="I431" s="19"/>
+      <c r="A431" s="23"/>
+      <c r="I431" s="21"/>
     </row>
     <row r="432">
-      <c r="I432" s="19"/>
+      <c r="A432" s="23"/>
+      <c r="I432" s="21"/>
     </row>
     <row r="433">
-      <c r="I433" s="19"/>
+      <c r="A433" s="23"/>
+      <c r="I433" s="21"/>
     </row>
     <row r="434">
-      <c r="I434" s="19"/>
+      <c r="A434" s="23"/>
+      <c r="I434" s="21"/>
     </row>
     <row r="435">
-      <c r="I435" s="19"/>
+      <c r="A435" s="23"/>
+      <c r="I435" s="21"/>
     </row>
     <row r="436">
-      <c r="I436" s="19"/>
+      <c r="A436" s="23"/>
+      <c r="I436" s="21"/>
     </row>
     <row r="437">
-      <c r="I437" s="19"/>
+      <c r="A437" s="23"/>
+      <c r="I437" s="21"/>
     </row>
     <row r="438">
-      <c r="I438" s="19"/>
+      <c r="A438" s="23"/>
+      <c r="I438" s="21"/>
     </row>
     <row r="439">
-      <c r="I439" s="19"/>
+      <c r="A439" s="23"/>
+      <c r="I439" s="21"/>
     </row>
     <row r="440">
-      <c r="I440" s="19"/>
+      <c r="A440" s="23"/>
+      <c r="I440" s="21"/>
     </row>
     <row r="441">
-      <c r="I441" s="19"/>
+      <c r="A441" s="23"/>
+      <c r="I441" s="21"/>
     </row>
     <row r="442">
-      <c r="I442" s="19"/>
+      <c r="A442" s="23"/>
+      <c r="I442" s="21"/>
     </row>
     <row r="443">
-      <c r="I443" s="19"/>
+      <c r="A443" s="23"/>
+      <c r="I443" s="21"/>
     </row>
     <row r="444">
-      <c r="I444" s="19"/>
+      <c r="A444" s="23"/>
+      <c r="I444" s="21"/>
     </row>
     <row r="445">
-      <c r="I445" s="19"/>
+      <c r="A445" s="23"/>
+      <c r="I445" s="21"/>
     </row>
     <row r="446">
-      <c r="I446" s="19"/>
+      <c r="A446" s="23"/>
+      <c r="I446" s="21"/>
     </row>
     <row r="447">
-      <c r="I447" s="19"/>
+      <c r="A447" s="23"/>
+      <c r="I447" s="21"/>
     </row>
     <row r="448">
-      <c r="I448" s="19"/>
+      <c r="A448" s="23"/>
+      <c r="I448" s="21"/>
     </row>
     <row r="449">
-      <c r="I449" s="19"/>
+      <c r="A449" s="23"/>
+      <c r="I449" s="21"/>
     </row>
     <row r="450">
-      <c r="I450" s="19"/>
+      <c r="A450" s="23"/>
+      <c r="I450" s="21"/>
     </row>
     <row r="451">
-      <c r="I451" s="19"/>
+      <c r="A451" s="23"/>
+      <c r="I451" s="21"/>
     </row>
     <row r="452">
-      <c r="I452" s="19"/>
+      <c r="A452" s="23"/>
+      <c r="I452" s="21"/>
     </row>
     <row r="453">
-      <c r="I453" s="19"/>
+      <c r="A453" s="23"/>
+      <c r="I453" s="21"/>
     </row>
     <row r="454">
-      <c r="I454" s="19"/>
+      <c r="A454" s="23"/>
+      <c r="I454" s="21"/>
     </row>
     <row r="455">
-      <c r="I455" s="19"/>
+      <c r="A455" s="23"/>
+      <c r="I455" s="21"/>
     </row>
     <row r="456">
-      <c r="I456" s="19"/>
+      <c r="A456" s="23"/>
+      <c r="I456" s="21"/>
     </row>
     <row r="457">
-      <c r="I457" s="19"/>
+      <c r="A457" s="23"/>
+      <c r="I457" s="21"/>
     </row>
     <row r="458">
-      <c r="I458" s="19"/>
+      <c r="A458" s="23"/>
+      <c r="I458" s="21"/>
     </row>
     <row r="459">
-      <c r="I459" s="19"/>
+      <c r="A459" s="23"/>
+      <c r="I459" s="21"/>
     </row>
     <row r="460">
-      <c r="I460" s="19"/>
+      <c r="A460" s="23"/>
+      <c r="I460" s="21"/>
     </row>
     <row r="461">
-      <c r="I461" s="19"/>
+      <c r="A461" s="23"/>
+      <c r="I461" s="21"/>
     </row>
     <row r="462">
-      <c r="I462" s="19"/>
+      <c r="A462" s="23"/>
+      <c r="I462" s="21"/>
     </row>
     <row r="463">
-      <c r="I463" s="19"/>
+      <c r="A463" s="23"/>
+      <c r="I463" s="21"/>
     </row>
     <row r="464">
-      <c r="I464" s="19"/>
+      <c r="A464" s="23"/>
+      <c r="I464" s="21"/>
     </row>
     <row r="465">
-      <c r="I465" s="19"/>
+      <c r="A465" s="23"/>
+      <c r="I465" s="21"/>
     </row>
     <row r="466">
-      <c r="I466" s="19"/>
+      <c r="A466" s="23"/>
+      <c r="I466" s="21"/>
     </row>
     <row r="467">
-      <c r="I467" s="19"/>
+      <c r="A467" s="23"/>
+      <c r="I467" s="21"/>
     </row>
     <row r="468">
-      <c r="I468" s="19"/>
+      <c r="A468" s="23"/>
+      <c r="I468" s="21"/>
     </row>
     <row r="469">
-      <c r="I469" s="19"/>
+      <c r="A469" s="23"/>
+      <c r="I469" s="21"/>
     </row>
     <row r="470">
-      <c r="I470" s="19"/>
+      <c r="A470" s="23"/>
+      <c r="I470" s="21"/>
     </row>
     <row r="471">
-      <c r="I471" s="19"/>
+      <c r="A471" s="23"/>
+      <c r="I471" s="21"/>
     </row>
     <row r="472">
-      <c r="I472" s="19"/>
+      <c r="A472" s="23"/>
+      <c r="I472" s="21"/>
     </row>
     <row r="473">
-      <c r="I473" s="19"/>
+      <c r="A473" s="23"/>
+      <c r="I473" s="21"/>
     </row>
     <row r="474">
-      <c r="I474" s="19"/>
+      <c r="A474" s="23"/>
+      <c r="I474" s="21"/>
     </row>
     <row r="475">
-      <c r="I475" s="19"/>
+      <c r="A475" s="23"/>
+      <c r="I475" s="21"/>
     </row>
     <row r="476">
-      <c r="I476" s="19"/>
+      <c r="A476" s="23"/>
+      <c r="I476" s="21"/>
     </row>
     <row r="477">
-      <c r="I477" s="19"/>
+      <c r="A477" s="23"/>
+      <c r="I477" s="21"/>
     </row>
     <row r="478">
-      <c r="I478" s="19"/>
+      <c r="A478" s="23"/>
+      <c r="I478" s="21"/>
     </row>
     <row r="479">
-      <c r="I479" s="19"/>
+      <c r="A479" s="23"/>
+      <c r="I479" s="21"/>
     </row>
     <row r="480">
-      <c r="I480" s="19"/>
+      <c r="A480" s="23"/>
+      <c r="I480" s="21"/>
     </row>
     <row r="481">
-      <c r="I481" s="19"/>
+      <c r="A481" s="23"/>
+      <c r="I481" s="21"/>
     </row>
     <row r="482">
-      <c r="I482" s="19"/>
+      <c r="A482" s="23"/>
+      <c r="I482" s="21"/>
     </row>
     <row r="483">
-      <c r="I483" s="19"/>
+      <c r="A483" s="23"/>
+      <c r="I483" s="21"/>
     </row>
     <row r="484">
-      <c r="I484" s="19"/>
+      <c r="A484" s="23"/>
+      <c r="I484" s="21"/>
     </row>
     <row r="485">
-      <c r="I485" s="19"/>
+      <c r="A485" s="23"/>
+      <c r="I485" s="21"/>
     </row>
     <row r="486">
-      <c r="I486" s="19"/>
+      <c r="A486" s="23"/>
+      <c r="I486" s="21"/>
     </row>
     <row r="487">
-      <c r="I487" s="19"/>
+      <c r="A487" s="23"/>
+      <c r="I487" s="21"/>
     </row>
     <row r="488">
-      <c r="I488" s="19"/>
+      <c r="A488" s="23"/>
+      <c r="I488" s="21"/>
     </row>
     <row r="489">
-      <c r="I489" s="19"/>
+      <c r="A489" s="23"/>
+      <c r="I489" s="21"/>
     </row>
     <row r="490">
-      <c r="I490" s="19"/>
+      <c r="A490" s="23"/>
+      <c r="I490" s="21"/>
     </row>
     <row r="491">
-      <c r="I491" s="19"/>
+      <c r="A491" s="23"/>
+      <c r="I491" s="21"/>
     </row>
     <row r="492">
-      <c r="I492" s="19"/>
+      <c r="A492" s="23"/>
+      <c r="I492" s="21"/>
     </row>
     <row r="493">
-      <c r="I493" s="19"/>
+      <c r="A493" s="23"/>
+      <c r="I493" s="21"/>
     </row>
     <row r="494">
-      <c r="I494" s="19"/>
+      <c r="A494" s="23"/>
+      <c r="I494" s="21"/>
     </row>
     <row r="495">
-      <c r="I495" s="19"/>
+      <c r="A495" s="23"/>
+      <c r="I495" s="21"/>
     </row>
     <row r="496">
-      <c r="I496" s="19"/>
+      <c r="A496" s="23"/>
+      <c r="I496" s="21"/>
     </row>
     <row r="497">
-      <c r="I497" s="19"/>
+      <c r="A497" s="23"/>
+      <c r="I497" s="21"/>
     </row>
     <row r="498">
-      <c r="I498" s="19"/>
+      <c r="A498" s="23"/>
+      <c r="I498" s="21"/>
     </row>
     <row r="499">
-      <c r="I499" s="19"/>
+      <c r="A499" s="23"/>
+      <c r="I499" s="21"/>
     </row>
     <row r="500">
-      <c r="I500" s="19"/>
+      <c r="A500" s="23"/>
+      <c r="I500" s="21"/>
     </row>
     <row r="501">
-      <c r="I501" s="19"/>
+      <c r="A501" s="23"/>
+      <c r="I501" s="21"/>
     </row>
     <row r="502">
-      <c r="I502" s="19"/>
+      <c r="A502" s="23"/>
+      <c r="I502" s="21"/>
     </row>
     <row r="503">
-      <c r="I503" s="19"/>
+      <c r="A503" s="23"/>
+      <c r="I503" s="21"/>
     </row>
     <row r="504">
-      <c r="I504" s="19"/>
+      <c r="A504" s="23"/>
+      <c r="I504" s="21"/>
     </row>
     <row r="505">
-      <c r="I505" s="19"/>
+      <c r="A505" s="23"/>
+      <c r="I505" s="21"/>
     </row>
     <row r="506">
-      <c r="I506" s="19"/>
+      <c r="A506" s="23"/>
+      <c r="I506" s="21"/>
     </row>
     <row r="507">
-      <c r="I507" s="19"/>
+      <c r="A507" s="23"/>
+      <c r="I507" s="21"/>
     </row>
     <row r="508">
-      <c r="I508" s="19"/>
+      <c r="A508" s="23"/>
+      <c r="I508" s="21"/>
     </row>
     <row r="509">
-      <c r="I509" s="19"/>
+      <c r="A509" s="23"/>
+      <c r="I509" s="21"/>
     </row>
     <row r="510">
-      <c r="I510" s="19"/>
+      <c r="A510" s="23"/>
+      <c r="I510" s="21"/>
     </row>
     <row r="511">
-      <c r="I511" s="19"/>
+      <c r="A511" s="23"/>
+      <c r="I511" s="21"/>
     </row>
     <row r="512">
-      <c r="I512" s="19"/>
+      <c r="A512" s="23"/>
+      <c r="I512" s="21"/>
     </row>
     <row r="513">
-      <c r="I513" s="19"/>
+      <c r="A513" s="23"/>
+      <c r="I513" s="21"/>
     </row>
     <row r="514">
-      <c r="I514" s="19"/>
+      <c r="A514" s="23"/>
+      <c r="I514" s="21"/>
     </row>
     <row r="515">
-      <c r="I515" s="19"/>
+      <c r="A515" s="23"/>
+      <c r="I515" s="21"/>
     </row>
     <row r="516">
-      <c r="I516" s="19"/>
+      <c r="A516" s="23"/>
+      <c r="I516" s="21"/>
     </row>
     <row r="517">
-      <c r="I517" s="19"/>
+      <c r="A517" s="23"/>
+      <c r="I517" s="21"/>
     </row>
     <row r="518">
-      <c r="I518" s="19"/>
+      <c r="A518" s="23"/>
+      <c r="I518" s="21"/>
     </row>
     <row r="519">
-      <c r="I519" s="19"/>
+      <c r="A519" s="23"/>
+      <c r="I519" s="21"/>
     </row>
     <row r="520">
-      <c r="I520" s="19"/>
+      <c r="A520" s="23"/>
+      <c r="I520" s="21"/>
     </row>
     <row r="521">
-      <c r="I521" s="19"/>
+      <c r="A521" s="23"/>
+      <c r="I521" s="21"/>
     </row>
     <row r="522">
-      <c r="I522" s="19"/>
+      <c r="A522" s="23"/>
+      <c r="I522" s="21"/>
     </row>
     <row r="523">
-      <c r="I523" s="19"/>
+      <c r="A523" s="23"/>
+      <c r="I523" s="21"/>
     </row>
     <row r="524">
-      <c r="I524" s="19"/>
+      <c r="A524" s="23"/>
+      <c r="I524" s="21"/>
     </row>
     <row r="525">
-      <c r="I525" s="19"/>
+      <c r="A525" s="23"/>
+      <c r="I525" s="21"/>
     </row>
     <row r="526">
-      <c r="I526" s="19"/>
+      <c r="A526" s="23"/>
+      <c r="I526" s="21"/>
     </row>
     <row r="527">
-      <c r="I527" s="19"/>
+      <c r="A527" s="23"/>
+      <c r="I527" s="21"/>
     </row>
     <row r="528">
-      <c r="I528" s="19"/>
+      <c r="A528" s="23"/>
+      <c r="I528" s="21"/>
     </row>
     <row r="529">
-      <c r="I529" s="19"/>
+      <c r="A529" s="23"/>
+      <c r="I529" s="21"/>
     </row>
     <row r="530">
-      <c r="I530" s="19"/>
+      <c r="A530" s="23"/>
+      <c r="I530" s="21"/>
     </row>
     <row r="531">
-      <c r="I531" s="19"/>
+      <c r="A531" s="23"/>
+      <c r="I531" s="21"/>
     </row>
     <row r="532">
-      <c r="I532" s="19"/>
+      <c r="A532" s="23"/>
+      <c r="I532" s="21"/>
     </row>
     <row r="533">
-      <c r="I533" s="19"/>
+      <c r="A533" s="23"/>
+      <c r="I533" s="21"/>
     </row>
     <row r="534">
-      <c r="I534" s="19"/>
+      <c r="A534" s="23"/>
+      <c r="I534" s="21"/>
     </row>
     <row r="535">
-      <c r="I535" s="19"/>
+      <c r="A535" s="23"/>
+      <c r="I535" s="21"/>
     </row>
     <row r="536">
-      <c r="I536" s="19"/>
+      <c r="A536" s="23"/>
+      <c r="I536" s="21"/>
     </row>
     <row r="537">
-      <c r="I537" s="19"/>
+      <c r="A537" s="23"/>
+      <c r="I537" s="21"/>
     </row>
     <row r="538">
-      <c r="I538" s="19"/>
+      <c r="A538" s="23"/>
+      <c r="I538" s="21"/>
     </row>
     <row r="539">
-      <c r="I539" s="19"/>
+      <c r="A539" s="23"/>
+      <c r="I539" s="21"/>
     </row>
     <row r="540">
-      <c r="I540" s="19"/>
+      <c r="A540" s="23"/>
+      <c r="I540" s="21"/>
     </row>
     <row r="541">
-      <c r="I541" s="19"/>
+      <c r="A541" s="23"/>
+      <c r="I541" s="21"/>
     </row>
     <row r="542">
-      <c r="I542" s="19"/>
+      <c r="A542" s="23"/>
+      <c r="I542" s="21"/>
     </row>
     <row r="543">
-      <c r="I543" s="19"/>
+      <c r="A543" s="23"/>
+      <c r="I543" s="21"/>
     </row>
     <row r="544">
-      <c r="I544" s="19"/>
+      <c r="A544" s="23"/>
+      <c r="I544" s="21"/>
     </row>
     <row r="545">
-      <c r="I545" s="19"/>
+      <c r="A545" s="23"/>
+      <c r="I545" s="21"/>
     </row>
     <row r="546">
-      <c r="I546" s="19"/>
+      <c r="A546" s="23"/>
+      <c r="I546" s="21"/>
     </row>
     <row r="547">
-      <c r="I547" s="19"/>
+      <c r="A547" s="23"/>
+      <c r="I547" s="21"/>
     </row>
     <row r="548">
-      <c r="I548" s="19"/>
+      <c r="A548" s="23"/>
+      <c r="I548" s="21"/>
     </row>
     <row r="549">
-      <c r="I549" s="19"/>
+      <c r="A549" s="23"/>
+      <c r="I549" s="21"/>
     </row>
     <row r="550">
-      <c r="I550" s="19"/>
+      <c r="A550" s="23"/>
+      <c r="I550" s="21"/>
     </row>
     <row r="551">
-      <c r="I551" s="19"/>
+      <c r="A551" s="23"/>
+      <c r="I551" s="21"/>
     </row>
     <row r="552">
-      <c r="I552" s="19"/>
+      <c r="A552" s="23"/>
+      <c r="I552" s="21"/>
     </row>
     <row r="553">
-      <c r="I553" s="19"/>
+      <c r="A553" s="23"/>
+      <c r="I553" s="21"/>
     </row>
     <row r="554">
-      <c r="I554" s="19"/>
+      <c r="A554" s="23"/>
+      <c r="I554" s="21"/>
     </row>
     <row r="555">
-      <c r="I555" s="19"/>
+      <c r="A555" s="23"/>
+      <c r="I555" s="21"/>
     </row>
     <row r="556">
-      <c r="I556" s="19"/>
+      <c r="A556" s="23"/>
+      <c r="I556" s="21"/>
     </row>
     <row r="557">
-      <c r="I557" s="19"/>
+      <c r="A557" s="23"/>
+      <c r="I557" s="21"/>
     </row>
     <row r="558">
-      <c r="I558" s="19"/>
+      <c r="A558" s="23"/>
+      <c r="I558" s="21"/>
     </row>
     <row r="559">
-      <c r="I559" s="19"/>
+      <c r="A559" s="23"/>
+      <c r="I559" s="21"/>
     </row>
     <row r="560">
-      <c r="I560" s="19"/>
+      <c r="A560" s="23"/>
+      <c r="I560" s="21"/>
     </row>
     <row r="561">
-      <c r="I561" s="19"/>
+      <c r="A561" s="23"/>
+      <c r="I561" s="21"/>
     </row>
     <row r="562">
-      <c r="I562" s="19"/>
+      <c r="A562" s="23"/>
+      <c r="I562" s="21"/>
     </row>
     <row r="563">
-      <c r="I563" s="19"/>
+      <c r="A563" s="23"/>
+      <c r="I563" s="21"/>
     </row>
     <row r="564">
-      <c r="I564" s="19"/>
+      <c r="A564" s="23"/>
+      <c r="I564" s="21"/>
     </row>
     <row r="565">
-      <c r="I565" s="19"/>
+      <c r="A565" s="23"/>
+      <c r="I565" s="21"/>
     </row>
     <row r="566">
-      <c r="I566" s="19"/>
+      <c r="A566" s="23"/>
+      <c r="I566" s="21"/>
     </row>
     <row r="567">
-      <c r="I567" s="19"/>
+      <c r="A567" s="23"/>
+      <c r="I567" s="21"/>
     </row>
     <row r="568">
-      <c r="I568" s="19"/>
+      <c r="A568" s="23"/>
+      <c r="I568" s="21"/>
     </row>
     <row r="569">
-      <c r="I569" s="19"/>
+      <c r="A569" s="23"/>
+      <c r="I569" s="21"/>
     </row>
     <row r="570">
-      <c r="I570" s="19"/>
+      <c r="A570" s="23"/>
+      <c r="I570" s="21"/>
     </row>
     <row r="571">
-      <c r="I571" s="19"/>
+      <c r="A571" s="23"/>
+      <c r="I571" s="21"/>
     </row>
     <row r="572">
-      <c r="I572" s="19"/>
+      <c r="A572" s="23"/>
+      <c r="I572" s="21"/>
     </row>
     <row r="573">
-      <c r="I573" s="19"/>
+      <c r="A573" s="23"/>
+      <c r="I573" s="21"/>
     </row>
     <row r="574">
-      <c r="I574" s="19"/>
+      <c r="A574" s="23"/>
+      <c r="I574" s="21"/>
     </row>
     <row r="575">
-      <c r="I575" s="19"/>
+      <c r="A575" s="23"/>
+      <c r="I575" s="21"/>
     </row>
     <row r="576">
-      <c r="I576" s="19"/>
+      <c r="A576" s="23"/>
+      <c r="I576" s="21"/>
     </row>
     <row r="577">
-      <c r="I577" s="19"/>
+      <c r="A577" s="23"/>
+      <c r="I577" s="21"/>
     </row>
     <row r="578">
-      <c r="I578" s="19"/>
+      <c r="A578" s="23"/>
+      <c r="I578" s="21"/>
     </row>
     <row r="579">
-      <c r="I579" s="19"/>
+      <c r="A579" s="23"/>
+      <c r="I579" s="21"/>
     </row>
     <row r="580">
-      <c r="I580" s="19"/>
+      <c r="A580" s="23"/>
+      <c r="I580" s="21"/>
     </row>
     <row r="581">
-      <c r="I581" s="19"/>
+      <c r="A581" s="23"/>
+      <c r="I581" s="21"/>
     </row>
     <row r="582">
-      <c r="I582" s="19"/>
+      <c r="A582" s="23"/>
+      <c r="I582" s="21"/>
     </row>
     <row r="583">
-      <c r="I583" s="19"/>
+      <c r="A583" s="23"/>
+      <c r="I583" s="21"/>
     </row>
     <row r="584">
-      <c r="I584" s="19"/>
+      <c r="A584" s="23"/>
+      <c r="I584" s="21"/>
     </row>
     <row r="585">
-      <c r="I585" s="19"/>
+      <c r="A585" s="23"/>
+      <c r="I585" s="21"/>
     </row>
     <row r="586">
-      <c r="I586" s="19"/>
+      <c r="A586" s="23"/>
+      <c r="I586" s="21"/>
     </row>
     <row r="587">
-      <c r="I587" s="19"/>
+      <c r="A587" s="23"/>
+      <c r="I587" s="21"/>
     </row>
     <row r="588">
-      <c r="I588" s="19"/>
+      <c r="A588" s="23"/>
+      <c r="I588" s="21"/>
     </row>
     <row r="589">
-      <c r="I589" s="19"/>
+      <c r="A589" s="23"/>
+      <c r="I589" s="21"/>
     </row>
     <row r="590">
-      <c r="I590" s="19"/>
+      <c r="A590" s="23"/>
+      <c r="I590" s="21"/>
     </row>
     <row r="591">
-      <c r="I591" s="19"/>
+      <c r="A591" s="23"/>
+      <c r="I591" s="21"/>
     </row>
     <row r="592">
-      <c r="I592" s="19"/>
+      <c r="A592" s="23"/>
+      <c r="I592" s="21"/>
     </row>
     <row r="593">
-      <c r="I593" s="19"/>
+      <c r="A593" s="23"/>
+      <c r="I593" s="21"/>
     </row>
     <row r="594">
-      <c r="I594" s="19"/>
+      <c r="A594" s="23"/>
+      <c r="I594" s="21"/>
     </row>
     <row r="595">
-      <c r="I595" s="19"/>
+      <c r="A595" s="23"/>
+      <c r="I595" s="21"/>
     </row>
     <row r="596">
-      <c r="I596" s="19"/>
+      <c r="A596" s="23"/>
+      <c r="I596" s="21"/>
     </row>
     <row r="597">
-      <c r="I597" s="19"/>
+      <c r="A597" s="23"/>
+      <c r="I597" s="21"/>
     </row>
     <row r="598">
-      <c r="I598" s="19"/>
+      <c r="A598" s="23"/>
+      <c r="I598" s="21"/>
     </row>
     <row r="599">
-      <c r="I599" s="19"/>
+      <c r="A599" s="23"/>
+      <c r="I599" s="21"/>
     </row>
     <row r="600">
-      <c r="I600" s="19"/>
+      <c r="A600" s="23"/>
+      <c r="I600" s="21"/>
     </row>
     <row r="601">
-      <c r="I601" s="19"/>
+      <c r="A601" s="23"/>
+      <c r="I601" s="21"/>
     </row>
     <row r="602">
-      <c r="I602" s="19"/>
+      <c r="A602" s="23"/>
+      <c r="I602" s="21"/>
     </row>
     <row r="603">
-      <c r="I603" s="19"/>
+      <c r="A603" s="23"/>
+      <c r="I603" s="21"/>
     </row>
     <row r="604">
-      <c r="I604" s="19"/>
+      <c r="A604" s="23"/>
+      <c r="I604" s="21"/>
     </row>
     <row r="605">
-      <c r="I605" s="19"/>
+      <c r="A605" s="23"/>
+      <c r="I605" s="21"/>
     </row>
     <row r="606">
-      <c r="I606" s="19"/>
+      <c r="A606" s="23"/>
+      <c r="I606" s="21"/>
     </row>
     <row r="607">
-      <c r="I607" s="19"/>
+      <c r="A607" s="23"/>
+      <c r="I607" s="21"/>
     </row>
     <row r="608">
-      <c r="I608" s="19"/>
+      <c r="A608" s="23"/>
+      <c r="I608" s="21"/>
     </row>
     <row r="609">
-      <c r="I609" s="19"/>
+      <c r="A609" s="23"/>
+      <c r="I609" s="21"/>
     </row>
     <row r="610">
-      <c r="I610" s="19"/>
+      <c r="A610" s="23"/>
+      <c r="I610" s="21"/>
     </row>
     <row r="611">
-      <c r="I611" s="19"/>
+      <c r="A611" s="23"/>
+      <c r="I611" s="21"/>
     </row>
     <row r="612">
-      <c r="I612" s="19"/>
+      <c r="A612" s="23"/>
+      <c r="I612" s="21"/>
     </row>
     <row r="613">
-      <c r="I613" s="19"/>
+      <c r="A613" s="23"/>
+      <c r="I613" s="21"/>
     </row>
     <row r="614">
-      <c r="I614" s="19"/>
+      <c r="A614" s="23"/>
+      <c r="I614" s="21"/>
     </row>
     <row r="615">
-      <c r="I615" s="19"/>
+      <c r="A615" s="23"/>
+      <c r="I615" s="21"/>
     </row>
     <row r="616">
-      <c r="I616" s="19"/>
+      <c r="A616" s="23"/>
+      <c r="I616" s="21"/>
     </row>
     <row r="617">
-      <c r="I617" s="19"/>
+      <c r="A617" s="23"/>
+      <c r="I617" s="21"/>
     </row>
     <row r="618">
-      <c r="I618" s="19"/>
+      <c r="A618" s="23"/>
+      <c r="I618" s="21"/>
     </row>
     <row r="619">
-      <c r="I619" s="19"/>
+      <c r="A619" s="23"/>
+      <c r="I619" s="21"/>
     </row>
     <row r="620">
-      <c r="I620" s="19"/>
+      <c r="A620" s="23"/>
+      <c r="I620" s="21"/>
     </row>
     <row r="621">
-      <c r="I621" s="19"/>
+      <c r="A621" s="23"/>
+      <c r="I621" s="21"/>
     </row>
     <row r="622">
-      <c r="I622" s="19"/>
+      <c r="A622" s="23"/>
+      <c r="I622" s="21"/>
     </row>
     <row r="623">
-      <c r="I623" s="19"/>
+      <c r="A623" s="23"/>
+      <c r="I623" s="21"/>
     </row>
     <row r="624">
-      <c r="I624" s="19"/>
+      <c r="A624" s="23"/>
+      <c r="I624" s="21"/>
     </row>
     <row r="625">
-      <c r="I625" s="19"/>
+      <c r="A625" s="23"/>
+      <c r="I625" s="21"/>
     </row>
     <row r="626">
-      <c r="I626" s="19"/>
+      <c r="A626" s="23"/>
+      <c r="I626" s="21"/>
     </row>
     <row r="627">
-      <c r="I627" s="19"/>
+      <c r="A627" s="23"/>
+      <c r="I627" s="21"/>
     </row>
     <row r="628">
-      <c r="I628" s="19"/>
+      <c r="A628" s="23"/>
+      <c r="I628" s="21"/>
     </row>
     <row r="629">
-      <c r="I629" s="19"/>
+      <c r="A629" s="23"/>
+      <c r="I629" s="21"/>
     </row>
     <row r="630">
-      <c r="I630" s="19"/>
+      <c r="A630" s="23"/>
+      <c r="I630" s="21"/>
     </row>
     <row r="631">
-      <c r="I631" s="19"/>
+      <c r="A631" s="23"/>
+      <c r="I631" s="21"/>
     </row>
     <row r="632">
-      <c r="I632" s="19"/>
+      <c r="A632" s="23"/>
+      <c r="I632" s="21"/>
     </row>
     <row r="633">
-      <c r="I633" s="19"/>
+      <c r="A633" s="23"/>
+      <c r="I633" s="21"/>
     </row>
     <row r="634">
-      <c r="I634" s="19"/>
+      <c r="A634" s="23"/>
+      <c r="I634" s="21"/>
     </row>
     <row r="635">
-      <c r="I635" s="19"/>
+      <c r="A635" s="23"/>
+      <c r="I635" s="21"/>
     </row>
     <row r="636">
-      <c r="I636" s="19"/>
+      <c r="A636" s="23"/>
+      <c r="I636" s="21"/>
     </row>
     <row r="637">
-      <c r="I637" s="19"/>
+      <c r="A637" s="23"/>
+      <c r="I637" s="21"/>
     </row>
     <row r="638">
-      <c r="I638" s="19"/>
+      <c r="A638" s="23"/>
+      <c r="I638" s="21"/>
     </row>
     <row r="639">
-      <c r="I639" s="19"/>
+      <c r="A639" s="23"/>
+      <c r="I639" s="21"/>
     </row>
     <row r="640">
-      <c r="I640" s="19"/>
+      <c r="A640" s="23"/>
+      <c r="I640" s="21"/>
     </row>
     <row r="641">
-      <c r="I641" s="19"/>
+      <c r="A641" s="23"/>
+      <c r="I641" s="21"/>
     </row>
     <row r="642">
-      <c r="I642" s="19"/>
+      <c r="A642" s="23"/>
+      <c r="I642" s="21"/>
     </row>
     <row r="643">
-      <c r="I643" s="19"/>
+      <c r="A643" s="23"/>
+      <c r="I643" s="21"/>
     </row>
     <row r="644">
-      <c r="I644" s="19"/>
+      <c r="A644" s="23"/>
+      <c r="I644" s="21"/>
     </row>
     <row r="645">
-      <c r="I645" s="19"/>
+      <c r="A645" s="23"/>
+      <c r="I645" s="21"/>
     </row>
     <row r="646">
-      <c r="I646" s="19"/>
+      <c r="A646" s="23"/>
+      <c r="I646" s="21"/>
     </row>
     <row r="647">
-      <c r="I647" s="19"/>
+      <c r="A647" s="23"/>
+      <c r="I647" s="21"/>
     </row>
     <row r="648">
-      <c r="I648" s="19"/>
+      <c r="A648" s="23"/>
+      <c r="I648" s="21"/>
     </row>
     <row r="649">
-      <c r="I649" s="19"/>
+      <c r="A649" s="23"/>
+      <c r="I649" s="21"/>
     </row>
     <row r="650">
-      <c r="I650" s="19"/>
+      <c r="A650" s="23"/>
+      <c r="I650" s="21"/>
     </row>
     <row r="651">
-      <c r="I651" s="19"/>
+      <c r="A651" s="23"/>
+      <c r="I651" s="21"/>
     </row>
     <row r="652">
-      <c r="I652" s="19"/>
+      <c r="A652" s="23"/>
+      <c r="I652" s="21"/>
     </row>
     <row r="653">
-      <c r="I653" s="19"/>
+      <c r="A653" s="23"/>
+      <c r="I653" s="21"/>
     </row>
     <row r="654">
-      <c r="I654" s="19"/>
+      <c r="A654" s="23"/>
+      <c r="I654" s="21"/>
     </row>
     <row r="655">
-      <c r="I655" s="19"/>
+      <c r="A655" s="23"/>
+      <c r="I655" s="21"/>
     </row>
     <row r="656">
-      <c r="I656" s="19"/>
+      <c r="A656" s="23"/>
+      <c r="I656" s="21"/>
     </row>
     <row r="657">
-      <c r="I657" s="19"/>
+      <c r="A657" s="23"/>
+      <c r="I657" s="21"/>
     </row>
     <row r="658">
-      <c r="I658" s="19"/>
+      <c r="A658" s="23"/>
+      <c r="I658" s="21"/>
     </row>
     <row r="659">
-      <c r="I659" s="19"/>
+      <c r="A659" s="23"/>
+      <c r="I659" s="21"/>
     </row>
     <row r="660">
-      <c r="I660" s="19"/>
+      <c r="A660" s="23"/>
+      <c r="I660" s="21"/>
     </row>
     <row r="661">
-      <c r="I661" s="19"/>
+      <c r="A661" s="23"/>
+      <c r="I661" s="21"/>
     </row>
     <row r="662">
-      <c r="I662" s="19"/>
+      <c r="A662" s="23"/>
+      <c r="I662" s="21"/>
     </row>
     <row r="663">
-      <c r="I663" s="19"/>
+      <c r="A663" s="23"/>
+      <c r="I663" s="21"/>
     </row>
     <row r="664">
-      <c r="I664" s="19"/>
+      <c r="A664" s="23"/>
+      <c r="I664" s="21"/>
     </row>
     <row r="665">
-      <c r="I665" s="19"/>
+      <c r="A665" s="23"/>
+      <c r="I665" s="21"/>
     </row>
     <row r="666">
-      <c r="I666" s="19"/>
+      <c r="A666" s="23"/>
+      <c r="I666" s="21"/>
     </row>
     <row r="667">
-      <c r="I667" s="19"/>
+      <c r="A667" s="23"/>
+      <c r="I667" s="21"/>
     </row>
     <row r="668">
-      <c r="I668" s="19"/>
+      <c r="A668" s="23"/>
+      <c r="I668" s="21"/>
     </row>
     <row r="669">
-      <c r="I669" s="19"/>
+      <c r="A669" s="23"/>
+      <c r="I669" s="21"/>
     </row>
     <row r="670">
-      <c r="I670" s="19"/>
+      <c r="A670" s="23"/>
+      <c r="I670" s="21"/>
     </row>
     <row r="671">
-      <c r="I671" s="19"/>
+      <c r="A671" s="23"/>
+      <c r="I671" s="21"/>
     </row>
     <row r="672">
-      <c r="I672" s="19"/>
+      <c r="A672" s="23"/>
+      <c r="I672" s="21"/>
     </row>
     <row r="673">
-      <c r="I673" s="19"/>
+      <c r="A673" s="23"/>
+      <c r="I673" s="21"/>
     </row>
     <row r="674">
-      <c r="I674" s="19"/>
+      <c r="A674" s="23"/>
+      <c r="I674" s="21"/>
     </row>
     <row r="675">
-      <c r="I675" s="19"/>
+      <c r="A675" s="23"/>
+      <c r="I675" s="21"/>
     </row>
     <row r="676">
-      <c r="I676" s="19"/>
+      <c r="A676" s="23"/>
+      <c r="I676" s="21"/>
     </row>
     <row r="677">
-      <c r="I677" s="19"/>
+      <c r="A677" s="23"/>
+      <c r="I677" s="21"/>
     </row>
     <row r="678">
-      <c r="I678" s="19"/>
+      <c r="A678" s="23"/>
+      <c r="I678" s="21"/>
     </row>
     <row r="679">
-      <c r="I679" s="19"/>
+      <c r="A679" s="23"/>
+      <c r="I679" s="21"/>
     </row>
     <row r="680">
-      <c r="I680" s="19"/>
+      <c r="A680" s="23"/>
+      <c r="I680" s="21"/>
     </row>
     <row r="681">
-      <c r="I681" s="19"/>
+      <c r="A681" s="23"/>
+      <c r="I681" s="21"/>
     </row>
     <row r="682">
-      <c r="I682" s="19"/>
+      <c r="A682" s="23"/>
+      <c r="I682" s="21"/>
     </row>
     <row r="683">
-      <c r="I683" s="19"/>
+      <c r="A683" s="23"/>
+      <c r="I683" s="21"/>
     </row>
     <row r="684">
-      <c r="I684" s="19"/>
+      <c r="A684" s="23"/>
+      <c r="I684" s="21"/>
     </row>
     <row r="685">
-      <c r="I685" s="19"/>
+      <c r="A685" s="23"/>
+      <c r="I685" s="21"/>
     </row>
     <row r="686">
-      <c r="I686" s="19"/>
+      <c r="A686" s="23"/>
+      <c r="I686" s="21"/>
     </row>
     <row r="687">
-      <c r="I687" s="19"/>
+      <c r="A687" s="23"/>
+      <c r="I687" s="21"/>
     </row>
     <row r="688">
-      <c r="I688" s="19"/>
+      <c r="A688" s="23"/>
+      <c r="I688" s="21"/>
     </row>
     <row r="689">
-      <c r="I689" s="19"/>
+      <c r="A689" s="23"/>
+      <c r="I689" s="21"/>
     </row>
     <row r="690">
-      <c r="I690" s="19"/>
+      <c r="A690" s="23"/>
+      <c r="I690" s="21"/>
     </row>
     <row r="691">
-      <c r="I691" s="19"/>
+      <c r="A691" s="23"/>
+      <c r="I691" s="21"/>
     </row>
     <row r="692">
-      <c r="I692" s="19"/>
+      <c r="A692" s="23"/>
+      <c r="I692" s="21"/>
     </row>
     <row r="693">
-      <c r="I693" s="19"/>
+      <c r="A693" s="23"/>
+      <c r="I693" s="21"/>
     </row>
     <row r="694">
-      <c r="I694" s="19"/>
+      <c r="A694" s="23"/>
+      <c r="I694" s="21"/>
     </row>
     <row r="695">
-      <c r="I695" s="19"/>
+      <c r="A695" s="23"/>
+      <c r="I695" s="21"/>
     </row>
     <row r="696">
-      <c r="I696" s="19"/>
+      <c r="A696" s="23"/>
+      <c r="I696" s="21"/>
     </row>
     <row r="697">
-      <c r="I697" s="19"/>
+      <c r="A697" s="23"/>
+      <c r="I697" s="21"/>
     </row>
     <row r="698">
-      <c r="I698" s="19"/>
+      <c r="A698" s="23"/>
+      <c r="I698" s="21"/>
     </row>
     <row r="699">
-      <c r="I699" s="19"/>
+      <c r="A699" s="23"/>
+      <c r="I699" s="21"/>
     </row>
     <row r="700">
-      <c r="I700" s="19"/>
+      <c r="A700" s="23"/>
+      <c r="I700" s="21"/>
     </row>
     <row r="701">
-      <c r="I701" s="19"/>
+      <c r="A701" s="23"/>
+      <c r="I701" s="21"/>
     </row>
     <row r="702">
-      <c r="I702" s="19"/>
+      <c r="A702" s="23"/>
+      <c r="I702" s="21"/>
     </row>
     <row r="703">
-      <c r="I703" s="19"/>
+      <c r="A703" s="23"/>
+      <c r="I703" s="21"/>
     </row>
     <row r="704">
-      <c r="I704" s="19"/>
+      <c r="A704" s="23"/>
+      <c r="I704" s="21"/>
     </row>
     <row r="705">
-      <c r="I705" s="19"/>
+      <c r="A705" s="23"/>
+      <c r="I705" s="21"/>
     </row>
     <row r="706">
-      <c r="I706" s="19"/>
+      <c r="A706" s="23"/>
+      <c r="I706" s="21"/>
     </row>
     <row r="707">
-      <c r="I707" s="19"/>
+      <c r="A707" s="23"/>
+      <c r="I707" s="21"/>
     </row>
     <row r="708">
-      <c r="I708" s="19"/>
+      <c r="A708" s="23"/>
+      <c r="I708" s="21"/>
     </row>
     <row r="709">
-      <c r="I709" s="19"/>
+      <c r="A709" s="23"/>
+      <c r="I709" s="21"/>
     </row>
     <row r="710">
-      <c r="I710" s="19"/>
+      <c r="A710" s="23"/>
+      <c r="I710" s="21"/>
     </row>
     <row r="711">
-      <c r="I711" s="19"/>
+      <c r="A711" s="23"/>
+      <c r="I711" s="21"/>
     </row>
     <row r="712">
-      <c r="I712" s="19"/>
+      <c r="A712" s="23"/>
+      <c r="I712" s="21"/>
     </row>
     <row r="713">
-      <c r="I713" s="19"/>
+      <c r="A713" s="23"/>
+      <c r="I713" s="21"/>
     </row>
     <row r="714">
-      <c r="I714" s="19"/>
+      <c r="A714" s="23"/>
+      <c r="I714" s="21"/>
     </row>
     <row r="715">
-      <c r="I715" s="19"/>
+      <c r="A715" s="23"/>
+      <c r="I715" s="21"/>
     </row>
     <row r="716">
-      <c r="I716" s="19"/>
+      <c r="A716" s="23"/>
+      <c r="I716" s="21"/>
     </row>
     <row r="717">
-      <c r="I717" s="19"/>
+      <c r="A717" s="23"/>
+      <c r="I717" s="21"/>
     </row>
     <row r="718">
-      <c r="I718" s="19"/>
+      <c r="A718" s="23"/>
+      <c r="I718" s="21"/>
     </row>
     <row r="719">
-      <c r="I719" s="19"/>
+      <c r="A719" s="23"/>
+      <c r="I719" s="21"/>
     </row>
     <row r="720">
-      <c r="I720" s="19"/>
+      <c r="A720" s="23"/>
+      <c r="I720" s="21"/>
     </row>
     <row r="721">
-      <c r="I721" s="19"/>
+      <c r="A721" s="23"/>
+      <c r="I721" s="21"/>
     </row>
     <row r="722">
-      <c r="I722" s="19"/>
+      <c r="A722" s="23"/>
+      <c r="I722" s="21"/>
     </row>
     <row r="723">
-      <c r="I723" s="19"/>
+      <c r="A723" s="23"/>
+      <c r="I723" s="21"/>
     </row>
     <row r="724">
-      <c r="I724" s="19"/>
+      <c r="A724" s="23"/>
+      <c r="I724" s="21"/>
     </row>
     <row r="725">
-      <c r="I725" s="19"/>
+      <c r="A725" s="23"/>
+      <c r="I725" s="21"/>
     </row>
     <row r="726">
-      <c r="I726" s="19"/>
+      <c r="A726" s="23"/>
+      <c r="I726" s="21"/>
     </row>
     <row r="727">
-      <c r="I727" s="19"/>
+      <c r="A727" s="23"/>
+      <c r="I727" s="21"/>
     </row>
     <row r="728">
-      <c r="I728" s="19"/>
+      <c r="A728" s="23"/>
+      <c r="I728" s="21"/>
     </row>
     <row r="729">
-      <c r="I729" s="19"/>
+      <c r="A729" s="23"/>
+      <c r="I729" s="21"/>
     </row>
     <row r="730">
-      <c r="I730" s="19"/>
+      <c r="A730" s="23"/>
+      <c r="I730" s="21"/>
     </row>
     <row r="731">
-      <c r="I731" s="19"/>
+      <c r="A731" s="23"/>
+      <c r="I731" s="21"/>
     </row>
     <row r="732">
-      <c r="I732" s="19"/>
+      <c r="A732" s="23"/>
+      <c r="I732" s="21"/>
     </row>
     <row r="733">
-      <c r="I733" s="19"/>
+      <c r="A733" s="23"/>
+      <c r="I733" s="21"/>
     </row>
     <row r="734">
-      <c r="I734" s="19"/>
+      <c r="A734" s="23"/>
+      <c r="I734" s="21"/>
     </row>
     <row r="735">
-      <c r="I735" s="19"/>
+      <c r="A735" s="23"/>
+      <c r="I735" s="21"/>
     </row>
     <row r="736">
-      <c r="I736" s="19"/>
+      <c r="A736" s="23"/>
+      <c r="I736" s="21"/>
     </row>
     <row r="737">
-      <c r="I737" s="19"/>
+      <c r="A737" s="23"/>
+      <c r="I737" s="21"/>
     </row>
     <row r="738">
-      <c r="I738" s="19"/>
+      <c r="A738" s="23"/>
+      <c r="I738" s="21"/>
     </row>
     <row r="739">
-      <c r="I739" s="19"/>
+      <c r="A739" s="23"/>
+      <c r="I739" s="21"/>
     </row>
     <row r="740">
-      <c r="I740" s="19"/>
+      <c r="A740" s="23"/>
+      <c r="I740" s="21"/>
     </row>
     <row r="741">
-      <c r="I741" s="19"/>
+      <c r="A741" s="23"/>
+      <c r="I741" s="21"/>
     </row>
     <row r="742">
-      <c r="I742" s="19"/>
+      <c r="A742" s="23"/>
+      <c r="I742" s="21"/>
     </row>
     <row r="743">
-      <c r="I743" s="19"/>
+      <c r="A743" s="23"/>
+      <c r="I743" s="21"/>
     </row>
     <row r="744">
-      <c r="I744" s="19"/>
+      <c r="A744" s="23"/>
+      <c r="I744" s="21"/>
     </row>
     <row r="745">
-      <c r="I745" s="19"/>
+      <c r="A745" s="23"/>
+      <c r="I745" s="21"/>
     </row>
     <row r="746">
-      <c r="I746" s="19"/>
+      <c r="A746" s="23"/>
+      <c r="I746" s="21"/>
     </row>
     <row r="747">
-      <c r="I747" s="19"/>
+      <c r="A747" s="23"/>
+      <c r="I747" s="21"/>
     </row>
     <row r="748">
-      <c r="I748" s="19"/>
+      <c r="A748" s="23"/>
+      <c r="I748" s="21"/>
     </row>
     <row r="749">
-      <c r="I749" s="19"/>
+      <c r="A749" s="23"/>
+      <c r="I749" s="21"/>
     </row>
     <row r="750">
-      <c r="I750" s="19"/>
+      <c r="A750" s="23"/>
+      <c r="I750" s="21"/>
     </row>
     <row r="751">
-      <c r="I751" s="19"/>
+      <c r="A751" s="23"/>
+      <c r="I751" s="21"/>
     </row>
     <row r="752">
-      <c r="I752" s="19"/>
+      <c r="A752" s="23"/>
+      <c r="I752" s="21"/>
     </row>
     <row r="753">
-      <c r="I753" s="19"/>
+      <c r="A753" s="23"/>
+      <c r="I753" s="21"/>
     </row>
     <row r="754">
-      <c r="I754" s="19"/>
+      <c r="A754" s="23"/>
+      <c r="I754" s="21"/>
     </row>
     <row r="755">
-      <c r="I755" s="19"/>
+      <c r="A755" s="23"/>
+      <c r="I755" s="21"/>
     </row>
     <row r="756">
-      <c r="I756" s="19"/>
+      <c r="A756" s="23"/>
+      <c r="I756" s="21"/>
     </row>
     <row r="757">
-      <c r="I757" s="19"/>
+      <c r="A757" s="23"/>
+      <c r="I757" s="21"/>
     </row>
     <row r="758">
-      <c r="I758" s="19"/>
+      <c r="A758" s="23"/>
+      <c r="I758" s="21"/>
     </row>
     <row r="759">
-      <c r="I759" s="19"/>
+      <c r="A759" s="23"/>
+      <c r="I759" s="21"/>
     </row>
     <row r="760">
-      <c r="I760" s="19"/>
+      <c r="A760" s="23"/>
+      <c r="I760" s="21"/>
     </row>
     <row r="761">
-      <c r="I761" s="19"/>
+      <c r="A761" s="23"/>
+      <c r="I761" s="21"/>
     </row>
     <row r="762">
-      <c r="I762" s="19"/>
+      <c r="A762" s="23"/>
+      <c r="I762" s="21"/>
     </row>
     <row r="763">
-      <c r="I763" s="19"/>
+      <c r="A763" s="23"/>
+      <c r="I763" s="21"/>
     </row>
     <row r="764">
-      <c r="I764" s="19"/>
+      <c r="A764" s="23"/>
+      <c r="I764" s="21"/>
     </row>
     <row r="765">
-      <c r="I765" s="19"/>
+      <c r="A765" s="23"/>
+      <c r="I765" s="21"/>
     </row>
     <row r="766">
-      <c r="I766" s="19"/>
+      <c r="A766" s="23"/>
+      <c r="I766" s="21"/>
     </row>
     <row r="767">
-      <c r="I767" s="19"/>
+      <c r="A767" s="23"/>
+      <c r="I767" s="21"/>
     </row>
     <row r="768">
-      <c r="I768" s="19"/>
+      <c r="A768" s="23"/>
+      <c r="I768" s="21"/>
     </row>
     <row r="769">
-      <c r="I769" s="19"/>
+      <c r="A769" s="23"/>
+      <c r="I769" s="21"/>
     </row>
     <row r="770">
-      <c r="I770" s="19"/>
+      <c r="A770" s="23"/>
+      <c r="I770" s="21"/>
     </row>
     <row r="771">
-      <c r="I771" s="19"/>
+      <c r="A771" s="23"/>
+      <c r="I771" s="21"/>
     </row>
     <row r="772">
-      <c r="I772" s="19"/>
+      <c r="A772" s="23"/>
+      <c r="I772" s="21"/>
     </row>
     <row r="773">
-      <c r="I773" s="19"/>
+      <c r="A773" s="23"/>
+      <c r="I773" s="21"/>
     </row>
     <row r="774">
-      <c r="I774" s="19"/>
+      <c r="A774" s="23"/>
+      <c r="I774" s="21"/>
     </row>
     <row r="775">
-      <c r="I775" s="19"/>
+      <c r="A775" s="23"/>
+      <c r="I775" s="21"/>
     </row>
     <row r="776">
-      <c r="I776" s="19"/>
+      <c r="A776" s="23"/>
+      <c r="I776" s="21"/>
     </row>
     <row r="777">
-      <c r="I777" s="19"/>
+      <c r="A777" s="23"/>
+      <c r="I777" s="21"/>
     </row>
     <row r="778">
-      <c r="I778" s="19"/>
+      <c r="A778" s="23"/>
+      <c r="I778" s="21"/>
     </row>
     <row r="779">
-      <c r="I779" s="19"/>
+      <c r="A779" s="23"/>
+      <c r="I779" s="21"/>
     </row>
     <row r="780">
-      <c r="I780" s="19"/>
+      <c r="A780" s="23"/>
+      <c r="I780" s="21"/>
     </row>
     <row r="781">
-      <c r="I781" s="19"/>
+      <c r="A781" s="23"/>
+      <c r="I781" s="21"/>
     </row>
     <row r="782">
-      <c r="I782" s="19"/>
+      <c r="A782" s="23"/>
+      <c r="I782" s="21"/>
     </row>
     <row r="783">
-      <c r="I783" s="19"/>
+      <c r="A783" s="23"/>
+      <c r="I783" s="21"/>
     </row>
     <row r="784">
-      <c r="I784" s="19"/>
+      <c r="A784" s="23"/>
+      <c r="I784" s="21"/>
     </row>
     <row r="785">
-      <c r="I785" s="19"/>
+      <c r="A785" s="23"/>
+      <c r="I785" s="21"/>
     </row>
     <row r="786">
-      <c r="I786" s="19"/>
+      <c r="A786" s="23"/>
+      <c r="I786" s="21"/>
     </row>
     <row r="787">
-      <c r="I787" s="19"/>
+      <c r="A787" s="23"/>
+      <c r="I787" s="21"/>
     </row>
     <row r="788">
-      <c r="I788" s="19"/>
+      <c r="A788" s="23"/>
+      <c r="I788" s="21"/>
     </row>
     <row r="789">
-      <c r="I789" s="19"/>
+      <c r="A789" s="23"/>
+      <c r="I789" s="21"/>
     </row>
     <row r="790">
-      <c r="I790" s="19"/>
+      <c r="A790" s="23"/>
+      <c r="I790" s="21"/>
     </row>
     <row r="791">
-      <c r="I791" s="19"/>
+      <c r="A791" s="23"/>
+      <c r="I791" s="21"/>
     </row>
     <row r="792">
-      <c r="I792" s="19"/>
+      <c r="A792" s="23"/>
+      <c r="I792" s="21"/>
     </row>
     <row r="793">
-      <c r="I793" s="19"/>
+      <c r="A793" s="23"/>
+      <c r="I793" s="21"/>
     </row>
     <row r="794">
-      <c r="I794" s="19"/>
+      <c r="A794" s="23"/>
+      <c r="I794" s="21"/>
     </row>
     <row r="795">
-      <c r="I795" s="19"/>
+      <c r="A795" s="23"/>
+      <c r="I795" s="21"/>
     </row>
     <row r="796">
-      <c r="I796" s="19"/>
+      <c r="A796" s="23"/>
+      <c r="I796" s="21"/>
     </row>
     <row r="797">
-      <c r="I797" s="19"/>
+      <c r="A797" s="23"/>
+      <c r="I797" s="21"/>
     </row>
     <row r="798">
-      <c r="I798" s="19"/>
+      <c r="A798" s="23"/>
+      <c r="I798" s="21"/>
     </row>
     <row r="799">
-      <c r="I799" s="19"/>
+      <c r="A799" s="23"/>
+      <c r="I799" s="21"/>
     </row>
     <row r="800">
-      <c r="I800" s="19"/>
+      <c r="A800" s="23"/>
+      <c r="I800" s="21"/>
     </row>
     <row r="801">
-      <c r="I801" s="19"/>
+      <c r="A801" s="23"/>
+      <c r="I801" s="21"/>
     </row>
     <row r="802">
-      <c r="I802" s="19"/>
+      <c r="A802" s="23"/>
+      <c r="I802" s="21"/>
     </row>
     <row r="803">
-      <c r="I803" s="19"/>
+      <c r="A803" s="23"/>
+      <c r="I803" s="21"/>
     </row>
     <row r="804">
-      <c r="I804" s="19"/>
+      <c r="A804" s="23"/>
+      <c r="I804" s="21"/>
     </row>
     <row r="805">
-      <c r="I805" s="19"/>
+      <c r="A805" s="23"/>
+      <c r="I805" s="21"/>
     </row>
     <row r="806">
-      <c r="I806" s="19"/>
+      <c r="A806" s="23"/>
+      <c r="I806" s="21"/>
     </row>
     <row r="807">
-      <c r="I807" s="19"/>
+      <c r="A807" s="23"/>
+      <c r="I807" s="21"/>
     </row>
     <row r="808">
-      <c r="I808" s="19"/>
+      <c r="A808" s="23"/>
+      <c r="I808" s="21"/>
     </row>
     <row r="809">
-      <c r="I809" s="19"/>
+      <c r="A809" s="23"/>
+      <c r="I809" s="21"/>
     </row>
     <row r="810">
-      <c r="I810" s="19"/>
+      <c r="A810" s="23"/>
+      <c r="I810" s="21"/>
     </row>
     <row r="811">
-      <c r="I811" s="19"/>
+      <c r="A811" s="23"/>
+      <c r="I811" s="21"/>
     </row>
     <row r="812">
-      <c r="I812" s="19"/>
+      <c r="A812" s="23"/>
+      <c r="I812" s="21"/>
     </row>
     <row r="813">
-      <c r="I813" s="19"/>
+      <c r="A813" s="23"/>
+      <c r="I813" s="21"/>
     </row>
     <row r="814">
-      <c r="I814" s="19"/>
+      <c r="A814" s="23"/>
+      <c r="I814" s="21"/>
     </row>
     <row r="815">
-      <c r="I815" s="19"/>
+      <c r="A815" s="23"/>
+      <c r="I815" s="21"/>
     </row>
     <row r="816">
-      <c r="I816" s="19"/>
+      <c r="A816" s="23"/>
+      <c r="I816" s="21"/>
     </row>
     <row r="817">
-      <c r="I817" s="19"/>
+      <c r="A817" s="23"/>
+      <c r="I817" s="21"/>
     </row>
     <row r="818">
-      <c r="I818" s="19"/>
+      <c r="A818" s="23"/>
+      <c r="I818" s="21"/>
     </row>
     <row r="819">
-      <c r="I819" s="19"/>
+      <c r="A819" s="23"/>
+      <c r="I819" s="21"/>
     </row>
     <row r="820">
-      <c r="I820" s="19"/>
+      <c r="A820" s="23"/>
+      <c r="I820" s="21"/>
     </row>
     <row r="821">
-      <c r="I821" s="19"/>
+      <c r="A821" s="23"/>
+      <c r="I821" s="21"/>
     </row>
     <row r="822">
-      <c r="I822" s="19"/>
+      <c r="A822" s="23"/>
+      <c r="I822" s="21"/>
     </row>
     <row r="823">
-      <c r="I823" s="19"/>
+      <c r="A823" s="23"/>
+      <c r="I823" s="21"/>
     </row>
     <row r="824">
-      <c r="I824" s="19"/>
+      <c r="A824" s="23"/>
+      <c r="I824" s="21"/>
     </row>
     <row r="825">
-      <c r="I825" s="19"/>
+      <c r="A825" s="23"/>
+      <c r="I825" s="21"/>
     </row>
     <row r="826">
-      <c r="I826" s="19"/>
+      <c r="A826" s="23"/>
+      <c r="I826" s="21"/>
     </row>
     <row r="827">
-      <c r="I827" s="19"/>
+      <c r="A827" s="23"/>
+      <c r="I827" s="21"/>
     </row>
     <row r="828">
-      <c r="I828" s="19"/>
+      <c r="A828" s="23"/>
+      <c r="I828" s="21"/>
     </row>
     <row r="829">
-      <c r="I829" s="19"/>
+      <c r="A829" s="23"/>
+      <c r="I829" s="21"/>
     </row>
     <row r="830">
-      <c r="I830" s="19"/>
+      <c r="A830" s="23"/>
+      <c r="I830" s="21"/>
     </row>
     <row r="831">
-      <c r="I831" s="19"/>
+      <c r="A831" s="23"/>
+      <c r="I831" s="21"/>
     </row>
     <row r="832">
-      <c r="I832" s="19"/>
+      <c r="A832" s="23"/>
+      <c r="I832" s="21"/>
     </row>
     <row r="833">
-      <c r="I833" s="19"/>
+      <c r="A833" s="23"/>
+      <c r="I833" s="21"/>
     </row>
     <row r="834">
-      <c r="I834" s="19"/>
+      <c r="A834" s="23"/>
+      <c r="I834" s="21"/>
     </row>
     <row r="835">
-      <c r="I835" s="19"/>
+      <c r="A835" s="23"/>
+      <c r="I835" s="21"/>
     </row>
     <row r="836">
-      <c r="I836" s="19"/>
+      <c r="A836" s="23"/>
+      <c r="I836" s="21"/>
     </row>
     <row r="837">
-      <c r="I837" s="19"/>
+      <c r="A837" s="23"/>
+      <c r="I837" s="21"/>
     </row>
     <row r="838">
-      <c r="I838" s="19"/>
+      <c r="A838" s="23"/>
+      <c r="I838" s="21"/>
     </row>
     <row r="839">
-      <c r="I839" s="19"/>
+      <c r="A839" s="23"/>
+      <c r="I839" s="21"/>
     </row>
     <row r="840">
-      <c r="I840" s="19"/>
+      <c r="A840" s="23"/>
+      <c r="I840" s="21"/>
     </row>
     <row r="841">
-      <c r="I841" s="19"/>
+      <c r="A841" s="23"/>
+      <c r="I841" s="21"/>
     </row>
     <row r="842">
-      <c r="I842" s="19"/>
+      <c r="A842" s="23"/>
+      <c r="I842" s="21"/>
     </row>
     <row r="843">
-      <c r="I843" s="19"/>
+      <c r="A843" s="23"/>
+      <c r="I843" s="21"/>
     </row>
     <row r="844">
-      <c r="I844" s="19"/>
+      <c r="A844" s="23"/>
+      <c r="I844" s="21"/>
     </row>
     <row r="845">
-      <c r="I845" s="19"/>
+      <c r="A845" s="23"/>
+      <c r="I845" s="21"/>
     </row>
     <row r="846">
-      <c r="I846" s="19"/>
+      <c r="A846" s="23"/>
+      <c r="I846" s="21"/>
     </row>
     <row r="847">
-      <c r="I847" s="19"/>
+      <c r="A847" s="23"/>
+      <c r="I847" s="21"/>
     </row>
     <row r="848">
-      <c r="I848" s="19"/>
+      <c r="A848" s="23"/>
+      <c r="I848" s="21"/>
     </row>
     <row r="849">
-      <c r="I849" s="19"/>
+      <c r="A849" s="23"/>
+      <c r="I849" s="21"/>
     </row>
     <row r="850">
-      <c r="I850" s="19"/>
+      <c r="A850" s="23"/>
+      <c r="I850" s="21"/>
     </row>
     <row r="851">
-      <c r="I851" s="19"/>
+      <c r="A851" s="23"/>
+      <c r="I851" s="21"/>
     </row>
     <row r="852">
-      <c r="I852" s="19"/>
+      <c r="A852" s="23"/>
+      <c r="I852" s="21"/>
     </row>
     <row r="853">
-      <c r="I853" s="19"/>
+      <c r="A853" s="23"/>
+      <c r="I853" s="21"/>
     </row>
     <row r="854">
-      <c r="I854" s="19"/>
+      <c r="A854" s="23"/>
+      <c r="I854" s="21"/>
     </row>
     <row r="855">
-      <c r="I855" s="19"/>
+      <c r="A855" s="23"/>
+      <c r="I855" s="21"/>
     </row>
     <row r="856">
-      <c r="I856" s="19"/>
+      <c r="A856" s="23"/>
+      <c r="I856" s="21"/>
     </row>
     <row r="857">
-      <c r="I857" s="19"/>
+      <c r="A857" s="23"/>
+      <c r="I857" s="21"/>
     </row>
     <row r="858">
-      <c r="I858" s="19"/>
+      <c r="A858" s="23"/>
+      <c r="I858" s="21"/>
     </row>
     <row r="859">
-      <c r="I859" s="19"/>
+      <c r="A859" s="23"/>
+      <c r="I859" s="21"/>
     </row>
     <row r="860">
-      <c r="I860" s="19"/>
+      <c r="A860" s="23"/>
+      <c r="I860" s="21"/>
     </row>
     <row r="861">
-      <c r="I861" s="19"/>
+      <c r="A861" s="23"/>
+      <c r="I861" s="21"/>
     </row>
     <row r="862">
-      <c r="I862" s="19"/>
+      <c r="A862" s="23"/>
+      <c r="I862" s="21"/>
     </row>
     <row r="863">
-      <c r="I863" s="19"/>
+      <c r="A863" s="23"/>
+      <c r="I863" s="21"/>
     </row>
     <row r="864">
-      <c r="I864" s="19"/>
+      <c r="A864" s="23"/>
+      <c r="I864" s="21"/>
     </row>
     <row r="865">
-      <c r="I865" s="19"/>
+      <c r="A865" s="23"/>
+      <c r="I865" s="21"/>
     </row>
     <row r="866">
-      <c r="I866" s="19"/>
+      <c r="A866" s="23"/>
+      <c r="I866" s="21"/>
     </row>
     <row r="867">
-      <c r="I867" s="19"/>
+      <c r="A867" s="23"/>
+      <c r="I867" s="21"/>
     </row>
     <row r="868">
-      <c r="I868" s="19"/>
+      <c r="A868" s="23"/>
+      <c r="I868" s="21"/>
     </row>
     <row r="869">
-      <c r="I869" s="19"/>
+      <c r="A869" s="23"/>
+      <c r="I869" s="21"/>
     </row>
     <row r="870">
-      <c r="I870" s="19"/>
+      <c r="A870" s="23"/>
+      <c r="I870" s="21"/>
     </row>
     <row r="871">
-      <c r="I871" s="19"/>
+      <c r="A871" s="23"/>
+      <c r="I871" s="21"/>
     </row>
     <row r="872">
-      <c r="I872" s="19"/>
+      <c r="A872" s="23"/>
+      <c r="I872" s="21"/>
     </row>
     <row r="873">
-      <c r="I873" s="19"/>
+      <c r="A873" s="23"/>
+      <c r="I873" s="21"/>
     </row>
     <row r="874">
-      <c r="I874" s="19"/>
+      <c r="A874" s="23"/>
+      <c r="I874" s="21"/>
     </row>
     <row r="875">
-      <c r="I875" s="19"/>
+      <c r="A875" s="23"/>
+      <c r="I875" s="21"/>
     </row>
     <row r="876">
-      <c r="I876" s="19"/>
+      <c r="A876" s="23"/>
+      <c r="I876" s="21"/>
     </row>
     <row r="877">
-      <c r="I877" s="19"/>
+      <c r="A877" s="23"/>
+      <c r="I877" s="21"/>
     </row>
     <row r="878">
-      <c r="I878" s="19"/>
+      <c r="A878" s="23"/>
+      <c r="I878" s="21"/>
     </row>
     <row r="879">
-      <c r="I879" s="19"/>
+      <c r="A879" s="23"/>
+      <c r="I879" s="21"/>
     </row>
     <row r="880">
-      <c r="I880" s="19"/>
+      <c r="A880" s="23"/>
+      <c r="I880" s="21"/>
     </row>
     <row r="881">
-      <c r="I881" s="19"/>
+      <c r="A881" s="23"/>
+      <c r="I881" s="21"/>
     </row>
     <row r="882">
-      <c r="I882" s="19"/>
+      <c r="A882" s="23"/>
+      <c r="I882" s="21"/>
     </row>
     <row r="883">
-      <c r="I883" s="19"/>
+      <c r="A883" s="23"/>
+      <c r="I883" s="21"/>
     </row>
     <row r="884">
-      <c r="I884" s="19"/>
+      <c r="A884" s="23"/>
+      <c r="I884" s="21"/>
     </row>
     <row r="885">
-      <c r="I885" s="19"/>
+      <c r="A885" s="23"/>
+      <c r="I885" s="21"/>
     </row>
     <row r="886">
-      <c r="I886" s="19"/>
+      <c r="A886" s="23"/>
+      <c r="I886" s="21"/>
     </row>
     <row r="887">
-      <c r="I887" s="19"/>
+      <c r="A887" s="23"/>
+      <c r="I887" s="21"/>
     </row>
     <row r="888">
-      <c r="I888" s="19"/>
+      <c r="A888" s="23"/>
+      <c r="I888" s="21"/>
     </row>
     <row r="889">
-      <c r="I889" s="19"/>
+      <c r="A889" s="23"/>
+      <c r="I889" s="21"/>
     </row>
     <row r="890">
-      <c r="I890" s="19"/>
+      <c r="A890" s="23"/>
+      <c r="I890" s="21"/>
     </row>
     <row r="891">
-      <c r="I891" s="19"/>
+      <c r="A891" s="23"/>
+      <c r="I891" s="21"/>
     </row>
     <row r="892">
-      <c r="I892" s="19"/>
+      <c r="A892" s="23"/>
+      <c r="I892" s="21"/>
     </row>
     <row r="893">
-      <c r="I893" s="19"/>
+      <c r="A893" s="23"/>
+      <c r="I893" s="21"/>
     </row>
     <row r="894">
-      <c r="I894" s="19"/>
+      <c r="A894" s="23"/>
+      <c r="I894" s="21"/>
     </row>
     <row r="895">
-      <c r="I895" s="19"/>
+      <c r="A895" s="23"/>
+      <c r="I895" s="21"/>
     </row>
     <row r="896">
-      <c r="I896" s="19"/>
+      <c r="A896" s="23"/>
+      <c r="I896" s="21"/>
     </row>
     <row r="897">
-      <c r="I897" s="19"/>
+      <c r="A897" s="23"/>
+      <c r="I897" s="21"/>
     </row>
     <row r="898">
-      <c r="I898" s="19"/>
+      <c r="A898" s="23"/>
+      <c r="I898" s="21"/>
     </row>
     <row r="899">
-      <c r="I899" s="19"/>
+      <c r="A899" s="23"/>
+      <c r="I899" s="21"/>
     </row>
     <row r="900">
-      <c r="I900" s="19"/>
+      <c r="A900" s="23"/>
+      <c r="I900" s="21"/>
     </row>
     <row r="901">
-      <c r="I901" s="19"/>
+      <c r="A901" s="23"/>
+      <c r="I901" s="21"/>
     </row>
     <row r="902">
-      <c r="I902" s="19"/>
+      <c r="A902" s="23"/>
+      <c r="I902" s="21"/>
     </row>
     <row r="903">
-      <c r="I903" s="19"/>
+      <c r="A903" s="23"/>
+      <c r="I903" s="21"/>
     </row>
     <row r="904">
-      <c r="I904" s="19"/>
+      <c r="A904" s="23"/>
+      <c r="I904" s="21"/>
     </row>
     <row r="905">
-      <c r="I905" s="19"/>
+      <c r="A905" s="23"/>
+      <c r="I905" s="21"/>
     </row>
     <row r="906">
-      <c r="I906" s="19"/>
+      <c r="A906" s="23"/>
+      <c r="I906" s="21"/>
     </row>
     <row r="907">
-      <c r="I907" s="19"/>
+      <c r="A907" s="23"/>
+      <c r="I907" s="21"/>
     </row>
     <row r="908">
-      <c r="I908" s="19"/>
+      <c r="A908" s="23"/>
+      <c r="I908" s="21"/>
     </row>
     <row r="909">
-      <c r="I909" s="19"/>
+      <c r="A909" s="23"/>
+      <c r="I909" s="21"/>
     </row>
     <row r="910">
-      <c r="I910" s="19"/>
+      <c r="A910" s="23"/>
+      <c r="I910" s="21"/>
     </row>
     <row r="911">
-      <c r="I911" s="19"/>
+      <c r="A911" s="23"/>
+      <c r="I911" s="21"/>
     </row>
     <row r="912">
-      <c r="I912" s="19"/>
+      <c r="A912" s="23"/>
+      <c r="I912" s="21"/>
     </row>
     <row r="913">
-      <c r="I913" s="19"/>
+      <c r="A913" s="23"/>
+      <c r="I913" s="21"/>
     </row>
     <row r="914">
-      <c r="I914" s="19"/>
+      <c r="A914" s="23"/>
+      <c r="I914" s="21"/>
     </row>
     <row r="915">
-      <c r="I915" s="19"/>
+      <c r="A915" s="23"/>
+      <c r="I915" s="21"/>
     </row>
     <row r="916">
-      <c r="I916" s="19"/>
+      <c r="A916" s="23"/>
+      <c r="I916" s="21"/>
     </row>
     <row r="917">
-      <c r="I917" s="19"/>
+      <c r="A917" s="23"/>
+      <c r="I917" s="21"/>
     </row>
     <row r="918">
-      <c r="I918" s="19"/>
+      <c r="A918" s="23"/>
+      <c r="I918" s="21"/>
     </row>
     <row r="919">
-      <c r="I919" s="19"/>
+      <c r="A919" s="23"/>
+      <c r="I919" s="21"/>
     </row>
     <row r="920">
-      <c r="I920" s="19"/>
+      <c r="A920" s="23"/>
+      <c r="I920" s="21"/>
     </row>
     <row r="921">
-      <c r="I921" s="19"/>
+      <c r="A921" s="23"/>
+      <c r="I921" s="21"/>
     </row>
     <row r="922">
-      <c r="I922" s="19"/>
+      <c r="A922" s="23"/>
+      <c r="I922" s="21"/>
     </row>
     <row r="923">
-      <c r="I923" s="19"/>
+      <c r="A923" s="23"/>
+      <c r="I923" s="21"/>
     </row>
     <row r="924">
-      <c r="I924" s="19"/>
+      <c r="A924" s="23"/>
+      <c r="I924" s="21"/>
     </row>
     <row r="925">
-      <c r="I925" s="19"/>
+      <c r="A925" s="23"/>
+      <c r="I925" s="21"/>
     </row>
     <row r="926">
-      <c r="I926" s="19"/>
+      <c r="A926" s="23"/>
+      <c r="I926" s="21"/>
     </row>
     <row r="927">
-      <c r="I927" s="19"/>
+      <c r="A927" s="23"/>
+      <c r="I927" s="21"/>
     </row>
     <row r="928">
-      <c r="I928" s="19"/>
+      <c r="A928" s="23"/>
+      <c r="I928" s="21"/>
     </row>
     <row r="929">
-      <c r="I929" s="19"/>
+      <c r="A929" s="23"/>
+      <c r="I929" s="21"/>
     </row>
     <row r="930">
-      <c r="I930" s="19"/>
+      <c r="A930" s="23"/>
+      <c r="I930" s="21"/>
     </row>
     <row r="931">
-      <c r="I931" s="19"/>
+      <c r="A931" s="23"/>
+      <c r="I931" s="21"/>
     </row>
     <row r="932">
-      <c r="I932" s="19"/>
+      <c r="A932" s="23"/>
+      <c r="I932" s="21"/>
     </row>
     <row r="933">
-      <c r="I933" s="19"/>
+      <c r="A933" s="23"/>
+      <c r="I933" s="21"/>
     </row>
     <row r="934">
-      <c r="I934" s="19"/>
+      <c r="A934" s="23"/>
+      <c r="I934" s="21"/>
     </row>
     <row r="935">
-      <c r="I935" s="19"/>
+      <c r="A935" s="23"/>
+      <c r="I935" s="21"/>
     </row>
     <row r="936">
-      <c r="I936" s="19"/>
+      <c r="A936" s="23"/>
+      <c r="I936" s="21"/>
     </row>
     <row r="937">
-      <c r="I937" s="19"/>
+      <c r="A937" s="23"/>
+      <c r="I937" s="21"/>
     </row>
     <row r="938">
-      <c r="I938" s="19"/>
+      <c r="A938" s="23"/>
+      <c r="I938" s="21"/>
     </row>
     <row r="939">
-      <c r="I939" s="19"/>
+      <c r="A939" s="23"/>
+      <c r="I939" s="21"/>
     </row>
     <row r="940">
-      <c r="I940" s="19"/>
+      <c r="A940" s="23"/>
+      <c r="I940" s="21"/>
     </row>
     <row r="941">
-      <c r="I941" s="19"/>
+      <c r="A941" s="23"/>
+      <c r="I941" s="21"/>
     </row>
     <row r="942">
-      <c r="I942" s="19"/>
+      <c r="A942" s="23"/>
+      <c r="I942" s="21"/>
     </row>
     <row r="943">
-      <c r="I943" s="19"/>
+      <c r="A943" s="23"/>
+      <c r="I943" s="21"/>
     </row>
     <row r="944">
-      <c r="I944" s="19"/>
+      <c r="A944" s="23"/>
+      <c r="I944" s="21"/>
     </row>
     <row r="945">
-      <c r="I945" s="19"/>
+      <c r="A945" s="23"/>
+      <c r="I945" s="21"/>
     </row>
     <row r="946">
-      <c r="I946" s="19"/>
+      <c r="A946" s="23"/>
+      <c r="I946" s="21"/>
     </row>
     <row r="947">
-      <c r="I947" s="19"/>
+      <c r="A947" s="23"/>
+      <c r="I947" s="21"/>
     </row>
     <row r="948">
-      <c r="I948" s="19"/>
+      <c r="A948" s="23"/>
+      <c r="I948" s="21"/>
     </row>
     <row r="949">
-      <c r="I949" s="19"/>
+      <c r="A949" s="23"/>
+      <c r="I949" s="21"/>
     </row>
     <row r="950">
-      <c r="I950" s="19"/>
+      <c r="A950" s="23"/>
+      <c r="I950" s="21"/>
     </row>
     <row r="951">
-      <c r="I951" s="19"/>
+      <c r="A951" s="23"/>
+      <c r="I951" s="21"/>
     </row>
     <row r="952">
-      <c r="I952" s="19"/>
+      <c r="A952" s="23"/>
+      <c r="I952" s="21"/>
     </row>
     <row r="953">
-      <c r="I953" s="19"/>
+      <c r="A953" s="23"/>
+      <c r="I953" s="21"/>
     </row>
     <row r="954">
-      <c r="I954" s="19"/>
+      <c r="A954" s="23"/>
+      <c r="I954" s="21"/>
     </row>
     <row r="955">
-      <c r="I955" s="19"/>
+      <c r="A955" s="23"/>
+      <c r="I955" s="21"/>
     </row>
     <row r="956">
-      <c r="I956" s="19"/>
+      <c r="A956" s="23"/>
+      <c r="I956" s="21"/>
     </row>
     <row r="957">
-      <c r="I957" s="19"/>
+      <c r="A957" s="23"/>
+      <c r="I957" s="21"/>
     </row>
     <row r="958">
-      <c r="I958" s="19"/>
+      <c r="A958" s="23"/>
+      <c r="I958" s="21"/>
     </row>
     <row r="959">
-      <c r="I959" s="19"/>
+      <c r="A959" s="23"/>
+      <c r="I959" s="21"/>
     </row>
     <row r="960">
-      <c r="I960" s="19"/>
+      <c r="A960" s="23"/>
+      <c r="I960" s="21"/>
     </row>
     <row r="961">
-      <c r="I961" s="19"/>
+      <c r="A961" s="23"/>
+      <c r="I961" s="21"/>
     </row>
     <row r="962">
-      <c r="I962" s="19"/>
+      <c r="A962" s="23"/>
+      <c r="I962" s="21"/>
     </row>
     <row r="963">
-      <c r="I963" s="19"/>
+      <c r="A963" s="23"/>
+      <c r="I963" s="21"/>
     </row>
     <row r="964">
-      <c r="I964" s="19"/>
+      <c r="A964" s="23"/>
+      <c r="I964" s="21"/>
     </row>
     <row r="965">
-      <c r="I965" s="19"/>
+      <c r="A965" s="23"/>
+      <c r="I965" s="21"/>
     </row>
     <row r="966">
-      <c r="I966" s="19"/>
+      <c r="A966" s="23"/>
+      <c r="I966" s="21"/>
     </row>
     <row r="967">
-      <c r="I967" s="19"/>
+      <c r="A967" s="23"/>
+      <c r="I967" s="21"/>
     </row>
     <row r="968">
-      <c r="I968" s="19"/>
+      <c r="A968" s="23"/>
+      <c r="I968" s="21"/>
     </row>
     <row r="969">
-      <c r="I969" s="19"/>
+      <c r="A969" s="23"/>
+      <c r="I969" s="21"/>
     </row>
     <row r="970">
-      <c r="I970" s="19"/>
+      <c r="A970" s="23"/>
+      <c r="I970" s="21"/>
     </row>
     <row r="971">
-      <c r="I971" s="19"/>
+      <c r="A971" s="23"/>
+      <c r="I971" s="21"/>
     </row>
     <row r="972">
-      <c r="I972" s="19"/>
+      <c r="A972" s="23"/>
+      <c r="I972" s="21"/>
     </row>
     <row r="973">
-      <c r="I973" s="19"/>
+      <c r="A973" s="23"/>
+      <c r="I973" s="21"/>
     </row>
     <row r="974">
-      <c r="I974" s="19"/>
+      <c r="A974" s="23"/>
+      <c r="I974" s="21"/>
     </row>
     <row r="975">
-      <c r="I975" s="19"/>
+      <c r="A975" s="23"/>
+      <c r="I975" s="21"/>
     </row>
     <row r="976">
-      <c r="I976" s="19"/>
+      <c r="A976" s="23"/>
+      <c r="I976" s="21"/>
     </row>
     <row r="977">
-      <c r="I977" s="19"/>
+      <c r="A977" s="23"/>
+      <c r="I977" s="21"/>
     </row>
     <row r="978">
-      <c r="I978" s="19"/>
+      <c r="A978" s="23"/>
+      <c r="I978" s="21"/>
     </row>
     <row r="979">
-      <c r="I979" s="19"/>
+      <c r="A979" s="23"/>
+      <c r="I979" s="21"/>
     </row>
     <row r="980">
-      <c r="I980" s="19"/>
+      <c r="A980" s="23"/>
+      <c r="I980" s="21"/>
     </row>
     <row r="981">
-      <c r="I981" s="19"/>
+      <c r="A981" s="23"/>
+      <c r="I981" s="21"/>
     </row>
     <row r="982">
-      <c r="I982" s="19"/>
+      <c r="A982" s="23"/>
+      <c r="I982" s="21"/>
     </row>
     <row r="983">
-      <c r="I983" s="19"/>
+      <c r="A983" s="23"/>
+      <c r="I983" s="21"/>
     </row>
     <row r="984">
-      <c r="I984" s="19"/>
+      <c r="A984" s="23"/>
+      <c r="I984" s="21"/>
     </row>
     <row r="985">
-      <c r="I985" s="19"/>
+      <c r="A985" s="23"/>
+      <c r="I985" s="21"/>
     </row>
     <row r="986">
-      <c r="I986" s="19"/>
+      <c r="A986" s="23"/>
+      <c r="I986" s="21"/>
     </row>
     <row r="987">
-      <c r="I987" s="19"/>
+      <c r="A987" s="23"/>
+      <c r="I987" s="21"/>
     </row>
     <row r="988">
-      <c r="I988" s="19"/>
+      <c r="A988" s="23"/>
+      <c r="I988" s="21"/>
     </row>
     <row r="989">
-      <c r="I989" s="19"/>
+      <c r="A989" s="23"/>
+      <c r="I989" s="21"/>
     </row>
     <row r="990">
-      <c r="I990" s="19"/>
+      <c r="A990" s="23"/>
+      <c r="I990" s="21"/>
     </row>
     <row r="991">
-      <c r="I991" s="19"/>
+      <c r="A991" s="23"/>
+      <c r="I991" s="21"/>
     </row>
     <row r="992">
-      <c r="I992" s="19"/>
+      <c r="A992" s="23"/>
+      <c r="I992" s="21"/>
     </row>
     <row r="993">
-      <c r="I993" s="19"/>
+      <c r="A993" s="23"/>
+      <c r="I993" s="21"/>
     </row>
     <row r="994">
-      <c r="I994" s="19"/>
+      <c r="A994" s="23"/>
+      <c r="I994" s="21"/>
     </row>
     <row r="995">
-      <c r="I995" s="19"/>
+      <c r="A995" s="23"/>
+      <c r="I995" s="21"/>
     </row>
     <row r="996">
-      <c r="I996" s="19"/>
+      <c r="A996" s="23"/>
+      <c r="I996" s="21"/>
     </row>
     <row r="997">
-      <c r="I997" s="19"/>
+      <c r="A997" s="23"/>
+      <c r="I997" s="21"/>
     </row>
     <row r="998">
-      <c r="I998" s="19"/>
+      <c r="A998" s="23"/>
+      <c r="I998" s="21"/>
     </row>
     <row r="999">
-      <c r="I999" s="19"/>
+      <c r="A999" s="23"/>
+      <c r="I999" s="21"/>
     </row>
     <row r="1000">
-      <c r="I1000" s="19"/>
+      <c r="A1000" s="23"/>
+      <c r="I1000" s="21"/>
     </row>
     <row r="1001">
-      <c r="I1001" s="19"/>
+      <c r="A1001" s="23"/>
+      <c r="I1001" s="21"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/src/data/AFCARS.xlsx
+++ b/src/data/AFCARS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="67">
   <si>
     <t>State</t>
   </si>
@@ -175,9 +175,6 @@
     <t>NULL</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>RI</t>
   </si>
   <si>
@@ -213,6 +210,9 @@
   <si>
     <t>WY</t>
   </si>
+  <si>
+    <t>&lt;10</t>
+  </si>
 </sst>
 </file>
 
@@ -221,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -241,6 +241,16 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -269,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border/>
     <border>
       <right style="thin">
@@ -281,11 +291,55 @@
         <color rgb="FF153D64"/>
       </right>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -337,9 +391,6 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -351,6 +402,35 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -637,7 +717,7 @@
         <v>1030.0</v>
       </c>
       <c r="K2" s="12">
-        <f t="shared" ref="K2:K40" si="1">J2/C2</f>
+        <f t="shared" ref="K2:K261" si="1">J2/C2</f>
         <v>0.385623362</v>
       </c>
       <c r="L2" s="7"/>
@@ -2388,8 +2468,9 @@
       <c r="J41" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="K41" s="17" t="s">
-        <v>54</v>
+      <c r="K41" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
       </c>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
@@ -2403,7 +2484,7 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42" s="2">
         <v>2023.0</v>
@@ -2433,7 +2514,7 @@
         <v>828.0</v>
       </c>
       <c r="K42" s="12">
-        <f t="shared" ref="K42:K45" si="2">J42/C42</f>
+        <f t="shared" si="1"/>
         <v>0.473955352</v>
       </c>
       <c r="L42" s="7"/>
@@ -2448,7 +2529,7 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B43" s="2">
         <v>2023.0</v>
@@ -2478,7 +2559,7 @@
         <v>1040.0</v>
       </c>
       <c r="K43" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.2912349482</v>
       </c>
       <c r="L43" s="7"/>
@@ -2493,7 +2574,7 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B44" s="2">
         <v>2023.0</v>
@@ -2523,7 +2604,7 @@
         <v>835.0</v>
       </c>
       <c r="K44" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.5027092113</v>
       </c>
       <c r="L44" s="7"/>
@@ -2538,7 +2619,7 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" s="2">
         <v>2023.0</v>
@@ -2568,7 +2649,7 @@
         <v>4509.0</v>
       </c>
       <c r="K45" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.4974076117</v>
       </c>
       <c r="L45" s="7"/>
@@ -2583,7 +2664,7 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B46" s="2">
         <v>2023.0</v>
@@ -2609,11 +2690,12 @@
       <c r="I46" s="14">
         <v>14743.0</v>
       </c>
-      <c r="J46" s="18" t="s">
+      <c r="J46" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="K46" s="17" t="s">
-        <v>54</v>
+      <c r="K46" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
       </c>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
@@ -2627,7 +2709,7 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47" s="2">
         <v>2023.0</v>
@@ -2657,7 +2739,7 @@
         <v>1120.0</v>
       </c>
       <c r="K47" s="12">
-        <f t="shared" ref="K47:K144" si="3">J47/C47</f>
+        <f t="shared" si="1"/>
         <v>0.6002143623</v>
       </c>
       <c r="L47" s="7"/>
@@ -2672,7 +2754,7 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48" s="2">
         <v>2023.0</v>
@@ -2702,7 +2784,7 @@
         <v>4735.0</v>
       </c>
       <c r="K48" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.9559862709</v>
       </c>
       <c r="L48" s="7"/>
@@ -2717,7 +2799,7 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49" s="2">
         <v>2023.0</v>
@@ -2747,7 +2829,7 @@
         <v>810.0</v>
       </c>
       <c r="K49" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.8051689861</v>
       </c>
       <c r="L49" s="7"/>
@@ -2762,7 +2844,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B50" s="2">
         <v>2023.0</v>
@@ -2792,7 +2874,7 @@
         <v>4341.0</v>
       </c>
       <c r="K50" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6160068114</v>
       </c>
       <c r="L50" s="7"/>
@@ -2807,7 +2889,7 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" s="2">
         <v>2023.0</v>
@@ -2837,7 +2919,7 @@
         <v>2968.0</v>
       </c>
       <c r="K51" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.4713355566</v>
       </c>
       <c r="L51" s="7"/>
@@ -2852,7 +2934,7 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52" s="2">
         <v>2023.0</v>
@@ -2880,7 +2962,7 @@
         <v>3148.0</v>
       </c>
       <c r="K52" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.4326553051</v>
       </c>
       <c r="L52" s="7"/>
@@ -2895,7 +2977,7 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" s="2">
         <v>2023.0</v>
@@ -2923,7 +3005,7 @@
         <v>468.0</v>
       </c>
       <c r="K53" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.5792079208</v>
       </c>
       <c r="L53" s="7"/>
@@ -2965,7 +3047,7 @@
         <v>12.0</v>
       </c>
       <c r="K54" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2998,7 +3080,7 @@
         <v>13</v>
       </c>
       <c r="K55" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3031,7 +3113,7 @@
         <v>1256.0</v>
       </c>
       <c r="K56" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3064,7 +3146,7 @@
         <v>952.0</v>
       </c>
       <c r="K57" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3097,7 +3179,7 @@
         <v>26580.0</v>
       </c>
       <c r="K58" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3130,7 +3212,7 @@
         <v>767.0</v>
       </c>
       <c r="K59" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3163,7 +3245,7 @@
         <v>115.0</v>
       </c>
       <c r="K60" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3196,7 +3278,7 @@
         <v>12.0</v>
       </c>
       <c r="K61" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3229,7 +3311,7 @@
         <v>52.0</v>
       </c>
       <c r="K62" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3262,7 +3344,7 @@
         <v>13</v>
       </c>
       <c r="K63" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3295,7 +3377,7 @@
         <v>3855.0</v>
       </c>
       <c r="K64" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3328,7 +3410,7 @@
         <v>83.0</v>
       </c>
       <c r="K65" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3361,7 +3443,7 @@
         <v>303.0</v>
       </c>
       <c r="K66" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3394,7 +3476,7 @@
         <v>13</v>
       </c>
       <c r="K67" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3427,7 +3509,7 @@
         <v>5903.0</v>
       </c>
       <c r="K68" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3460,7 +3542,7 @@
         <v>13</v>
       </c>
       <c r="K69" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3493,7 +3575,7 @@
         <v>75.0</v>
       </c>
       <c r="K70" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3526,7 +3608,7 @@
         <v>4380.0</v>
       </c>
       <c r="K71" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3559,7 +3641,7 @@
         <v>1816.0</v>
       </c>
       <c r="K72" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3592,7 +3674,7 @@
         <v>13</v>
       </c>
       <c r="K73" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3625,7 +3707,7 @@
         <v>13</v>
       </c>
       <c r="K74" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3658,7 +3740,7 @@
         <v>3097.0</v>
       </c>
       <c r="K75" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3691,7 +3773,7 @@
         <v>1485.0</v>
       </c>
       <c r="K76" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3724,7 +3806,7 @@
         <v>99.0</v>
       </c>
       <c r="K77" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3757,7 +3839,7 @@
         <v>32</v>
       </c>
       <c r="K78" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3790,7 +3872,7 @@
         <v>150.0</v>
       </c>
       <c r="K79" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3823,7 +3905,7 @@
         <v>189.0</v>
       </c>
       <c r="K80" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3856,7 +3938,7 @@
         <v>339.0</v>
       </c>
       <c r="K81" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3889,7 +3971,7 @@
         <v>1100.0</v>
       </c>
       <c r="K82" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3922,7 +4004,7 @@
         <v>80.0</v>
       </c>
       <c r="K83" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3955,7 +4037,7 @@
         <v>753.0</v>
       </c>
       <c r="K84" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3988,7 +4070,7 @@
         <v>155.0</v>
       </c>
       <c r="K85" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4021,7 +4103,7 @@
         <v>13</v>
       </c>
       <c r="K86" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4054,7 +4136,7 @@
         <v>181.0</v>
       </c>
       <c r="K87" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4087,7 +4169,7 @@
         <v>91.0</v>
       </c>
       <c r="K88" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4120,7 +4202,7 @@
         <v>113.0</v>
       </c>
       <c r="K89" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4153,7 +4235,7 @@
         <v>475.0</v>
       </c>
       <c r="K90" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4186,7 +4268,7 @@
         <v>32</v>
       </c>
       <c r="K91" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4219,7 +4301,7 @@
         <v>41.0</v>
       </c>
       <c r="K92" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4252,13 +4334,13 @@
         <v>1724.0</v>
       </c>
       <c r="K93" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B94" s="3">
         <v>2022.0</v>
@@ -4285,13 +4367,13 @@
         <v>13</v>
       </c>
       <c r="K94" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B95" s="3">
         <v>2022.0</v>
@@ -4318,13 +4400,13 @@
         <v>540.0</v>
       </c>
       <c r="K95" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B96" s="3">
         <v>2022.0</v>
@@ -4351,13 +4433,13 @@
         <v>13</v>
       </c>
       <c r="K96" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B97" s="3">
         <v>2022.0</v>
@@ -4384,13 +4466,13 @@
         <v>13</v>
       </c>
       <c r="K97" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B98" s="3">
         <v>2022.0</v>
@@ -4417,13 +4499,13 @@
         <v>10598.0</v>
       </c>
       <c r="K98" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B99" s="3">
         <v>2022.0</v>
@@ -4450,13 +4532,13 @@
         <v>1219.0</v>
       </c>
       <c r="K99" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B100" s="3">
         <v>2022.0</v>
@@ -4483,13 +4565,13 @@
         <v>13</v>
       </c>
       <c r="K100" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B101" s="3">
         <v>2022.0</v>
@@ -4516,13 +4598,13 @@
         <v>13</v>
       </c>
       <c r="K101" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B102" s="3">
         <v>2022.0</v>
@@ -4549,13 +4631,13 @@
         <v>281.0</v>
       </c>
       <c r="K102" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B103" s="3">
         <v>2022.0</v>
@@ -4582,13 +4664,13 @@
         <v>477.0</v>
       </c>
       <c r="K103" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B104" s="3">
         <v>2022.0</v>
@@ -4615,13 +4697,13 @@
         <v>13</v>
       </c>
       <c r="K104" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B105" s="3">
         <v>2022.0</v>
@@ -4648,7 +4730,7 @@
         <v>483.0</v>
       </c>
       <c r="K105" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4684,7 +4766,7 @@
         <v>1205.0</v>
       </c>
       <c r="K106" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.4156605726</v>
       </c>
     </row>
@@ -4720,7 +4802,7 @@
         <v>2039.0</v>
       </c>
       <c r="K107" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.3775925926</v>
       </c>
     </row>
@@ -4756,7 +4838,7 @@
         <v>1509.0</v>
       </c>
       <c r="K108" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.3348125139</v>
       </c>
     </row>
@@ -4792,7 +4874,7 @@
         <v>3509.0</v>
       </c>
       <c r="K109" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.2525914195</v>
       </c>
     </row>
@@ -4828,7 +4910,7 @@
         <v>32597.0</v>
       </c>
       <c r="K110" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6688210431</v>
       </c>
     </row>
@@ -4864,7 +4946,7 @@
         <v>1586.0</v>
       </c>
       <c r="K111" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.3684088269</v>
       </c>
     </row>
@@ -4900,7 +4982,7 @@
         <v>2842.0</v>
       </c>
       <c r="K112" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.7861687414</v>
       </c>
     </row>
@@ -4936,7 +5018,7 @@
         <v>505.0</v>
       </c>
       <c r="K113" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.001984127</v>
       </c>
     </row>
@@ -4972,7 +5054,7 @@
         <v>400.0</v>
       </c>
       <c r="K114" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.8771929825</v>
       </c>
     </row>
@@ -5008,7 +5090,7 @@
         <v>8867.0</v>
       </c>
       <c r="K115" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.3752115775</v>
       </c>
     </row>
@@ -5044,7 +5126,7 @@
         <v>4650.0</v>
       </c>
       <c r="K116" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.4414696668</v>
       </c>
     </row>
@@ -5080,7 +5162,7 @@
         <v>1186.0</v>
       </c>
       <c r="K117" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.8253305498</v>
       </c>
     </row>
@@ -5116,7 +5198,7 @@
         <v>2223.0</v>
       </c>
       <c r="K118" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.5246636771</v>
       </c>
     </row>
@@ -5152,7 +5234,7 @@
         <v>1131.0</v>
       </c>
       <c r="K119" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6850393701</v>
       </c>
     </row>
@@ -5188,7 +5270,7 @@
         <v>9058.0</v>
       </c>
       <c r="K120" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.4260783668</v>
       </c>
     </row>
@@ -5224,7 +5306,7 @@
         <v>5428.0</v>
       </c>
       <c r="K121" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.4060139128</v>
       </c>
     </row>
@@ -5260,7 +5342,7 @@
         <v>2805.0</v>
       </c>
       <c r="K122" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.3941821248</v>
       </c>
     </row>
@@ -5296,7 +5378,7 @@
         <v>5679.0</v>
       </c>
       <c r="K123" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6764740917</v>
       </c>
     </row>
@@ -5332,7 +5414,7 @@
         <v>1834.0</v>
       </c>
       <c r="K124" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.5577858881</v>
       </c>
     </row>
@@ -5368,7 +5450,7 @@
         <v>5919.0</v>
       </c>
       <c r="K125" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6473805097</v>
       </c>
     </row>
@@ -5404,7 +5486,7 @@
         <v>3267.0</v>
       </c>
       <c r="K126" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.8943334246</v>
       </c>
     </row>
@@ -5440,7 +5522,7 @@
         <v>1717.0</v>
       </c>
       <c r="K127" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.7783318223</v>
       </c>
     </row>
@@ -5476,7 +5558,7 @@
         <v>5434.0</v>
       </c>
       <c r="K128" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.5688265466</v>
       </c>
     </row>
@@ -5512,7 +5594,7 @@
         <v>4827.0</v>
       </c>
       <c r="K129" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6943325662</v>
       </c>
     </row>
@@ -5548,7 +5630,7 @@
         <v>4971.0</v>
       </c>
       <c r="K130" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.3765909091</v>
       </c>
     </row>
@@ -5584,7 +5666,7 @@
         <v>1870.0</v>
       </c>
       <c r="K131" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.5251333895</v>
       </c>
     </row>
@@ -5620,7 +5702,7 @@
         <v>1674.0</v>
       </c>
       <c r="K132" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.5254237288</v>
       </c>
     </row>
@@ -5656,7 +5738,7 @@
         <v>7052.0</v>
       </c>
       <c r="K133" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6705971852</v>
       </c>
     </row>
@@ -5692,7 +5774,7 @@
         <v>953.0</v>
       </c>
       <c r="K134" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.597492163</v>
       </c>
     </row>
@@ -5728,7 +5810,7 @@
         <v>1502.0</v>
       </c>
       <c r="K135" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.3888169816</v>
       </c>
     </row>
@@ -5764,7 +5846,7 @@
         <v>708.0</v>
       </c>
       <c r="K136" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6361185984</v>
       </c>
     </row>
@@ -5800,7 +5882,7 @@
         <v>3467.0</v>
       </c>
       <c r="K137" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.080735661</v>
       </c>
     </row>
@@ -5836,7 +5918,7 @@
         <v>1383.0</v>
       </c>
       <c r="K138" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.7439483593</v>
       </c>
     </row>
@@ -5872,7 +5954,7 @@
         <v>1441.0</v>
       </c>
       <c r="K139" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.3420365535</v>
       </c>
     </row>
@@ -5908,7 +5990,7 @@
         <v>11197.0</v>
       </c>
       <c r="K140" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.7523854321</v>
       </c>
     </row>
@@ -5944,7 +6026,7 @@
         <v>8167.0</v>
       </c>
       <c r="K141" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.5290878466</v>
       </c>
     </row>
@@ -5980,7 +6062,7 @@
         <v>4958.0</v>
       </c>
       <c r="K142" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.6637215529</v>
       </c>
     </row>
@@ -6016,7 +6098,7 @@
         <v>3805.0</v>
       </c>
       <c r="K143" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.7177890964</v>
       </c>
     </row>
@@ -6052,7 +6134,7 @@
         <v>12970.0</v>
       </c>
       <c r="K144" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.9581147965</v>
       </c>
     </row>
@@ -6087,13 +6169,14 @@
       <c r="J145" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="K145" s="17" t="s">
-        <v>54</v>
+      <c r="K145" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B146" s="3">
         <v>2021.0</v>
@@ -6123,13 +6206,13 @@
         <v>1292.0</v>
       </c>
       <c r="K146" s="12">
-        <f t="shared" ref="K146:K151" si="4">J146/C146</f>
+        <f t="shared" si="1"/>
         <v>0.7017925041</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B147" s="3">
         <v>2021.0</v>
@@ -6159,13 +6242,13 @@
         <v>3040.0</v>
       </c>
       <c r="K147" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.7684529828</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B148" s="3">
         <v>2021.0</v>
@@ -6195,13 +6278,13 @@
         <v>828.0</v>
       </c>
       <c r="K148" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.500907441</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B149" s="3">
         <v>2021.0</v>
@@ -6231,13 +6314,13 @@
         <v>5175.0</v>
       </c>
       <c r="K149" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.5593385214</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B150" s="3">
         <v>2021.0</v>
@@ -6267,13 +6350,13 @@
         <v>11583.0</v>
       </c>
       <c r="K150" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.4131326461</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B151" s="3">
         <v>2021.0</v>
@@ -6303,13 +6386,13 @@
         <v>1476.0</v>
       </c>
       <c r="K151" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0.6958981612</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B152" s="3">
         <v>2021.0</v>
@@ -6338,13 +6421,14 @@
       <c r="J152" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="K152" s="17" t="s">
-        <v>54</v>
+      <c r="K152" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B153" s="3">
         <v>2021.0</v>
@@ -6374,13 +6458,13 @@
         <v>1299.0</v>
       </c>
       <c r="K153" s="12">
-        <f t="shared" ref="K153:K157" si="5">J153/C153</f>
+        <f t="shared" si="1"/>
         <v>1.193933824</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B154" s="3">
         <v>2021.0</v>
@@ -6410,13 +6494,13 @@
         <v>4831.0</v>
       </c>
       <c r="K154" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0.5380931165</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B155" s="3">
         <v>2021.0</v>
@@ -6446,13 +6530,13 @@
         <v>2488.0</v>
       </c>
       <c r="K155" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0.3644353303</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B156" s="3">
         <v>2021.0</v>
@@ -6482,13 +6566,13 @@
         <v>3431.0</v>
       </c>
       <c r="K156" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0.4706447188</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B157" s="3">
         <v>2021.0</v>
@@ -6518,12 +6602,12 @@
         <v>447.0</v>
       </c>
       <c r="K157" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0.5228070175</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="19" t="s">
+      <c r="A158" s="18" t="s">
         <v>11</v>
       </c>
       <c r="B158" s="3">
@@ -6544,13 +6628,17 @@
       <c r="G158" s="3">
         <v>214.0</v>
       </c>
-      <c r="H158" s="20">
+      <c r="H158" s="19">
         <v>0.548</v>
       </c>
-      <c r="J158" s="21"/>
+      <c r="J158" s="20"/>
+      <c r="K158" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="19" t="s">
+      <c r="A159" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B159" s="3">
@@ -6571,13 +6659,17 @@
       <c r="G159" s="3">
         <v>611.0</v>
       </c>
-      <c r="H159" s="20">
+      <c r="H159" s="19">
         <v>0.4</v>
       </c>
-      <c r="J159" s="21"/>
+      <c r="J159" s="20"/>
+      <c r="K159" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="19" t="s">
+      <c r="A160" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B160" s="3">
@@ -6598,13 +6690,17 @@
       <c r="G160" s="3">
         <v>698.0</v>
       </c>
-      <c r="H160" s="20">
+      <c r="H160" s="19">
         <v>0.383</v>
       </c>
-      <c r="J160" s="21"/>
+      <c r="J160" s="20"/>
+      <c r="K160" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="19" t="s">
+      <c r="A161" s="18" t="s">
         <v>15</v>
       </c>
       <c r="B161" s="3">
@@ -6625,13 +6721,17 @@
       <c r="G161" s="3">
         <v>1719.0</v>
       </c>
-      <c r="H161" s="20">
+      <c r="H161" s="19">
         <v>0.464</v>
       </c>
-      <c r="J161" s="21"/>
+      <c r="J161" s="20"/>
+      <c r="K161" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="19" t="s">
+      <c r="A162" s="18" t="s">
         <v>16</v>
       </c>
       <c r="B162" s="3">
@@ -6652,13 +6752,17 @@
       <c r="G162" s="3">
         <v>5923.0</v>
       </c>
-      <c r="H162" s="20">
+      <c r="H162" s="19">
         <v>0.479</v>
       </c>
-      <c r="J162" s="21"/>
+      <c r="J162" s="20"/>
+      <c r="K162" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="19" t="s">
+      <c r="A163" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B163" s="3">
@@ -6679,13 +6783,17 @@
       <c r="G163" s="3">
         <v>534.0</v>
       </c>
-      <c r="H163" s="20">
+      <c r="H163" s="19">
         <v>0.419</v>
       </c>
-      <c r="J163" s="21"/>
+      <c r="J163" s="20"/>
+      <c r="K163" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="19" t="s">
+      <c r="A164" s="18" t="s">
         <v>18</v>
       </c>
       <c r="B164" s="3">
@@ -6706,13 +6814,17 @@
       <c r="G164" s="3">
         <v>384.0</v>
       </c>
-      <c r="H164" s="20">
+      <c r="H164" s="19">
         <v>0.384</v>
       </c>
-      <c r="J164" s="21"/>
+      <c r="J164" s="20"/>
+      <c r="K164" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="19" t="s">
+      <c r="A165" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B165" s="3">
@@ -6733,13 +6845,17 @@
       <c r="G165" s="3">
         <v>63.0</v>
       </c>
-      <c r="H165" s="20">
+      <c r="H165" s="19">
         <v>0.33</v>
       </c>
-      <c r="J165" s="21"/>
+      <c r="J165" s="20"/>
+      <c r="K165" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="19" t="s">
+      <c r="A166" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B166" s="3">
@@ -6760,13 +6876,17 @@
       <c r="G166" s="3">
         <v>91.0</v>
       </c>
-      <c r="H166" s="20">
+      <c r="H166" s="19">
         <v>0.327</v>
       </c>
-      <c r="J166" s="21"/>
+      <c r="J166" s="20"/>
+      <c r="K166" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="19" t="s">
+      <c r="A167" s="18" t="s">
         <v>21</v>
       </c>
       <c r="B167" s="3">
@@ -6787,13 +6907,17 @@
       <c r="G167" s="3">
         <v>4037.0</v>
       </c>
-      <c r="H167" s="20">
+      <c r="H167" s="19">
         <v>0.378</v>
       </c>
-      <c r="J167" s="21"/>
+      <c r="J167" s="20"/>
+      <c r="K167" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="19" t="s">
+      <c r="A168" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B168" s="3">
@@ -6814,13 +6938,17 @@
       <c r="G168" s="3">
         <v>1247.0</v>
       </c>
-      <c r="H168" s="20">
+      <c r="H168" s="19">
         <v>0.415</v>
       </c>
-      <c r="J168" s="21"/>
+      <c r="J168" s="20"/>
+      <c r="K168" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="19" t="s">
+      <c r="A169" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B169" s="3">
@@ -6841,13 +6969,17 @@
       <c r="G169" s="3">
         <v>164.0</v>
       </c>
-      <c r="H169" s="20">
+      <c r="H169" s="19">
         <v>0.538</v>
       </c>
-      <c r="J169" s="21"/>
+      <c r="J169" s="20"/>
+      <c r="K169" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="19" t="s">
+      <c r="A170" s="18" t="s">
         <v>24</v>
       </c>
       <c r="B170" s="3">
@@ -6868,13 +7000,17 @@
       <c r="G170" s="3">
         <v>867.0</v>
       </c>
-      <c r="H170" s="20">
+      <c r="H170" s="19">
         <v>0.482</v>
       </c>
-      <c r="J170" s="21"/>
+      <c r="J170" s="20"/>
+      <c r="K170" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="19" t="s">
+      <c r="A171" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B171" s="3">
@@ -6895,13 +7031,17 @@
       <c r="G171" s="3">
         <v>293.0</v>
       </c>
-      <c r="H171" s="20">
+      <c r="H171" s="19">
         <v>0.626</v>
       </c>
-      <c r="J171" s="21"/>
+      <c r="J171" s="20"/>
+      <c r="K171" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="19" t="s">
+      <c r="A172" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B172" s="3">
@@ -6922,13 +7062,17 @@
       <c r="G172" s="3">
         <v>2179.0</v>
       </c>
-      <c r="H172" s="20">
+      <c r="H172" s="19">
         <v>0.482</v>
       </c>
-      <c r="J172" s="21"/>
+      <c r="J172" s="20"/>
+      <c r="K172" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="19" t="s">
+      <c r="A173" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B173" s="3">
@@ -6949,13 +7093,17 @@
       <c r="G173" s="3">
         <v>1557.0</v>
       </c>
-      <c r="H173" s="20">
+      <c r="H173" s="19">
         <v>0.547</v>
       </c>
-      <c r="J173" s="21"/>
+      <c r="J173" s="20"/>
+      <c r="K173" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="19" t="s">
+      <c r="A174" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B174" s="3">
@@ -6976,13 +7124,17 @@
       <c r="G174" s="3">
         <v>744.0</v>
       </c>
-      <c r="H174" s="20">
+      <c r="H174" s="19">
         <v>0.511</v>
       </c>
-      <c r="J174" s="21"/>
+      <c r="J174" s="20"/>
+      <c r="K174" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="19" t="s">
+      <c r="A175" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B175" s="3">
@@ -7003,13 +7155,17 @@
       <c r="G175" s="3">
         <v>1257.0</v>
       </c>
-      <c r="H175" s="20">
+      <c r="H175" s="19">
         <v>0.394</v>
       </c>
-      <c r="J175" s="21"/>
+      <c r="J175" s="20"/>
+      <c r="K175" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="19" t="s">
+      <c r="A176" s="18" t="s">
         <v>30</v>
       </c>
       <c r="B176" s="3">
@@ -7030,13 +7186,17 @@
       <c r="G176" s="3">
         <v>608.0</v>
       </c>
-      <c r="H176" s="20">
+      <c r="H176" s="19">
         <v>0.494</v>
       </c>
-      <c r="J176" s="21"/>
+      <c r="J176" s="20"/>
+      <c r="K176" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="19" t="s">
+      <c r="A177" s="18" t="s">
         <v>31</v>
       </c>
       <c r="B177" s="3">
@@ -7057,13 +7217,17 @@
       <c r="G177" s="3">
         <v>869.0</v>
       </c>
-      <c r="H177" s="20">
+      <c r="H177" s="19">
         <v>0.553</v>
       </c>
-      <c r="J177" s="21"/>
+      <c r="J177" s="20"/>
+      <c r="K177" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="19" t="s">
+      <c r="A178" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B178" s="3">
@@ -7084,13 +7248,17 @@
       <c r="G178" s="3">
         <v>333.0</v>
       </c>
-      <c r="H178" s="20">
+      <c r="H178" s="19">
         <v>0.343</v>
       </c>
-      <c r="J178" s="21"/>
+      <c r="J178" s="20"/>
+      <c r="K178" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="19" t="s">
+      <c r="A179" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B179" s="3">
@@ -7111,13 +7279,17 @@
       <c r="G179" s="3">
         <v>385.0</v>
       </c>
-      <c r="H179" s="20">
+      <c r="H179" s="19">
         <v>0.448</v>
       </c>
-      <c r="J179" s="21"/>
+      <c r="J179" s="20"/>
+      <c r="K179" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="19" t="s">
+      <c r="A180" s="18" t="s">
         <v>35</v>
       </c>
       <c r="B180" s="3">
@@ -7138,13 +7310,17 @@
       <c r="G180" s="3">
         <v>1426.0</v>
       </c>
-      <c r="H180" s="20">
+      <c r="H180" s="19">
         <v>0.361</v>
       </c>
-      <c r="J180" s="21"/>
+      <c r="J180" s="20"/>
+      <c r="K180" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="19" t="s">
+      <c r="A181" s="18" t="s">
         <v>36</v>
       </c>
       <c r="B181" s="3">
@@ -7165,13 +7341,17 @@
       <c r="G181" s="3">
         <v>693.0</v>
       </c>
-      <c r="H181" s="20">
+      <c r="H181" s="19">
         <v>0.547</v>
       </c>
-      <c r="J181" s="21"/>
+      <c r="J181" s="20"/>
+      <c r="K181" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="19" t="s">
+      <c r="A182" s="18" t="s">
         <v>37</v>
       </c>
       <c r="B182" s="3">
@@ -7192,13 +7372,17 @@
       <c r="G182" s="3">
         <v>1309.0</v>
       </c>
-      <c r="H182" s="20">
+      <c r="H182" s="19">
         <v>0.563</v>
       </c>
-      <c r="J182" s="21"/>
+      <c r="J182" s="20"/>
+      <c r="K182" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="19" t="s">
+      <c r="A183" s="18" t="s">
         <v>38</v>
       </c>
       <c r="B183" s="3">
@@ -7219,13 +7403,17 @@
       <c r="G183" s="3">
         <v>592.0</v>
       </c>
-      <c r="H183" s="20">
+      <c r="H183" s="19">
         <v>0.469</v>
       </c>
-      <c r="J183" s="21"/>
+      <c r="J183" s="20"/>
+      <c r="K183" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="19" t="s">
+      <c r="A184" s="18" t="s">
         <v>39</v>
       </c>
       <c r="B184" s="3">
@@ -7246,13 +7434,17 @@
       <c r="G184" s="3">
         <v>264.0</v>
       </c>
-      <c r="H184" s="20">
+      <c r="H184" s="19">
         <v>0.559</v>
       </c>
-      <c r="J184" s="21"/>
+      <c r="J184" s="20"/>
+      <c r="K184" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="19" t="s">
+      <c r="A185" s="18" t="s">
         <v>40</v>
       </c>
       <c r="B185" s="3">
@@ -7273,13 +7465,17 @@
       <c r="G185" s="3">
         <v>1205.0</v>
       </c>
-      <c r="H185" s="20">
+      <c r="H185" s="19">
         <v>0.323</v>
       </c>
-      <c r="J185" s="21"/>
+      <c r="J185" s="20"/>
+      <c r="K185" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="19" t="s">
+      <c r="A186" s="18" t="s">
         <v>41</v>
       </c>
       <c r="B186" s="3">
@@ -7300,13 +7496,17 @@
       <c r="G186" s="3">
         <v>238.0</v>
       </c>
-      <c r="H186" s="20">
+      <c r="H186" s="19">
         <v>0.476</v>
       </c>
-      <c r="J186" s="21"/>
+      <c r="J186" s="20"/>
+      <c r="K186" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="19" t="s">
+      <c r="A187" s="18" t="s">
         <v>42</v>
       </c>
       <c r="B187" s="3">
@@ -7327,13 +7527,17 @@
       <c r="G187" s="3">
         <v>485.0</v>
       </c>
-      <c r="H187" s="20">
+      <c r="H187" s="19">
         <v>0.509</v>
       </c>
-      <c r="J187" s="21"/>
+      <c r="J187" s="20"/>
+      <c r="K187" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="19" t="s">
+      <c r="A188" s="18" t="s">
         <v>43</v>
       </c>
       <c r="B188" s="3">
@@ -7354,13 +7558,17 @@
       <c r="G188" s="3">
         <v>143.0</v>
       </c>
-      <c r="H188" s="20">
+      <c r="H188" s="19">
         <v>0.582</v>
       </c>
-      <c r="J188" s="21"/>
+      <c r="J188" s="20"/>
+      <c r="K188" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="19" t="s">
+      <c r="A189" s="18" t="s">
         <v>44</v>
       </c>
       <c r="B189" s="3">
@@ -7381,13 +7589,17 @@
       <c r="G189" s="3">
         <v>383.0</v>
       </c>
-      <c r="H189" s="20">
+      <c r="H189" s="19">
         <v>0.451</v>
       </c>
-      <c r="J189" s="21"/>
+      <c r="J189" s="20"/>
+      <c r="K189" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" s="19" t="s">
+      <c r="A190" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B190" s="3">
@@ -7408,13 +7620,17 @@
       <c r="G190" s="3">
         <v>152.0</v>
       </c>
-      <c r="H190" s="20">
+      <c r="H190" s="19">
         <v>0.616</v>
       </c>
-      <c r="J190" s="21"/>
+      <c r="J190" s="20"/>
+      <c r="K190" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="19" t="s">
+      <c r="A191" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B191" s="3">
@@ -7435,13 +7651,17 @@
       <c r="G191" s="3">
         <v>726.0</v>
       </c>
-      <c r="H191" s="20">
+      <c r="H191" s="19">
         <v>0.555</v>
       </c>
-      <c r="J191" s="21"/>
+      <c r="J191" s="20"/>
+      <c r="K191" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="19" t="s">
+      <c r="A192" s="18" t="s">
         <v>47</v>
       </c>
       <c r="B192" s="3">
@@ -7462,13 +7682,17 @@
       <c r="G192" s="3">
         <v>1434.0</v>
       </c>
-      <c r="H192" s="20">
+      <c r="H192" s="19">
         <v>0.47</v>
       </c>
-      <c r="J192" s="21"/>
+      <c r="J192" s="20"/>
+      <c r="K192" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="19" t="s">
+      <c r="A193" s="18" t="s">
         <v>48</v>
       </c>
       <c r="B193" s="3">
@@ -7489,13 +7713,17 @@
       <c r="G193" s="3">
         <v>1527.0</v>
       </c>
-      <c r="H193" s="20">
+      <c r="H193" s="19">
         <v>0.42</v>
       </c>
-      <c r="J193" s="21"/>
+      <c r="J193" s="20"/>
+      <c r="K193" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="19" t="s">
+      <c r="A194" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B194" s="3">
@@ -7516,13 +7744,17 @@
       <c r="G194" s="3">
         <v>1349.0</v>
       </c>
-      <c r="H194" s="20">
+      <c r="H194" s="19">
         <v>0.461</v>
       </c>
-      <c r="J194" s="21"/>
+      <c r="J194" s="20"/>
+      <c r="K194" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="19" t="s">
+      <c r="A195" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B195" s="3">
@@ -7543,13 +7775,17 @@
       <c r="G195" s="3">
         <v>390.0</v>
       </c>
-      <c r="H195" s="20">
+      <c r="H195" s="19">
         <v>0.516</v>
       </c>
-      <c r="J195" s="21"/>
+      <c r="J195" s="20"/>
+      <c r="K195" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="19" t="s">
+      <c r="A196" s="18" t="s">
         <v>51</v>
       </c>
       <c r="B196" s="3">
@@ -7570,13 +7806,17 @@
       <c r="G196" s="3">
         <v>1672.0</v>
       </c>
-      <c r="H196" s="20">
+      <c r="H196" s="19">
         <v>0.479</v>
       </c>
-      <c r="J196" s="21"/>
+      <c r="J196" s="20"/>
+      <c r="K196" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="19" t="s">
+      <c r="A197" s="18" t="s">
         <v>52</v>
       </c>
       <c r="B197" s="3">
@@ -7585,7 +7825,7 @@
       <c r="C197" s="3">
         <v>2356.0</v>
       </c>
-      <c r="D197" s="22"/>
+      <c r="D197" s="21"/>
       <c r="E197" s="3">
         <v>366.0</v>
       </c>
@@ -7595,14 +7835,18 @@
       <c r="G197" s="3">
         <v>34.0</v>
       </c>
-      <c r="H197" s="20">
+      <c r="H197" s="19">
         <v>0.522</v>
       </c>
-      <c r="J197" s="21"/>
+      <c r="J197" s="20"/>
+      <c r="K197" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
-      <c r="A198" s="19" t="s">
-        <v>55</v>
+      <c r="A198" s="18" t="s">
+        <v>54</v>
       </c>
       <c r="B198" s="3">
         <v>2024.0</v>
@@ -7622,14 +7866,18 @@
       <c r="G198" s="3">
         <v>110.0</v>
       </c>
-      <c r="H198" s="20">
+      <c r="H198" s="19">
         <v>0.538</v>
       </c>
-      <c r="J198" s="21"/>
+      <c r="J198" s="20"/>
+      <c r="K198" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="19" t="s">
-        <v>56</v>
+      <c r="A199" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="B199" s="3">
         <v>2024.0</v>
@@ -7649,14 +7897,18 @@
       <c r="G199" s="3">
         <v>562.0</v>
       </c>
-      <c r="H199" s="20">
+      <c r="H199" s="19">
         <v>0.452</v>
       </c>
-      <c r="J199" s="21"/>
+      <c r="J199" s="20"/>
+      <c r="K199" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="19" t="s">
-        <v>57</v>
+      <c r="A200" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="B200" s="3">
         <v>2024.0</v>
@@ -7676,14 +7928,18 @@
       <c r="G200" s="3">
         <v>260.0</v>
       </c>
-      <c r="H200" s="20">
+      <c r="H200" s="19">
         <v>0.471</v>
       </c>
-      <c r="J200" s="21"/>
+      <c r="J200" s="20"/>
+      <c r="K200" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="19" t="s">
-        <v>58</v>
+      <c r="A201" s="18" t="s">
+        <v>57</v>
       </c>
       <c r="B201" s="3">
         <v>2024.0</v>
@@ -7703,14 +7959,18 @@
       <c r="G201" s="3">
         <v>1165.0</v>
       </c>
-      <c r="H201" s="20">
+      <c r="H201" s="19">
         <v>0.434</v>
       </c>
-      <c r="J201" s="21"/>
+      <c r="J201" s="20"/>
+      <c r="K201" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
-      <c r="A202" s="19" t="s">
-        <v>59</v>
+      <c r="A202" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="B202" s="3">
         <v>2024.0</v>
@@ -7730,14 +7990,18 @@
       <c r="G202" s="3">
         <v>3075.0</v>
       </c>
-      <c r="H202" s="20">
+      <c r="H202" s="19">
         <v>0.39</v>
       </c>
-      <c r="J202" s="21"/>
+      <c r="J202" s="20"/>
+      <c r="K202" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="19" t="s">
-        <v>60</v>
+      <c r="A203" s="18" t="s">
+        <v>59</v>
       </c>
       <c r="B203" s="3">
         <v>2024.0</v>
@@ -7757,14 +8021,18 @@
       <c r="G203" s="3">
         <v>316.0</v>
       </c>
-      <c r="H203" s="20">
+      <c r="H203" s="19">
         <v>0.442</v>
       </c>
-      <c r="J203" s="21"/>
+      <c r="J203" s="20"/>
+      <c r="K203" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" s="19" t="s">
-        <v>61</v>
+      <c r="A204" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="B204" s="3">
         <v>2024.0</v>
@@ -7784,14 +8052,18 @@
       <c r="G204" s="3">
         <v>571.0</v>
       </c>
-      <c r="H204" s="20">
+      <c r="H204" s="19">
         <v>0.285</v>
       </c>
-      <c r="J204" s="21"/>
+      <c r="J204" s="20"/>
+      <c r="K204" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
-      <c r="A205" s="19" t="s">
-        <v>62</v>
+      <c r="A205" s="18" t="s">
+        <v>61</v>
       </c>
       <c r="B205" s="3">
         <v>2024.0</v>
@@ -7811,14 +8083,18 @@
       <c r="G205" s="3">
         <v>222.0</v>
       </c>
-      <c r="H205" s="20">
+      <c r="H205" s="19">
         <v>0.381</v>
       </c>
-      <c r="J205" s="21"/>
+      <c r="J205" s="20"/>
+      <c r="K205" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="19" t="s">
-        <v>63</v>
+      <c r="A206" s="18" t="s">
+        <v>62</v>
       </c>
       <c r="B206" s="3">
         <v>2024.0</v>
@@ -7838,14 +8114,18 @@
       <c r="G206" s="3">
         <v>712.0</v>
       </c>
-      <c r="H206" s="20">
+      <c r="H206" s="19">
         <v>0.623</v>
       </c>
-      <c r="J206" s="21"/>
+      <c r="J206" s="20"/>
+      <c r="K206" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
-      <c r="A207" s="19" t="s">
-        <v>64</v>
+      <c r="A207" s="18" t="s">
+        <v>63</v>
       </c>
       <c r="B207" s="3">
         <v>2024.0</v>
@@ -7865,14 +8145,18 @@
       <c r="G207" s="3">
         <v>589.0</v>
       </c>
-      <c r="H207" s="20">
+      <c r="H207" s="19">
         <v>0.514</v>
       </c>
-      <c r="J207" s="21"/>
+      <c r="J207" s="20"/>
+      <c r="K207" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
-      <c r="A208" s="19" t="s">
-        <v>65</v>
+      <c r="A208" s="18" t="s">
+        <v>64</v>
       </c>
       <c r="B208" s="3">
         <v>2024.0</v>
@@ -7892,14 +8176,18 @@
       <c r="G208" s="3">
         <v>1064.0</v>
       </c>
-      <c r="H208" s="20">
+      <c r="H208" s="19">
         <v>0.472</v>
       </c>
-      <c r="J208" s="21"/>
+      <c r="J208" s="20"/>
+      <c r="K208" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="19" t="s">
-        <v>66</v>
+      <c r="A209" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="B209" s="3">
         <v>2024.0</v>
@@ -7913,3182 +8201,4730 @@
       <c r="E209" s="3">
         <v>97.0</v>
       </c>
-      <c r="F209" s="22"/>
+      <c r="F209" s="21"/>
       <c r="G209" s="3">
         <v>84.0</v>
       </c>
-      <c r="H209" s="20">
+      <c r="H209" s="19">
         <v>0.717</v>
       </c>
-      <c r="J209" s="21"/>
+      <c r="J209" s="20"/>
+      <c r="K209" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="23"/>
-      <c r="I210" s="21"/>
+      <c r="A210" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B210" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C210" s="22">
+        <v>2460.0</v>
+      </c>
+      <c r="D210" s="23">
+        <v>771.0</v>
+      </c>
+      <c r="E210" s="24">
+        <v>1199.0</v>
+      </c>
+      <c r="F210" s="23">
+        <v>297.0</v>
+      </c>
+      <c r="G210" s="23">
+        <v>196.0</v>
+      </c>
+      <c r="H210" s="25">
+        <v>0.559</v>
+      </c>
+      <c r="I210" s="26"/>
+      <c r="J210" s="23">
+        <v>912.0</v>
+      </c>
+      <c r="K210" s="12">
+        <f t="shared" si="1"/>
+        <v>0.3707317073</v>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="23"/>
-      <c r="I211" s="21"/>
+      <c r="A211" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B211" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C211" s="27">
+        <v>5616.0</v>
+      </c>
+      <c r="D211" s="28">
+        <v>3189.0</v>
+      </c>
+      <c r="E211" s="29">
+        <v>866.0</v>
+      </c>
+      <c r="F211" s="29">
+        <v>398.0</v>
+      </c>
+      <c r="G211" s="29">
+        <v>720.0</v>
+      </c>
+      <c r="H211" s="30">
+        <v>0.361</v>
+      </c>
+      <c r="I211" s="31"/>
+      <c r="J211" s="28">
+        <v>2697.0</v>
+      </c>
+      <c r="K211" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4802350427</v>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="23"/>
-      <c r="I212" s="21"/>
+      <c r="A212" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B212" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C212" s="27">
+        <v>3264.0</v>
+      </c>
+      <c r="D212" s="28">
+        <v>1011.0</v>
+      </c>
+      <c r="E212" s="28">
+        <v>1028.0</v>
+      </c>
+      <c r="F212" s="29">
+        <v>96.0</v>
+      </c>
+      <c r="G212" s="29">
+        <v>511.0</v>
+      </c>
+      <c r="H212" s="30">
+        <v>0.415</v>
+      </c>
+      <c r="I212" s="31"/>
+      <c r="J212" s="28">
+        <v>1618.0</v>
+      </c>
+      <c r="K212" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4957107843</v>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="23"/>
-      <c r="I213" s="21"/>
+      <c r="A213" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B213" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C213" s="27">
+        <v>8306.0</v>
+      </c>
+      <c r="D213" s="28">
+        <v>1929.0</v>
+      </c>
+      <c r="E213" s="28">
+        <v>3232.0</v>
+      </c>
+      <c r="F213" s="28">
+        <v>1073.0</v>
+      </c>
+      <c r="G213" s="28">
+        <v>1440.0</v>
+      </c>
+      <c r="H213" s="30">
+        <v>0.452</v>
+      </c>
+      <c r="I213" s="31"/>
+      <c r="J213" s="28">
+        <v>1918.0</v>
+      </c>
+      <c r="K213" s="12">
+        <f t="shared" si="1"/>
+        <v>0.2309174091</v>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="23"/>
-      <c r="I214" s="21"/>
+      <c r="A214" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B214" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C214" s="27">
+        <v>36212.0</v>
+      </c>
+      <c r="D214" s="28">
+        <v>16560.0</v>
+      </c>
+      <c r="E214" s="28">
+        <v>14495.0</v>
+      </c>
+      <c r="F214" s="28">
+        <v>4916.0</v>
+      </c>
+      <c r="G214" s="28">
+        <v>5352.0</v>
+      </c>
+      <c r="H214" s="30">
+        <v>0.476</v>
+      </c>
+      <c r="I214" s="31"/>
+      <c r="J214" s="28">
+        <v>30945.0</v>
+      </c>
+      <c r="K214" s="12">
+        <f t="shared" si="1"/>
+        <v>0.8545509776</v>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="23"/>
-      <c r="I215" s="21"/>
+      <c r="A215" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B215" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C215" s="27">
+        <v>4194.0</v>
+      </c>
+      <c r="D215" s="28">
+        <v>1394.0</v>
+      </c>
+      <c r="E215" s="28">
+        <v>1772.0</v>
+      </c>
+      <c r="F215" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G215" s="29">
+        <v>451.0</v>
+      </c>
+      <c r="H215" s="30">
+        <v>0.443</v>
+      </c>
+      <c r="I215" s="31"/>
+      <c r="J215" s="28">
+        <v>2179.0</v>
+      </c>
+      <c r="K215" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5195517406</v>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="23"/>
-      <c r="I216" s="21"/>
+      <c r="A216" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B216" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C216" s="27">
+        <v>3440.0</v>
+      </c>
+      <c r="D216" s="29">
+        <v>755.0</v>
+      </c>
+      <c r="E216" s="28">
+        <v>1517.0</v>
+      </c>
+      <c r="F216" s="31"/>
+      <c r="G216" s="29">
+        <v>133.0</v>
+      </c>
+      <c r="H216" s="30">
+        <v>0.196</v>
+      </c>
+      <c r="I216" s="31"/>
+      <c r="J216" s="28">
+        <v>2090.0</v>
+      </c>
+      <c r="K216" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6075581395</v>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="23"/>
-      <c r="I217" s="21"/>
+      <c r="A217" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B217" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C217" s="32">
+        <v>523.0</v>
+      </c>
+      <c r="D217" s="29">
+        <v>267.0</v>
+      </c>
+      <c r="E217" s="29">
+        <v>103.0</v>
+      </c>
+      <c r="F217" s="31"/>
+      <c r="G217" s="29">
+        <v>60.0</v>
+      </c>
+      <c r="H217" s="30">
+        <v>0.357</v>
+      </c>
+      <c r="I217" s="31"/>
+      <c r="J217" s="29">
+        <v>346.0</v>
+      </c>
+      <c r="K217" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6615678776</v>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="23"/>
-      <c r="I218" s="21"/>
+      <c r="A218" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B218" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C218" s="32">
+        <v>469.0</v>
+      </c>
+      <c r="D218" s="29">
+        <v>244.0</v>
+      </c>
+      <c r="E218" s="29">
+        <v>95.0</v>
+      </c>
+      <c r="F218" s="29">
+        <v>101.0</v>
+      </c>
+      <c r="G218" s="29">
+        <v>80.0</v>
+      </c>
+      <c r="H218" s="30">
+        <v>0.293</v>
+      </c>
+      <c r="I218" s="31"/>
+      <c r="J218" s="29">
+        <v>358.0</v>
+      </c>
+      <c r="K218" s="12">
+        <f t="shared" si="1"/>
+        <v>0.763326226</v>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="23"/>
-      <c r="I219" s="21"/>
+      <c r="A219" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B219" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C219" s="27">
+        <v>15346.0</v>
+      </c>
+      <c r="D219" s="28">
+        <v>4603.0</v>
+      </c>
+      <c r="E219" s="28">
+        <v>7187.0</v>
+      </c>
+      <c r="F219" s="28">
+        <v>1539.0</v>
+      </c>
+      <c r="G219" s="28">
+        <v>3591.0</v>
+      </c>
+      <c r="H219" s="30">
+        <v>0.372</v>
+      </c>
+      <c r="I219" s="31"/>
+      <c r="J219" s="28">
+        <v>6699.0</v>
+      </c>
+      <c r="K219" s="12">
+        <f t="shared" si="1"/>
+        <v>0.436530692</v>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="23"/>
-      <c r="I220" s="21"/>
+      <c r="A220" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B220" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C220" s="27">
+        <v>10877.0</v>
+      </c>
+      <c r="D220" s="28">
+        <v>6449.0</v>
+      </c>
+      <c r="E220" s="28">
+        <v>2376.0</v>
+      </c>
+      <c r="F220" s="29">
+        <v>891.0</v>
+      </c>
+      <c r="G220" s="28">
+        <v>1051.0</v>
+      </c>
+      <c r="H220" s="30">
+        <v>0.458</v>
+      </c>
+      <c r="I220" s="31"/>
+      <c r="J220" s="28">
+        <v>4495.0</v>
+      </c>
+      <c r="K220" s="12">
+        <f t="shared" si="1"/>
+        <v>0.413257332</v>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="23"/>
-      <c r="I221" s="21"/>
+      <c r="A221" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B221" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C221" s="32">
+        <v>913.0</v>
+      </c>
+      <c r="D221" s="29">
+        <v>332.0</v>
+      </c>
+      <c r="E221" s="29">
+        <v>307.0</v>
+      </c>
+      <c r="F221" s="29">
+        <v>178.0</v>
+      </c>
+      <c r="G221" s="29">
+        <v>122.0</v>
+      </c>
+      <c r="H221" s="30">
+        <v>0.57</v>
+      </c>
+      <c r="I221" s="31"/>
+      <c r="J221" s="29">
+        <v>702.0</v>
+      </c>
+      <c r="K221" s="12">
+        <f t="shared" si="1"/>
+        <v>0.7688937568</v>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="23"/>
-      <c r="I222" s="21"/>
+      <c r="A222" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B222" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C222" s="27">
+        <v>3365.0</v>
+      </c>
+      <c r="D222" s="29">
+        <v>824.0</v>
+      </c>
+      <c r="E222" s="28">
+        <v>1770.0</v>
+      </c>
+      <c r="F222" s="29">
+        <v>600.0</v>
+      </c>
+      <c r="G222" s="29">
+        <v>806.0</v>
+      </c>
+      <c r="H222" s="30">
+        <v>0.477</v>
+      </c>
+      <c r="I222" s="31"/>
+      <c r="J222" s="28">
+        <v>1951.0</v>
+      </c>
+      <c r="K222" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5797919762</v>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="23"/>
-      <c r="I223" s="21"/>
+      <c r="A223" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B223" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C223" s="27">
+        <v>1258.0</v>
+      </c>
+      <c r="D223" s="29">
+        <v>534.0</v>
+      </c>
+      <c r="E223" s="29">
+        <v>361.0</v>
+      </c>
+      <c r="F223" s="29">
+        <v>104.0</v>
+      </c>
+      <c r="G223" s="29">
+        <v>237.0</v>
+      </c>
+      <c r="H223" s="30">
+        <v>0.598</v>
+      </c>
+      <c r="I223" s="31"/>
+      <c r="J223" s="28">
+        <v>1197.0</v>
+      </c>
+      <c r="K223" s="12">
+        <f t="shared" si="1"/>
+        <v>0.9515103339</v>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="23"/>
-      <c r="I224" s="21"/>
+      <c r="A224" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B224" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C224" s="27">
+        <v>16610.0</v>
+      </c>
+      <c r="D224" s="28">
+        <v>4398.0</v>
+      </c>
+      <c r="E224" s="28">
+        <v>9483.0</v>
+      </c>
+      <c r="F224" s="28">
+        <v>2454.0</v>
+      </c>
+      <c r="G224" s="28">
+        <v>2549.0</v>
+      </c>
+      <c r="H224" s="30">
+        <v>0.395</v>
+      </c>
+      <c r="I224" s="31"/>
+      <c r="J224" s="28">
+        <v>6781.0</v>
+      </c>
+      <c r="K224" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4082480433</v>
+      </c>
     </row>
     <row r="225">
-      <c r="A225" s="23"/>
-      <c r="I225" s="21"/>
+      <c r="A225" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B225" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C225" s="27">
+        <v>11843.0</v>
+      </c>
+      <c r="D225" s="28">
+        <v>2529.0</v>
+      </c>
+      <c r="E225" s="28">
+        <v>6552.0</v>
+      </c>
+      <c r="F225" s="28">
+        <v>1007.0</v>
+      </c>
+      <c r="G225" s="28">
+        <v>1729.0</v>
+      </c>
+      <c r="H225" s="30">
+        <v>0.584</v>
+      </c>
+      <c r="I225" s="31"/>
+      <c r="J225" s="28">
+        <v>3837.0</v>
+      </c>
+      <c r="K225" s="12">
+        <f t="shared" si="1"/>
+        <v>0.3239888542</v>
+      </c>
     </row>
     <row r="226">
-      <c r="A226" s="23"/>
-      <c r="I226" s="21"/>
+      <c r="A226" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B226" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C226" s="27">
+        <v>7022.0</v>
+      </c>
+      <c r="D226" s="29">
+        <v>685.0</v>
+      </c>
+      <c r="E226" s="28">
+        <v>2894.0</v>
+      </c>
+      <c r="F226" s="28">
+        <v>1926.0</v>
+      </c>
+      <c r="G226" s="29">
+        <v>421.0</v>
+      </c>
+      <c r="H226" s="30">
+        <v>0.495</v>
+      </c>
+      <c r="I226" s="31"/>
+      <c r="J226" s="28">
+        <v>1923.0</v>
+      </c>
+      <c r="K226" s="12">
+        <f t="shared" si="1"/>
+        <v>0.273853603</v>
+      </c>
     </row>
     <row r="227">
-      <c r="A227" s="23"/>
-      <c r="I227" s="21"/>
+      <c r="A227" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B227" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C227" s="27">
+        <v>8569.0</v>
+      </c>
+      <c r="D227" s="28">
+        <v>2519.0</v>
+      </c>
+      <c r="E227" s="28">
+        <v>1683.0</v>
+      </c>
+      <c r="F227" s="28">
+        <v>1697.0</v>
+      </c>
+      <c r="G227" s="28">
+        <v>1125.0</v>
+      </c>
+      <c r="H227" s="30">
+        <v>0.41</v>
+      </c>
+      <c r="I227" s="31"/>
+      <c r="J227" s="28">
+        <v>4516.0</v>
+      </c>
+      <c r="K227" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5270159879</v>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="23"/>
-      <c r="I228" s="21"/>
+      <c r="A228" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B228" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C228" s="27">
+        <v>4619.0</v>
+      </c>
+      <c r="D228" s="28">
+        <v>1532.0</v>
+      </c>
+      <c r="E228" s="28">
+        <v>1960.0</v>
+      </c>
+      <c r="F228" s="29">
+        <v>496.0</v>
+      </c>
+      <c r="G228" s="29">
+        <v>651.0</v>
+      </c>
+      <c r="H228" s="30">
+        <v>0.506</v>
+      </c>
+      <c r="I228" s="31"/>
+      <c r="J228" s="28">
+        <v>2114.0</v>
+      </c>
+      <c r="K228" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4576748214</v>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="23"/>
-      <c r="I229" s="21"/>
+      <c r="A229" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B229" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C229" s="27">
+        <v>8323.0</v>
+      </c>
+      <c r="D229" s="28">
+        <v>2062.0</v>
+      </c>
+      <c r="E229" s="28">
+        <v>2491.0</v>
+      </c>
+      <c r="F229" s="28">
+        <v>1309.0</v>
+      </c>
+      <c r="G229" s="29">
+        <v>758.0</v>
+      </c>
+      <c r="H229" s="30">
+        <v>0.556</v>
+      </c>
+      <c r="I229" s="31"/>
+      <c r="J229" s="28">
+        <v>3029.0</v>
+      </c>
+      <c r="K229" s="12">
+        <f t="shared" si="1"/>
+        <v>0.3639312748</v>
+      </c>
     </row>
     <row r="230">
-      <c r="A230" s="23"/>
-      <c r="I230" s="21"/>
+      <c r="A230" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B230" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C230" s="27">
+        <v>3703.0</v>
+      </c>
+      <c r="D230" s="29">
+        <v>489.0</v>
+      </c>
+      <c r="E230" s="28">
+        <v>1124.0</v>
+      </c>
+      <c r="F230" s="29">
+        <v>133.0</v>
+      </c>
+      <c r="G230" s="29">
+        <v>265.0</v>
+      </c>
+      <c r="H230" s="30">
+        <v>0.351</v>
+      </c>
+      <c r="I230" s="31"/>
+      <c r="J230" s="28">
+        <v>2270.0</v>
+      </c>
+      <c r="K230" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6130164731</v>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="23"/>
-      <c r="I231" s="21"/>
+      <c r="A231" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B231" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C231" s="27">
+        <v>2133.0</v>
+      </c>
+      <c r="D231" s="29">
+        <v>881.0</v>
+      </c>
+      <c r="E231" s="29">
+        <v>815.0</v>
+      </c>
+      <c r="F231" s="29">
+        <v>565.0</v>
+      </c>
+      <c r="G231" s="29">
+        <v>426.0</v>
+      </c>
+      <c r="H231" s="30">
+        <v>0.462</v>
+      </c>
+      <c r="I231" s="31"/>
+      <c r="J231" s="28">
+        <v>1557.0</v>
+      </c>
+      <c r="K231" s="12">
+        <f t="shared" si="1"/>
+        <v>0.7299578059</v>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="23"/>
-      <c r="I232" s="21"/>
+      <c r="A232" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B232" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C232" s="27">
+        <v>9558.0</v>
+      </c>
+      <c r="D232" s="28">
+        <v>2374.0</v>
+      </c>
+      <c r="E232" s="28">
+        <v>4777.0</v>
+      </c>
+      <c r="F232" s="28">
+        <v>2234.0</v>
+      </c>
+      <c r="G232" s="28">
+        <v>1254.0</v>
+      </c>
+      <c r="H232" s="30">
+        <v>0.429</v>
+      </c>
+      <c r="I232" s="31"/>
+      <c r="J232" s="28">
+        <v>3718.0</v>
+      </c>
+      <c r="K232" s="12">
+        <f t="shared" si="1"/>
+        <v>0.3889935133</v>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="23"/>
-      <c r="I233" s="21"/>
+      <c r="A233" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B233" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C233" s="27">
+        <v>5434.0</v>
+      </c>
+      <c r="D233" s="28">
+        <v>1144.0</v>
+      </c>
+      <c r="E233" s="28">
+        <v>2471.0</v>
+      </c>
+      <c r="F233" s="28">
+        <v>1048.0</v>
+      </c>
+      <c r="G233" s="29">
+        <v>597.0</v>
+      </c>
+      <c r="H233" s="30">
+        <v>0.546</v>
+      </c>
+      <c r="I233" s="31"/>
+      <c r="J233" s="28">
+        <v>3186.0</v>
+      </c>
+      <c r="K233" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5863084284</v>
+      </c>
     </row>
     <row r="234">
-      <c r="A234" s="23"/>
-      <c r="I234" s="21"/>
+      <c r="A234" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B234" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C234" s="27">
+        <v>11727.0</v>
+      </c>
+      <c r="D234" s="28">
+        <v>1624.0</v>
+      </c>
+      <c r="E234" s="28">
+        <v>5956.0</v>
+      </c>
+      <c r="F234" s="29">
+        <v>417.0</v>
+      </c>
+      <c r="G234" s="28">
+        <v>1058.0</v>
+      </c>
+      <c r="H234" s="30">
+        <v>0.569</v>
+      </c>
+      <c r="I234" s="31"/>
+      <c r="J234" s="28">
+        <v>5047.0</v>
+      </c>
+      <c r="K234" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4303743498</v>
+      </c>
     </row>
     <row r="235">
-      <c r="A235" s="23"/>
-      <c r="I235" s="21"/>
+      <c r="A235" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B235" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C235" s="27">
+        <v>3787.0</v>
+      </c>
+      <c r="D235" s="28">
+        <v>1294.0</v>
+      </c>
+      <c r="E235" s="28">
+        <v>1479.0</v>
+      </c>
+      <c r="F235" s="29">
+        <v>562.0</v>
+      </c>
+      <c r="G235" s="29">
+        <v>583.0</v>
+      </c>
+      <c r="H235" s="30">
+        <v>0.479</v>
+      </c>
+      <c r="I235" s="31"/>
+      <c r="J235" s="28">
+        <v>1699.0</v>
+      </c>
+      <c r="K235" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4486400845</v>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="23"/>
-      <c r="I236" s="21"/>
+      <c r="A236" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B236" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C236" s="27">
+        <v>1965.0</v>
+      </c>
+      <c r="D236" s="29">
+        <v>584.0</v>
+      </c>
+      <c r="E236" s="29">
+        <v>837.0</v>
+      </c>
+      <c r="F236" s="29">
+        <v>216.0</v>
+      </c>
+      <c r="G236" s="29">
+        <v>212.0</v>
+      </c>
+      <c r="H236" s="30">
+        <v>0.588</v>
+      </c>
+      <c r="I236" s="31"/>
+      <c r="J236" s="28">
+        <v>1054.0</v>
+      </c>
+      <c r="K236" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5363867684</v>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="23"/>
-      <c r="I237" s="21"/>
+      <c r="A237" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B237" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C237" s="27">
+        <v>11056.0</v>
+      </c>
+      <c r="D237" s="28">
+        <v>3966.0</v>
+      </c>
+      <c r="E237" s="28">
+        <v>3316.0</v>
+      </c>
+      <c r="F237" s="28">
+        <v>1113.0</v>
+      </c>
+      <c r="G237" s="28">
+        <v>1063.0</v>
+      </c>
+      <c r="H237" s="30">
+        <v>0.212</v>
+      </c>
+      <c r="I237" s="31"/>
+      <c r="J237" s="28">
+        <v>5820.0</v>
+      </c>
+      <c r="K237" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5264109986</v>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="23"/>
-      <c r="I238" s="21"/>
+      <c r="A238" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B238" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C238" s="27">
+        <v>1102.0</v>
+      </c>
+      <c r="D238" s="29">
+        <v>506.0</v>
+      </c>
+      <c r="E238" s="29">
+        <v>357.0</v>
+      </c>
+      <c r="F238" s="29">
+        <v>186.0</v>
+      </c>
+      <c r="G238" s="29">
+        <v>264.0</v>
+      </c>
+      <c r="H238" s="30">
+        <v>0.414</v>
+      </c>
+      <c r="I238" s="31"/>
+      <c r="J238" s="29">
+        <v>724.0</v>
+      </c>
+      <c r="K238" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6569872958</v>
+      </c>
     </row>
     <row r="239">
-      <c r="A239" s="23"/>
-      <c r="I239" s="21"/>
+      <c r="A239" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B239" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C239" s="27">
+        <v>3599.0</v>
+      </c>
+      <c r="D239" s="28">
+        <v>1253.0</v>
+      </c>
+      <c r="E239" s="28">
+        <v>1587.0</v>
+      </c>
+      <c r="F239" s="29">
+        <v>521.0</v>
+      </c>
+      <c r="G239" s="29">
+        <v>476.0</v>
+      </c>
+      <c r="H239" s="30">
+        <v>0.537</v>
+      </c>
+      <c r="I239" s="31"/>
+      <c r="J239" s="28">
+        <v>2480.0</v>
+      </c>
+      <c r="K239" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6890803001</v>
+      </c>
     </row>
     <row r="240">
-      <c r="A240" s="23"/>
-      <c r="I240" s="21"/>
+      <c r="A240" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B240" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C240" s="27">
+        <v>1062.0</v>
+      </c>
+      <c r="D240" s="29">
+        <v>348.0</v>
+      </c>
+      <c r="E240" s="29">
+        <v>376.0</v>
+      </c>
+      <c r="F240" s="29">
+        <v>30.0</v>
+      </c>
+      <c r="G240" s="29">
+        <v>186.0</v>
+      </c>
+      <c r="H240" s="30">
+        <v>0.532</v>
+      </c>
+      <c r="I240" s="31"/>
+      <c r="J240" s="29">
+        <v>671.0</v>
+      </c>
+      <c r="K240" s="12">
+        <f t="shared" si="1"/>
+        <v>0.631826742</v>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="23"/>
-      <c r="I241" s="21"/>
+      <c r="A241" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B241" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C241" s="27">
+        <v>2846.0</v>
+      </c>
+      <c r="D241" s="28">
+        <v>1063.0</v>
+      </c>
+      <c r="E241" s="28">
+        <v>1387.0</v>
+      </c>
+      <c r="F241" s="29">
+        <v>381.0</v>
+      </c>
+      <c r="G241" s="29">
+        <v>327.0</v>
+      </c>
+      <c r="H241" s="30">
+        <v>0.498</v>
+      </c>
+      <c r="I241" s="31"/>
+      <c r="J241" s="28">
+        <v>2056.0</v>
+      </c>
+      <c r="K241" s="12">
+        <f t="shared" si="1"/>
+        <v>0.722417428</v>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="23"/>
-      <c r="I242" s="21"/>
+      <c r="A242" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B242" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C242" s="27">
+        <v>2282.0</v>
+      </c>
+      <c r="D242" s="29">
+        <v>713.0</v>
+      </c>
+      <c r="E242" s="29">
+        <v>940.0</v>
+      </c>
+      <c r="F242" s="29">
+        <v>418.0</v>
+      </c>
+      <c r="G242" s="29">
+        <v>175.0</v>
+      </c>
+      <c r="H242" s="30">
+        <v>0.6</v>
+      </c>
+      <c r="I242" s="31"/>
+      <c r="J242" s="28">
+        <v>1059.0</v>
+      </c>
+      <c r="K242" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4640666082</v>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="23"/>
-      <c r="I243" s="21"/>
+      <c r="A243" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B243" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C243" s="27">
+        <v>4048.0</v>
+      </c>
+      <c r="D243" s="28">
+        <v>1008.0</v>
+      </c>
+      <c r="E243" s="28">
+        <v>1729.0</v>
+      </c>
+      <c r="F243" s="29">
+        <v>428.0</v>
+      </c>
+      <c r="G243" s="29">
+        <v>577.0</v>
+      </c>
+      <c r="H243" s="30">
+        <v>0.58</v>
+      </c>
+      <c r="I243" s="31"/>
+      <c r="J243" s="28">
+        <v>1209.0</v>
+      </c>
+      <c r="K243" s="12">
+        <f t="shared" si="1"/>
+        <v>0.2986660079</v>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="23"/>
-      <c r="I244" s="21"/>
+      <c r="A244" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B244" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C244" s="27">
+        <v>14455.0</v>
+      </c>
+      <c r="D244" s="28">
+        <v>2219.0</v>
+      </c>
+      <c r="E244" s="28">
+        <v>4936.0</v>
+      </c>
+      <c r="F244" s="28">
+        <v>1512.0</v>
+      </c>
+      <c r="G244" s="28">
+        <v>1392.0</v>
+      </c>
+      <c r="H244" s="30">
+        <v>0.46</v>
+      </c>
+      <c r="I244" s="31"/>
+      <c r="J244" s="28">
+        <v>9936.0</v>
+      </c>
+      <c r="K244" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6873746109</v>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="23"/>
-      <c r="I245" s="21"/>
+      <c r="A245" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B245" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C245" s="27">
+        <v>15268.0</v>
+      </c>
+      <c r="D245" s="28">
+        <v>2451.0</v>
+      </c>
+      <c r="E245" s="28">
+        <v>4622.0</v>
+      </c>
+      <c r="F245" s="28">
+        <v>3803.0</v>
+      </c>
+      <c r="G245" s="28">
+        <v>1439.0</v>
+      </c>
+      <c r="H245" s="30">
+        <v>0.418</v>
+      </c>
+      <c r="I245" s="31"/>
+      <c r="J245" s="28">
+        <v>6976.0</v>
+      </c>
+      <c r="K245" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4569033272</v>
+      </c>
     </row>
     <row r="246">
-      <c r="A246" s="23"/>
-      <c r="I246" s="21"/>
+      <c r="A246" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B246" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C246" s="27">
+        <v>6171.0</v>
+      </c>
+      <c r="D246" s="28">
+        <v>2075.0</v>
+      </c>
+      <c r="E246" s="28">
+        <v>2892.0</v>
+      </c>
+      <c r="F246" s="28">
+        <v>1245.0</v>
+      </c>
+      <c r="G246" s="28">
+        <v>1103.0</v>
+      </c>
+      <c r="H246" s="30">
+        <v>0.477</v>
+      </c>
+      <c r="I246" s="31"/>
+      <c r="J246" s="28">
+        <v>3820.0</v>
+      </c>
+      <c r="K246" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6190244693</v>
+      </c>
     </row>
     <row r="247">
-      <c r="A247" s="23"/>
-      <c r="I247" s="21"/>
+      <c r="A247" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B247" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C247" s="27">
+        <v>4526.0</v>
+      </c>
+      <c r="D247" s="29">
+        <v>829.0</v>
+      </c>
+      <c r="E247" s="28">
+        <v>1888.0</v>
+      </c>
+      <c r="F247" s="29">
+        <v>346.0</v>
+      </c>
+      <c r="G247" s="29">
+        <v>362.0</v>
+      </c>
+      <c r="H247" s="30">
+        <v>0.524</v>
+      </c>
+      <c r="I247" s="31"/>
+      <c r="J247" s="28">
+        <v>2865.0</v>
+      </c>
+      <c r="K247" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6330092797</v>
+      </c>
     </row>
     <row r="248">
-      <c r="A248" s="23"/>
-      <c r="I248" s="21"/>
+      <c r="A248" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B248" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C248" s="27">
+        <v>10865.0</v>
+      </c>
+      <c r="D248" s="28">
+        <v>3611.0</v>
+      </c>
+      <c r="E248" s="28">
+        <v>4091.0</v>
+      </c>
+      <c r="F248" s="28">
+        <v>1031.0</v>
+      </c>
+      <c r="G248" s="28">
+        <v>1709.0</v>
+      </c>
+      <c r="H248" s="30">
+        <v>0.452</v>
+      </c>
+      <c r="I248" s="31"/>
+      <c r="J248" s="28">
+        <v>8985.0</v>
+      </c>
+      <c r="K248" s="12">
+        <f t="shared" si="1"/>
+        <v>0.8269673263</v>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="23"/>
-      <c r="I249" s="21"/>
+      <c r="A249" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B249" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C249" s="27">
+        <v>2432.0</v>
+      </c>
+      <c r="D249" s="31"/>
+      <c r="E249" s="31"/>
+      <c r="F249" s="29">
+        <v>19.0</v>
+      </c>
+      <c r="G249" s="31"/>
+      <c r="H249" s="31"/>
+      <c r="I249" s="31"/>
+      <c r="J249" s="31"/>
+      <c r="K249" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="23"/>
-      <c r="I250" s="21"/>
+      <c r="A250" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B250" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C250" s="27">
+        <v>1574.0</v>
+      </c>
+      <c r="D250" s="29">
+        <v>122.0</v>
+      </c>
+      <c r="E250" s="29">
+        <v>633.0</v>
+      </c>
+      <c r="F250" s="29">
+        <v>64.0</v>
+      </c>
+      <c r="G250" s="29">
+        <v>107.0</v>
+      </c>
+      <c r="H250" s="30">
+        <v>0.492</v>
+      </c>
+      <c r="I250" s="31"/>
+      <c r="J250" s="29">
+        <v>686.0</v>
+      </c>
+      <c r="K250" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4358322745</v>
+      </c>
     </row>
     <row r="251">
-      <c r="A251" s="23"/>
-      <c r="I251" s="21"/>
+      <c r="A251" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B251" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C251" s="27">
+        <v>3322.0</v>
+      </c>
+      <c r="D251" s="29">
+        <v>915.0</v>
+      </c>
+      <c r="E251" s="29">
+        <v>998.0</v>
+      </c>
+      <c r="F251" s="29">
+        <v>567.0</v>
+      </c>
+      <c r="G251" s="29">
+        <v>522.0</v>
+      </c>
+      <c r="H251" s="30">
+        <v>0.482</v>
+      </c>
+      <c r="I251" s="31"/>
+      <c r="J251" s="28">
+        <v>2151.0</v>
+      </c>
+      <c r="K251" s="12">
+        <f t="shared" si="1"/>
+        <v>0.6475015051</v>
+      </c>
     </row>
     <row r="252">
-      <c r="A252" s="23"/>
-      <c r="I252" s="21"/>
+      <c r="A252" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B252" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C252" s="27">
+        <v>1698.0</v>
+      </c>
+      <c r="D252" s="29">
+        <v>672.0</v>
+      </c>
+      <c r="E252" s="29">
+        <v>597.0</v>
+      </c>
+      <c r="F252" s="29">
+        <v>545.0</v>
+      </c>
+      <c r="G252" s="29">
+        <v>265.0</v>
+      </c>
+      <c r="H252" s="30">
+        <v>0.399</v>
+      </c>
+      <c r="I252" s="31"/>
+      <c r="J252" s="29">
+        <v>805.0</v>
+      </c>
+      <c r="K252" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4740871614</v>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="23"/>
-      <c r="I253" s="21"/>
+      <c r="A253" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B253" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C253" s="27">
+        <v>8990.0</v>
+      </c>
+      <c r="D253" s="29">
+        <v>563.0</v>
+      </c>
+      <c r="E253" s="29">
+        <v>937.0</v>
+      </c>
+      <c r="F253" s="28">
+        <v>1116.0</v>
+      </c>
+      <c r="G253" s="28">
+        <v>1147.0</v>
+      </c>
+      <c r="H253" s="30">
+        <v>0.413</v>
+      </c>
+      <c r="I253" s="31"/>
+      <c r="J253" s="28">
+        <v>4840.0</v>
+      </c>
+      <c r="K253" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5383759733</v>
+      </c>
     </row>
     <row r="254">
-      <c r="A254" s="23"/>
-      <c r="I254" s="21"/>
+      <c r="A254" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B254" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C254" s="27">
+        <v>17520.0</v>
+      </c>
+      <c r="D254" s="28">
+        <v>3112.0</v>
+      </c>
+      <c r="E254" s="28">
+        <v>6998.0</v>
+      </c>
+      <c r="F254" s="28">
+        <v>5146.0</v>
+      </c>
+      <c r="G254" s="28">
+        <v>2581.0</v>
+      </c>
+      <c r="H254" s="30">
+        <v>0.4</v>
+      </c>
+      <c r="I254" s="31"/>
+      <c r="J254" s="28">
+        <v>6911.0</v>
+      </c>
+      <c r="K254" s="12">
+        <f t="shared" si="1"/>
+        <v>0.3944634703</v>
+      </c>
     </row>
     <row r="255">
-      <c r="A255" s="23"/>
-      <c r="I255" s="21"/>
+      <c r="A255" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B255" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C255" s="27">
+        <v>1593.0</v>
+      </c>
+      <c r="D255" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E255" s="29">
+        <v>585.0</v>
+      </c>
+      <c r="F255" s="29">
+        <v>216.0</v>
+      </c>
+      <c r="G255" s="29">
+        <v>276.0</v>
+      </c>
+      <c r="H255" s="30">
+        <v>0.468</v>
+      </c>
+      <c r="I255" s="31"/>
+      <c r="J255" s="29">
+        <v>936.0</v>
+      </c>
+      <c r="K255" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5875706215</v>
+      </c>
     </row>
     <row r="256">
-      <c r="A256" s="23"/>
-      <c r="I256" s="21"/>
+      <c r="A256" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B256" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C256" s="27">
+        <v>5576.0</v>
+      </c>
+      <c r="D256" s="28">
+        <v>1089.0</v>
+      </c>
+      <c r="E256" s="28">
+        <v>1064.0</v>
+      </c>
+      <c r="F256" s="28">
+        <v>1208.0</v>
+      </c>
+      <c r="G256" s="29">
+        <v>620.0</v>
+      </c>
+      <c r="H256" s="30">
+        <v>0.335</v>
+      </c>
+      <c r="I256" s="31"/>
+      <c r="J256" s="28">
+        <v>4506.0</v>
+      </c>
+      <c r="K256" s="12">
+        <f t="shared" si="1"/>
+        <v>0.8081061693</v>
+      </c>
     </row>
     <row r="257">
-      <c r="A257" s="23"/>
-      <c r="I257" s="21"/>
+      <c r="A257" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B257" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C257" s="32">
+        <v>828.0</v>
+      </c>
+      <c r="D257" s="29">
+        <v>257.0</v>
+      </c>
+      <c r="E257" s="29">
+        <v>362.0</v>
+      </c>
+      <c r="F257" s="29">
+        <v>173.0</v>
+      </c>
+      <c r="G257" s="29">
+        <v>184.0</v>
+      </c>
+      <c r="H257" s="30">
+        <v>0.411</v>
+      </c>
+      <c r="I257" s="31"/>
+      <c r="J257" s="29">
+        <v>795.0</v>
+      </c>
+      <c r="K257" s="12">
+        <f t="shared" si="1"/>
+        <v>0.9601449275</v>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="23"/>
-      <c r="I258" s="21"/>
+      <c r="A258" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B258" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C258" s="27">
+        <v>5480.0</v>
+      </c>
+      <c r="D258" s="28">
+        <v>1649.0</v>
+      </c>
+      <c r="E258" s="28">
+        <v>2600.0</v>
+      </c>
+      <c r="F258" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G258" s="29">
+        <v>497.0</v>
+      </c>
+      <c r="H258" s="30">
+        <v>0.594</v>
+      </c>
+      <c r="I258" s="31"/>
+      <c r="J258" s="28">
+        <v>4800.0</v>
+      </c>
+      <c r="K258" s="12">
+        <f t="shared" si="1"/>
+        <v>0.8759124088</v>
+      </c>
     </row>
     <row r="259">
-      <c r="A259" s="23"/>
-      <c r="I259" s="21"/>
+      <c r="A259" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B259" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C259" s="27">
+        <v>5687.0</v>
+      </c>
+      <c r="D259" s="28">
+        <v>1749.0</v>
+      </c>
+      <c r="E259" s="28">
+        <v>2408.0</v>
+      </c>
+      <c r="F259" s="29">
+        <v>655.0</v>
+      </c>
+      <c r="G259" s="29">
+        <v>563.0</v>
+      </c>
+      <c r="H259" s="30">
+        <v>0.505</v>
+      </c>
+      <c r="I259" s="31"/>
+      <c r="J259" s="28">
+        <v>2866.0</v>
+      </c>
+      <c r="K259" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5039563918</v>
+      </c>
     </row>
     <row r="260">
-      <c r="A260" s="23"/>
-      <c r="I260" s="21"/>
+      <c r="A260" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B260" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C260" s="27">
+        <v>6616.0</v>
+      </c>
+      <c r="D260" s="29">
+        <v>51.0</v>
+      </c>
+      <c r="E260" s="28">
+        <v>3038.0</v>
+      </c>
+      <c r="F260" s="28">
+        <v>1303.0</v>
+      </c>
+      <c r="G260" s="28">
+        <v>1037.0</v>
+      </c>
+      <c r="H260" s="30">
+        <v>0.516</v>
+      </c>
+      <c r="I260" s="31"/>
+      <c r="J260" s="28">
+        <v>3135.0</v>
+      </c>
+      <c r="K260" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4738512696</v>
+      </c>
     </row>
     <row r="261">
-      <c r="A261" s="23"/>
-      <c r="I261" s="21"/>
+      <c r="A261" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B261" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="C261" s="32">
+        <v>688.0</v>
+      </c>
+      <c r="D261" s="29">
+        <v>162.0</v>
+      </c>
+      <c r="E261" s="29">
+        <v>159.0</v>
+      </c>
+      <c r="F261" s="31"/>
+      <c r="G261" s="29">
+        <v>60.0</v>
+      </c>
+      <c r="H261" s="30">
+        <v>0.704</v>
+      </c>
+      <c r="I261" s="31"/>
+      <c r="J261" s="29">
+        <v>502.0</v>
+      </c>
+      <c r="K261" s="12">
+        <f t="shared" si="1"/>
+        <v>0.7296511628</v>
+      </c>
     </row>
     <row r="262">
-      <c r="A262" s="23"/>
-      <c r="I262" s="21"/>
+      <c r="A262" s="33"/>
+      <c r="I262" s="20"/>
     </row>
     <row r="263">
-      <c r="A263" s="23"/>
-      <c r="I263" s="21"/>
+      <c r="A263" s="33"/>
+      <c r="I263" s="20"/>
     </row>
     <row r="264">
-      <c r="A264" s="23"/>
-      <c r="I264" s="21"/>
+      <c r="A264" s="33"/>
+      <c r="I264" s="20"/>
     </row>
     <row r="265">
-      <c r="A265" s="23"/>
-      <c r="I265" s="21"/>
+      <c r="A265" s="33"/>
+      <c r="I265" s="20"/>
     </row>
     <row r="266">
-      <c r="A266" s="23"/>
-      <c r="I266" s="21"/>
+      <c r="A266" s="33"/>
+      <c r="I266" s="20"/>
     </row>
     <row r="267">
-      <c r="A267" s="23"/>
-      <c r="I267" s="21"/>
+      <c r="A267" s="33"/>
+      <c r="I267" s="20"/>
     </row>
     <row r="268">
-      <c r="A268" s="23"/>
-      <c r="I268" s="21"/>
+      <c r="A268" s="33"/>
+      <c r="I268" s="20"/>
     </row>
     <row r="269">
-      <c r="A269" s="23"/>
-      <c r="I269" s="21"/>
+      <c r="A269" s="33"/>
+      <c r="I269" s="20"/>
     </row>
     <row r="270">
-      <c r="A270" s="23"/>
-      <c r="I270" s="21"/>
+      <c r="A270" s="33"/>
+      <c r="I270" s="20"/>
     </row>
     <row r="271">
-      <c r="A271" s="23"/>
-      <c r="I271" s="21"/>
+      <c r="A271" s="33"/>
+      <c r="I271" s="20"/>
     </row>
     <row r="272">
-      <c r="A272" s="23"/>
-      <c r="I272" s="21"/>
+      <c r="A272" s="33"/>
+      <c r="I272" s="20"/>
     </row>
     <row r="273">
-      <c r="A273" s="23"/>
-      <c r="I273" s="21"/>
+      <c r="A273" s="33"/>
+      <c r="I273" s="20"/>
     </row>
     <row r="274">
-      <c r="A274" s="23"/>
-      <c r="I274" s="21"/>
+      <c r="A274" s="33"/>
+      <c r="I274" s="20"/>
     </row>
     <row r="275">
-      <c r="A275" s="23"/>
-      <c r="I275" s="21"/>
+      <c r="A275" s="33"/>
+      <c r="I275" s="20"/>
     </row>
     <row r="276">
-      <c r="A276" s="23"/>
-      <c r="I276" s="21"/>
+      <c r="A276" s="33"/>
+      <c r="I276" s="20"/>
     </row>
     <row r="277">
-      <c r="A277" s="23"/>
-      <c r="I277" s="21"/>
+      <c r="A277" s="33"/>
+      <c r="I277" s="20"/>
     </row>
     <row r="278">
-      <c r="A278" s="23"/>
-      <c r="I278" s="21"/>
+      <c r="A278" s="33"/>
+      <c r="I278" s="20"/>
     </row>
     <row r="279">
-      <c r="A279" s="23"/>
-      <c r="I279" s="21"/>
+      <c r="A279" s="33"/>
+      <c r="I279" s="20"/>
     </row>
     <row r="280">
-      <c r="A280" s="23"/>
-      <c r="I280" s="21"/>
+      <c r="A280" s="33"/>
+      <c r="I280" s="20"/>
     </row>
     <row r="281">
-      <c r="A281" s="23"/>
-      <c r="I281" s="21"/>
+      <c r="A281" s="33"/>
+      <c r="I281" s="20"/>
     </row>
     <row r="282">
-      <c r="A282" s="23"/>
-      <c r="I282" s="21"/>
+      <c r="A282" s="33"/>
+      <c r="I282" s="20"/>
     </row>
     <row r="283">
-      <c r="A283" s="23"/>
-      <c r="I283" s="21"/>
+      <c r="A283" s="33"/>
+      <c r="I283" s="20"/>
     </row>
     <row r="284">
-      <c r="A284" s="23"/>
-      <c r="I284" s="21"/>
+      <c r="A284" s="33"/>
+      <c r="I284" s="20"/>
     </row>
     <row r="285">
-      <c r="A285" s="23"/>
-      <c r="I285" s="21"/>
+      <c r="A285" s="33"/>
+      <c r="I285" s="20"/>
     </row>
     <row r="286">
-      <c r="A286" s="23"/>
-      <c r="I286" s="21"/>
+      <c r="A286" s="33"/>
+      <c r="I286" s="20"/>
     </row>
     <row r="287">
-      <c r="A287" s="23"/>
-      <c r="I287" s="21"/>
+      <c r="A287" s="33"/>
+      <c r="I287" s="20"/>
     </row>
     <row r="288">
-      <c r="A288" s="23"/>
-      <c r="I288" s="21"/>
+      <c r="A288" s="33"/>
+      <c r="I288" s="20"/>
     </row>
     <row r="289">
-      <c r="A289" s="23"/>
-      <c r="I289" s="21"/>
+      <c r="A289" s="33"/>
+      <c r="I289" s="20"/>
     </row>
     <row r="290">
-      <c r="A290" s="23"/>
-      <c r="I290" s="21"/>
+      <c r="A290" s="33"/>
+      <c r="I290" s="20"/>
     </row>
     <row r="291">
-      <c r="A291" s="23"/>
-      <c r="I291" s="21"/>
+      <c r="A291" s="33"/>
+      <c r="I291" s="20"/>
     </row>
     <row r="292">
-      <c r="A292" s="23"/>
-      <c r="I292" s="21"/>
+      <c r="A292" s="33"/>
+      <c r="I292" s="20"/>
     </row>
     <row r="293">
-      <c r="A293" s="23"/>
-      <c r="I293" s="21"/>
+      <c r="A293" s="33"/>
+      <c r="I293" s="20"/>
     </row>
     <row r="294">
-      <c r="A294" s="23"/>
-      <c r="I294" s="21"/>
+      <c r="A294" s="33"/>
+      <c r="I294" s="20"/>
     </row>
     <row r="295">
-      <c r="A295" s="23"/>
-      <c r="I295" s="21"/>
+      <c r="A295" s="33"/>
+      <c r="I295" s="20"/>
     </row>
     <row r="296">
-      <c r="A296" s="23"/>
-      <c r="I296" s="21"/>
+      <c r="A296" s="33"/>
+      <c r="I296" s="20"/>
     </row>
     <row r="297">
-      <c r="A297" s="23"/>
-      <c r="I297" s="21"/>
+      <c r="A297" s="33"/>
+      <c r="I297" s="20"/>
     </row>
     <row r="298">
-      <c r="A298" s="23"/>
-      <c r="I298" s="21"/>
+      <c r="A298" s="33"/>
+      <c r="I298" s="20"/>
     </row>
     <row r="299">
-      <c r="A299" s="23"/>
-      <c r="I299" s="21"/>
+      <c r="A299" s="33"/>
+      <c r="I299" s="20"/>
     </row>
     <row r="300">
-      <c r="A300" s="23"/>
-      <c r="I300" s="21"/>
+      <c r="A300" s="33"/>
+      <c r="I300" s="20"/>
     </row>
     <row r="301">
-      <c r="A301" s="23"/>
-      <c r="I301" s="21"/>
+      <c r="A301" s="33"/>
+      <c r="I301" s="20"/>
     </row>
     <row r="302">
-      <c r="A302" s="23"/>
-      <c r="I302" s="21"/>
+      <c r="A302" s="33"/>
+      <c r="I302" s="20"/>
     </row>
     <row r="303">
-      <c r="A303" s="23"/>
-      <c r="I303" s="21"/>
+      <c r="A303" s="33"/>
+      <c r="I303" s="20"/>
     </row>
     <row r="304">
-      <c r="A304" s="23"/>
-      <c r="I304" s="21"/>
+      <c r="A304" s="33"/>
+      <c r="I304" s="20"/>
     </row>
     <row r="305">
-      <c r="A305" s="23"/>
-      <c r="I305" s="21"/>
+      <c r="A305" s="33"/>
+      <c r="I305" s="20"/>
     </row>
     <row r="306">
-      <c r="A306" s="23"/>
-      <c r="I306" s="21"/>
+      <c r="A306" s="33"/>
+      <c r="I306" s="20"/>
     </row>
     <row r="307">
-      <c r="A307" s="23"/>
-      <c r="I307" s="21"/>
+      <c r="A307" s="33"/>
+      <c r="I307" s="20"/>
     </row>
     <row r="308">
-      <c r="A308" s="23"/>
-      <c r="I308" s="21"/>
+      <c r="A308" s="33"/>
+      <c r="I308" s="20"/>
     </row>
     <row r="309">
-      <c r="A309" s="23"/>
-      <c r="I309" s="21"/>
+      <c r="A309" s="33"/>
+      <c r="I309" s="20"/>
     </row>
     <row r="310">
-      <c r="A310" s="23"/>
-      <c r="I310" s="21"/>
+      <c r="A310" s="33"/>
+      <c r="I310" s="20"/>
     </row>
     <row r="311">
-      <c r="A311" s="23"/>
-      <c r="I311" s="21"/>
+      <c r="A311" s="33"/>
+      <c r="I311" s="20"/>
     </row>
     <row r="312">
-      <c r="A312" s="23"/>
-      <c r="I312" s="21"/>
+      <c r="A312" s="33"/>
+      <c r="I312" s="20"/>
     </row>
     <row r="313">
-      <c r="A313" s="23"/>
-      <c r="I313" s="21"/>
+      <c r="A313" s="33"/>
+      <c r="I313" s="20"/>
     </row>
     <row r="314">
-      <c r="A314" s="23"/>
-      <c r="I314" s="21"/>
+      <c r="A314" s="33"/>
+      <c r="I314" s="20"/>
     </row>
     <row r="315">
-      <c r="A315" s="23"/>
-      <c r="I315" s="21"/>
+      <c r="A315" s="33"/>
+      <c r="I315" s="20"/>
     </row>
     <row r="316">
-      <c r="A316" s="23"/>
-      <c r="I316" s="21"/>
+      <c r="A316" s="33"/>
+      <c r="I316" s="20"/>
     </row>
     <row r="317">
-      <c r="A317" s="23"/>
-      <c r="I317" s="21"/>
+      <c r="A317" s="33"/>
+      <c r="I317" s="20"/>
     </row>
     <row r="318">
-      <c r="A318" s="23"/>
-      <c r="I318" s="21"/>
+      <c r="A318" s="33"/>
+      <c r="I318" s="20"/>
     </row>
     <row r="319">
-      <c r="A319" s="23"/>
-      <c r="I319" s="21"/>
+      <c r="A319" s="33"/>
+      <c r="I319" s="20"/>
     </row>
     <row r="320">
-      <c r="A320" s="23"/>
-      <c r="I320" s="21"/>
+      <c r="A320" s="33"/>
+      <c r="I320" s="20"/>
     </row>
     <row r="321">
-      <c r="A321" s="23"/>
-      <c r="I321" s="21"/>
+      <c r="A321" s="33"/>
+      <c r="I321" s="20"/>
     </row>
     <row r="322">
-      <c r="A322" s="23"/>
-      <c r="I322" s="21"/>
+      <c r="A322" s="33"/>
+      <c r="I322" s="20"/>
     </row>
     <row r="323">
-      <c r="A323" s="23"/>
-      <c r="I323" s="21"/>
+      <c r="A323" s="33"/>
+      <c r="I323" s="20"/>
     </row>
     <row r="324">
-      <c r="A324" s="23"/>
-      <c r="I324" s="21"/>
+      <c r="A324" s="33"/>
+      <c r="I324" s="20"/>
     </row>
     <row r="325">
-      <c r="A325" s="23"/>
-      <c r="I325" s="21"/>
+      <c r="A325" s="33"/>
+      <c r="I325" s="20"/>
     </row>
     <row r="326">
-      <c r="A326" s="23"/>
-      <c r="I326" s="21"/>
+      <c r="A326" s="33"/>
+      <c r="I326" s="20"/>
     </row>
     <row r="327">
-      <c r="A327" s="23"/>
-      <c r="I327" s="21"/>
+      <c r="A327" s="33"/>
+      <c r="I327" s="20"/>
     </row>
     <row r="328">
-      <c r="A328" s="23"/>
-      <c r="I328" s="21"/>
+      <c r="A328" s="33"/>
+      <c r="I328" s="20"/>
     </row>
     <row r="329">
-      <c r="A329" s="23"/>
-      <c r="I329" s="21"/>
+      <c r="A329" s="33"/>
+      <c r="I329" s="20"/>
     </row>
     <row r="330">
-      <c r="A330" s="23"/>
-      <c r="I330" s="21"/>
+      <c r="A330" s="33"/>
+      <c r="I330" s="20"/>
     </row>
     <row r="331">
-      <c r="A331" s="23"/>
-      <c r="I331" s="21"/>
+      <c r="A331" s="33"/>
+      <c r="I331" s="20"/>
     </row>
     <row r="332">
-      <c r="A332" s="23"/>
-      <c r="I332" s="21"/>
+      <c r="A332" s="33"/>
+      <c r="I332" s="20"/>
     </row>
     <row r="333">
-      <c r="A333" s="23"/>
-      <c r="I333" s="21"/>
+      <c r="A333" s="33"/>
+      <c r="I333" s="20"/>
     </row>
     <row r="334">
-      <c r="A334" s="23"/>
-      <c r="I334" s="21"/>
+      <c r="A334" s="33"/>
+      <c r="I334" s="20"/>
     </row>
     <row r="335">
-      <c r="A335" s="23"/>
-      <c r="I335" s="21"/>
+      <c r="A335" s="33"/>
+      <c r="I335" s="20"/>
     </row>
     <row r="336">
-      <c r="A336" s="23"/>
-      <c r="I336" s="21"/>
+      <c r="A336" s="33"/>
+      <c r="I336" s="20"/>
     </row>
     <row r="337">
-      <c r="A337" s="23"/>
-      <c r="I337" s="21"/>
+      <c r="A337" s="33"/>
+      <c r="I337" s="20"/>
     </row>
     <row r="338">
-      <c r="A338" s="23"/>
-      <c r="I338" s="21"/>
+      <c r="A338" s="33"/>
+      <c r="I338" s="20"/>
     </row>
     <row r="339">
-      <c r="A339" s="23"/>
-      <c r="I339" s="21"/>
+      <c r="A339" s="33"/>
+      <c r="I339" s="20"/>
     </row>
     <row r="340">
-      <c r="A340" s="23"/>
-      <c r="I340" s="21"/>
+      <c r="A340" s="33"/>
+      <c r="I340" s="20"/>
     </row>
     <row r="341">
-      <c r="A341" s="23"/>
-      <c r="I341" s="21"/>
+      <c r="A341" s="33"/>
+      <c r="I341" s="20"/>
     </row>
     <row r="342">
-      <c r="A342" s="23"/>
-      <c r="I342" s="21"/>
+      <c r="A342" s="33"/>
+      <c r="I342" s="20"/>
     </row>
     <row r="343">
-      <c r="A343" s="23"/>
-      <c r="I343" s="21"/>
+      <c r="A343" s="33"/>
+      <c r="I343" s="20"/>
     </row>
     <row r="344">
-      <c r="A344" s="23"/>
-      <c r="I344" s="21"/>
+      <c r="A344" s="33"/>
+      <c r="I344" s="20"/>
     </row>
     <row r="345">
-      <c r="A345" s="23"/>
-      <c r="I345" s="21"/>
+      <c r="A345" s="33"/>
+      <c r="I345" s="20"/>
     </row>
     <row r="346">
-      <c r="A346" s="23"/>
-      <c r="I346" s="21"/>
+      <c r="A346" s="33"/>
+      <c r="I346" s="20"/>
     </row>
     <row r="347">
-      <c r="A347" s="23"/>
-      <c r="I347" s="21"/>
+      <c r="A347" s="33"/>
+      <c r="I347" s="20"/>
     </row>
     <row r="348">
-      <c r="A348" s="23"/>
-      <c r="I348" s="21"/>
+      <c r="A348" s="33"/>
+      <c r="I348" s="20"/>
     </row>
     <row r="349">
-      <c r="A349" s="23"/>
-      <c r="I349" s="21"/>
+      <c r="A349" s="33"/>
+      <c r="I349" s="20"/>
     </row>
     <row r="350">
-      <c r="A350" s="23"/>
-      <c r="I350" s="21"/>
+      <c r="A350" s="33"/>
+      <c r="I350" s="20"/>
     </row>
     <row r="351">
-      <c r="A351" s="23"/>
-      <c r="I351" s="21"/>
+      <c r="A351" s="33"/>
+      <c r="I351" s="20"/>
     </row>
     <row r="352">
-      <c r="A352" s="23"/>
-      <c r="I352" s="21"/>
+      <c r="A352" s="33"/>
+      <c r="I352" s="20"/>
     </row>
     <row r="353">
-      <c r="A353" s="23"/>
-      <c r="I353" s="21"/>
+      <c r="A353" s="33"/>
+      <c r="I353" s="20"/>
     </row>
     <row r="354">
-      <c r="A354" s="23"/>
-      <c r="I354" s="21"/>
+      <c r="A354" s="33"/>
+      <c r="I354" s="20"/>
     </row>
     <row r="355">
-      <c r="A355" s="23"/>
-      <c r="I355" s="21"/>
+      <c r="A355" s="33"/>
+      <c r="I355" s="20"/>
     </row>
     <row r="356">
-      <c r="A356" s="23"/>
-      <c r="I356" s="21"/>
+      <c r="A356" s="33"/>
+      <c r="I356" s="20"/>
     </row>
     <row r="357">
-      <c r="A357" s="23"/>
-      <c r="I357" s="21"/>
+      <c r="A357" s="33"/>
+      <c r="I357" s="20"/>
     </row>
     <row r="358">
-      <c r="A358" s="23"/>
-      <c r="I358" s="21"/>
+      <c r="A358" s="33"/>
+      <c r="I358" s="20"/>
     </row>
     <row r="359">
-      <c r="A359" s="23"/>
-      <c r="I359" s="21"/>
+      <c r="A359" s="33"/>
+      <c r="I359" s="20"/>
     </row>
     <row r="360">
-      <c r="A360" s="23"/>
-      <c r="I360" s="21"/>
+      <c r="A360" s="33"/>
+      <c r="I360" s="20"/>
     </row>
     <row r="361">
-      <c r="A361" s="23"/>
-      <c r="I361" s="21"/>
+      <c r="A361" s="33"/>
+      <c r="I361" s="20"/>
     </row>
     <row r="362">
-      <c r="A362" s="23"/>
-      <c r="I362" s="21"/>
+      <c r="A362" s="33"/>
+      <c r="I362" s="20"/>
     </row>
     <row r="363">
-      <c r="A363" s="23"/>
-      <c r="I363" s="21"/>
+      <c r="A363" s="33"/>
+      <c r="I363" s="20"/>
     </row>
     <row r="364">
-      <c r="A364" s="23"/>
-      <c r="I364" s="21"/>
+      <c r="A364" s="33"/>
+      <c r="I364" s="20"/>
     </row>
     <row r="365">
-      <c r="A365" s="23"/>
-      <c r="I365" s="21"/>
+      <c r="A365" s="33"/>
+      <c r="I365" s="20"/>
     </row>
     <row r="366">
-      <c r="A366" s="23"/>
-      <c r="I366" s="21"/>
+      <c r="A366" s="33"/>
+      <c r="I366" s="20"/>
     </row>
     <row r="367">
-      <c r="A367" s="23"/>
-      <c r="I367" s="21"/>
+      <c r="A367" s="33"/>
+      <c r="I367" s="20"/>
     </row>
     <row r="368">
-      <c r="A368" s="23"/>
-      <c r="I368" s="21"/>
+      <c r="A368" s="33"/>
+      <c r="I368" s="20"/>
     </row>
     <row r="369">
-      <c r="A369" s="23"/>
-      <c r="I369" s="21"/>
+      <c r="A369" s="33"/>
+      <c r="I369" s="20"/>
     </row>
     <row r="370">
-      <c r="A370" s="23"/>
-      <c r="I370" s="21"/>
+      <c r="A370" s="33"/>
+      <c r="I370" s="20"/>
     </row>
     <row r="371">
-      <c r="A371" s="23"/>
-      <c r="I371" s="21"/>
+      <c r="A371" s="33"/>
+      <c r="I371" s="20"/>
     </row>
     <row r="372">
-      <c r="A372" s="23"/>
-      <c r="I372" s="21"/>
+      <c r="A372" s="33"/>
+      <c r="I372" s="20"/>
     </row>
     <row r="373">
-      <c r="A373" s="23"/>
-      <c r="I373" s="21"/>
+      <c r="A373" s="33"/>
+      <c r="I373" s="20"/>
     </row>
     <row r="374">
-      <c r="A374" s="23"/>
-      <c r="I374" s="21"/>
+      <c r="A374" s="33"/>
+      <c r="I374" s="20"/>
     </row>
     <row r="375">
-      <c r="A375" s="23"/>
-      <c r="I375" s="21"/>
+      <c r="A375" s="33"/>
+      <c r="I375" s="20"/>
     </row>
     <row r="376">
-      <c r="A376" s="23"/>
-      <c r="I376" s="21"/>
+      <c r="A376" s="33"/>
+      <c r="I376" s="20"/>
     </row>
     <row r="377">
-      <c r="A377" s="23"/>
-      <c r="I377" s="21"/>
+      <c r="A377" s="33"/>
+      <c r="I377" s="20"/>
     </row>
     <row r="378">
-      <c r="A378" s="23"/>
-      <c r="I378" s="21"/>
+      <c r="A378" s="33"/>
+      <c r="I378" s="20"/>
     </row>
     <row r="379">
-      <c r="A379" s="23"/>
-      <c r="I379" s="21"/>
+      <c r="A379" s="33"/>
+      <c r="I379" s="20"/>
     </row>
     <row r="380">
-      <c r="A380" s="23"/>
-      <c r="I380" s="21"/>
+      <c r="A380" s="33"/>
+      <c r="I380" s="20"/>
     </row>
     <row r="381">
-      <c r="A381" s="23"/>
-      <c r="I381" s="21"/>
+      <c r="A381" s="33"/>
+      <c r="I381" s="20"/>
     </row>
     <row r="382">
-      <c r="A382" s="23"/>
-      <c r="I382" s="21"/>
+      <c r="A382" s="33"/>
+      <c r="I382" s="20"/>
     </row>
     <row r="383">
-      <c r="A383" s="23"/>
-      <c r="I383" s="21"/>
+      <c r="A383" s="33"/>
+      <c r="I383" s="20"/>
     </row>
     <row r="384">
-      <c r="A384" s="23"/>
-      <c r="I384" s="21"/>
+      <c r="A384" s="33"/>
+      <c r="I384" s="20"/>
     </row>
     <row r="385">
-      <c r="A385" s="23"/>
-      <c r="I385" s="21"/>
+      <c r="A385" s="33"/>
+      <c r="I385" s="20"/>
     </row>
     <row r="386">
-      <c r="A386" s="23"/>
-      <c r="I386" s="21"/>
+      <c r="A386" s="33"/>
+      <c r="I386" s="20"/>
     </row>
     <row r="387">
-      <c r="A387" s="23"/>
-      <c r="I387" s="21"/>
+      <c r="A387" s="33"/>
+      <c r="I387" s="20"/>
     </row>
     <row r="388">
-      <c r="A388" s="23"/>
-      <c r="I388" s="21"/>
+      <c r="A388" s="33"/>
+      <c r="I388" s="20"/>
     </row>
     <row r="389">
-      <c r="A389" s="23"/>
-      <c r="I389" s="21"/>
+      <c r="A389" s="33"/>
+      <c r="I389" s="20"/>
     </row>
     <row r="390">
-      <c r="A390" s="23"/>
-      <c r="I390" s="21"/>
+      <c r="A390" s="33"/>
+      <c r="I390" s="20"/>
     </row>
     <row r="391">
-      <c r="A391" s="23"/>
-      <c r="I391" s="21"/>
+      <c r="A391" s="33"/>
+      <c r="I391" s="20"/>
     </row>
     <row r="392">
-      <c r="A392" s="23"/>
-      <c r="I392" s="21"/>
+      <c r="A392" s="33"/>
+      <c r="I392" s="20"/>
     </row>
     <row r="393">
-      <c r="A393" s="23"/>
-      <c r="I393" s="21"/>
+      <c r="A393" s="33"/>
+      <c r="I393" s="20"/>
     </row>
     <row r="394">
-      <c r="A394" s="23"/>
-      <c r="I394" s="21"/>
+      <c r="A394" s="33"/>
+      <c r="I394" s="20"/>
     </row>
     <row r="395">
-      <c r="A395" s="23"/>
-      <c r="I395" s="21"/>
+      <c r="A395" s="33"/>
+      <c r="I395" s="20"/>
     </row>
     <row r="396">
-      <c r="A396" s="23"/>
-      <c r="I396" s="21"/>
+      <c r="A396" s="33"/>
+      <c r="I396" s="20"/>
     </row>
     <row r="397">
-      <c r="A397" s="23"/>
-      <c r="I397" s="21"/>
+      <c r="A397" s="33"/>
+      <c r="I397" s="20"/>
     </row>
     <row r="398">
-      <c r="A398" s="23"/>
-      <c r="I398" s="21"/>
+      <c r="A398" s="33"/>
+      <c r="I398" s="20"/>
     </row>
     <row r="399">
-      <c r="A399" s="23"/>
-      <c r="I399" s="21"/>
+      <c r="A399" s="33"/>
+      <c r="I399" s="20"/>
     </row>
     <row r="400">
-      <c r="A400" s="23"/>
-      <c r="I400" s="21"/>
+      <c r="A400" s="33"/>
+      <c r="I400" s="20"/>
     </row>
     <row r="401">
-      <c r="A401" s="23"/>
-      <c r="I401" s="21"/>
+      <c r="A401" s="33"/>
+      <c r="I401" s="20"/>
     </row>
     <row r="402">
-      <c r="A402" s="23"/>
-      <c r="I402" s="21"/>
+      <c r="A402" s="33"/>
+      <c r="I402" s="20"/>
     </row>
     <row r="403">
-      <c r="A403" s="23"/>
-      <c r="I403" s="21"/>
+      <c r="A403" s="33"/>
+      <c r="I403" s="20"/>
     </row>
     <row r="404">
-      <c r="A404" s="23"/>
-      <c r="I404" s="21"/>
+      <c r="A404" s="33"/>
+      <c r="I404" s="20"/>
     </row>
     <row r="405">
-      <c r="A405" s="23"/>
-      <c r="I405" s="21"/>
+      <c r="A405" s="33"/>
+      <c r="I405" s="20"/>
     </row>
     <row r="406">
-      <c r="A406" s="23"/>
-      <c r="I406" s="21"/>
+      <c r="A406" s="33"/>
+      <c r="I406" s="20"/>
     </row>
     <row r="407">
-      <c r="A407" s="23"/>
-      <c r="I407" s="21"/>
+      <c r="A407" s="33"/>
+      <c r="I407" s="20"/>
     </row>
     <row r="408">
-      <c r="A408" s="23"/>
-      <c r="I408" s="21"/>
+      <c r="A408" s="33"/>
+      <c r="I408" s="20"/>
     </row>
     <row r="409">
-      <c r="A409" s="23"/>
-      <c r="I409" s="21"/>
+      <c r="A409" s="33"/>
+      <c r="I409" s="20"/>
     </row>
     <row r="410">
-      <c r="A410" s="23"/>
-      <c r="I410" s="21"/>
+      <c r="A410" s="33"/>
+      <c r="I410" s="20"/>
     </row>
     <row r="411">
-      <c r="A411" s="23"/>
-      <c r="I411" s="21"/>
+      <c r="A411" s="33"/>
+      <c r="I411" s="20"/>
     </row>
     <row r="412">
-      <c r="A412" s="23"/>
-      <c r="I412" s="21"/>
+      <c r="A412" s="33"/>
+      <c r="I412" s="20"/>
     </row>
     <row r="413">
-      <c r="A413" s="23"/>
-      <c r="I413" s="21"/>
+      <c r="A413" s="33"/>
+      <c r="I413" s="20"/>
     </row>
     <row r="414">
-      <c r="A414" s="23"/>
-      <c r="I414" s="21"/>
+      <c r="A414" s="33"/>
+      <c r="I414" s="20"/>
     </row>
     <row r="415">
-      <c r="A415" s="23"/>
-      <c r="I415" s="21"/>
+      <c r="A415" s="33"/>
+      <c r="I415" s="20"/>
     </row>
     <row r="416">
-      <c r="A416" s="23"/>
-      <c r="I416" s="21"/>
+      <c r="A416" s="33"/>
+      <c r="I416" s="20"/>
     </row>
     <row r="417">
-      <c r="A417" s="23"/>
-      <c r="I417" s="21"/>
+      <c r="A417" s="33"/>
+      <c r="I417" s="20"/>
     </row>
     <row r="418">
-      <c r="A418" s="23"/>
-      <c r="I418" s="21"/>
+      <c r="A418" s="33"/>
+      <c r="I418" s="20"/>
     </row>
     <row r="419">
-      <c r="A419" s="23"/>
-      <c r="I419" s="21"/>
+      <c r="A419" s="33"/>
+      <c r="I419" s="20"/>
     </row>
     <row r="420">
-      <c r="A420" s="23"/>
-      <c r="I420" s="21"/>
+      <c r="A420" s="33"/>
+      <c r="I420" s="20"/>
     </row>
     <row r="421">
-      <c r="A421" s="23"/>
-      <c r="I421" s="21"/>
+      <c r="A421" s="33"/>
+      <c r="I421" s="20"/>
     </row>
     <row r="422">
-      <c r="A422" s="23"/>
-      <c r="I422" s="21"/>
+      <c r="A422" s="33"/>
+      <c r="I422" s="20"/>
     </row>
     <row r="423">
-      <c r="A423" s="23"/>
-      <c r="I423" s="21"/>
+      <c r="A423" s="33"/>
+      <c r="I423" s="20"/>
     </row>
     <row r="424">
-      <c r="A424" s="23"/>
-      <c r="I424" s="21"/>
+      <c r="A424" s="33"/>
+      <c r="I424" s="20"/>
     </row>
     <row r="425">
-      <c r="A425" s="23"/>
-      <c r="I425" s="21"/>
+      <c r="A425" s="33"/>
+      <c r="I425" s="20"/>
     </row>
     <row r="426">
-      <c r="A426" s="23"/>
-      <c r="I426" s="21"/>
+      <c r="A426" s="33"/>
+      <c r="I426" s="20"/>
     </row>
     <row r="427">
-      <c r="A427" s="23"/>
-      <c r="I427" s="21"/>
+      <c r="A427" s="33"/>
+      <c r="I427" s="20"/>
     </row>
     <row r="428">
-      <c r="A428" s="23"/>
-      <c r="I428" s="21"/>
+      <c r="A428" s="33"/>
+      <c r="I428" s="20"/>
     </row>
     <row r="429">
-      <c r="A429" s="23"/>
-      <c r="I429" s="21"/>
+      <c r="A429" s="33"/>
+      <c r="I429" s="20"/>
     </row>
     <row r="430">
-      <c r="A430" s="23"/>
-      <c r="I430" s="21"/>
+      <c r="A430" s="33"/>
+      <c r="I430" s="20"/>
     </row>
     <row r="431">
-      <c r="A431" s="23"/>
-      <c r="I431" s="21"/>
+      <c r="A431" s="33"/>
+      <c r="I431" s="20"/>
     </row>
     <row r="432">
-      <c r="A432" s="23"/>
-      <c r="I432" s="21"/>
+      <c r="A432" s="33"/>
+      <c r="I432" s="20"/>
     </row>
     <row r="433">
-      <c r="A433" s="23"/>
-      <c r="I433" s="21"/>
+      <c r="A433" s="33"/>
+      <c r="I433" s="20"/>
     </row>
     <row r="434">
-      <c r="A434" s="23"/>
-      <c r="I434" s="21"/>
+      <c r="A434" s="33"/>
+      <c r="I434" s="20"/>
     </row>
     <row r="435">
-      <c r="A435" s="23"/>
-      <c r="I435" s="21"/>
+      <c r="A435" s="33"/>
+      <c r="I435" s="20"/>
     </row>
     <row r="436">
-      <c r="A436" s="23"/>
-      <c r="I436" s="21"/>
+      <c r="A436" s="33"/>
+      <c r="I436" s="20"/>
     </row>
     <row r="437">
-      <c r="A437" s="23"/>
-      <c r="I437" s="21"/>
+      <c r="A437" s="33"/>
+      <c r="I437" s="20"/>
     </row>
     <row r="438">
-      <c r="A438" s="23"/>
-      <c r="I438" s="21"/>
+      <c r="A438" s="33"/>
+      <c r="I438" s="20"/>
     </row>
     <row r="439">
-      <c r="A439" s="23"/>
-      <c r="I439" s="21"/>
+      <c r="A439" s="33"/>
+      <c r="I439" s="20"/>
     </row>
     <row r="440">
-      <c r="A440" s="23"/>
-      <c r="I440" s="21"/>
+      <c r="A440" s="33"/>
+      <c r="I440" s="20"/>
     </row>
     <row r="441">
-      <c r="A441" s="23"/>
-      <c r="I441" s="21"/>
+      <c r="A441" s="33"/>
+      <c r="I441" s="20"/>
     </row>
     <row r="442">
-      <c r="A442" s="23"/>
-      <c r="I442" s="21"/>
+      <c r="A442" s="33"/>
+      <c r="I442" s="20"/>
     </row>
     <row r="443">
-      <c r="A443" s="23"/>
-      <c r="I443" s="21"/>
+      <c r="A443" s="33"/>
+      <c r="I443" s="20"/>
     </row>
     <row r="444">
-      <c r="A444" s="23"/>
-      <c r="I444" s="21"/>
+      <c r="A444" s="33"/>
+      <c r="I444" s="20"/>
     </row>
     <row r="445">
-      <c r="A445" s="23"/>
-      <c r="I445" s="21"/>
+      <c r="A445" s="33"/>
+      <c r="I445" s="20"/>
     </row>
     <row r="446">
-      <c r="A446" s="23"/>
-      <c r="I446" s="21"/>
+      <c r="A446" s="33"/>
+      <c r="I446" s="20"/>
     </row>
     <row r="447">
-      <c r="A447" s="23"/>
-      <c r="I447" s="21"/>
+      <c r="A447" s="33"/>
+      <c r="I447" s="20"/>
     </row>
     <row r="448">
-      <c r="A448" s="23"/>
-      <c r="I448" s="21"/>
+      <c r="A448" s="33"/>
+      <c r="I448" s="20"/>
     </row>
     <row r="449">
-      <c r="A449" s="23"/>
-      <c r="I449" s="21"/>
+      <c r="A449" s="33"/>
+      <c r="I449" s="20"/>
     </row>
     <row r="450">
-      <c r="A450" s="23"/>
-      <c r="I450" s="21"/>
+      <c r="A450" s="33"/>
+      <c r="I450" s="20"/>
     </row>
     <row r="451">
-      <c r="A451" s="23"/>
-      <c r="I451" s="21"/>
+      <c r="A451" s="33"/>
+      <c r="I451" s="20"/>
     </row>
     <row r="452">
-      <c r="A452" s="23"/>
-      <c r="I452" s="21"/>
+      <c r="A452" s="33"/>
+      <c r="I452" s="20"/>
     </row>
     <row r="453">
-      <c r="A453" s="23"/>
-      <c r="I453" s="21"/>
+      <c r="A453" s="33"/>
+      <c r="I453" s="20"/>
     </row>
     <row r="454">
-      <c r="A454" s="23"/>
-      <c r="I454" s="21"/>
+      <c r="A454" s="33"/>
+      <c r="I454" s="20"/>
     </row>
     <row r="455">
-      <c r="A455" s="23"/>
-      <c r="I455" s="21"/>
+      <c r="A455" s="33"/>
+      <c r="I455" s="20"/>
     </row>
     <row r="456">
-      <c r="A456" s="23"/>
-      <c r="I456" s="21"/>
+      <c r="A456" s="33"/>
+      <c r="I456" s="20"/>
     </row>
     <row r="457">
-      <c r="A457" s="23"/>
-      <c r="I457" s="21"/>
+      <c r="A457" s="33"/>
+      <c r="I457" s="20"/>
     </row>
     <row r="458">
-      <c r="A458" s="23"/>
-      <c r="I458" s="21"/>
+      <c r="A458" s="33"/>
+      <c r="I458" s="20"/>
     </row>
     <row r="459">
-      <c r="A459" s="23"/>
-      <c r="I459" s="21"/>
+      <c r="A459" s="33"/>
+      <c r="I459" s="20"/>
     </row>
     <row r="460">
-      <c r="A460" s="23"/>
-      <c r="I460" s="21"/>
+      <c r="A460" s="33"/>
+      <c r="I460" s="20"/>
     </row>
     <row r="461">
-      <c r="A461" s="23"/>
-      <c r="I461" s="21"/>
+      <c r="A461" s="33"/>
+      <c r="I461" s="20"/>
     </row>
     <row r="462">
-      <c r="A462" s="23"/>
-      <c r="I462" s="21"/>
+      <c r="A462" s="33"/>
+      <c r="I462" s="20"/>
     </row>
     <row r="463">
-      <c r="A463" s="23"/>
-      <c r="I463" s="21"/>
+      <c r="A463" s="33"/>
+      <c r="I463" s="20"/>
     </row>
     <row r="464">
-      <c r="A464" s="23"/>
-      <c r="I464" s="21"/>
+      <c r="A464" s="33"/>
+      <c r="I464" s="20"/>
     </row>
     <row r="465">
-      <c r="A465" s="23"/>
-      <c r="I465" s="21"/>
+      <c r="A465" s="33"/>
+      <c r="I465" s="20"/>
     </row>
     <row r="466">
-      <c r="A466" s="23"/>
-      <c r="I466" s="21"/>
+      <c r="A466" s="33"/>
+      <c r="I466" s="20"/>
     </row>
     <row r="467">
-      <c r="A467" s="23"/>
-      <c r="I467" s="21"/>
+      <c r="A467" s="33"/>
+      <c r="I467" s="20"/>
     </row>
     <row r="468">
-      <c r="A468" s="23"/>
-      <c r="I468" s="21"/>
+      <c r="A468" s="33"/>
+      <c r="I468" s="20"/>
     </row>
     <row r="469">
-      <c r="A469" s="23"/>
-      <c r="I469" s="21"/>
+      <c r="A469" s="33"/>
+      <c r="I469" s="20"/>
     </row>
     <row r="470">
-      <c r="A470" s="23"/>
-      <c r="I470" s="21"/>
+      <c r="A470" s="33"/>
+      <c r="I470" s="20"/>
     </row>
     <row r="471">
-      <c r="A471" s="23"/>
-      <c r="I471" s="21"/>
+      <c r="A471" s="33"/>
+      <c r="I471" s="20"/>
     </row>
     <row r="472">
-      <c r="A472" s="23"/>
-      <c r="I472" s="21"/>
+      <c r="A472" s="33"/>
+      <c r="I472" s="20"/>
     </row>
     <row r="473">
-      <c r="A473" s="23"/>
-      <c r="I473" s="21"/>
+      <c r="A473" s="33"/>
+      <c r="I473" s="20"/>
     </row>
     <row r="474">
-      <c r="A474" s="23"/>
-      <c r="I474" s="21"/>
+      <c r="A474" s="33"/>
+      <c r="I474" s="20"/>
     </row>
     <row r="475">
-      <c r="A475" s="23"/>
-      <c r="I475" s="21"/>
+      <c r="A475" s="33"/>
+      <c r="I475" s="20"/>
     </row>
     <row r="476">
-      <c r="A476" s="23"/>
-      <c r="I476" s="21"/>
+      <c r="A476" s="33"/>
+      <c r="I476" s="20"/>
     </row>
     <row r="477">
-      <c r="A477" s="23"/>
-      <c r="I477" s="21"/>
+      <c r="A477" s="33"/>
+      <c r="I477" s="20"/>
     </row>
     <row r="478">
-      <c r="A478" s="23"/>
-      <c r="I478" s="21"/>
+      <c r="A478" s="33"/>
+      <c r="I478" s="20"/>
     </row>
     <row r="479">
-      <c r="A479" s="23"/>
-      <c r="I479" s="21"/>
+      <c r="A479" s="33"/>
+      <c r="I479" s="20"/>
     </row>
     <row r="480">
-      <c r="A480" s="23"/>
-      <c r="I480" s="21"/>
+      <c r="A480" s="33"/>
+      <c r="I480" s="20"/>
     </row>
     <row r="481">
-      <c r="A481" s="23"/>
-      <c r="I481" s="21"/>
+      <c r="A481" s="33"/>
+      <c r="I481" s="20"/>
     </row>
     <row r="482">
-      <c r="A482" s="23"/>
-      <c r="I482" s="21"/>
+      <c r="A482" s="33"/>
+      <c r="I482" s="20"/>
     </row>
     <row r="483">
-      <c r="A483" s="23"/>
-      <c r="I483" s="21"/>
+      <c r="A483" s="33"/>
+      <c r="I483" s="20"/>
     </row>
     <row r="484">
-      <c r="A484" s="23"/>
-      <c r="I484" s="21"/>
+      <c r="A484" s="33"/>
+      <c r="I484" s="20"/>
     </row>
     <row r="485">
-      <c r="A485" s="23"/>
-      <c r="I485" s="21"/>
+      <c r="A485" s="33"/>
+      <c r="I485" s="20"/>
     </row>
     <row r="486">
-      <c r="A486" s="23"/>
-      <c r="I486" s="21"/>
+      <c r="A486" s="33"/>
+      <c r="I486" s="20"/>
     </row>
     <row r="487">
-      <c r="A487" s="23"/>
-      <c r="I487" s="21"/>
+      <c r="A487" s="33"/>
+      <c r="I487" s="20"/>
     </row>
     <row r="488">
-      <c r="A488" s="23"/>
-      <c r="I488" s="21"/>
+      <c r="A488" s="33"/>
+      <c r="I488" s="20"/>
     </row>
     <row r="489">
-      <c r="A489" s="23"/>
-      <c r="I489" s="21"/>
+      <c r="A489" s="33"/>
+      <c r="I489" s="20"/>
     </row>
     <row r="490">
-      <c r="A490" s="23"/>
-      <c r="I490" s="21"/>
+      <c r="A490" s="33"/>
+      <c r="I490" s="20"/>
     </row>
     <row r="491">
-      <c r="A491" s="23"/>
-      <c r="I491" s="21"/>
+      <c r="A491" s="33"/>
+      <c r="I491" s="20"/>
     </row>
     <row r="492">
-      <c r="A492" s="23"/>
-      <c r="I492" s="21"/>
+      <c r="A492" s="33"/>
+      <c r="I492" s="20"/>
     </row>
     <row r="493">
-      <c r="A493" s="23"/>
-      <c r="I493" s="21"/>
+      <c r="A493" s="33"/>
+      <c r="I493" s="20"/>
     </row>
     <row r="494">
-      <c r="A494" s="23"/>
-      <c r="I494" s="21"/>
+      <c r="A494" s="33"/>
+      <c r="I494" s="20"/>
     </row>
     <row r="495">
-      <c r="A495" s="23"/>
-      <c r="I495" s="21"/>
+      <c r="A495" s="33"/>
+      <c r="I495" s="20"/>
     </row>
     <row r="496">
-      <c r="A496" s="23"/>
-      <c r="I496" s="21"/>
+      <c r="A496" s="33"/>
+      <c r="I496" s="20"/>
     </row>
     <row r="497">
-      <c r="A497" s="23"/>
-      <c r="I497" s="21"/>
+      <c r="A497" s="33"/>
+      <c r="I497" s="20"/>
     </row>
     <row r="498">
-      <c r="A498" s="23"/>
-      <c r="I498" s="21"/>
+      <c r="A498" s="33"/>
+      <c r="I498" s="20"/>
     </row>
     <row r="499">
-      <c r="A499" s="23"/>
-      <c r="I499" s="21"/>
+      <c r="A499" s="33"/>
+      <c r="I499" s="20"/>
     </row>
     <row r="500">
-      <c r="A500" s="23"/>
-      <c r="I500" s="21"/>
+      <c r="A500" s="33"/>
+      <c r="I500" s="20"/>
     </row>
     <row r="501">
-      <c r="A501" s="23"/>
-      <c r="I501" s="21"/>
+      <c r="A501" s="33"/>
+      <c r="I501" s="20"/>
     </row>
     <row r="502">
-      <c r="A502" s="23"/>
-      <c r="I502" s="21"/>
+      <c r="A502" s="33"/>
+      <c r="I502" s="20"/>
     </row>
     <row r="503">
-      <c r="A503" s="23"/>
-      <c r="I503" s="21"/>
+      <c r="A503" s="33"/>
+      <c r="I503" s="20"/>
     </row>
     <row r="504">
-      <c r="A504" s="23"/>
-      <c r="I504" s="21"/>
+      <c r="A504" s="33"/>
+      <c r="I504" s="20"/>
     </row>
     <row r="505">
-      <c r="A505" s="23"/>
-      <c r="I505" s="21"/>
+      <c r="A505" s="33"/>
+      <c r="I505" s="20"/>
     </row>
     <row r="506">
-      <c r="A506" s="23"/>
-      <c r="I506" s="21"/>
+      <c r="A506" s="33"/>
+      <c r="I506" s="20"/>
     </row>
     <row r="507">
-      <c r="A507" s="23"/>
-      <c r="I507" s="21"/>
+      <c r="A507" s="33"/>
+      <c r="I507" s="20"/>
     </row>
     <row r="508">
-      <c r="A508" s="23"/>
-      <c r="I508" s="21"/>
+      <c r="A508" s="33"/>
+      <c r="I508" s="20"/>
     </row>
     <row r="509">
-      <c r="A509" s="23"/>
-      <c r="I509" s="21"/>
+      <c r="A509" s="33"/>
+      <c r="I509" s="20"/>
     </row>
     <row r="510">
-      <c r="A510" s="23"/>
-      <c r="I510" s="21"/>
+      <c r="A510" s="33"/>
+      <c r="I510" s="20"/>
     </row>
     <row r="511">
-      <c r="A511" s="23"/>
-      <c r="I511" s="21"/>
+      <c r="A511" s="33"/>
+      <c r="I511" s="20"/>
     </row>
     <row r="512">
-      <c r="A512" s="23"/>
-      <c r="I512" s="21"/>
+      <c r="A512" s="33"/>
+      <c r="I512" s="20"/>
     </row>
     <row r="513">
-      <c r="A513" s="23"/>
-      <c r="I513" s="21"/>
+      <c r="A513" s="33"/>
+      <c r="I513" s="20"/>
     </row>
     <row r="514">
-      <c r="A514" s="23"/>
-      <c r="I514" s="21"/>
+      <c r="A514" s="33"/>
+      <c r="I514" s="20"/>
     </row>
     <row r="515">
-      <c r="A515" s="23"/>
-      <c r="I515" s="21"/>
+      <c r="A515" s="33"/>
+      <c r="I515" s="20"/>
     </row>
     <row r="516">
-      <c r="A516" s="23"/>
-      <c r="I516" s="21"/>
+      <c r="A516" s="33"/>
+      <c r="I516" s="20"/>
     </row>
     <row r="517">
-      <c r="A517" s="23"/>
-      <c r="I517" s="21"/>
+      <c r="A517" s="33"/>
+      <c r="I517" s="20"/>
     </row>
     <row r="518">
-      <c r="A518" s="23"/>
-      <c r="I518" s="21"/>
+      <c r="A518" s="33"/>
+      <c r="I518" s="20"/>
     </row>
     <row r="519">
-      <c r="A519" s="23"/>
-      <c r="I519" s="21"/>
+      <c r="A519" s="33"/>
+      <c r="I519" s="20"/>
     </row>
     <row r="520">
-      <c r="A520" s="23"/>
-      <c r="I520" s="21"/>
+      <c r="A520" s="33"/>
+      <c r="I520" s="20"/>
     </row>
     <row r="521">
-      <c r="A521" s="23"/>
-      <c r="I521" s="21"/>
+      <c r="A521" s="33"/>
+      <c r="I521" s="20"/>
     </row>
     <row r="522">
-      <c r="A522" s="23"/>
-      <c r="I522" s="21"/>
+      <c r="A522" s="33"/>
+      <c r="I522" s="20"/>
     </row>
     <row r="523">
-      <c r="A523" s="23"/>
-      <c r="I523" s="21"/>
+      <c r="A523" s="33"/>
+      <c r="I523" s="20"/>
     </row>
     <row r="524">
-      <c r="A524" s="23"/>
-      <c r="I524" s="21"/>
+      <c r="A524" s="33"/>
+      <c r="I524" s="20"/>
     </row>
     <row r="525">
-      <c r="A525" s="23"/>
-      <c r="I525" s="21"/>
+      <c r="A525" s="33"/>
+      <c r="I525" s="20"/>
     </row>
     <row r="526">
-      <c r="A526" s="23"/>
-      <c r="I526" s="21"/>
+      <c r="A526" s="33"/>
+      <c r="I526" s="20"/>
     </row>
     <row r="527">
-      <c r="A527" s="23"/>
-      <c r="I527" s="21"/>
+      <c r="A527" s="33"/>
+      <c r="I527" s="20"/>
     </row>
     <row r="528">
-      <c r="A528" s="23"/>
-      <c r="I528" s="21"/>
+      <c r="A528" s="33"/>
+      <c r="I528" s="20"/>
     </row>
     <row r="529">
-      <c r="A529" s="23"/>
-      <c r="I529" s="21"/>
+      <c r="A529" s="33"/>
+      <c r="I529" s="20"/>
     </row>
     <row r="530">
-      <c r="A530" s="23"/>
-      <c r="I530" s="21"/>
+      <c r="A530" s="33"/>
+      <c r="I530" s="20"/>
     </row>
     <row r="531">
-      <c r="A531" s="23"/>
-      <c r="I531" s="21"/>
+      <c r="A531" s="33"/>
+      <c r="I531" s="20"/>
     </row>
     <row r="532">
-      <c r="A532" s="23"/>
-      <c r="I532" s="21"/>
+      <c r="A532" s="33"/>
+      <c r="I532" s="20"/>
     </row>
     <row r="533">
-      <c r="A533" s="23"/>
-      <c r="I533" s="21"/>
+      <c r="A533" s="33"/>
+      <c r="I533" s="20"/>
     </row>
     <row r="534">
-      <c r="A534" s="23"/>
-      <c r="I534" s="21"/>
+      <c r="A534" s="33"/>
+      <c r="I534" s="20"/>
     </row>
     <row r="535">
-      <c r="A535" s="23"/>
-      <c r="I535" s="21"/>
+      <c r="A535" s="33"/>
+      <c r="I535" s="20"/>
     </row>
     <row r="536">
-      <c r="A536" s="23"/>
-      <c r="I536" s="21"/>
+      <c r="A536" s="33"/>
+      <c r="I536" s="20"/>
     </row>
     <row r="537">
-      <c r="A537" s="23"/>
-      <c r="I537" s="21"/>
+      <c r="A537" s="33"/>
+      <c r="I537" s="20"/>
     </row>
     <row r="538">
-      <c r="A538" s="23"/>
-      <c r="I538" s="21"/>
+      <c r="A538" s="33"/>
+      <c r="I538" s="20"/>
     </row>
     <row r="539">
-      <c r="A539" s="23"/>
-      <c r="I539" s="21"/>
+      <c r="A539" s="33"/>
+      <c r="I539" s="20"/>
     </row>
     <row r="540">
-      <c r="A540" s="23"/>
-      <c r="I540" s="21"/>
+      <c r="A540" s="33"/>
+      <c r="I540" s="20"/>
     </row>
     <row r="541">
-      <c r="A541" s="23"/>
-      <c r="I541" s="21"/>
+      <c r="A541" s="33"/>
+      <c r="I541" s="20"/>
     </row>
     <row r="542">
-      <c r="A542" s="23"/>
-      <c r="I542" s="21"/>
+      <c r="A542" s="33"/>
+      <c r="I542" s="20"/>
     </row>
     <row r="543">
-      <c r="A543" s="23"/>
-      <c r="I543" s="21"/>
+      <c r="A543" s="33"/>
+      <c r="I543" s="20"/>
     </row>
     <row r="544">
-      <c r="A544" s="23"/>
-      <c r="I544" s="21"/>
+      <c r="A544" s="33"/>
+      <c r="I544" s="20"/>
     </row>
     <row r="545">
-      <c r="A545" s="23"/>
-      <c r="I545" s="21"/>
+      <c r="A545" s="33"/>
+      <c r="I545" s="20"/>
     </row>
     <row r="546">
-      <c r="A546" s="23"/>
-      <c r="I546" s="21"/>
+      <c r="A546" s="33"/>
+      <c r="I546" s="20"/>
     </row>
     <row r="547">
-      <c r="A547" s="23"/>
-      <c r="I547" s="21"/>
+      <c r="A547" s="33"/>
+      <c r="I547" s="20"/>
     </row>
     <row r="548">
-      <c r="A548" s="23"/>
-      <c r="I548" s="21"/>
+      <c r="A548" s="33"/>
+      <c r="I548" s="20"/>
     </row>
     <row r="549">
-      <c r="A549" s="23"/>
-      <c r="I549" s="21"/>
+      <c r="A549" s="33"/>
+      <c r="I549" s="20"/>
     </row>
     <row r="550">
-      <c r="A550" s="23"/>
-      <c r="I550" s="21"/>
+      <c r="A550" s="33"/>
+      <c r="I550" s="20"/>
     </row>
     <row r="551">
-      <c r="A551" s="23"/>
-      <c r="I551" s="21"/>
+      <c r="A551" s="33"/>
+      <c r="I551" s="20"/>
     </row>
     <row r="552">
-      <c r="A552" s="23"/>
-      <c r="I552" s="21"/>
+      <c r="A552" s="33"/>
+      <c r="I552" s="20"/>
     </row>
     <row r="553">
-      <c r="A553" s="23"/>
-      <c r="I553" s="21"/>
+      <c r="A553" s="33"/>
+      <c r="I553" s="20"/>
     </row>
     <row r="554">
-      <c r="A554" s="23"/>
-      <c r="I554" s="21"/>
+      <c r="A554" s="33"/>
+      <c r="I554" s="20"/>
     </row>
     <row r="555">
-      <c r="A555" s="23"/>
-      <c r="I555" s="21"/>
+      <c r="A555" s="33"/>
+      <c r="I555" s="20"/>
     </row>
     <row r="556">
-      <c r="A556" s="23"/>
-      <c r="I556" s="21"/>
+      <c r="A556" s="33"/>
+      <c r="I556" s="20"/>
     </row>
     <row r="557">
-      <c r="A557" s="23"/>
-      <c r="I557" s="21"/>
+      <c r="A557" s="33"/>
+      <c r="I557" s="20"/>
     </row>
     <row r="558">
-      <c r="A558" s="23"/>
-      <c r="I558" s="21"/>
+      <c r="A558" s="33"/>
+      <c r="I558" s="20"/>
     </row>
     <row r="559">
-      <c r="A559" s="23"/>
-      <c r="I559" s="21"/>
+      <c r="A559" s="33"/>
+      <c r="I559" s="20"/>
     </row>
     <row r="560">
-      <c r="A560" s="23"/>
-      <c r="I560" s="21"/>
+      <c r="A560" s="33"/>
+      <c r="I560" s="20"/>
     </row>
     <row r="561">
-      <c r="A561" s="23"/>
-      <c r="I561" s="21"/>
+      <c r="A561" s="33"/>
+      <c r="I561" s="20"/>
     </row>
     <row r="562">
-      <c r="A562" s="23"/>
-      <c r="I562" s="21"/>
+      <c r="A562" s="33"/>
+      <c r="I562" s="20"/>
     </row>
     <row r="563">
-      <c r="A563" s="23"/>
-      <c r="I563" s="21"/>
+      <c r="A563" s="33"/>
+      <c r="I563" s="20"/>
     </row>
     <row r="564">
-      <c r="A564" s="23"/>
-      <c r="I564" s="21"/>
+      <c r="A564" s="33"/>
+      <c r="I564" s="20"/>
     </row>
     <row r="565">
-      <c r="A565" s="23"/>
-      <c r="I565" s="21"/>
+      <c r="A565" s="33"/>
+      <c r="I565" s="20"/>
     </row>
     <row r="566">
-      <c r="A566" s="23"/>
-      <c r="I566" s="21"/>
+      <c r="A566" s="33"/>
+      <c r="I566" s="20"/>
     </row>
     <row r="567">
-      <c r="A567" s="23"/>
-      <c r="I567" s="21"/>
+      <c r="A567" s="33"/>
+      <c r="I567" s="20"/>
     </row>
     <row r="568">
-      <c r="A568" s="23"/>
-      <c r="I568" s="21"/>
+      <c r="A568" s="33"/>
+      <c r="I568" s="20"/>
     </row>
     <row r="569">
-      <c r="A569" s="23"/>
-      <c r="I569" s="21"/>
+      <c r="A569" s="33"/>
+      <c r="I569" s="20"/>
     </row>
     <row r="570">
-      <c r="A570" s="23"/>
-      <c r="I570" s="21"/>
+      <c r="A570" s="33"/>
+      <c r="I570" s="20"/>
     </row>
     <row r="571">
-      <c r="A571" s="23"/>
-      <c r="I571" s="21"/>
+      <c r="A571" s="33"/>
+      <c r="I571" s="20"/>
     </row>
     <row r="572">
-      <c r="A572" s="23"/>
-      <c r="I572" s="21"/>
+      <c r="A572" s="33"/>
+      <c r="I572" s="20"/>
     </row>
     <row r="573">
-      <c r="A573" s="23"/>
-      <c r="I573" s="21"/>
+      <c r="A573" s="33"/>
+      <c r="I573" s="20"/>
     </row>
     <row r="574">
-      <c r="A574" s="23"/>
-      <c r="I574" s="21"/>
+      <c r="A574" s="33"/>
+      <c r="I574" s="20"/>
     </row>
     <row r="575">
-      <c r="A575" s="23"/>
-      <c r="I575" s="21"/>
+      <c r="A575" s="33"/>
+      <c r="I575" s="20"/>
     </row>
     <row r="576">
-      <c r="A576" s="23"/>
-      <c r="I576" s="21"/>
+      <c r="A576" s="33"/>
+      <c r="I576" s="20"/>
     </row>
     <row r="577">
-      <c r="A577" s="23"/>
-      <c r="I577" s="21"/>
+      <c r="A577" s="33"/>
+      <c r="I577" s="20"/>
     </row>
     <row r="578">
-      <c r="A578" s="23"/>
-      <c r="I578" s="21"/>
+      <c r="A578" s="33"/>
+      <c r="I578" s="20"/>
     </row>
     <row r="579">
-      <c r="A579" s="23"/>
-      <c r="I579" s="21"/>
+      <c r="A579" s="33"/>
+      <c r="I579" s="20"/>
     </row>
     <row r="580">
-      <c r="A580" s="23"/>
-      <c r="I580" s="21"/>
+      <c r="A580" s="33"/>
+      <c r="I580" s="20"/>
     </row>
     <row r="581">
-      <c r="A581" s="23"/>
-      <c r="I581" s="21"/>
+      <c r="A581" s="33"/>
+      <c r="I581" s="20"/>
     </row>
     <row r="582">
-      <c r="A582" s="23"/>
-      <c r="I582" s="21"/>
+      <c r="A582" s="33"/>
+      <c r="I582" s="20"/>
     </row>
     <row r="583">
-      <c r="A583" s="23"/>
-      <c r="I583" s="21"/>
+      <c r="A583" s="33"/>
+      <c r="I583" s="20"/>
     </row>
     <row r="584">
-      <c r="A584" s="23"/>
-      <c r="I584" s="21"/>
+      <c r="A584" s="33"/>
+      <c r="I584" s="20"/>
     </row>
     <row r="585">
-      <c r="A585" s="23"/>
-      <c r="I585" s="21"/>
+      <c r="A585" s="33"/>
+      <c r="I585" s="20"/>
     </row>
     <row r="586">
-      <c r="A586" s="23"/>
-      <c r="I586" s="21"/>
+      <c r="A586" s="33"/>
+      <c r="I586" s="20"/>
     </row>
     <row r="587">
-      <c r="A587" s="23"/>
-      <c r="I587" s="21"/>
+      <c r="A587" s="33"/>
+      <c r="I587" s="20"/>
     </row>
     <row r="588">
-      <c r="A588" s="23"/>
-      <c r="I588" s="21"/>
+      <c r="A588" s="33"/>
+      <c r="I588" s="20"/>
     </row>
     <row r="589">
-      <c r="A589" s="23"/>
-      <c r="I589" s="21"/>
+      <c r="A589" s="33"/>
+      <c r="I589" s="20"/>
     </row>
     <row r="590">
-      <c r="A590" s="23"/>
-      <c r="I590" s="21"/>
+      <c r="A590" s="33"/>
+      <c r="I590" s="20"/>
     </row>
     <row r="591">
-      <c r="A591" s="23"/>
-      <c r="I591" s="21"/>
+      <c r="A591" s="33"/>
+      <c r="I591" s="20"/>
     </row>
     <row r="592">
-      <c r="A592" s="23"/>
-      <c r="I592" s="21"/>
+      <c r="A592" s="33"/>
+      <c r="I592" s="20"/>
     </row>
     <row r="593">
-      <c r="A593" s="23"/>
-      <c r="I593" s="21"/>
+      <c r="A593" s="33"/>
+      <c r="I593" s="20"/>
     </row>
     <row r="594">
-      <c r="A594" s="23"/>
-      <c r="I594" s="21"/>
+      <c r="A594" s="33"/>
+      <c r="I594" s="20"/>
     </row>
     <row r="595">
-      <c r="A595" s="23"/>
-      <c r="I595" s="21"/>
+      <c r="A595" s="33"/>
+      <c r="I595" s="20"/>
     </row>
     <row r="596">
-      <c r="A596" s="23"/>
-      <c r="I596" s="21"/>
+      <c r="A596" s="33"/>
+      <c r="I596" s="20"/>
     </row>
     <row r="597">
-      <c r="A597" s="23"/>
-      <c r="I597" s="21"/>
+      <c r="A597" s="33"/>
+      <c r="I597" s="20"/>
     </row>
     <row r="598">
-      <c r="A598" s="23"/>
-      <c r="I598" s="21"/>
+      <c r="A598" s="33"/>
+      <c r="I598" s="20"/>
     </row>
     <row r="599">
-      <c r="A599" s="23"/>
-      <c r="I599" s="21"/>
+      <c r="A599" s="33"/>
+      <c r="I599" s="20"/>
     </row>
     <row r="600">
-      <c r="A600" s="23"/>
-      <c r="I600" s="21"/>
+      <c r="A600" s="33"/>
+      <c r="I600" s="20"/>
     </row>
     <row r="601">
-      <c r="A601" s="23"/>
-      <c r="I601" s="21"/>
+      <c r="A601" s="33"/>
+      <c r="I601" s="20"/>
     </row>
     <row r="602">
-      <c r="A602" s="23"/>
-      <c r="I602" s="21"/>
+      <c r="A602" s="33"/>
+      <c r="I602" s="20"/>
     </row>
     <row r="603">
-      <c r="A603" s="23"/>
-      <c r="I603" s="21"/>
+      <c r="A603" s="33"/>
+      <c r="I603" s="20"/>
     </row>
     <row r="604">
-      <c r="A604" s="23"/>
-      <c r="I604" s="21"/>
+      <c r="A604" s="33"/>
+      <c r="I604" s="20"/>
     </row>
     <row r="605">
-      <c r="A605" s="23"/>
-      <c r="I605" s="21"/>
+      <c r="A605" s="33"/>
+      <c r="I605" s="20"/>
     </row>
     <row r="606">
-      <c r="A606" s="23"/>
-      <c r="I606" s="21"/>
+      <c r="A606" s="33"/>
+      <c r="I606" s="20"/>
     </row>
     <row r="607">
-      <c r="A607" s="23"/>
-      <c r="I607" s="21"/>
+      <c r="A607" s="33"/>
+      <c r="I607" s="20"/>
     </row>
     <row r="608">
-      <c r="A608" s="23"/>
-      <c r="I608" s="21"/>
+      <c r="A608" s="33"/>
+      <c r="I608" s="20"/>
     </row>
     <row r="609">
-      <c r="A609" s="23"/>
-      <c r="I609" s="21"/>
+      <c r="A609" s="33"/>
+      <c r="I609" s="20"/>
     </row>
     <row r="610">
-      <c r="A610" s="23"/>
-      <c r="I610" s="21"/>
+      <c r="A610" s="33"/>
+      <c r="I610" s="20"/>
     </row>
     <row r="611">
-      <c r="A611" s="23"/>
-      <c r="I611" s="21"/>
+      <c r="A611" s="33"/>
+      <c r="I611" s="20"/>
     </row>
     <row r="612">
-      <c r="A612" s="23"/>
-      <c r="I612" s="21"/>
+      <c r="A612" s="33"/>
+      <c r="I612" s="20"/>
     </row>
     <row r="613">
-      <c r="A613" s="23"/>
-      <c r="I613" s="21"/>
+      <c r="A613" s="33"/>
+      <c r="I613" s="20"/>
     </row>
     <row r="614">
-      <c r="A614" s="23"/>
-      <c r="I614" s="21"/>
+      <c r="A614" s="33"/>
+      <c r="I614" s="20"/>
     </row>
     <row r="615">
-      <c r="A615" s="23"/>
-      <c r="I615" s="21"/>
+      <c r="A615" s="33"/>
+      <c r="I615" s="20"/>
     </row>
     <row r="616">
-      <c r="A616" s="23"/>
-      <c r="I616" s="21"/>
+      <c r="A616" s="33"/>
+      <c r="I616" s="20"/>
     </row>
     <row r="617">
-      <c r="A617" s="23"/>
-      <c r="I617" s="21"/>
+      <c r="A617" s="33"/>
+      <c r="I617" s="20"/>
     </row>
     <row r="618">
-      <c r="A618" s="23"/>
-      <c r="I618" s="21"/>
+      <c r="A618" s="33"/>
+      <c r="I618" s="20"/>
     </row>
     <row r="619">
-      <c r="A619" s="23"/>
-      <c r="I619" s="21"/>
+      <c r="A619" s="33"/>
+      <c r="I619" s="20"/>
     </row>
     <row r="620">
-      <c r="A620" s="23"/>
-      <c r="I620" s="21"/>
+      <c r="A620" s="33"/>
+      <c r="I620" s="20"/>
     </row>
     <row r="621">
-      <c r="A621" s="23"/>
-      <c r="I621" s="21"/>
+      <c r="A621" s="33"/>
+      <c r="I621" s="20"/>
     </row>
     <row r="622">
-      <c r="A622" s="23"/>
-      <c r="I622" s="21"/>
+      <c r="A622" s="33"/>
+      <c r="I622" s="20"/>
     </row>
     <row r="623">
-      <c r="A623" s="23"/>
-      <c r="I623" s="21"/>
+      <c r="A623" s="33"/>
+      <c r="I623" s="20"/>
     </row>
     <row r="624">
-      <c r="A624" s="23"/>
-      <c r="I624" s="21"/>
+      <c r="A624" s="33"/>
+      <c r="I624" s="20"/>
     </row>
     <row r="625">
-      <c r="A625" s="23"/>
-      <c r="I625" s="21"/>
+      <c r="A625" s="33"/>
+      <c r="I625" s="20"/>
     </row>
     <row r="626">
-      <c r="A626" s="23"/>
-      <c r="I626" s="21"/>
+      <c r="A626" s="33"/>
+      <c r="I626" s="20"/>
     </row>
     <row r="627">
-      <c r="A627" s="23"/>
-      <c r="I627" s="21"/>
+      <c r="A627" s="33"/>
+      <c r="I627" s="20"/>
     </row>
     <row r="628">
-      <c r="A628" s="23"/>
-      <c r="I628" s="21"/>
+      <c r="A628" s="33"/>
+      <c r="I628" s="20"/>
     </row>
     <row r="629">
-      <c r="A629" s="23"/>
-      <c r="I629" s="21"/>
+      <c r="A629" s="33"/>
+      <c r="I629" s="20"/>
     </row>
     <row r="630">
-      <c r="A630" s="23"/>
-      <c r="I630" s="21"/>
+      <c r="A630" s="33"/>
+      <c r="I630" s="20"/>
     </row>
     <row r="631">
-      <c r="A631" s="23"/>
-      <c r="I631" s="21"/>
+      <c r="A631" s="33"/>
+      <c r="I631" s="20"/>
     </row>
     <row r="632">
-      <c r="A632" s="23"/>
-      <c r="I632" s="21"/>
+      <c r="A632" s="33"/>
+      <c r="I632" s="20"/>
     </row>
     <row r="633">
-      <c r="A633" s="23"/>
-      <c r="I633" s="21"/>
+      <c r="A633" s="33"/>
+      <c r="I633" s="20"/>
     </row>
     <row r="634">
-      <c r="A634" s="23"/>
-      <c r="I634" s="21"/>
+      <c r="A634" s="33"/>
+      <c r="I634" s="20"/>
     </row>
     <row r="635">
-      <c r="A635" s="23"/>
-      <c r="I635" s="21"/>
+      <c r="A635" s="33"/>
+      <c r="I635" s="20"/>
     </row>
     <row r="636">
-      <c r="A636" s="23"/>
-      <c r="I636" s="21"/>
+      <c r="A636" s="33"/>
+      <c r="I636" s="20"/>
     </row>
     <row r="637">
-      <c r="A637" s="23"/>
-      <c r="I637" s="21"/>
+      <c r="A637" s="33"/>
+      <c r="I637" s="20"/>
     </row>
     <row r="638">
-      <c r="A638" s="23"/>
-      <c r="I638" s="21"/>
+      <c r="A638" s="33"/>
+      <c r="I638" s="20"/>
     </row>
     <row r="639">
-      <c r="A639" s="23"/>
-      <c r="I639" s="21"/>
+      <c r="A639" s="33"/>
+      <c r="I639" s="20"/>
     </row>
     <row r="640">
-      <c r="A640" s="23"/>
-      <c r="I640" s="21"/>
+      <c r="A640" s="33"/>
+      <c r="I640" s="20"/>
     </row>
     <row r="641">
-      <c r="A641" s="23"/>
-      <c r="I641" s="21"/>
+      <c r="A641" s="33"/>
+      <c r="I641" s="20"/>
     </row>
     <row r="642">
-      <c r="A642" s="23"/>
-      <c r="I642" s="21"/>
+      <c r="A642" s="33"/>
+      <c r="I642" s="20"/>
     </row>
     <row r="643">
-      <c r="A643" s="23"/>
-      <c r="I643" s="21"/>
+      <c r="A643" s="33"/>
+      <c r="I643" s="20"/>
     </row>
     <row r="644">
-      <c r="A644" s="23"/>
-      <c r="I644" s="21"/>
+      <c r="A644" s="33"/>
+      <c r="I644" s="20"/>
     </row>
     <row r="645">
-      <c r="A645" s="23"/>
-      <c r="I645" s="21"/>
+      <c r="A645" s="33"/>
+      <c r="I645" s="20"/>
     </row>
     <row r="646">
-      <c r="A646" s="23"/>
-      <c r="I646" s="21"/>
+      <c r="A646" s="33"/>
+      <c r="I646" s="20"/>
     </row>
     <row r="647">
-      <c r="A647" s="23"/>
-      <c r="I647" s="21"/>
+      <c r="A647" s="33"/>
+      <c r="I647" s="20"/>
     </row>
     <row r="648">
-      <c r="A648" s="23"/>
-      <c r="I648" s="21"/>
+      <c r="A648" s="33"/>
+      <c r="I648" s="20"/>
     </row>
     <row r="649">
-      <c r="A649" s="23"/>
-      <c r="I649" s="21"/>
+      <c r="A649" s="33"/>
+      <c r="I649" s="20"/>
     </row>
     <row r="650">
-      <c r="A650" s="23"/>
-      <c r="I650" s="21"/>
+      <c r="A650" s="33"/>
+      <c r="I650" s="20"/>
     </row>
     <row r="651">
-      <c r="A651" s="23"/>
-      <c r="I651" s="21"/>
+      <c r="A651" s="33"/>
+      <c r="I651" s="20"/>
     </row>
     <row r="652">
-      <c r="A652" s="23"/>
-      <c r="I652" s="21"/>
+      <c r="A652" s="33"/>
+      <c r="I652" s="20"/>
     </row>
     <row r="653">
-      <c r="A653" s="23"/>
-      <c r="I653" s="21"/>
+      <c r="A653" s="33"/>
+      <c r="I653" s="20"/>
     </row>
     <row r="654">
-      <c r="A654" s="23"/>
-      <c r="I654" s="21"/>
+      <c r="A654" s="33"/>
+      <c r="I654" s="20"/>
     </row>
     <row r="655">
-      <c r="A655" s="23"/>
-      <c r="I655" s="21"/>
+      <c r="A655" s="33"/>
+      <c r="I655" s="20"/>
     </row>
     <row r="656">
-      <c r="A656" s="23"/>
-      <c r="I656" s="21"/>
+      <c r="A656" s="33"/>
+      <c r="I656" s="20"/>
     </row>
     <row r="657">
-      <c r="A657" s="23"/>
-      <c r="I657" s="21"/>
+      <c r="A657" s="33"/>
+      <c r="I657" s="20"/>
     </row>
     <row r="658">
-      <c r="A658" s="23"/>
-      <c r="I658" s="21"/>
+      <c r="A658" s="33"/>
+      <c r="I658" s="20"/>
     </row>
     <row r="659">
-      <c r="A659" s="23"/>
-      <c r="I659" s="21"/>
+      <c r="A659" s="33"/>
+      <c r="I659" s="20"/>
     </row>
     <row r="660">
-      <c r="A660" s="23"/>
-      <c r="I660" s="21"/>
+      <c r="A660" s="33"/>
+      <c r="I660" s="20"/>
     </row>
     <row r="661">
-      <c r="A661" s="23"/>
-      <c r="I661" s="21"/>
+      <c r="A661" s="33"/>
+      <c r="I661" s="20"/>
     </row>
     <row r="662">
-      <c r="A662" s="23"/>
-      <c r="I662" s="21"/>
+      <c r="A662" s="33"/>
+      <c r="I662" s="20"/>
     </row>
     <row r="663">
-      <c r="A663" s="23"/>
-      <c r="I663" s="21"/>
+      <c r="A663" s="33"/>
+      <c r="I663" s="20"/>
     </row>
     <row r="664">
-      <c r="A664" s="23"/>
-      <c r="I664" s="21"/>
+      <c r="A664" s="33"/>
+      <c r="I664" s="20"/>
     </row>
     <row r="665">
-      <c r="A665" s="23"/>
-      <c r="I665" s="21"/>
+      <c r="A665" s="33"/>
+      <c r="I665" s="20"/>
     </row>
     <row r="666">
-      <c r="A666" s="23"/>
-      <c r="I666" s="21"/>
+      <c r="A666" s="33"/>
+      <c r="I666" s="20"/>
     </row>
     <row r="667">
-      <c r="A667" s="23"/>
-      <c r="I667" s="21"/>
+      <c r="A667" s="33"/>
+      <c r="I667" s="20"/>
     </row>
     <row r="668">
-      <c r="A668" s="23"/>
-      <c r="I668" s="21"/>
+      <c r="A668" s="33"/>
+      <c r="I668" s="20"/>
     </row>
     <row r="669">
-      <c r="A669" s="23"/>
-      <c r="I669" s="21"/>
+      <c r="A669" s="33"/>
+      <c r="I669" s="20"/>
     </row>
     <row r="670">
-      <c r="A670" s="23"/>
-      <c r="I670" s="21"/>
+      <c r="A670" s="33"/>
+      <c r="I670" s="20"/>
     </row>
     <row r="671">
-      <c r="A671" s="23"/>
-      <c r="I671" s="21"/>
+      <c r="A671" s="33"/>
+      <c r="I671" s="20"/>
     </row>
     <row r="672">
-      <c r="A672" s="23"/>
-      <c r="I672" s="21"/>
+      <c r="A672" s="33"/>
+      <c r="I672" s="20"/>
     </row>
     <row r="673">
-      <c r="A673" s="23"/>
-      <c r="I673" s="21"/>
+      <c r="A673" s="33"/>
+      <c r="I673" s="20"/>
     </row>
     <row r="674">
-      <c r="A674" s="23"/>
-      <c r="I674" s="21"/>
+      <c r="A674" s="33"/>
+      <c r="I674" s="20"/>
     </row>
     <row r="675">
-      <c r="A675" s="23"/>
-      <c r="I675" s="21"/>
+      <c r="A675" s="33"/>
+      <c r="I675" s="20"/>
     </row>
     <row r="676">
-      <c r="A676" s="23"/>
-      <c r="I676" s="21"/>
+      <c r="A676" s="33"/>
+      <c r="I676" s="20"/>
     </row>
     <row r="677">
-      <c r="A677" s="23"/>
-      <c r="I677" s="21"/>
+      <c r="A677" s="33"/>
+      <c r="I677" s="20"/>
     </row>
     <row r="678">
-      <c r="A678" s="23"/>
-      <c r="I678" s="21"/>
+      <c r="A678" s="33"/>
+      <c r="I678" s="20"/>
     </row>
     <row r="679">
-      <c r="A679" s="23"/>
-      <c r="I679" s="21"/>
+      <c r="A679" s="33"/>
+      <c r="I679" s="20"/>
     </row>
     <row r="680">
-      <c r="A680" s="23"/>
-      <c r="I680" s="21"/>
+      <c r="A680" s="33"/>
+      <c r="I680" s="20"/>
     </row>
     <row r="681">
-      <c r="A681" s="23"/>
-      <c r="I681" s="21"/>
+      <c r="A681" s="33"/>
+      <c r="I681" s="20"/>
     </row>
     <row r="682">
-      <c r="A682" s="23"/>
-      <c r="I682" s="21"/>
+      <c r="A682" s="33"/>
+      <c r="I682" s="20"/>
     </row>
     <row r="683">
-      <c r="A683" s="23"/>
-      <c r="I683" s="21"/>
+      <c r="A683" s="33"/>
+      <c r="I683" s="20"/>
     </row>
     <row r="684">
-      <c r="A684" s="23"/>
-      <c r="I684" s="21"/>
+      <c r="A684" s="33"/>
+      <c r="I684" s="20"/>
     </row>
     <row r="685">
-      <c r="A685" s="23"/>
-      <c r="I685" s="21"/>
+      <c r="A685" s="33"/>
+      <c r="I685" s="20"/>
     </row>
     <row r="686">
-      <c r="A686" s="23"/>
-      <c r="I686" s="21"/>
+      <c r="A686" s="33"/>
+      <c r="I686" s="20"/>
     </row>
     <row r="687">
-      <c r="A687" s="23"/>
-      <c r="I687" s="21"/>
+      <c r="A687" s="33"/>
+      <c r="I687" s="20"/>
     </row>
     <row r="688">
-      <c r="A688" s="23"/>
-      <c r="I688" s="21"/>
+      <c r="A688" s="33"/>
+      <c r="I688" s="20"/>
     </row>
     <row r="689">
-      <c r="A689" s="23"/>
-      <c r="I689" s="21"/>
+      <c r="A689" s="33"/>
+      <c r="I689" s="20"/>
     </row>
     <row r="690">
-      <c r="A690" s="23"/>
-      <c r="I690" s="21"/>
+      <c r="A690" s="33"/>
+      <c r="I690" s="20"/>
     </row>
     <row r="691">
-      <c r="A691" s="23"/>
-      <c r="I691" s="21"/>
+      <c r="A691" s="33"/>
+      <c r="I691" s="20"/>
     </row>
     <row r="692">
-      <c r="A692" s="23"/>
-      <c r="I692" s="21"/>
+      <c r="A692" s="33"/>
+      <c r="I692" s="20"/>
     </row>
     <row r="693">
-      <c r="A693" s="23"/>
-      <c r="I693" s="21"/>
+      <c r="A693" s="33"/>
+      <c r="I693" s="20"/>
     </row>
     <row r="694">
-      <c r="A694" s="23"/>
-      <c r="I694" s="21"/>
+      <c r="A694" s="33"/>
+      <c r="I694" s="20"/>
     </row>
     <row r="695">
-      <c r="A695" s="23"/>
-      <c r="I695" s="21"/>
+      <c r="A695" s="33"/>
+      <c r="I695" s="20"/>
     </row>
     <row r="696">
-      <c r="A696" s="23"/>
-      <c r="I696" s="21"/>
+      <c r="A696" s="33"/>
+      <c r="I696" s="20"/>
     </row>
     <row r="697">
-      <c r="A697" s="23"/>
-      <c r="I697" s="21"/>
+      <c r="A697" s="33"/>
+      <c r="I697" s="20"/>
     </row>
     <row r="698">
-      <c r="A698" s="23"/>
-      <c r="I698" s="21"/>
+      <c r="A698" s="33"/>
+      <c r="I698" s="20"/>
     </row>
     <row r="699">
-      <c r="A699" s="23"/>
-      <c r="I699" s="21"/>
+      <c r="A699" s="33"/>
+      <c r="I699" s="20"/>
     </row>
     <row r="700">
-      <c r="A700" s="23"/>
-      <c r="I700" s="21"/>
+      <c r="A700" s="33"/>
+      <c r="I700" s="20"/>
     </row>
     <row r="701">
-      <c r="A701" s="23"/>
-      <c r="I701" s="21"/>
+      <c r="A701" s="33"/>
+      <c r="I701" s="20"/>
     </row>
     <row r="702">
-      <c r="A702" s="23"/>
-      <c r="I702" s="21"/>
+      <c r="A702" s="33"/>
+      <c r="I702" s="20"/>
     </row>
     <row r="703">
-      <c r="A703" s="23"/>
-      <c r="I703" s="21"/>
+      <c r="A703" s="33"/>
+      <c r="I703" s="20"/>
     </row>
     <row r="704">
-      <c r="A704" s="23"/>
-      <c r="I704" s="21"/>
+      <c r="A704" s="33"/>
+      <c r="I704" s="20"/>
     </row>
     <row r="705">
-      <c r="A705" s="23"/>
-      <c r="I705" s="21"/>
+      <c r="A705" s="33"/>
+      <c r="I705" s="20"/>
     </row>
     <row r="706">
-      <c r="A706" s="23"/>
-      <c r="I706" s="21"/>
+      <c r="A706" s="33"/>
+      <c r="I706" s="20"/>
     </row>
     <row r="707">
-      <c r="A707" s="23"/>
-      <c r="I707" s="21"/>
+      <c r="A707" s="33"/>
+      <c r="I707" s="20"/>
     </row>
     <row r="708">
-      <c r="A708" s="23"/>
-      <c r="I708" s="21"/>
+      <c r="A708" s="33"/>
+      <c r="I708" s="20"/>
     </row>
     <row r="709">
-      <c r="A709" s="23"/>
-      <c r="I709" s="21"/>
+      <c r="A709" s="33"/>
+      <c r="I709" s="20"/>
     </row>
     <row r="710">
-      <c r="A710" s="23"/>
-      <c r="I710" s="21"/>
+      <c r="A710" s="33"/>
+      <c r="I710" s="20"/>
     </row>
     <row r="711">
-      <c r="A711" s="23"/>
-      <c r="I711" s="21"/>
+      <c r="A711" s="33"/>
+      <c r="I711" s="20"/>
     </row>
     <row r="712">
-      <c r="A712" s="23"/>
-      <c r="I712" s="21"/>
+      <c r="A712" s="33"/>
+      <c r="I712" s="20"/>
     </row>
     <row r="713">
-      <c r="A713" s="23"/>
-      <c r="I713" s="21"/>
+      <c r="A713" s="33"/>
+      <c r="I713" s="20"/>
     </row>
     <row r="714">
-      <c r="A714" s="23"/>
-      <c r="I714" s="21"/>
+      <c r="A714" s="33"/>
+      <c r="I714" s="20"/>
     </row>
     <row r="715">
-      <c r="A715" s="23"/>
-      <c r="I715" s="21"/>
+      <c r="A715" s="33"/>
+      <c r="I715" s="20"/>
     </row>
     <row r="716">
-      <c r="A716" s="23"/>
-      <c r="I716" s="21"/>
+      <c r="A716" s="33"/>
+      <c r="I716" s="20"/>
     </row>
     <row r="717">
-      <c r="A717" s="23"/>
-      <c r="I717" s="21"/>
+      <c r="A717" s="33"/>
+      <c r="I717" s="20"/>
     </row>
     <row r="718">
-      <c r="A718" s="23"/>
-      <c r="I718" s="21"/>
+      <c r="A718" s="33"/>
+      <c r="I718" s="20"/>
     </row>
     <row r="719">
-      <c r="A719" s="23"/>
-      <c r="I719" s="21"/>
+      <c r="A719" s="33"/>
+      <c r="I719" s="20"/>
     </row>
     <row r="720">
-      <c r="A720" s="23"/>
-      <c r="I720" s="21"/>
+      <c r="A720" s="33"/>
+      <c r="I720" s="20"/>
     </row>
     <row r="721">
-      <c r="A721" s="23"/>
-      <c r="I721" s="21"/>
+      <c r="A721" s="33"/>
+      <c r="I721" s="20"/>
     </row>
     <row r="722">
-      <c r="A722" s="23"/>
-      <c r="I722" s="21"/>
+      <c r="A722" s="33"/>
+      <c r="I722" s="20"/>
     </row>
     <row r="723">
-      <c r="A723" s="23"/>
-      <c r="I723" s="21"/>
+      <c r="A723" s="33"/>
+      <c r="I723" s="20"/>
     </row>
     <row r="724">
-      <c r="A724" s="23"/>
-      <c r="I724" s="21"/>
+      <c r="A724" s="33"/>
+      <c r="I724" s="20"/>
     </row>
     <row r="725">
-      <c r="A725" s="23"/>
-      <c r="I725" s="21"/>
+      <c r="A725" s="33"/>
+      <c r="I725" s="20"/>
     </row>
     <row r="726">
-      <c r="A726" s="23"/>
-      <c r="I726" s="21"/>
+      <c r="A726" s="33"/>
+      <c r="I726" s="20"/>
     </row>
     <row r="727">
-      <c r="A727" s="23"/>
-      <c r="I727" s="21"/>
+      <c r="A727" s="33"/>
+      <c r="I727" s="20"/>
     </row>
     <row r="728">
-      <c r="A728" s="23"/>
-      <c r="I728" s="21"/>
+      <c r="A728" s="33"/>
+      <c r="I728" s="20"/>
     </row>
     <row r="729">
-      <c r="A729" s="23"/>
-      <c r="I729" s="21"/>
+      <c r="A729" s="33"/>
+      <c r="I729" s="20"/>
     </row>
     <row r="730">
-      <c r="A730" s="23"/>
-      <c r="I730" s="21"/>
+      <c r="A730" s="33"/>
+      <c r="I730" s="20"/>
     </row>
     <row r="731">
-      <c r="A731" s="23"/>
-      <c r="I731" s="21"/>
+      <c r="A731" s="33"/>
+      <c r="I731" s="20"/>
     </row>
     <row r="732">
-      <c r="A732" s="23"/>
-      <c r="I732" s="21"/>
+      <c r="A732" s="33"/>
+      <c r="I732" s="20"/>
     </row>
     <row r="733">
-      <c r="A733" s="23"/>
-      <c r="I733" s="21"/>
+      <c r="A733" s="33"/>
+      <c r="I733" s="20"/>
     </row>
     <row r="734">
-      <c r="A734" s="23"/>
-      <c r="I734" s="21"/>
+      <c r="A734" s="33"/>
+      <c r="I734" s="20"/>
     </row>
     <row r="735">
-      <c r="A735" s="23"/>
-      <c r="I735" s="21"/>
+      <c r="A735" s="33"/>
+      <c r="I735" s="20"/>
     </row>
     <row r="736">
-      <c r="A736" s="23"/>
-      <c r="I736" s="21"/>
+      <c r="A736" s="33"/>
+      <c r="I736" s="20"/>
     </row>
     <row r="737">
-      <c r="A737" s="23"/>
-      <c r="I737" s="21"/>
+      <c r="A737" s="33"/>
+      <c r="I737" s="20"/>
     </row>
     <row r="738">
-      <c r="A738" s="23"/>
-      <c r="I738" s="21"/>
+      <c r="A738" s="33"/>
+      <c r="I738" s="20"/>
     </row>
     <row r="739">
-      <c r="A739" s="23"/>
-      <c r="I739" s="21"/>
+      <c r="A739" s="33"/>
+      <c r="I739" s="20"/>
     </row>
     <row r="740">
-      <c r="A740" s="23"/>
-      <c r="I740" s="21"/>
+      <c r="A740" s="33"/>
+      <c r="I740" s="20"/>
     </row>
     <row r="741">
-      <c r="A741" s="23"/>
-      <c r="I741" s="21"/>
+      <c r="A741" s="33"/>
+      <c r="I741" s="20"/>
     </row>
     <row r="742">
-      <c r="A742" s="23"/>
-      <c r="I742" s="21"/>
+      <c r="A742" s="33"/>
+      <c r="I742" s="20"/>
     </row>
     <row r="743">
-      <c r="A743" s="23"/>
-      <c r="I743" s="21"/>
+      <c r="A743" s="33"/>
+      <c r="I743" s="20"/>
     </row>
     <row r="744">
-      <c r="A744" s="23"/>
-      <c r="I744" s="21"/>
+      <c r="A744" s="33"/>
+      <c r="I744" s="20"/>
     </row>
     <row r="745">
-      <c r="A745" s="23"/>
-      <c r="I745" s="21"/>
+      <c r="A745" s="33"/>
+      <c r="I745" s="20"/>
     </row>
     <row r="746">
-      <c r="A746" s="23"/>
-      <c r="I746" s="21"/>
+      <c r="A746" s="33"/>
+      <c r="I746" s="20"/>
     </row>
     <row r="747">
-      <c r="A747" s="23"/>
-      <c r="I747" s="21"/>
+      <c r="A747" s="33"/>
+      <c r="I747" s="20"/>
     </row>
     <row r="748">
-      <c r="A748" s="23"/>
-      <c r="I748" s="21"/>
+      <c r="A748" s="33"/>
+      <c r="I748" s="20"/>
     </row>
     <row r="749">
-      <c r="A749" s="23"/>
-      <c r="I749" s="21"/>
+      <c r="A749" s="33"/>
+      <c r="I749" s="20"/>
     </row>
     <row r="750">
-      <c r="A750" s="23"/>
-      <c r="I750" s="21"/>
+      <c r="A750" s="33"/>
+      <c r="I750" s="20"/>
     </row>
     <row r="751">
-      <c r="A751" s="23"/>
-      <c r="I751" s="21"/>
+      <c r="A751" s="33"/>
+      <c r="I751" s="20"/>
     </row>
     <row r="752">
-      <c r="A752" s="23"/>
-      <c r="I752" s="21"/>
+      <c r="A752" s="33"/>
+      <c r="I752" s="20"/>
     </row>
     <row r="753">
-      <c r="A753" s="23"/>
-      <c r="I753" s="21"/>
+      <c r="A753" s="33"/>
+      <c r="I753" s="20"/>
     </row>
     <row r="754">
-      <c r="A754" s="23"/>
-      <c r="I754" s="21"/>
+      <c r="A754" s="33"/>
+      <c r="I754" s="20"/>
     </row>
     <row r="755">
-      <c r="A755" s="23"/>
-      <c r="I755" s="21"/>
+      <c r="A755" s="33"/>
+      <c r="I755" s="20"/>
     </row>
     <row r="756">
-      <c r="A756" s="23"/>
-      <c r="I756" s="21"/>
+      <c r="A756" s="33"/>
+      <c r="I756" s="20"/>
     </row>
     <row r="757">
-      <c r="A757" s="23"/>
-      <c r="I757" s="21"/>
+      <c r="A757" s="33"/>
+      <c r="I757" s="20"/>
     </row>
     <row r="758">
-      <c r="A758" s="23"/>
-      <c r="I758" s="21"/>
+      <c r="A758" s="33"/>
+      <c r="I758" s="20"/>
     </row>
     <row r="759">
-      <c r="A759" s="23"/>
-      <c r="I759" s="21"/>
+      <c r="A759" s="33"/>
+      <c r="I759" s="20"/>
     </row>
     <row r="760">
-      <c r="A760" s="23"/>
-      <c r="I760" s="21"/>
+      <c r="A760" s="33"/>
+      <c r="I760" s="20"/>
     </row>
     <row r="761">
-      <c r="A761" s="23"/>
-      <c r="I761" s="21"/>
+      <c r="A761" s="33"/>
+      <c r="I761" s="20"/>
     </row>
     <row r="762">
-      <c r="A762" s="23"/>
-      <c r="I762" s="21"/>
+      <c r="A762" s="33"/>
+      <c r="I762" s="20"/>
     </row>
     <row r="763">
-      <c r="A763" s="23"/>
-      <c r="I763" s="21"/>
+      <c r="A763" s="33"/>
+      <c r="I763" s="20"/>
     </row>
     <row r="764">
-      <c r="A764" s="23"/>
-      <c r="I764" s="21"/>
+      <c r="A764" s="33"/>
+      <c r="I764" s="20"/>
     </row>
     <row r="765">
-      <c r="A765" s="23"/>
-      <c r="I765" s="21"/>
+      <c r="A765" s="33"/>
+      <c r="I765" s="20"/>
     </row>
     <row r="766">
-      <c r="A766" s="23"/>
-      <c r="I766" s="21"/>
+      <c r="A766" s="33"/>
+      <c r="I766" s="20"/>
     </row>
     <row r="767">
-      <c r="A767" s="23"/>
-      <c r="I767" s="21"/>
+      <c r="A767" s="33"/>
+      <c r="I767" s="20"/>
     </row>
     <row r="768">
-      <c r="A768" s="23"/>
-      <c r="I768" s="21"/>
+      <c r="A768" s="33"/>
+      <c r="I768" s="20"/>
     </row>
     <row r="769">
-      <c r="A769" s="23"/>
-      <c r="I769" s="21"/>
+      <c r="A769" s="33"/>
+      <c r="I769" s="20"/>
     </row>
     <row r="770">
-      <c r="A770" s="23"/>
-      <c r="I770" s="21"/>
+      <c r="A770" s="33"/>
+      <c r="I770" s="20"/>
     </row>
     <row r="771">
-      <c r="A771" s="23"/>
-      <c r="I771" s="21"/>
+      <c r="A771" s="33"/>
+      <c r="I771" s="20"/>
     </row>
     <row r="772">
-      <c r="A772" s="23"/>
-      <c r="I772" s="21"/>
+      <c r="A772" s="33"/>
+      <c r="I772" s="20"/>
     </row>
     <row r="773">
-      <c r="A773" s="23"/>
-      <c r="I773" s="21"/>
+      <c r="A773" s="33"/>
+      <c r="I773" s="20"/>
     </row>
     <row r="774">
-      <c r="A774" s="23"/>
-      <c r="I774" s="21"/>
+      <c r="A774" s="33"/>
+      <c r="I774" s="20"/>
     </row>
     <row r="775">
-      <c r="A775" s="23"/>
-      <c r="I775" s="21"/>
+      <c r="A775" s="33"/>
+      <c r="I775" s="20"/>
     </row>
     <row r="776">
-      <c r="A776" s="23"/>
-      <c r="I776" s="21"/>
+      <c r="A776" s="33"/>
+      <c r="I776" s="20"/>
     </row>
     <row r="777">
-      <c r="A777" s="23"/>
-      <c r="I777" s="21"/>
+      <c r="A777" s="33"/>
+      <c r="I777" s="20"/>
     </row>
     <row r="778">
-      <c r="A778" s="23"/>
-      <c r="I778" s="21"/>
+      <c r="A778" s="33"/>
+      <c r="I778" s="20"/>
     </row>
     <row r="779">
-      <c r="A779" s="23"/>
-      <c r="I779" s="21"/>
+      <c r="A779" s="33"/>
+      <c r="I779" s="20"/>
     </row>
     <row r="780">
-      <c r="A780" s="23"/>
-      <c r="I780" s="21"/>
+      <c r="A780" s="33"/>
+      <c r="I780" s="20"/>
     </row>
     <row r="781">
-      <c r="A781" s="23"/>
-      <c r="I781" s="21"/>
+      <c r="A781" s="33"/>
+      <c r="I781" s="20"/>
     </row>
     <row r="782">
-      <c r="A782" s="23"/>
-      <c r="I782" s="21"/>
+      <c r="A782" s="33"/>
+      <c r="I782" s="20"/>
     </row>
     <row r="783">
-      <c r="A783" s="23"/>
-      <c r="I783" s="21"/>
+      <c r="A783" s="33"/>
+      <c r="I783" s="20"/>
     </row>
     <row r="784">
-      <c r="A784" s="23"/>
-      <c r="I784" s="21"/>
+      <c r="A784" s="33"/>
+      <c r="I784" s="20"/>
     </row>
     <row r="785">
-      <c r="A785" s="23"/>
-      <c r="I785" s="21"/>
+      <c r="A785" s="33"/>
+      <c r="I785" s="20"/>
     </row>
     <row r="786">
-      <c r="A786" s="23"/>
-      <c r="I786" s="21"/>
+      <c r="A786" s="33"/>
+      <c r="I786" s="20"/>
     </row>
     <row r="787">
-      <c r="A787" s="23"/>
-      <c r="I787" s="21"/>
+      <c r="A787" s="33"/>
+      <c r="I787" s="20"/>
     </row>
     <row r="788">
-      <c r="A788" s="23"/>
-      <c r="I788" s="21"/>
+      <c r="A788" s="33"/>
+      <c r="I788" s="20"/>
     </row>
     <row r="789">
-      <c r="A789" s="23"/>
-      <c r="I789" s="21"/>
+      <c r="A789" s="33"/>
+      <c r="I789" s="20"/>
     </row>
     <row r="790">
-      <c r="A790" s="23"/>
-      <c r="I790" s="21"/>
+      <c r="A790" s="33"/>
+      <c r="I790" s="20"/>
     </row>
     <row r="791">
-      <c r="A791" s="23"/>
-      <c r="I791" s="21"/>
+      <c r="A791" s="33"/>
+      <c r="I791" s="20"/>
     </row>
     <row r="792">
-      <c r="A792" s="23"/>
-      <c r="I792" s="21"/>
+      <c r="A792" s="33"/>
+      <c r="I792" s="20"/>
     </row>
     <row r="793">
-      <c r="A793" s="23"/>
-      <c r="I793" s="21"/>
+      <c r="A793" s="33"/>
+      <c r="I793" s="20"/>
     </row>
     <row r="794">
-      <c r="A794" s="23"/>
-      <c r="I794" s="21"/>
+      <c r="A794" s="33"/>
+      <c r="I794" s="20"/>
     </row>
     <row r="795">
-      <c r="A795" s="23"/>
-      <c r="I795" s="21"/>
+      <c r="A795" s="33"/>
+      <c r="I795" s="20"/>
     </row>
     <row r="796">
-      <c r="A796" s="23"/>
-      <c r="I796" s="21"/>
+      <c r="A796" s="33"/>
+      <c r="I796" s="20"/>
     </row>
     <row r="797">
-      <c r="A797" s="23"/>
-      <c r="I797" s="21"/>
+      <c r="A797" s="33"/>
+      <c r="I797" s="20"/>
     </row>
     <row r="798">
-      <c r="A798" s="23"/>
-      <c r="I798" s="21"/>
+      <c r="A798" s="33"/>
+      <c r="I798" s="20"/>
     </row>
     <row r="799">
-      <c r="A799" s="23"/>
-      <c r="I799" s="21"/>
+      <c r="A799" s="33"/>
+      <c r="I799" s="20"/>
     </row>
     <row r="800">
-      <c r="A800" s="23"/>
-      <c r="I800" s="21"/>
+      <c r="A800" s="33"/>
+      <c r="I800" s="20"/>
     </row>
     <row r="801">
-      <c r="A801" s="23"/>
-      <c r="I801" s="21"/>
+      <c r="A801" s="33"/>
+      <c r="I801" s="20"/>
     </row>
     <row r="802">
-      <c r="A802" s="23"/>
-      <c r="I802" s="21"/>
+      <c r="A802" s="33"/>
+      <c r="I802" s="20"/>
     </row>
     <row r="803">
-      <c r="A803" s="23"/>
-      <c r="I803" s="21"/>
+      <c r="A803" s="33"/>
+      <c r="I803" s="20"/>
     </row>
     <row r="804">
-      <c r="A804" s="23"/>
-      <c r="I804" s="21"/>
+      <c r="A804" s="33"/>
+      <c r="I804" s="20"/>
     </row>
     <row r="805">
-      <c r="A805" s="23"/>
-      <c r="I805" s="21"/>
+      <c r="A805" s="33"/>
+      <c r="I805" s="20"/>
     </row>
     <row r="806">
-      <c r="A806" s="23"/>
-      <c r="I806" s="21"/>
+      <c r="A806" s="33"/>
+      <c r="I806" s="20"/>
     </row>
     <row r="807">
-      <c r="A807" s="23"/>
-      <c r="I807" s="21"/>
+      <c r="A807" s="33"/>
+      <c r="I807" s="20"/>
     </row>
     <row r="808">
-      <c r="A808" s="23"/>
-      <c r="I808" s="21"/>
+      <c r="A808" s="33"/>
+      <c r="I808" s="20"/>
     </row>
     <row r="809">
-      <c r="A809" s="23"/>
-      <c r="I809" s="21"/>
+      <c r="A809" s="33"/>
+      <c r="I809" s="20"/>
     </row>
     <row r="810">
-      <c r="A810" s="23"/>
-      <c r="I810" s="21"/>
+      <c r="A810" s="33"/>
+      <c r="I810" s="20"/>
     </row>
     <row r="811">
-      <c r="A811" s="23"/>
-      <c r="I811" s="21"/>
+      <c r="A811" s="33"/>
+      <c r="I811" s="20"/>
     </row>
     <row r="812">
-      <c r="A812" s="23"/>
-      <c r="I812" s="21"/>
+      <c r="A812" s="33"/>
+      <c r="I812" s="20"/>
     </row>
     <row r="813">
-      <c r="A813" s="23"/>
-      <c r="I813" s="21"/>
+      <c r="A813" s="33"/>
+      <c r="I813" s="20"/>
     </row>
     <row r="814">
-      <c r="A814" s="23"/>
-      <c r="I814" s="21"/>
+      <c r="A814" s="33"/>
+      <c r="I814" s="20"/>
     </row>
     <row r="815">
-      <c r="A815" s="23"/>
-      <c r="I815" s="21"/>
+      <c r="A815" s="33"/>
+      <c r="I815" s="20"/>
     </row>
     <row r="816">
-      <c r="A816" s="23"/>
-      <c r="I816" s="21"/>
+      <c r="A816" s="33"/>
+      <c r="I816" s="20"/>
     </row>
     <row r="817">
-      <c r="A817" s="23"/>
-      <c r="I817" s="21"/>
+      <c r="A817" s="33"/>
+      <c r="I817" s="20"/>
     </row>
     <row r="818">
-      <c r="A818" s="23"/>
-      <c r="I818" s="21"/>
+      <c r="A818" s="33"/>
+      <c r="I818" s="20"/>
     </row>
     <row r="819">
-      <c r="A819" s="23"/>
-      <c r="I819" s="21"/>
+      <c r="A819" s="33"/>
+      <c r="I819" s="20"/>
     </row>
     <row r="820">
-      <c r="A820" s="23"/>
-      <c r="I820" s="21"/>
+      <c r="A820" s="33"/>
+      <c r="I820" s="20"/>
     </row>
     <row r="821">
-      <c r="A821" s="23"/>
-      <c r="I821" s="21"/>
+      <c r="A821" s="33"/>
+      <c r="I821" s="20"/>
     </row>
     <row r="822">
-      <c r="A822" s="23"/>
-      <c r="I822" s="21"/>
+      <c r="A822" s="33"/>
+      <c r="I822" s="20"/>
     </row>
     <row r="823">
-      <c r="A823" s="23"/>
-      <c r="I823" s="21"/>
+      <c r="A823" s="33"/>
+      <c r="I823" s="20"/>
     </row>
     <row r="824">
-      <c r="A824" s="23"/>
-      <c r="I824" s="21"/>
+      <c r="A824" s="33"/>
+      <c r="I824" s="20"/>
     </row>
     <row r="825">
-      <c r="A825" s="23"/>
-      <c r="I825" s="21"/>
+      <c r="A825" s="33"/>
+      <c r="I825" s="20"/>
     </row>
     <row r="826">
-      <c r="A826" s="23"/>
-      <c r="I826" s="21"/>
+      <c r="A826" s="33"/>
+      <c r="I826" s="20"/>
     </row>
     <row r="827">
-      <c r="A827" s="23"/>
-      <c r="I827" s="21"/>
+      <c r="A827" s="33"/>
+      <c r="I827" s="20"/>
     </row>
     <row r="828">
-      <c r="A828" s="23"/>
-      <c r="I828" s="21"/>
+      <c r="A828" s="33"/>
+      <c r="I828" s="20"/>
     </row>
     <row r="829">
-      <c r="A829" s="23"/>
-      <c r="I829" s="21"/>
+      <c r="A829" s="33"/>
+      <c r="I829" s="20"/>
     </row>
     <row r="830">
-      <c r="A830" s="23"/>
-      <c r="I830" s="21"/>
+      <c r="A830" s="33"/>
+      <c r="I830" s="20"/>
     </row>
     <row r="831">
-      <c r="A831" s="23"/>
-      <c r="I831" s="21"/>
+      <c r="A831" s="33"/>
+      <c r="I831" s="20"/>
     </row>
     <row r="832">
-      <c r="A832" s="23"/>
-      <c r="I832" s="21"/>
+      <c r="A832" s="33"/>
+      <c r="I832" s="20"/>
     </row>
     <row r="833">
-      <c r="A833" s="23"/>
-      <c r="I833" s="21"/>
+      <c r="A833" s="33"/>
+      <c r="I833" s="20"/>
     </row>
     <row r="834">
-      <c r="A834" s="23"/>
-      <c r="I834" s="21"/>
+      <c r="A834" s="33"/>
+      <c r="I834" s="20"/>
     </row>
     <row r="835">
-      <c r="A835" s="23"/>
-      <c r="I835" s="21"/>
+      <c r="A835" s="33"/>
+      <c r="I835" s="20"/>
     </row>
     <row r="836">
-      <c r="A836" s="23"/>
-      <c r="I836" s="21"/>
+      <c r="A836" s="33"/>
+      <c r="I836" s="20"/>
     </row>
     <row r="837">
-      <c r="A837" s="23"/>
-      <c r="I837" s="21"/>
+      <c r="A837" s="33"/>
+      <c r="I837" s="20"/>
     </row>
     <row r="838">
-      <c r="A838" s="23"/>
-      <c r="I838" s="21"/>
+      <c r="A838" s="33"/>
+      <c r="I838" s="20"/>
     </row>
     <row r="839">
-      <c r="A839" s="23"/>
-      <c r="I839" s="21"/>
+      <c r="A839" s="33"/>
+      <c r="I839" s="20"/>
     </row>
     <row r="840">
-      <c r="A840" s="23"/>
-      <c r="I840" s="21"/>
+      <c r="A840" s="33"/>
+      <c r="I840" s="20"/>
     </row>
     <row r="841">
-      <c r="A841" s="23"/>
-      <c r="I841" s="21"/>
+      <c r="A841" s="33"/>
+      <c r="I841" s="20"/>
     </row>
     <row r="842">
-      <c r="A842" s="23"/>
-      <c r="I842" s="21"/>
+      <c r="A842" s="33"/>
+      <c r="I842" s="20"/>
     </row>
     <row r="843">
-      <c r="A843" s="23"/>
-      <c r="I843" s="21"/>
+      <c r="A843" s="33"/>
+      <c r="I843" s="20"/>
     </row>
     <row r="844">
-      <c r="A844" s="23"/>
-      <c r="I844" s="21"/>
+      <c r="A844" s="33"/>
+      <c r="I844" s="20"/>
     </row>
     <row r="845">
-      <c r="A845" s="23"/>
-      <c r="I845" s="21"/>
+      <c r="A845" s="33"/>
+      <c r="I845" s="20"/>
     </row>
     <row r="846">
-      <c r="A846" s="23"/>
-      <c r="I846" s="21"/>
+      <c r="A846" s="33"/>
+      <c r="I846" s="20"/>
     </row>
     <row r="847">
-      <c r="A847" s="23"/>
-      <c r="I847" s="21"/>
+      <c r="A847" s="33"/>
+      <c r="I847" s="20"/>
     </row>
     <row r="848">
-      <c r="A848" s="23"/>
-      <c r="I848" s="21"/>
+      <c r="A848" s="33"/>
+      <c r="I848" s="20"/>
     </row>
     <row r="849">
-      <c r="A849" s="23"/>
-      <c r="I849" s="21"/>
+      <c r="A849" s="33"/>
+      <c r="I849" s="20"/>
     </row>
     <row r="850">
-      <c r="A850" s="23"/>
-      <c r="I850" s="21"/>
+      <c r="A850" s="33"/>
+      <c r="I850" s="20"/>
     </row>
     <row r="851">
-      <c r="A851" s="23"/>
-      <c r="I851" s="21"/>
+      <c r="A851" s="33"/>
+      <c r="I851" s="20"/>
     </row>
     <row r="852">
-      <c r="A852" s="23"/>
-      <c r="I852" s="21"/>
+      <c r="A852" s="33"/>
+      <c r="I852" s="20"/>
     </row>
     <row r="853">
-      <c r="A853" s="23"/>
-      <c r="I853" s="21"/>
+      <c r="A853" s="33"/>
+      <c r="I853" s="20"/>
     </row>
     <row r="854">
-      <c r="A854" s="23"/>
-      <c r="I854" s="21"/>
+      <c r="A854" s="33"/>
+      <c r="I854" s="20"/>
     </row>
     <row r="855">
-      <c r="A855" s="23"/>
-      <c r="I855" s="21"/>
+      <c r="A855" s="33"/>
+      <c r="I855" s="20"/>
     </row>
     <row r="856">
-      <c r="A856" s="23"/>
-      <c r="I856" s="21"/>
+      <c r="A856" s="33"/>
+      <c r="I856" s="20"/>
     </row>
     <row r="857">
-      <c r="A857" s="23"/>
-      <c r="I857" s="21"/>
+      <c r="A857" s="33"/>
+      <c r="I857" s="20"/>
     </row>
     <row r="858">
-      <c r="A858" s="23"/>
-      <c r="I858" s="21"/>
+      <c r="A858" s="33"/>
+      <c r="I858" s="20"/>
     </row>
     <row r="859">
-      <c r="A859" s="23"/>
-      <c r="I859" s="21"/>
+      <c r="A859" s="33"/>
+      <c r="I859" s="20"/>
     </row>
     <row r="860">
-      <c r="A860" s="23"/>
-      <c r="I860" s="21"/>
+      <c r="A860" s="33"/>
+      <c r="I860" s="20"/>
     </row>
     <row r="861">
-      <c r="A861" s="23"/>
-      <c r="I861" s="21"/>
+      <c r="A861" s="33"/>
+      <c r="I861" s="20"/>
     </row>
     <row r="862">
-      <c r="A862" s="23"/>
-      <c r="I862" s="21"/>
+      <c r="A862" s="33"/>
+      <c r="I862" s="20"/>
     </row>
     <row r="863">
-      <c r="A863" s="23"/>
-      <c r="I863" s="21"/>
+      <c r="A863" s="33"/>
+      <c r="I863" s="20"/>
     </row>
     <row r="864">
-      <c r="A864" s="23"/>
-      <c r="I864" s="21"/>
+      <c r="A864" s="33"/>
+      <c r="I864" s="20"/>
     </row>
     <row r="865">
-      <c r="A865" s="23"/>
-      <c r="I865" s="21"/>
+      <c r="A865" s="33"/>
+      <c r="I865" s="20"/>
     </row>
     <row r="866">
-      <c r="A866" s="23"/>
-      <c r="I866" s="21"/>
+      <c r="A866" s="33"/>
+      <c r="I866" s="20"/>
     </row>
     <row r="867">
-      <c r="A867" s="23"/>
-      <c r="I867" s="21"/>
+      <c r="A867" s="33"/>
+      <c r="I867" s="20"/>
     </row>
     <row r="868">
-      <c r="A868" s="23"/>
-      <c r="I868" s="21"/>
+      <c r="A868" s="33"/>
+      <c r="I868" s="20"/>
     </row>
     <row r="869">
-      <c r="A869" s="23"/>
-      <c r="I869" s="21"/>
+      <c r="A869" s="33"/>
+      <c r="I869" s="20"/>
     </row>
     <row r="870">
-      <c r="A870" s="23"/>
-      <c r="I870" s="21"/>
+      <c r="A870" s="33"/>
+      <c r="I870" s="20"/>
     </row>
     <row r="871">
-      <c r="A871" s="23"/>
-      <c r="I871" s="21"/>
+      <c r="A871" s="33"/>
+      <c r="I871" s="20"/>
     </row>
     <row r="872">
-      <c r="A872" s="23"/>
-      <c r="I872" s="21"/>
+      <c r="A872" s="33"/>
+      <c r="I872" s="20"/>
     </row>
     <row r="873">
-      <c r="A873" s="23"/>
-      <c r="I873" s="21"/>
+      <c r="A873" s="33"/>
+      <c r="I873" s="20"/>
     </row>
     <row r="874">
-      <c r="A874" s="23"/>
-      <c r="I874" s="21"/>
+      <c r="A874" s="33"/>
+      <c r="I874" s="20"/>
     </row>
     <row r="875">
-      <c r="A875" s="23"/>
-      <c r="I875" s="21"/>
+      <c r="A875" s="33"/>
+      <c r="I875" s="20"/>
     </row>
     <row r="876">
-      <c r="A876" s="23"/>
-      <c r="I876" s="21"/>
+      <c r="A876" s="33"/>
+      <c r="I876" s="20"/>
     </row>
     <row r="877">
-      <c r="A877" s="23"/>
-      <c r="I877" s="21"/>
+      <c r="A877" s="33"/>
+      <c r="I877" s="20"/>
     </row>
     <row r="878">
-      <c r="A878" s="23"/>
-      <c r="I878" s="21"/>
+      <c r="A878" s="33"/>
+      <c r="I878" s="20"/>
     </row>
     <row r="879">
-      <c r="A879" s="23"/>
-      <c r="I879" s="21"/>
+      <c r="A879" s="33"/>
+      <c r="I879" s="20"/>
     </row>
     <row r="880">
-      <c r="A880" s="23"/>
-      <c r="I880" s="21"/>
+      <c r="A880" s="33"/>
+      <c r="I880" s="20"/>
     </row>
     <row r="881">
-      <c r="A881" s="23"/>
-      <c r="I881" s="21"/>
+      <c r="A881" s="33"/>
+      <c r="I881" s="20"/>
     </row>
     <row r="882">
-      <c r="A882" s="23"/>
-      <c r="I882" s="21"/>
+      <c r="A882" s="33"/>
+      <c r="I882" s="20"/>
     </row>
     <row r="883">
-      <c r="A883" s="23"/>
-      <c r="I883" s="21"/>
+      <c r="A883" s="33"/>
+      <c r="I883" s="20"/>
     </row>
     <row r="884">
-      <c r="A884" s="23"/>
-      <c r="I884" s="21"/>
+      <c r="A884" s="33"/>
+      <c r="I884" s="20"/>
     </row>
     <row r="885">
-      <c r="A885" s="23"/>
-      <c r="I885" s="21"/>
+      <c r="A885" s="33"/>
+      <c r="I885" s="20"/>
     </row>
     <row r="886">
-      <c r="A886" s="23"/>
-      <c r="I886" s="21"/>
+      <c r="A886" s="33"/>
+      <c r="I886" s="20"/>
     </row>
     <row r="887">
-      <c r="A887" s="23"/>
-      <c r="I887" s="21"/>
+      <c r="A887" s="33"/>
+      <c r="I887" s="20"/>
     </row>
     <row r="888">
-      <c r="A888" s="23"/>
-      <c r="I888" s="21"/>
+      <c r="A888" s="33"/>
+      <c r="I888" s="20"/>
     </row>
     <row r="889">
-      <c r="A889" s="23"/>
-      <c r="I889" s="21"/>
+      <c r="A889" s="33"/>
+      <c r="I889" s="20"/>
     </row>
     <row r="890">
-      <c r="A890" s="23"/>
-      <c r="I890" s="21"/>
+      <c r="A890" s="33"/>
+      <c r="I890" s="20"/>
     </row>
     <row r="891">
-      <c r="A891" s="23"/>
-      <c r="I891" s="21"/>
+      <c r="A891" s="33"/>
+      <c r="I891" s="20"/>
     </row>
     <row r="892">
-      <c r="A892" s="23"/>
-      <c r="I892" s="21"/>
+      <c r="A892" s="33"/>
+      <c r="I892" s="20"/>
     </row>
     <row r="893">
-      <c r="A893" s="23"/>
-      <c r="I893" s="21"/>
+      <c r="A893" s="33"/>
+      <c r="I893" s="20"/>
     </row>
     <row r="894">
-      <c r="A894" s="23"/>
-      <c r="I894" s="21"/>
+      <c r="A894" s="33"/>
+      <c r="I894" s="20"/>
     </row>
     <row r="895">
-      <c r="A895" s="23"/>
-      <c r="I895" s="21"/>
+      <c r="A895" s="33"/>
+      <c r="I895" s="20"/>
     </row>
     <row r="896">
-      <c r="A896" s="23"/>
-      <c r="I896" s="21"/>
+      <c r="A896" s="33"/>
+      <c r="I896" s="20"/>
     </row>
     <row r="897">
-      <c r="A897" s="23"/>
-      <c r="I897" s="21"/>
+      <c r="A897" s="33"/>
+      <c r="I897" s="20"/>
     </row>
     <row r="898">
-      <c r="A898" s="23"/>
-      <c r="I898" s="21"/>
+      <c r="A898" s="33"/>
+      <c r="I898" s="20"/>
     </row>
     <row r="899">
-      <c r="A899" s="23"/>
-      <c r="I899" s="21"/>
+      <c r="A899" s="33"/>
+      <c r="I899" s="20"/>
     </row>
     <row r="900">
-      <c r="A900" s="23"/>
-      <c r="I900" s="21"/>
+      <c r="A900" s="33"/>
+      <c r="I900" s="20"/>
     </row>
     <row r="901">
-      <c r="A901" s="23"/>
-      <c r="I901" s="21"/>
+      <c r="A901" s="33"/>
+      <c r="I901" s="20"/>
     </row>
     <row r="902">
-      <c r="A902" s="23"/>
-      <c r="I902" s="21"/>
+      <c r="A902" s="33"/>
+      <c r="I902" s="20"/>
     </row>
     <row r="903">
-      <c r="A903" s="23"/>
-      <c r="I903" s="21"/>
+      <c r="A903" s="33"/>
+      <c r="I903" s="20"/>
     </row>
     <row r="904">
-      <c r="A904" s="23"/>
-      <c r="I904" s="21"/>
+      <c r="A904" s="33"/>
+      <c r="I904" s="20"/>
     </row>
     <row r="905">
-      <c r="A905" s="23"/>
-      <c r="I905" s="21"/>
+      <c r="A905" s="33"/>
+      <c r="I905" s="20"/>
     </row>
     <row r="906">
-      <c r="A906" s="23"/>
-      <c r="I906" s="21"/>
+      <c r="A906" s="33"/>
+      <c r="I906" s="20"/>
     </row>
     <row r="907">
-      <c r="A907" s="23"/>
-      <c r="I907" s="21"/>
+      <c r="A907" s="33"/>
+      <c r="I907" s="20"/>
     </row>
     <row r="908">
-      <c r="A908" s="23"/>
-      <c r="I908" s="21"/>
+      <c r="A908" s="33"/>
+      <c r="I908" s="20"/>
     </row>
     <row r="909">
-      <c r="A909" s="23"/>
-      <c r="I909" s="21"/>
+      <c r="A909" s="33"/>
+      <c r="I909" s="20"/>
     </row>
     <row r="910">
-      <c r="A910" s="23"/>
-      <c r="I910" s="21"/>
+      <c r="A910" s="33"/>
+      <c r="I910" s="20"/>
     </row>
     <row r="911">
-      <c r="A911" s="23"/>
-      <c r="I911" s="21"/>
+      <c r="A911" s="33"/>
+      <c r="I911" s="20"/>
     </row>
     <row r="912">
-      <c r="A912" s="23"/>
-      <c r="I912" s="21"/>
+      <c r="A912" s="33"/>
+      <c r="I912" s="20"/>
     </row>
     <row r="913">
-      <c r="A913" s="23"/>
-      <c r="I913" s="21"/>
+      <c r="A913" s="33"/>
+      <c r="I913" s="20"/>
     </row>
     <row r="914">
-      <c r="A914" s="23"/>
-      <c r="I914" s="21"/>
+      <c r="A914" s="33"/>
+      <c r="I914" s="20"/>
     </row>
     <row r="915">
-      <c r="A915" s="23"/>
-      <c r="I915" s="21"/>
+      <c r="A915" s="33"/>
+      <c r="I915" s="20"/>
     </row>
     <row r="916">
-      <c r="A916" s="23"/>
-      <c r="I916" s="21"/>
+      <c r="A916" s="33"/>
+      <c r="I916" s="20"/>
     </row>
     <row r="917">
-      <c r="A917" s="23"/>
-      <c r="I917" s="21"/>
+      <c r="A917" s="33"/>
+      <c r="I917" s="20"/>
     </row>
     <row r="918">
-      <c r="A918" s="23"/>
-      <c r="I918" s="21"/>
+      <c r="A918" s="33"/>
+      <c r="I918" s="20"/>
     </row>
     <row r="919">
-      <c r="A919" s="23"/>
-      <c r="I919" s="21"/>
+      <c r="A919" s="33"/>
+      <c r="I919" s="20"/>
     </row>
     <row r="920">
-      <c r="A920" s="23"/>
-      <c r="I920" s="21"/>
+      <c r="A920" s="33"/>
+      <c r="I920" s="20"/>
     </row>
     <row r="921">
-      <c r="A921" s="23"/>
-      <c r="I921" s="21"/>
+      <c r="A921" s="33"/>
+      <c r="I921" s="20"/>
     </row>
     <row r="922">
-      <c r="A922" s="23"/>
-      <c r="I922" s="21"/>
+      <c r="A922" s="33"/>
+      <c r="I922" s="20"/>
     </row>
     <row r="923">
-      <c r="A923" s="23"/>
-      <c r="I923" s="21"/>
+      <c r="A923" s="33"/>
+      <c r="I923" s="20"/>
     </row>
     <row r="924">
-      <c r="A924" s="23"/>
-      <c r="I924" s="21"/>
+      <c r="A924" s="33"/>
+      <c r="I924" s="20"/>
     </row>
     <row r="925">
-      <c r="A925" s="23"/>
-      <c r="I925" s="21"/>
+      <c r="A925" s="33"/>
+      <c r="I925" s="20"/>
     </row>
     <row r="926">
-      <c r="A926" s="23"/>
-      <c r="I926" s="21"/>
+      <c r="A926" s="33"/>
+      <c r="I926" s="20"/>
     </row>
     <row r="927">
-      <c r="A927" s="23"/>
-      <c r="I927" s="21"/>
+      <c r="A927" s="33"/>
+      <c r="I927" s="20"/>
     </row>
     <row r="928">
-      <c r="A928" s="23"/>
-      <c r="I928" s="21"/>
+      <c r="A928" s="33"/>
+      <c r="I928" s="20"/>
     </row>
     <row r="929">
-      <c r="A929" s="23"/>
-      <c r="I929" s="21"/>
+      <c r="A929" s="33"/>
+      <c r="I929" s="20"/>
     </row>
     <row r="930">
-      <c r="A930" s="23"/>
-      <c r="I930" s="21"/>
+      <c r="A930" s="33"/>
+      <c r="I930" s="20"/>
     </row>
     <row r="931">
-      <c r="A931" s="23"/>
-      <c r="I931" s="21"/>
+      <c r="A931" s="33"/>
+      <c r="I931" s="20"/>
     </row>
     <row r="932">
-      <c r="A932" s="23"/>
-      <c r="I932" s="21"/>
+      <c r="A932" s="33"/>
+      <c r="I932" s="20"/>
     </row>
     <row r="933">
-      <c r="A933" s="23"/>
-      <c r="I933" s="21"/>
+      <c r="A933" s="33"/>
+      <c r="I933" s="20"/>
     </row>
     <row r="934">
-      <c r="A934" s="23"/>
-      <c r="I934" s="21"/>
+      <c r="A934" s="33"/>
+      <c r="I934" s="20"/>
     </row>
     <row r="935">
-      <c r="A935" s="23"/>
-      <c r="I935" s="21"/>
+      <c r="A935" s="33"/>
+      <c r="I935" s="20"/>
     </row>
     <row r="936">
-      <c r="A936" s="23"/>
-      <c r="I936" s="21"/>
+      <c r="A936" s="33"/>
+      <c r="I936" s="20"/>
     </row>
     <row r="937">
-      <c r="A937" s="23"/>
-      <c r="I937" s="21"/>
+      <c r="A937" s="33"/>
+      <c r="I937" s="20"/>
     </row>
     <row r="938">
-      <c r="A938" s="23"/>
-      <c r="I938" s="21"/>
+      <c r="A938" s="33"/>
+      <c r="I938" s="20"/>
     </row>
     <row r="939">
-      <c r="A939" s="23"/>
-      <c r="I939" s="21"/>
+      <c r="A939" s="33"/>
+      <c r="I939" s="20"/>
     </row>
     <row r="940">
-      <c r="A940" s="23"/>
-      <c r="I940" s="21"/>
+      <c r="A940" s="33"/>
+      <c r="I940" s="20"/>
     </row>
     <row r="941">
-      <c r="A941" s="23"/>
-      <c r="I941" s="21"/>
+      <c r="A941" s="33"/>
+      <c r="I941" s="20"/>
     </row>
     <row r="942">
-      <c r="A942" s="23"/>
-      <c r="I942" s="21"/>
+      <c r="A942" s="33"/>
+      <c r="I942" s="20"/>
     </row>
     <row r="943">
-      <c r="A943" s="23"/>
-      <c r="I943" s="21"/>
+      <c r="A943" s="33"/>
+      <c r="I943" s="20"/>
     </row>
     <row r="944">
-      <c r="A944" s="23"/>
-      <c r="I944" s="21"/>
+      <c r="A944" s="33"/>
+      <c r="I944" s="20"/>
     </row>
     <row r="945">
-      <c r="A945" s="23"/>
-      <c r="I945" s="21"/>
+      <c r="A945" s="33"/>
+      <c r="I945" s="20"/>
     </row>
     <row r="946">
-      <c r="A946" s="23"/>
-      <c r="I946" s="21"/>
+      <c r="A946" s="33"/>
+      <c r="I946" s="20"/>
     </row>
     <row r="947">
-      <c r="A947" s="23"/>
-      <c r="I947" s="21"/>
+      <c r="A947" s="33"/>
+      <c r="I947" s="20"/>
     </row>
     <row r="948">
-      <c r="A948" s="23"/>
-      <c r="I948" s="21"/>
+      <c r="A948" s="33"/>
+      <c r="I948" s="20"/>
     </row>
     <row r="949">
-      <c r="A949" s="23"/>
-      <c r="I949" s="21"/>
+      <c r="A949" s="33"/>
+      <c r="I949" s="20"/>
     </row>
     <row r="950">
-      <c r="A950" s="23"/>
-      <c r="I950" s="21"/>
+      <c r="A950" s="33"/>
+      <c r="I950" s="20"/>
     </row>
     <row r="951">
-      <c r="A951" s="23"/>
-      <c r="I951" s="21"/>
+      <c r="A951" s="33"/>
+      <c r="I951" s="20"/>
     </row>
     <row r="952">
-      <c r="A952" s="23"/>
-      <c r="I952" s="21"/>
+      <c r="A952" s="33"/>
+      <c r="I952" s="20"/>
     </row>
     <row r="953">
-      <c r="A953" s="23"/>
-      <c r="I953" s="21"/>
+      <c r="A953" s="33"/>
+      <c r="I953" s="20"/>
     </row>
     <row r="954">
-      <c r="A954" s="23"/>
-      <c r="I954" s="21"/>
+      <c r="A954" s="33"/>
+      <c r="I954" s="20"/>
     </row>
     <row r="955">
-      <c r="A955" s="23"/>
-      <c r="I955" s="21"/>
+      <c r="A955" s="33"/>
+      <c r="I955" s="20"/>
     </row>
     <row r="956">
-      <c r="A956" s="23"/>
-      <c r="I956" s="21"/>
+      <c r="A956" s="33"/>
+      <c r="I956" s="20"/>
     </row>
     <row r="957">
-      <c r="A957" s="23"/>
-      <c r="I957" s="21"/>
+      <c r="A957" s="33"/>
+      <c r="I957" s="20"/>
     </row>
     <row r="958">
-      <c r="A958" s="23"/>
-      <c r="I958" s="21"/>
+      <c r="A958" s="33"/>
+      <c r="I958" s="20"/>
     </row>
     <row r="959">
-      <c r="A959" s="23"/>
-      <c r="I959" s="21"/>
+      <c r="A959" s="33"/>
+      <c r="I959" s="20"/>
     </row>
     <row r="960">
-      <c r="A960" s="23"/>
-      <c r="I960" s="21"/>
+      <c r="A960" s="33"/>
+      <c r="I960" s="20"/>
     </row>
     <row r="961">
-      <c r="A961" s="23"/>
-      <c r="I961" s="21"/>
+      <c r="A961" s="33"/>
+      <c r="I961" s="20"/>
     </row>
     <row r="962">
-      <c r="A962" s="23"/>
-      <c r="I962" s="21"/>
+      <c r="A962" s="33"/>
+      <c r="I962" s="20"/>
     </row>
     <row r="963">
-      <c r="A963" s="23"/>
-      <c r="I963" s="21"/>
+      <c r="A963" s="33"/>
+      <c r="I963" s="20"/>
     </row>
     <row r="964">
-      <c r="A964" s="23"/>
-      <c r="I964" s="21"/>
+      <c r="A964" s="33"/>
+      <c r="I964" s="20"/>
     </row>
     <row r="965">
-      <c r="A965" s="23"/>
-      <c r="I965" s="21"/>
+      <c r="A965" s="33"/>
+      <c r="I965" s="20"/>
     </row>
     <row r="966">
-      <c r="A966" s="23"/>
-      <c r="I966" s="21"/>
+      <c r="A966" s="33"/>
+      <c r="I966" s="20"/>
     </row>
     <row r="967">
-      <c r="A967" s="23"/>
-      <c r="I967" s="21"/>
+      <c r="A967" s="33"/>
+      <c r="I967" s="20"/>
     </row>
     <row r="968">
-      <c r="A968" s="23"/>
-      <c r="I968" s="21"/>
+      <c r="A968" s="33"/>
+      <c r="I968" s="20"/>
     </row>
     <row r="969">
-      <c r="A969" s="23"/>
-      <c r="I969" s="21"/>
+      <c r="A969" s="33"/>
+      <c r="I969" s="20"/>
     </row>
     <row r="970">
-      <c r="A970" s="23"/>
-      <c r="I970" s="21"/>
+      <c r="A970" s="33"/>
+      <c r="I970" s="20"/>
     </row>
     <row r="971">
-      <c r="A971" s="23"/>
-      <c r="I971" s="21"/>
+      <c r="A971" s="33"/>
+      <c r="I971" s="20"/>
     </row>
     <row r="972">
-      <c r="A972" s="23"/>
-      <c r="I972" s="21"/>
+      <c r="A972" s="33"/>
+      <c r="I972" s="20"/>
     </row>
     <row r="973">
-      <c r="A973" s="23"/>
-      <c r="I973" s="21"/>
+      <c r="A973" s="33"/>
+      <c r="I973" s="20"/>
     </row>
     <row r="974">
-      <c r="A974" s="23"/>
-      <c r="I974" s="21"/>
+      <c r="A974" s="33"/>
+      <c r="I974" s="20"/>
     </row>
     <row r="975">
-      <c r="A975" s="23"/>
-      <c r="I975" s="21"/>
+      <c r="A975" s="33"/>
+      <c r="I975" s="20"/>
     </row>
     <row r="976">
-      <c r="A976" s="23"/>
-      <c r="I976" s="21"/>
+      <c r="A976" s="33"/>
+      <c r="I976" s="20"/>
     </row>
     <row r="977">
-      <c r="A977" s="23"/>
-      <c r="I977" s="21"/>
+      <c r="A977" s="33"/>
+      <c r="I977" s="20"/>
     </row>
     <row r="978">
-      <c r="A978" s="23"/>
-      <c r="I978" s="21"/>
+      <c r="A978" s="33"/>
+      <c r="I978" s="20"/>
     </row>
     <row r="979">
-      <c r="A979" s="23"/>
-      <c r="I979" s="21"/>
+      <c r="A979" s="33"/>
+      <c r="I979" s="20"/>
     </row>
     <row r="980">
-      <c r="A980" s="23"/>
-      <c r="I980" s="21"/>
+      <c r="A980" s="33"/>
+      <c r="I980" s="20"/>
     </row>
     <row r="981">
-      <c r="A981" s="23"/>
-      <c r="I981" s="21"/>
+      <c r="A981" s="33"/>
+      <c r="I981" s="20"/>
     </row>
     <row r="982">
-      <c r="A982" s="23"/>
-      <c r="I982" s="21"/>
+      <c r="A982" s="33"/>
+      <c r="I982" s="20"/>
     </row>
     <row r="983">
-      <c r="A983" s="23"/>
-      <c r="I983" s="21"/>
+      <c r="A983" s="33"/>
+      <c r="I983" s="20"/>
     </row>
     <row r="984">
-      <c r="A984" s="23"/>
-      <c r="I984" s="21"/>
+      <c r="A984" s="33"/>
+      <c r="I984" s="20"/>
     </row>
     <row r="985">
-      <c r="A985" s="23"/>
-      <c r="I985" s="21"/>
+      <c r="A985" s="33"/>
+      <c r="I985" s="20"/>
     </row>
     <row r="986">
-      <c r="A986" s="23"/>
-      <c r="I986" s="21"/>
+      <c r="A986" s="33"/>
+      <c r="I986" s="20"/>
     </row>
     <row r="987">
-      <c r="A987" s="23"/>
-      <c r="I987" s="21"/>
+      <c r="A987" s="33"/>
+      <c r="I987" s="20"/>
     </row>
     <row r="988">
-      <c r="A988" s="23"/>
-      <c r="I988" s="21"/>
+      <c r="A988" s="33"/>
+      <c r="I988" s="20"/>
     </row>
     <row r="989">
-      <c r="A989" s="23"/>
-      <c r="I989" s="21"/>
+      <c r="A989" s="33"/>
+      <c r="I989" s="20"/>
     </row>
     <row r="990">
-      <c r="A990" s="23"/>
-      <c r="I990" s="21"/>
+      <c r="A990" s="33"/>
+      <c r="I990" s="20"/>
     </row>
     <row r="991">
-      <c r="A991" s="23"/>
-      <c r="I991" s="21"/>
+      <c r="A991" s="33"/>
+      <c r="I991" s="20"/>
     </row>
     <row r="992">
-      <c r="A992" s="23"/>
-      <c r="I992" s="21"/>
+      <c r="A992" s="33"/>
+      <c r="I992" s="20"/>
     </row>
     <row r="993">
-      <c r="A993" s="23"/>
-      <c r="I993" s="21"/>
+      <c r="A993" s="33"/>
+      <c r="I993" s="20"/>
     </row>
     <row r="994">
-      <c r="A994" s="23"/>
-      <c r="I994" s="21"/>
+      <c r="A994" s="33"/>
+      <c r="I994" s="20"/>
     </row>
     <row r="995">
-      <c r="A995" s="23"/>
-      <c r="I995" s="21"/>
+      <c r="A995" s="33"/>
+      <c r="I995" s="20"/>
     </row>
     <row r="996">
-      <c r="A996" s="23"/>
-      <c r="I996" s="21"/>
+      <c r="A996" s="33"/>
+      <c r="I996" s="20"/>
     </row>
     <row r="997">
-      <c r="A997" s="23"/>
-      <c r="I997" s="21"/>
+      <c r="A997" s="33"/>
+      <c r="I997" s="20"/>
     </row>
     <row r="998">
-      <c r="A998" s="23"/>
-      <c r="I998" s="21"/>
+      <c r="A998" s="33"/>
+      <c r="I998" s="20"/>
     </row>
     <row r="999">
-      <c r="A999" s="23"/>
-      <c r="I999" s="21"/>
+      <c r="A999" s="33"/>
+      <c r="I999" s="20"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="23"/>
-      <c r="I1000" s="21"/>
+      <c r="A1000" s="33"/>
+      <c r="I1000" s="20"/>
     </row>
     <row r="1001">
-      <c r="A1001" s="23"/>
-      <c r="I1001" s="21"/>
+      <c r="A1001" s="33"/>
+      <c r="I1001" s="20"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/src/data/AFCARS.xlsx
+++ b/src/data/AFCARS.xlsx
@@ -12922,10 +12922,6 @@
       <c r="A1000" s="33"/>
       <c r="I1000" s="20"/>
     </row>
-    <row r="1001">
-      <c r="A1001" s="33"/>
-      <c r="I1001" s="20"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/src/data/AFCARS.xlsx
+++ b/src/data/AFCARS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="67">
   <si>
     <t>State</t>
   </si>
@@ -221,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -246,6 +246,11 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -279,7 +284,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border/>
     <border>
       <right style="thin">
@@ -317,6 +322,11 @@
       </bottom>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF215E99"/>
+      </right>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -335,11 +345,24 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF215E99"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF215E99"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF215E99"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -414,22 +437,36 @@
     <xf borderId="4" fillId="0" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -8239,7 +8276,9 @@
       <c r="H210" s="25">
         <v>0.559</v>
       </c>
-      <c r="I210" s="26"/>
+      <c r="I210" s="26" t="s">
+        <v>13</v>
+      </c>
       <c r="J210" s="23">
         <v>912.0</v>
       </c>
@@ -8247,6 +8286,7 @@
         <f t="shared" si="1"/>
         <v>0.3707317073</v>
       </c>
+      <c r="L210" s="27"/>
     </row>
     <row r="211">
       <c r="A211" s="18" t="s">
@@ -8255,32 +8295,35 @@
       <c r="B211" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C211" s="27">
+      <c r="C211" s="28">
         <v>5616.0</v>
       </c>
-      <c r="D211" s="28">
+      <c r="D211" s="29">
         <v>3189.0</v>
       </c>
-      <c r="E211" s="29">
+      <c r="E211" s="30">
         <v>866.0</v>
       </c>
-      <c r="F211" s="29">
+      <c r="F211" s="30">
         <v>398.0</v>
       </c>
-      <c r="G211" s="29">
+      <c r="G211" s="30">
         <v>720.0</v>
       </c>
-      <c r="H211" s="30">
+      <c r="H211" s="31">
         <v>0.361</v>
       </c>
-      <c r="I211" s="31"/>
-      <c r="J211" s="28">
+      <c r="I211" s="26">
+        <v>11.0</v>
+      </c>
+      <c r="J211" s="29">
         <v>2697.0</v>
       </c>
       <c r="K211" s="12">
         <f t="shared" si="1"/>
         <v>0.4802350427</v>
       </c>
+      <c r="L211" s="27"/>
     </row>
     <row r="212">
       <c r="A212" s="18" t="s">
@@ -8289,32 +8332,35 @@
       <c r="B212" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C212" s="27">
+      <c r="C212" s="28">
         <v>3264.0</v>
       </c>
-      <c r="D212" s="28">
+      <c r="D212" s="29">
         <v>1011.0</v>
       </c>
-      <c r="E212" s="28">
+      <c r="E212" s="29">
         <v>1028.0</v>
       </c>
-      <c r="F212" s="29">
+      <c r="F212" s="30">
         <v>96.0</v>
       </c>
-      <c r="G212" s="29">
+      <c r="G212" s="30">
         <v>511.0</v>
       </c>
-      <c r="H212" s="30">
+      <c r="H212" s="31">
         <v>0.415</v>
       </c>
-      <c r="I212" s="31"/>
-      <c r="J212" s="28">
+      <c r="I212" s="26">
+        <v>648.0</v>
+      </c>
+      <c r="J212" s="29">
         <v>1618.0</v>
       </c>
       <c r="K212" s="12">
         <f t="shared" si="1"/>
         <v>0.4957107843</v>
       </c>
+      <c r="L212" s="27"/>
     </row>
     <row r="213">
       <c r="A213" s="18" t="s">
@@ -8323,32 +8369,35 @@
       <c r="B213" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C213" s="27">
+      <c r="C213" s="28">
         <v>8306.0</v>
       </c>
-      <c r="D213" s="28">
+      <c r="D213" s="29">
         <v>1929.0</v>
       </c>
-      <c r="E213" s="28">
+      <c r="E213" s="29">
         <v>3232.0</v>
       </c>
-      <c r="F213" s="28">
+      <c r="F213" s="29">
         <v>1073.0</v>
       </c>
-      <c r="G213" s="28">
+      <c r="G213" s="29">
         <v>1440.0</v>
       </c>
-      <c r="H213" s="30">
+      <c r="H213" s="31">
         <v>0.452</v>
       </c>
-      <c r="I213" s="31"/>
-      <c r="J213" s="28">
+      <c r="I213" s="32">
+        <v>1131.0</v>
+      </c>
+      <c r="J213" s="29">
         <v>1918.0</v>
       </c>
       <c r="K213" s="12">
         <f t="shared" si="1"/>
         <v>0.2309174091</v>
       </c>
+      <c r="L213" s="27"/>
     </row>
     <row r="214">
       <c r="A214" s="18" t="s">
@@ -8357,32 +8406,35 @@
       <c r="B214" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C214" s="27">
+      <c r="C214" s="28">
         <v>36212.0</v>
       </c>
-      <c r="D214" s="28">
+      <c r="D214" s="29">
         <v>16560.0</v>
       </c>
-      <c r="E214" s="28">
+      <c r="E214" s="29">
         <v>14495.0</v>
       </c>
-      <c r="F214" s="28">
+      <c r="F214" s="29">
         <v>4916.0</v>
       </c>
-      <c r="G214" s="28">
+      <c r="G214" s="29">
         <v>5352.0</v>
       </c>
-      <c r="H214" s="30">
+      <c r="H214" s="31">
         <v>0.476</v>
       </c>
-      <c r="I214" s="31"/>
-      <c r="J214" s="28">
+      <c r="I214" s="32">
+        <v>23372.0</v>
+      </c>
+      <c r="J214" s="29">
         <v>30945.0</v>
       </c>
       <c r="K214" s="12">
         <f t="shared" si="1"/>
         <v>0.8545509776</v>
       </c>
+      <c r="L214" s="27"/>
     </row>
     <row r="215">
       <c r="A215" s="18" t="s">
@@ -8391,32 +8443,35 @@
       <c r="B215" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C215" s="27">
+      <c r="C215" s="28">
         <v>4194.0</v>
       </c>
-      <c r="D215" s="28">
+      <c r="D215" s="29">
         <v>1394.0</v>
       </c>
-      <c r="E215" s="28">
+      <c r="E215" s="29">
         <v>1772.0</v>
       </c>
-      <c r="F215" s="29" t="s">
+      <c r="F215" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="G215" s="29">
+      <c r="G215" s="30">
         <v>451.0</v>
       </c>
-      <c r="H215" s="30">
+      <c r="H215" s="31">
         <v>0.443</v>
       </c>
-      <c r="I215" s="31"/>
-      <c r="J215" s="28">
+      <c r="I215" s="26">
+        <v>613.0</v>
+      </c>
+      <c r="J215" s="29">
         <v>2179.0</v>
       </c>
       <c r="K215" s="12">
         <f t="shared" si="1"/>
         <v>0.5195517406</v>
       </c>
+      <c r="L215" s="27"/>
     </row>
     <row r="216">
       <c r="A216" s="18" t="s">
@@ -8425,30 +8480,33 @@
       <c r="B216" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C216" s="27">
+      <c r="C216" s="28">
         <v>3440.0</v>
       </c>
-      <c r="D216" s="29">
+      <c r="D216" s="30">
         <v>755.0</v>
       </c>
-      <c r="E216" s="28">
+      <c r="E216" s="29">
         <v>1517.0</v>
       </c>
-      <c r="F216" s="31"/>
-      <c r="G216" s="29">
+      <c r="F216" s="33"/>
+      <c r="G216" s="30">
         <v>133.0</v>
       </c>
-      <c r="H216" s="30">
+      <c r="H216" s="31">
         <v>0.196</v>
       </c>
-      <c r="I216" s="31"/>
-      <c r="J216" s="28">
+      <c r="I216" s="26">
+        <v>151.0</v>
+      </c>
+      <c r="J216" s="29">
         <v>2090.0</v>
       </c>
       <c r="K216" s="12">
         <f t="shared" si="1"/>
         <v>0.6075581395</v>
       </c>
+      <c r="L216" s="27"/>
     </row>
     <row r="217">
       <c r="A217" s="18" t="s">
@@ -8457,30 +8515,33 @@
       <c r="B217" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C217" s="32">
+      <c r="C217" s="34">
         <v>523.0</v>
       </c>
-      <c r="D217" s="29">
+      <c r="D217" s="30">
         <v>267.0</v>
       </c>
-      <c r="E217" s="29">
+      <c r="E217" s="30">
         <v>103.0</v>
       </c>
-      <c r="F217" s="31"/>
-      <c r="G217" s="29">
+      <c r="F217" s="33"/>
+      <c r="G217" s="30">
         <v>60.0</v>
       </c>
-      <c r="H217" s="30">
+      <c r="H217" s="31">
         <v>0.357</v>
       </c>
-      <c r="I217" s="31"/>
-      <c r="J217" s="29">
+      <c r="I217" s="26">
+        <v>49.0</v>
+      </c>
+      <c r="J217" s="30">
         <v>346.0</v>
       </c>
       <c r="K217" s="12">
         <f t="shared" si="1"/>
         <v>0.6615678776</v>
       </c>
+      <c r="L217" s="27"/>
     </row>
     <row r="218">
       <c r="A218" s="18" t="s">
@@ -8489,32 +8550,35 @@
       <c r="B218" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C218" s="32">
+      <c r="C218" s="34">
         <v>469.0</v>
       </c>
-      <c r="D218" s="29">
+      <c r="D218" s="30">
         <v>244.0</v>
       </c>
-      <c r="E218" s="29">
+      <c r="E218" s="30">
         <v>95.0</v>
       </c>
-      <c r="F218" s="29">
+      <c r="F218" s="30">
         <v>101.0</v>
       </c>
-      <c r="G218" s="29">
+      <c r="G218" s="30">
         <v>80.0</v>
       </c>
-      <c r="H218" s="30">
+      <c r="H218" s="31">
         <v>0.293</v>
       </c>
-      <c r="I218" s="31"/>
-      <c r="J218" s="29">
+      <c r="I218" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J218" s="30">
         <v>358.0</v>
       </c>
       <c r="K218" s="12">
         <f t="shared" si="1"/>
         <v>0.763326226</v>
       </c>
+      <c r="L218" s="27"/>
     </row>
     <row r="219">
       <c r="A219" s="18" t="s">
@@ -8523,32 +8587,35 @@
       <c r="B219" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C219" s="27">
+      <c r="C219" s="28">
         <v>15346.0</v>
       </c>
-      <c r="D219" s="28">
+      <c r="D219" s="29">
         <v>4603.0</v>
       </c>
-      <c r="E219" s="28">
+      <c r="E219" s="29">
         <v>7187.0</v>
       </c>
-      <c r="F219" s="28">
+      <c r="F219" s="29">
         <v>1539.0</v>
       </c>
-      <c r="G219" s="28">
+      <c r="G219" s="29">
         <v>3591.0</v>
       </c>
-      <c r="H219" s="30">
+      <c r="H219" s="31">
         <v>0.372</v>
       </c>
-      <c r="I219" s="31"/>
-      <c r="J219" s="28">
+      <c r="I219" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J219" s="29">
         <v>6699.0</v>
       </c>
       <c r="K219" s="12">
         <f t="shared" si="1"/>
         <v>0.436530692</v>
       </c>
+      <c r="L219" s="27"/>
     </row>
     <row r="220">
       <c r="A220" s="18" t="s">
@@ -8557,32 +8624,35 @@
       <c r="B220" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C220" s="27">
+      <c r="C220" s="28">
         <v>10877.0</v>
       </c>
-      <c r="D220" s="28">
+      <c r="D220" s="29">
         <v>6449.0</v>
       </c>
-      <c r="E220" s="28">
+      <c r="E220" s="29">
         <v>2376.0</v>
       </c>
-      <c r="F220" s="29">
+      <c r="F220" s="30">
         <v>891.0</v>
       </c>
-      <c r="G220" s="28">
+      <c r="G220" s="29">
         <v>1051.0</v>
       </c>
-      <c r="H220" s="30">
+      <c r="H220" s="31">
         <v>0.458</v>
       </c>
-      <c r="I220" s="31"/>
-      <c r="J220" s="28">
+      <c r="I220" s="32">
+        <v>4402.0</v>
+      </c>
+      <c r="J220" s="29">
         <v>4495.0</v>
       </c>
       <c r="K220" s="12">
         <f t="shared" si="1"/>
         <v>0.413257332</v>
       </c>
+      <c r="L220" s="27"/>
     </row>
     <row r="221">
       <c r="A221" s="18" t="s">
@@ -8591,32 +8661,35 @@
       <c r="B221" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C221" s="32">
+      <c r="C221" s="34">
         <v>913.0</v>
       </c>
-      <c r="D221" s="29">
+      <c r="D221" s="30">
         <v>332.0</v>
       </c>
-      <c r="E221" s="29">
+      <c r="E221" s="30">
         <v>307.0</v>
       </c>
-      <c r="F221" s="29">
+      <c r="F221" s="30">
         <v>178.0</v>
       </c>
-      <c r="G221" s="29">
+      <c r="G221" s="30">
         <v>122.0</v>
       </c>
-      <c r="H221" s="30">
+      <c r="H221" s="31">
         <v>0.57</v>
       </c>
-      <c r="I221" s="31"/>
-      <c r="J221" s="29">
+      <c r="I221" s="26">
+        <v>83.0</v>
+      </c>
+      <c r="J221" s="30">
         <v>702.0</v>
       </c>
       <c r="K221" s="12">
         <f t="shared" si="1"/>
         <v>0.7688937568</v>
       </c>
+      <c r="L221" s="27"/>
     </row>
     <row r="222">
       <c r="A222" s="18" t="s">
@@ -8625,32 +8698,35 @@
       <c r="B222" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C222" s="27">
+      <c r="C222" s="28">
         <v>3365.0</v>
       </c>
-      <c r="D222" s="29">
+      <c r="D222" s="30">
         <v>824.0</v>
       </c>
-      <c r="E222" s="28">
+      <c r="E222" s="29">
         <v>1770.0</v>
       </c>
-      <c r="F222" s="29">
+      <c r="F222" s="30">
         <v>600.0</v>
       </c>
-      <c r="G222" s="29">
+      <c r="G222" s="30">
         <v>806.0</v>
       </c>
-      <c r="H222" s="30">
+      <c r="H222" s="31">
         <v>0.477</v>
       </c>
-      <c r="I222" s="31"/>
-      <c r="J222" s="28">
+      <c r="I222" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J222" s="29">
         <v>1951.0</v>
       </c>
       <c r="K222" s="12">
         <f t="shared" si="1"/>
         <v>0.5797919762</v>
       </c>
+      <c r="L222" s="27"/>
     </row>
     <row r="223">
       <c r="A223" s="18" t="s">
@@ -8659,32 +8735,35 @@
       <c r="B223" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C223" s="27">
+      <c r="C223" s="28">
         <v>1258.0</v>
       </c>
-      <c r="D223" s="29">
+      <c r="D223" s="30">
         <v>534.0</v>
       </c>
-      <c r="E223" s="29">
+      <c r="E223" s="30">
         <v>361.0</v>
       </c>
-      <c r="F223" s="29">
+      <c r="F223" s="30">
         <v>104.0</v>
       </c>
-      <c r="G223" s="29">
+      <c r="G223" s="30">
         <v>237.0</v>
       </c>
-      <c r="H223" s="30">
+      <c r="H223" s="31">
         <v>0.598</v>
       </c>
-      <c r="I223" s="31"/>
-      <c r="J223" s="28">
+      <c r="I223" s="26">
+        <v>215.0</v>
+      </c>
+      <c r="J223" s="29">
         <v>1197.0</v>
       </c>
       <c r="K223" s="12">
         <f t="shared" si="1"/>
         <v>0.9515103339</v>
       </c>
+      <c r="L223" s="27"/>
     </row>
     <row r="224">
       <c r="A224" s="18" t="s">
@@ -8693,32 +8772,35 @@
       <c r="B224" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C224" s="27">
+      <c r="C224" s="28">
         <v>16610.0</v>
       </c>
-      <c r="D224" s="28">
+      <c r="D224" s="29">
         <v>4398.0</v>
       </c>
-      <c r="E224" s="28">
+      <c r="E224" s="29">
         <v>9483.0</v>
       </c>
-      <c r="F224" s="28">
+      <c r="F224" s="29">
         <v>2454.0</v>
       </c>
-      <c r="G224" s="28">
+      <c r="G224" s="29">
         <v>2549.0</v>
       </c>
-      <c r="H224" s="30">
+      <c r="H224" s="31">
         <v>0.395</v>
       </c>
-      <c r="I224" s="31"/>
-      <c r="J224" s="28">
+      <c r="I224" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J224" s="29">
         <v>6781.0</v>
       </c>
       <c r="K224" s="12">
         <f t="shared" si="1"/>
         <v>0.4082480433</v>
       </c>
+      <c r="L224" s="27"/>
     </row>
     <row r="225">
       <c r="A225" s="18" t="s">
@@ -8727,32 +8809,35 @@
       <c r="B225" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C225" s="27">
+      <c r="C225" s="28">
         <v>11843.0</v>
       </c>
-      <c r="D225" s="28">
+      <c r="D225" s="29">
         <v>2529.0</v>
       </c>
-      <c r="E225" s="28">
+      <c r="E225" s="29">
         <v>6552.0</v>
       </c>
-      <c r="F225" s="28">
+      <c r="F225" s="29">
         <v>1007.0</v>
       </c>
-      <c r="G225" s="28">
+      <c r="G225" s="29">
         <v>1729.0</v>
       </c>
-      <c r="H225" s="30">
+      <c r="H225" s="31">
         <v>0.584</v>
       </c>
-      <c r="I225" s="31"/>
-      <c r="J225" s="28">
+      <c r="I225" s="32">
+        <v>7292.0</v>
+      </c>
+      <c r="J225" s="29">
         <v>3837.0</v>
       </c>
       <c r="K225" s="12">
         <f t="shared" si="1"/>
         <v>0.3239888542</v>
       </c>
+      <c r="L225" s="27"/>
     </row>
     <row r="226">
       <c r="A226" s="18" t="s">
@@ -8761,32 +8846,35 @@
       <c r="B226" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C226" s="27">
+      <c r="C226" s="28">
         <v>7022.0</v>
       </c>
-      <c r="D226" s="29">
+      <c r="D226" s="30">
         <v>685.0</v>
       </c>
-      <c r="E226" s="28">
+      <c r="E226" s="29">
         <v>2894.0</v>
       </c>
-      <c r="F226" s="28">
+      <c r="F226" s="29">
         <v>1926.0</v>
       </c>
-      <c r="G226" s="29">
+      <c r="G226" s="30">
         <v>421.0</v>
       </c>
-      <c r="H226" s="30">
+      <c r="H226" s="31">
         <v>0.495</v>
       </c>
-      <c r="I226" s="31"/>
-      <c r="J226" s="28">
+      <c r="I226" s="26">
+        <v>101.0</v>
+      </c>
+      <c r="J226" s="29">
         <v>1923.0</v>
       </c>
       <c r="K226" s="12">
         <f t="shared" si="1"/>
         <v>0.273853603</v>
       </c>
+      <c r="L226" s="27"/>
     </row>
     <row r="227">
       <c r="A227" s="18" t="s">
@@ -8795,32 +8883,35 @@
       <c r="B227" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C227" s="27">
+      <c r="C227" s="28">
         <v>8569.0</v>
       </c>
-      <c r="D227" s="28">
+      <c r="D227" s="29">
         <v>2519.0</v>
       </c>
-      <c r="E227" s="28">
+      <c r="E227" s="29">
         <v>1683.0</v>
       </c>
-      <c r="F227" s="28">
+      <c r="F227" s="29">
         <v>1697.0</v>
       </c>
-      <c r="G227" s="28">
+      <c r="G227" s="29">
         <v>1125.0</v>
       </c>
-      <c r="H227" s="30">
+      <c r="H227" s="31">
         <v>0.41</v>
       </c>
-      <c r="I227" s="31"/>
-      <c r="J227" s="28">
+      <c r="I227" s="26">
+        <v>960.0</v>
+      </c>
+      <c r="J227" s="29">
         <v>4516.0</v>
       </c>
       <c r="K227" s="12">
         <f t="shared" si="1"/>
         <v>0.5270159879</v>
       </c>
+      <c r="L227" s="27"/>
     </row>
     <row r="228">
       <c r="A228" s="18" t="s">
@@ -8829,32 +8920,35 @@
       <c r="B228" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C228" s="27">
+      <c r="C228" s="28">
         <v>4619.0</v>
       </c>
-      <c r="D228" s="28">
+      <c r="D228" s="29">
         <v>1532.0</v>
       </c>
-      <c r="E228" s="28">
+      <c r="E228" s="29">
         <v>1960.0</v>
       </c>
-      <c r="F228" s="29">
+      <c r="F228" s="30">
         <v>496.0</v>
       </c>
-      <c r="G228" s="29">
+      <c r="G228" s="30">
         <v>651.0</v>
       </c>
-      <c r="H228" s="30">
+      <c r="H228" s="31">
         <v>0.506</v>
       </c>
-      <c r="I228" s="31"/>
-      <c r="J228" s="28">
+      <c r="I228" s="32">
+        <v>2000.0</v>
+      </c>
+      <c r="J228" s="29">
         <v>2114.0</v>
       </c>
       <c r="K228" s="12">
         <f t="shared" si="1"/>
         <v>0.4576748214</v>
       </c>
+      <c r="L228" s="27"/>
     </row>
     <row r="229">
       <c r="A229" s="18" t="s">
@@ -8863,32 +8957,35 @@
       <c r="B229" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C229" s="27">
+      <c r="C229" s="28">
         <v>8323.0</v>
       </c>
-      <c r="D229" s="28">
+      <c r="D229" s="29">
         <v>2062.0</v>
       </c>
-      <c r="E229" s="28">
+      <c r="E229" s="29">
         <v>2491.0</v>
       </c>
-      <c r="F229" s="28">
+      <c r="F229" s="29">
         <v>1309.0</v>
       </c>
-      <c r="G229" s="29">
+      <c r="G229" s="30">
         <v>758.0</v>
       </c>
-      <c r="H229" s="30">
+      <c r="H229" s="31">
         <v>0.556</v>
       </c>
-      <c r="I229" s="31"/>
-      <c r="J229" s="28">
+      <c r="I229" s="32">
+        <v>2941.0</v>
+      </c>
+      <c r="J229" s="29">
         <v>3029.0</v>
       </c>
       <c r="K229" s="12">
         <f t="shared" si="1"/>
         <v>0.3639312748</v>
       </c>
+      <c r="L229" s="27"/>
     </row>
     <row r="230">
       <c r="A230" s="18" t="s">
@@ -8897,32 +8994,35 @@
       <c r="B230" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C230" s="27">
+      <c r="C230" s="28">
         <v>3703.0</v>
       </c>
-      <c r="D230" s="29">
+      <c r="D230" s="30">
         <v>489.0</v>
       </c>
-      <c r="E230" s="28">
+      <c r="E230" s="29">
         <v>1124.0</v>
       </c>
-      <c r="F230" s="29">
+      <c r="F230" s="30">
         <v>133.0</v>
       </c>
-      <c r="G230" s="29">
+      <c r="G230" s="30">
         <v>265.0</v>
       </c>
-      <c r="H230" s="30">
+      <c r="H230" s="31">
         <v>0.351</v>
       </c>
-      <c r="I230" s="31"/>
-      <c r="J230" s="28">
+      <c r="I230" s="26">
+        <v>485.0</v>
+      </c>
+      <c r="J230" s="29">
         <v>2270.0</v>
       </c>
       <c r="K230" s="12">
         <f t="shared" si="1"/>
         <v>0.6130164731</v>
       </c>
+      <c r="L230" s="27"/>
     </row>
     <row r="231">
       <c r="A231" s="18" t="s">
@@ -8931,32 +9031,35 @@
       <c r="B231" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C231" s="27">
+      <c r="C231" s="28">
         <v>2133.0</v>
       </c>
-      <c r="D231" s="29">
+      <c r="D231" s="30">
         <v>881.0</v>
       </c>
-      <c r="E231" s="29">
+      <c r="E231" s="30">
         <v>815.0</v>
       </c>
-      <c r="F231" s="29">
+      <c r="F231" s="30">
         <v>565.0</v>
       </c>
-      <c r="G231" s="29">
+      <c r="G231" s="30">
         <v>426.0</v>
       </c>
-      <c r="H231" s="30">
+      <c r="H231" s="31">
         <v>0.462</v>
       </c>
-      <c r="I231" s="31"/>
-      <c r="J231" s="28">
+      <c r="I231" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J231" s="29">
         <v>1557.0</v>
       </c>
       <c r="K231" s="12">
         <f t="shared" si="1"/>
         <v>0.7299578059</v>
       </c>
+      <c r="L231" s="27"/>
     </row>
     <row r="232">
       <c r="A232" s="18" t="s">
@@ -8965,32 +9068,35 @@
       <c r="B232" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C232" s="27">
+      <c r="C232" s="28">
         <v>9558.0</v>
       </c>
-      <c r="D232" s="28">
+      <c r="D232" s="29">
         <v>2374.0</v>
       </c>
-      <c r="E232" s="28">
+      <c r="E232" s="29">
         <v>4777.0</v>
       </c>
-      <c r="F232" s="28">
+      <c r="F232" s="29">
         <v>2234.0</v>
       </c>
-      <c r="G232" s="28">
+      <c r="G232" s="29">
         <v>1254.0</v>
       </c>
-      <c r="H232" s="30">
+      <c r="H232" s="31">
         <v>0.429</v>
       </c>
-      <c r="I232" s="31"/>
-      <c r="J232" s="28">
+      <c r="I232" s="32">
+        <v>1290.0</v>
+      </c>
+      <c r="J232" s="29">
         <v>3718.0</v>
       </c>
       <c r="K232" s="12">
         <f t="shared" si="1"/>
         <v>0.3889935133</v>
       </c>
+      <c r="L232" s="27"/>
     </row>
     <row r="233">
       <c r="A233" s="18" t="s">
@@ -8999,32 +9105,35 @@
       <c r="B233" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C233" s="27">
+      <c r="C233" s="28">
         <v>5434.0</v>
       </c>
-      <c r="D233" s="28">
+      <c r="D233" s="29">
         <v>1144.0</v>
       </c>
-      <c r="E233" s="28">
+      <c r="E233" s="29">
         <v>2471.0</v>
       </c>
-      <c r="F233" s="28">
+      <c r="F233" s="29">
         <v>1048.0</v>
       </c>
-      <c r="G233" s="29">
+      <c r="G233" s="30">
         <v>597.0</v>
       </c>
-      <c r="H233" s="30">
+      <c r="H233" s="31">
         <v>0.546</v>
       </c>
-      <c r="I233" s="31"/>
-      <c r="J233" s="28">
+      <c r="I233" s="26">
+        <v>64.0</v>
+      </c>
+      <c r="J233" s="29">
         <v>3186.0</v>
       </c>
       <c r="K233" s="12">
         <f t="shared" si="1"/>
         <v>0.5863084284</v>
       </c>
+      <c r="L233" s="27"/>
     </row>
     <row r="234">
       <c r="A234" s="18" t="s">
@@ -9033,32 +9142,35 @@
       <c r="B234" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C234" s="27">
+      <c r="C234" s="28">
         <v>11727.0</v>
       </c>
-      <c r="D234" s="28">
+      <c r="D234" s="29">
         <v>1624.0</v>
       </c>
-      <c r="E234" s="28">
+      <c r="E234" s="29">
         <v>5956.0</v>
       </c>
-      <c r="F234" s="29">
+      <c r="F234" s="30">
         <v>417.0</v>
       </c>
-      <c r="G234" s="28">
+      <c r="G234" s="29">
         <v>1058.0</v>
       </c>
-      <c r="H234" s="30">
+      <c r="H234" s="31">
         <v>0.569</v>
       </c>
-      <c r="I234" s="31"/>
-      <c r="J234" s="28">
+      <c r="I234" s="26">
+        <v>131.0</v>
+      </c>
+      <c r="J234" s="29">
         <v>5047.0</v>
       </c>
       <c r="K234" s="12">
         <f t="shared" si="1"/>
         <v>0.4303743498</v>
       </c>
+      <c r="L234" s="27"/>
     </row>
     <row r="235">
       <c r="A235" s="18" t="s">
@@ -9067,32 +9179,35 @@
       <c r="B235" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C235" s="27">
+      <c r="C235" s="28">
         <v>3787.0</v>
       </c>
-      <c r="D235" s="28">
+      <c r="D235" s="29">
         <v>1294.0</v>
       </c>
-      <c r="E235" s="28">
+      <c r="E235" s="29">
         <v>1479.0</v>
       </c>
-      <c r="F235" s="29">
+      <c r="F235" s="30">
         <v>562.0</v>
       </c>
-      <c r="G235" s="29">
+      <c r="G235" s="30">
         <v>583.0</v>
       </c>
-      <c r="H235" s="30">
+      <c r="H235" s="31">
         <v>0.479</v>
       </c>
-      <c r="I235" s="31"/>
-      <c r="J235" s="28">
+      <c r="I235" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J235" s="29">
         <v>1699.0</v>
       </c>
       <c r="K235" s="12">
         <f t="shared" si="1"/>
         <v>0.4486400845</v>
       </c>
+      <c r="L235" s="27"/>
     </row>
     <row r="236">
       <c r="A236" s="18" t="s">
@@ -9101,32 +9216,35 @@
       <c r="B236" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C236" s="27">
+      <c r="C236" s="28">
         <v>1965.0</v>
       </c>
-      <c r="D236" s="29">
+      <c r="D236" s="30">
         <v>584.0</v>
       </c>
-      <c r="E236" s="29">
+      <c r="E236" s="30">
         <v>837.0</v>
       </c>
-      <c r="F236" s="29">
+      <c r="F236" s="30">
         <v>216.0</v>
       </c>
-      <c r="G236" s="29">
+      <c r="G236" s="30">
         <v>212.0</v>
       </c>
-      <c r="H236" s="30">
+      <c r="H236" s="31">
         <v>0.588</v>
       </c>
-      <c r="I236" s="31"/>
-      <c r="J236" s="28">
+      <c r="I236" s="26">
+        <v>225.0</v>
+      </c>
+      <c r="J236" s="29">
         <v>1054.0</v>
       </c>
       <c r="K236" s="12">
         <f t="shared" si="1"/>
         <v>0.5363867684</v>
       </c>
+      <c r="L236" s="27"/>
     </row>
     <row r="237">
       <c r="A237" s="18" t="s">
@@ -9135,32 +9253,35 @@
       <c r="B237" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C237" s="27">
+      <c r="C237" s="28">
         <v>11056.0</v>
       </c>
-      <c r="D237" s="28">
+      <c r="D237" s="29">
         <v>3966.0</v>
       </c>
-      <c r="E237" s="28">
+      <c r="E237" s="29">
         <v>3316.0</v>
       </c>
-      <c r="F237" s="28">
+      <c r="F237" s="29">
         <v>1113.0</v>
       </c>
-      <c r="G237" s="28">
+      <c r="G237" s="29">
         <v>1063.0</v>
       </c>
-      <c r="H237" s="30">
+      <c r="H237" s="31">
         <v>0.212</v>
       </c>
-      <c r="I237" s="31"/>
-      <c r="J237" s="28">
+      <c r="I237" s="26">
+        <v>196.0</v>
+      </c>
+      <c r="J237" s="29">
         <v>5820.0</v>
       </c>
       <c r="K237" s="12">
         <f t="shared" si="1"/>
         <v>0.5264109986</v>
       </c>
+      <c r="L237" s="27"/>
     </row>
     <row r="238">
       <c r="A238" s="18" t="s">
@@ -9169,32 +9290,35 @@
       <c r="B238" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C238" s="27">
+      <c r="C238" s="28">
         <v>1102.0</v>
       </c>
-      <c r="D238" s="29">
+      <c r="D238" s="30">
         <v>506.0</v>
       </c>
-      <c r="E238" s="29">
+      <c r="E238" s="30">
         <v>357.0</v>
       </c>
-      <c r="F238" s="29">
+      <c r="F238" s="30">
         <v>186.0</v>
       </c>
-      <c r="G238" s="29">
+      <c r="G238" s="30">
         <v>264.0</v>
       </c>
-      <c r="H238" s="30">
+      <c r="H238" s="31">
         <v>0.414</v>
       </c>
-      <c r="I238" s="31"/>
-      <c r="J238" s="29">
+      <c r="I238" s="26">
+        <v>77.0</v>
+      </c>
+      <c r="J238" s="30">
         <v>724.0</v>
       </c>
       <c r="K238" s="12">
         <f t="shared" si="1"/>
         <v>0.6569872958</v>
       </c>
+      <c r="L238" s="27"/>
     </row>
     <row r="239">
       <c r="A239" s="18" t="s">
@@ -9203,32 +9327,35 @@
       <c r="B239" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C239" s="27">
+      <c r="C239" s="28">
         <v>3599.0</v>
       </c>
-      <c r="D239" s="28">
+      <c r="D239" s="29">
         <v>1253.0</v>
       </c>
-      <c r="E239" s="28">
+      <c r="E239" s="29">
         <v>1587.0</v>
       </c>
-      <c r="F239" s="29">
+      <c r="F239" s="30">
         <v>521.0</v>
       </c>
-      <c r="G239" s="29">
+      <c r="G239" s="30">
         <v>476.0</v>
       </c>
-      <c r="H239" s="30">
+      <c r="H239" s="31">
         <v>0.537</v>
       </c>
-      <c r="I239" s="31"/>
-      <c r="J239" s="28">
+      <c r="I239" s="26">
+        <v>384.0</v>
+      </c>
+      <c r="J239" s="29">
         <v>2480.0</v>
       </c>
       <c r="K239" s="12">
         <f t="shared" si="1"/>
         <v>0.6890803001</v>
       </c>
+      <c r="L239" s="27"/>
     </row>
     <row r="240">
       <c r="A240" s="18" t="s">
@@ -9237,32 +9364,35 @@
       <c r="B240" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C240" s="27">
+      <c r="C240" s="28">
         <v>1062.0</v>
       </c>
-      <c r="D240" s="29">
+      <c r="D240" s="30">
         <v>348.0</v>
       </c>
-      <c r="E240" s="29">
+      <c r="E240" s="30">
         <v>376.0</v>
       </c>
-      <c r="F240" s="29">
+      <c r="F240" s="30">
         <v>30.0</v>
       </c>
-      <c r="G240" s="29">
+      <c r="G240" s="30">
         <v>186.0</v>
       </c>
-      <c r="H240" s="30">
+      <c r="H240" s="31">
         <v>0.532</v>
       </c>
-      <c r="I240" s="31"/>
-      <c r="J240" s="29">
+      <c r="I240" s="26">
+        <v>91.0</v>
+      </c>
+      <c r="J240" s="30">
         <v>671.0</v>
       </c>
       <c r="K240" s="12">
         <f t="shared" si="1"/>
         <v>0.631826742</v>
       </c>
+      <c r="L240" s="27"/>
     </row>
     <row r="241">
       <c r="A241" s="18" t="s">
@@ -9271,32 +9401,35 @@
       <c r="B241" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C241" s="27">
+      <c r="C241" s="28">
         <v>2846.0</v>
       </c>
-      <c r="D241" s="28">
+      <c r="D241" s="29">
         <v>1063.0</v>
       </c>
-      <c r="E241" s="28">
+      <c r="E241" s="29">
         <v>1387.0</v>
       </c>
-      <c r="F241" s="29">
+      <c r="F241" s="30">
         <v>381.0</v>
       </c>
-      <c r="G241" s="29">
+      <c r="G241" s="30">
         <v>327.0</v>
       </c>
-      <c r="H241" s="30">
+      <c r="H241" s="31">
         <v>0.498</v>
       </c>
-      <c r="I241" s="31"/>
-      <c r="J241" s="28">
+      <c r="I241" s="26">
+        <v>569.0</v>
+      </c>
+      <c r="J241" s="29">
         <v>2056.0</v>
       </c>
       <c r="K241" s="12">
         <f t="shared" si="1"/>
         <v>0.722417428</v>
       </c>
+      <c r="L241" s="27"/>
     </row>
     <row r="242">
       <c r="A242" s="18" t="s">
@@ -9305,32 +9438,35 @@
       <c r="B242" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C242" s="27">
+      <c r="C242" s="28">
         <v>2282.0</v>
       </c>
-      <c r="D242" s="29">
+      <c r="D242" s="30">
         <v>713.0</v>
       </c>
-      <c r="E242" s="29">
+      <c r="E242" s="30">
         <v>940.0</v>
       </c>
-      <c r="F242" s="29">
+      <c r="F242" s="30">
         <v>418.0</v>
       </c>
-      <c r="G242" s="29">
+      <c r="G242" s="30">
         <v>175.0</v>
       </c>
-      <c r="H242" s="30">
+      <c r="H242" s="31">
         <v>0.6</v>
       </c>
-      <c r="I242" s="31"/>
-      <c r="J242" s="28">
+      <c r="I242" s="26">
+        <v>147.0</v>
+      </c>
+      <c r="J242" s="29">
         <v>1059.0</v>
       </c>
       <c r="K242" s="12">
         <f t="shared" si="1"/>
         <v>0.4640666082</v>
       </c>
+      <c r="L242" s="27"/>
     </row>
     <row r="243">
       <c r="A243" s="18" t="s">
@@ -9339,32 +9475,35 @@
       <c r="B243" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C243" s="27">
+      <c r="C243" s="28">
         <v>4048.0</v>
       </c>
-      <c r="D243" s="28">
+      <c r="D243" s="29">
         <v>1008.0</v>
       </c>
-      <c r="E243" s="28">
+      <c r="E243" s="29">
         <v>1729.0</v>
       </c>
-      <c r="F243" s="29">
+      <c r="F243" s="30">
         <v>428.0</v>
       </c>
-      <c r="G243" s="29">
+      <c r="G243" s="30">
         <v>577.0</v>
       </c>
-      <c r="H243" s="30">
+      <c r="H243" s="31">
         <v>0.58</v>
       </c>
-      <c r="I243" s="31"/>
-      <c r="J243" s="28">
+      <c r="I243" s="26">
+        <v>895.0</v>
+      </c>
+      <c r="J243" s="29">
         <v>1209.0</v>
       </c>
       <c r="K243" s="12">
         <f t="shared" si="1"/>
         <v>0.2986660079</v>
       </c>
+      <c r="L243" s="27"/>
     </row>
     <row r="244">
       <c r="A244" s="18" t="s">
@@ -9373,32 +9512,35 @@
       <c r="B244" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C244" s="27">
+      <c r="C244" s="28">
         <v>14455.0</v>
       </c>
-      <c r="D244" s="28">
+      <c r="D244" s="29">
         <v>2219.0</v>
       </c>
-      <c r="E244" s="28">
+      <c r="E244" s="29">
         <v>4936.0</v>
       </c>
-      <c r="F244" s="28">
+      <c r="F244" s="29">
         <v>1512.0</v>
       </c>
-      <c r="G244" s="28">
+      <c r="G244" s="29">
         <v>1392.0</v>
       </c>
-      <c r="H244" s="30">
+      <c r="H244" s="31">
         <v>0.46</v>
       </c>
-      <c r="I244" s="31"/>
-      <c r="J244" s="28">
+      <c r="I244" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J244" s="29">
         <v>9936.0</v>
       </c>
       <c r="K244" s="12">
         <f t="shared" si="1"/>
         <v>0.6873746109</v>
       </c>
+      <c r="L244" s="27"/>
     </row>
     <row r="245">
       <c r="A245" s="18" t="s">
@@ -9407,32 +9549,35 @@
       <c r="B245" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C245" s="27">
+      <c r="C245" s="28">
         <v>15268.0</v>
       </c>
-      <c r="D245" s="28">
+      <c r="D245" s="29">
         <v>2451.0</v>
       </c>
-      <c r="E245" s="28">
+      <c r="E245" s="29">
         <v>4622.0</v>
       </c>
-      <c r="F245" s="28">
+      <c r="F245" s="29">
         <v>3803.0</v>
       </c>
-      <c r="G245" s="28">
+      <c r="G245" s="29">
         <v>1439.0</v>
       </c>
-      <c r="H245" s="30">
+      <c r="H245" s="31">
         <v>0.418</v>
       </c>
-      <c r="I245" s="31"/>
-      <c r="J245" s="28">
+      <c r="I245" s="26">
+        <v>55.0</v>
+      </c>
+      <c r="J245" s="29">
         <v>6976.0</v>
       </c>
       <c r="K245" s="12">
         <f t="shared" si="1"/>
         <v>0.4569033272</v>
       </c>
+      <c r="L245" s="27"/>
     </row>
     <row r="246">
       <c r="A246" s="18" t="s">
@@ -9441,32 +9586,35 @@
       <c r="B246" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C246" s="27">
+      <c r="C246" s="28">
         <v>6171.0</v>
       </c>
-      <c r="D246" s="28">
+      <c r="D246" s="29">
         <v>2075.0</v>
       </c>
-      <c r="E246" s="28">
+      <c r="E246" s="29">
         <v>2892.0</v>
       </c>
-      <c r="F246" s="28">
+      <c r="F246" s="29">
         <v>1245.0</v>
       </c>
-      <c r="G246" s="28">
+      <c r="G246" s="29">
         <v>1103.0</v>
       </c>
-      <c r="H246" s="30">
+      <c r="H246" s="31">
         <v>0.477</v>
       </c>
-      <c r="I246" s="31"/>
-      <c r="J246" s="28">
+      <c r="I246" s="26">
+        <v>447.0</v>
+      </c>
+      <c r="J246" s="29">
         <v>3820.0</v>
       </c>
       <c r="K246" s="12">
         <f t="shared" si="1"/>
         <v>0.6190244693</v>
       </c>
+      <c r="L246" s="27"/>
     </row>
     <row r="247">
       <c r="A247" s="18" t="s">
@@ -9475,32 +9623,35 @@
       <c r="B247" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C247" s="27">
+      <c r="C247" s="28">
         <v>4526.0</v>
       </c>
-      <c r="D247" s="29">
+      <c r="D247" s="30">
         <v>829.0</v>
       </c>
-      <c r="E247" s="28">
+      <c r="E247" s="29">
         <v>1888.0</v>
       </c>
-      <c r="F247" s="29">
+      <c r="F247" s="30">
         <v>346.0</v>
       </c>
-      <c r="G247" s="29">
+      <c r="G247" s="30">
         <v>362.0</v>
       </c>
-      <c r="H247" s="30">
+      <c r="H247" s="31">
         <v>0.524</v>
       </c>
-      <c r="I247" s="31"/>
-      <c r="J247" s="28">
+      <c r="I247" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J247" s="29">
         <v>2865.0</v>
       </c>
       <c r="K247" s="12">
         <f t="shared" si="1"/>
         <v>0.6330092797</v>
       </c>
+      <c r="L247" s="27"/>
     </row>
     <row r="248">
       <c r="A248" s="18" t="s">
@@ -9509,32 +9660,35 @@
       <c r="B248" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C248" s="27">
+      <c r="C248" s="28">
         <v>10865.0</v>
       </c>
-      <c r="D248" s="28">
+      <c r="D248" s="29">
         <v>3611.0</v>
       </c>
-      <c r="E248" s="28">
+      <c r="E248" s="29">
         <v>4091.0</v>
       </c>
-      <c r="F248" s="28">
+      <c r="F248" s="29">
         <v>1031.0</v>
       </c>
-      <c r="G248" s="28">
+      <c r="G248" s="29">
         <v>1709.0</v>
       </c>
-      <c r="H248" s="30">
+      <c r="H248" s="31">
         <v>0.452</v>
       </c>
-      <c r="I248" s="31"/>
-      <c r="J248" s="28">
+      <c r="I248" s="26">
+        <v>34.0</v>
+      </c>
+      <c r="J248" s="29">
         <v>8985.0</v>
       </c>
       <c r="K248" s="12">
         <f t="shared" si="1"/>
         <v>0.8269673263</v>
       </c>
+      <c r="L248" s="27"/>
     </row>
     <row r="249">
       <c r="A249" s="18" t="s">
@@ -9543,22 +9697,25 @@
       <c r="B249" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C249" s="27">
+      <c r="C249" s="28">
         <v>2432.0</v>
       </c>
-      <c r="D249" s="31"/>
-      <c r="E249" s="31"/>
-      <c r="F249" s="29">
+      <c r="D249" s="33"/>
+      <c r="E249" s="33"/>
+      <c r="F249" s="30">
         <v>19.0</v>
       </c>
-      <c r="G249" s="31"/>
-      <c r="H249" s="31"/>
-      <c r="I249" s="31"/>
-      <c r="J249" s="31"/>
+      <c r="G249" s="33"/>
+      <c r="H249" s="33"/>
+      <c r="I249" s="32">
+        <v>2285.0</v>
+      </c>
+      <c r="J249" s="33"/>
       <c r="K249" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L249" s="27"/>
     </row>
     <row r="250">
       <c r="A250" s="18" t="s">
@@ -9567,32 +9724,35 @@
       <c r="B250" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C250" s="27">
+      <c r="C250" s="28">
         <v>1574.0</v>
       </c>
-      <c r="D250" s="29">
+      <c r="D250" s="30">
         <v>122.0</v>
       </c>
-      <c r="E250" s="29">
+      <c r="E250" s="30">
         <v>633.0</v>
       </c>
-      <c r="F250" s="29">
+      <c r="F250" s="30">
         <v>64.0</v>
       </c>
-      <c r="G250" s="29">
+      <c r="G250" s="30">
         <v>107.0</v>
       </c>
-      <c r="H250" s="30">
+      <c r="H250" s="31">
         <v>0.492</v>
       </c>
-      <c r="I250" s="31"/>
-      <c r="J250" s="29">
+      <c r="I250" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J250" s="30">
         <v>686.0</v>
       </c>
       <c r="K250" s="12">
         <f t="shared" si="1"/>
         <v>0.4358322745</v>
       </c>
+      <c r="L250" s="27"/>
     </row>
     <row r="251">
       <c r="A251" s="18" t="s">
@@ -9601,32 +9761,35 @@
       <c r="B251" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C251" s="27">
+      <c r="C251" s="28">
         <v>3322.0</v>
       </c>
-      <c r="D251" s="29">
+      <c r="D251" s="30">
         <v>915.0</v>
       </c>
-      <c r="E251" s="29">
+      <c r="E251" s="30">
         <v>998.0</v>
       </c>
-      <c r="F251" s="29">
+      <c r="F251" s="30">
         <v>567.0</v>
       </c>
-      <c r="G251" s="29">
+      <c r="G251" s="30">
         <v>522.0</v>
       </c>
-      <c r="H251" s="30">
+      <c r="H251" s="31">
         <v>0.482</v>
       </c>
-      <c r="I251" s="31"/>
-      <c r="J251" s="28">
+      <c r="I251" s="26">
+        <v>474.0</v>
+      </c>
+      <c r="J251" s="29">
         <v>2151.0</v>
       </c>
       <c r="K251" s="12">
         <f t="shared" si="1"/>
         <v>0.6475015051</v>
       </c>
+      <c r="L251" s="27"/>
     </row>
     <row r="252">
       <c r="A252" s="18" t="s">
@@ -9635,32 +9798,35 @@
       <c r="B252" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C252" s="27">
+      <c r="C252" s="28">
         <v>1698.0</v>
       </c>
-      <c r="D252" s="29">
+      <c r="D252" s="30">
         <v>672.0</v>
       </c>
-      <c r="E252" s="29">
+      <c r="E252" s="30">
         <v>597.0</v>
       </c>
-      <c r="F252" s="29">
+      <c r="F252" s="30">
         <v>545.0</v>
       </c>
-      <c r="G252" s="29">
+      <c r="G252" s="30">
         <v>265.0</v>
       </c>
-      <c r="H252" s="30">
+      <c r="H252" s="31">
         <v>0.399</v>
       </c>
-      <c r="I252" s="31"/>
-      <c r="J252" s="29">
+      <c r="I252" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J252" s="30">
         <v>805.0</v>
       </c>
       <c r="K252" s="12">
         <f t="shared" si="1"/>
         <v>0.4740871614</v>
       </c>
+      <c r="L252" s="27"/>
     </row>
     <row r="253">
       <c r="A253" s="18" t="s">
@@ -9669,32 +9835,35 @@
       <c r="B253" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C253" s="27">
+      <c r="C253" s="28">
         <v>8990.0</v>
       </c>
-      <c r="D253" s="29">
+      <c r="D253" s="30">
         <v>563.0</v>
       </c>
-      <c r="E253" s="29">
+      <c r="E253" s="30">
         <v>937.0</v>
       </c>
-      <c r="F253" s="28">
+      <c r="F253" s="29">
         <v>1116.0</v>
       </c>
-      <c r="G253" s="28">
+      <c r="G253" s="29">
         <v>1147.0</v>
       </c>
-      <c r="H253" s="30">
+      <c r="H253" s="31">
         <v>0.413</v>
       </c>
-      <c r="I253" s="31"/>
-      <c r="J253" s="28">
+      <c r="I253" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J253" s="29">
         <v>4840.0</v>
       </c>
       <c r="K253" s="12">
         <f t="shared" si="1"/>
         <v>0.5383759733</v>
       </c>
+      <c r="L253" s="27"/>
     </row>
     <row r="254">
       <c r="A254" s="18" t="s">
@@ -9703,32 +9872,35 @@
       <c r="B254" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C254" s="27">
+      <c r="C254" s="28">
         <v>17520.0</v>
       </c>
-      <c r="D254" s="28">
+      <c r="D254" s="29">
         <v>3112.0</v>
       </c>
-      <c r="E254" s="28">
+      <c r="E254" s="29">
         <v>6998.0</v>
       </c>
-      <c r="F254" s="28">
+      <c r="F254" s="29">
         <v>5146.0</v>
       </c>
-      <c r="G254" s="28">
+      <c r="G254" s="29">
         <v>2581.0</v>
       </c>
-      <c r="H254" s="30">
+      <c r="H254" s="31">
         <v>0.4</v>
       </c>
-      <c r="I254" s="31"/>
-      <c r="J254" s="28">
+      <c r="I254" s="32">
+        <v>15156.0</v>
+      </c>
+      <c r="J254" s="29">
         <v>6911.0</v>
       </c>
       <c r="K254" s="12">
         <f t="shared" si="1"/>
         <v>0.3944634703</v>
       </c>
+      <c r="L254" s="27"/>
     </row>
     <row r="255">
       <c r="A255" s="18" t="s">
@@ -9737,32 +9909,35 @@
       <c r="B255" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C255" s="27">
+      <c r="C255" s="28">
         <v>1593.0</v>
       </c>
-      <c r="D255" s="29" t="s">
+      <c r="D255" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="E255" s="29">
+      <c r="E255" s="30">
         <v>585.0</v>
       </c>
-      <c r="F255" s="29">
+      <c r="F255" s="30">
         <v>216.0</v>
       </c>
-      <c r="G255" s="29">
+      <c r="G255" s="30">
         <v>276.0</v>
       </c>
-      <c r="H255" s="30">
+      <c r="H255" s="31">
         <v>0.468</v>
       </c>
-      <c r="I255" s="31"/>
-      <c r="J255" s="29">
+      <c r="I255" s="32">
+        <v>1266.0</v>
+      </c>
+      <c r="J255" s="30">
         <v>936.0</v>
       </c>
       <c r="K255" s="12">
         <f t="shared" si="1"/>
         <v>0.5875706215</v>
       </c>
+      <c r="L255" s="27"/>
     </row>
     <row r="256">
       <c r="A256" s="18" t="s">
@@ -9771,32 +9946,35 @@
       <c r="B256" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C256" s="27">
+      <c r="C256" s="28">
         <v>5576.0</v>
       </c>
-      <c r="D256" s="28">
+      <c r="D256" s="29">
         <v>1089.0</v>
       </c>
-      <c r="E256" s="28">
+      <c r="E256" s="29">
         <v>1064.0</v>
       </c>
-      <c r="F256" s="28">
+      <c r="F256" s="29">
         <v>1208.0</v>
       </c>
-      <c r="G256" s="29">
+      <c r="G256" s="30">
         <v>620.0</v>
       </c>
-      <c r="H256" s="30">
+      <c r="H256" s="31">
         <v>0.335</v>
       </c>
-      <c r="I256" s="31"/>
-      <c r="J256" s="28">
+      <c r="I256" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J256" s="29">
         <v>4506.0</v>
       </c>
       <c r="K256" s="12">
         <f t="shared" si="1"/>
         <v>0.8081061693</v>
       </c>
+      <c r="L256" s="27"/>
     </row>
     <row r="257">
       <c r="A257" s="18" t="s">
@@ -9805,32 +9983,35 @@
       <c r="B257" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C257" s="32">
+      <c r="C257" s="34">
         <v>828.0</v>
       </c>
-      <c r="D257" s="29">
+      <c r="D257" s="30">
         <v>257.0</v>
       </c>
-      <c r="E257" s="29">
+      <c r="E257" s="30">
         <v>362.0</v>
       </c>
-      <c r="F257" s="29">
+      <c r="F257" s="30">
         <v>173.0</v>
       </c>
-      <c r="G257" s="29">
+      <c r="G257" s="30">
         <v>184.0</v>
       </c>
-      <c r="H257" s="30">
+      <c r="H257" s="31">
         <v>0.411</v>
       </c>
-      <c r="I257" s="31"/>
-      <c r="J257" s="29">
+      <c r="I257" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J257" s="30">
         <v>795.0</v>
       </c>
       <c r="K257" s="12">
         <f t="shared" si="1"/>
         <v>0.9601449275</v>
       </c>
+      <c r="L257" s="27"/>
     </row>
     <row r="258">
       <c r="A258" s="18" t="s">
@@ -9839,32 +10020,35 @@
       <c r="B258" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C258" s="27">
+      <c r="C258" s="28">
         <v>5480.0</v>
       </c>
-      <c r="D258" s="28">
+      <c r="D258" s="29">
         <v>1649.0</v>
       </c>
-      <c r="E258" s="28">
+      <c r="E258" s="29">
         <v>2600.0</v>
       </c>
-      <c r="F258" s="29" t="s">
+      <c r="F258" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="G258" s="29">
+      <c r="G258" s="30">
         <v>497.0</v>
       </c>
-      <c r="H258" s="30">
+      <c r="H258" s="31">
         <v>0.594</v>
       </c>
-      <c r="I258" s="31"/>
-      <c r="J258" s="28">
+      <c r="I258" s="26">
+        <v>422.0</v>
+      </c>
+      <c r="J258" s="29">
         <v>4800.0</v>
       </c>
       <c r="K258" s="12">
         <f t="shared" si="1"/>
         <v>0.8759124088</v>
       </c>
+      <c r="L258" s="27"/>
     </row>
     <row r="259">
       <c r="A259" s="18" t="s">
@@ -9873,32 +10057,35 @@
       <c r="B259" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C259" s="27">
+      <c r="C259" s="28">
         <v>5687.0</v>
       </c>
-      <c r="D259" s="28">
+      <c r="D259" s="29">
         <v>1749.0</v>
       </c>
-      <c r="E259" s="28">
+      <c r="E259" s="29">
         <v>2408.0</v>
       </c>
-      <c r="F259" s="29">
+      <c r="F259" s="30">
         <v>655.0</v>
       </c>
-      <c r="G259" s="29">
+      <c r="G259" s="30">
         <v>563.0</v>
       </c>
-      <c r="H259" s="30">
+      <c r="H259" s="31">
         <v>0.505</v>
       </c>
-      <c r="I259" s="31"/>
-      <c r="J259" s="28">
+      <c r="I259" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J259" s="29">
         <v>2866.0</v>
       </c>
       <c r="K259" s="12">
         <f t="shared" si="1"/>
         <v>0.5039563918</v>
       </c>
+      <c r="L259" s="27"/>
     </row>
     <row r="260">
       <c r="A260" s="18" t="s">
@@ -9907,32 +10094,35 @@
       <c r="B260" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C260" s="27">
+      <c r="C260" s="28">
         <v>6616.0</v>
       </c>
-      <c r="D260" s="29">
+      <c r="D260" s="30">
         <v>51.0</v>
       </c>
-      <c r="E260" s="28">
+      <c r="E260" s="29">
         <v>3038.0</v>
       </c>
-      <c r="F260" s="28">
+      <c r="F260" s="29">
         <v>1303.0</v>
       </c>
-      <c r="G260" s="28">
+      <c r="G260" s="29">
         <v>1037.0</v>
       </c>
-      <c r="H260" s="30">
+      <c r="H260" s="31">
         <v>0.516</v>
       </c>
-      <c r="I260" s="31"/>
-      <c r="J260" s="28">
+      <c r="I260" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J260" s="29">
         <v>3135.0</v>
       </c>
       <c r="K260" s="12">
         <f t="shared" si="1"/>
         <v>0.4738512696</v>
       </c>
+      <c r="L260" s="27"/>
     </row>
     <row r="261">
       <c r="A261" s="18" t="s">
@@ -9941,2985 +10131,2988 @@
       <c r="B261" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C261" s="32">
+      <c r="C261" s="34">
         <v>688.0</v>
       </c>
-      <c r="D261" s="29">
+      <c r="D261" s="30">
         <v>162.0</v>
       </c>
-      <c r="E261" s="29">
+      <c r="E261" s="30">
         <v>159.0</v>
       </c>
-      <c r="F261" s="31"/>
-      <c r="G261" s="29">
+      <c r="F261" s="33"/>
+      <c r="G261" s="30">
         <v>60.0</v>
       </c>
-      <c r="H261" s="30">
+      <c r="H261" s="31">
         <v>0.704</v>
       </c>
-      <c r="I261" s="31"/>
-      <c r="J261" s="29">
+      <c r="I261" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J261" s="30">
         <v>502.0</v>
       </c>
       <c r="K261" s="12">
         <f t="shared" si="1"/>
         <v>0.7296511628</v>
       </c>
+      <c r="L261" s="36"/>
     </row>
     <row r="262">
-      <c r="A262" s="33"/>
+      <c r="A262" s="37"/>
       <c r="I262" s="20"/>
     </row>
     <row r="263">
-      <c r="A263" s="33"/>
+      <c r="A263" s="37"/>
       <c r="I263" s="20"/>
     </row>
     <row r="264">
-      <c r="A264" s="33"/>
+      <c r="A264" s="37"/>
       <c r="I264" s="20"/>
     </row>
     <row r="265">
-      <c r="A265" s="33"/>
+      <c r="A265" s="37"/>
       <c r="I265" s="20"/>
     </row>
     <row r="266">
-      <c r="A266" s="33"/>
+      <c r="A266" s="37"/>
       <c r="I266" s="20"/>
     </row>
     <row r="267">
-      <c r="A267" s="33"/>
+      <c r="A267" s="37"/>
       <c r="I267" s="20"/>
     </row>
     <row r="268">
-      <c r="A268" s="33"/>
+      <c r="A268" s="37"/>
       <c r="I268" s="20"/>
     </row>
     <row r="269">
-      <c r="A269" s="33"/>
+      <c r="A269" s="37"/>
       <c r="I269" s="20"/>
     </row>
     <row r="270">
-      <c r="A270" s="33"/>
+      <c r="A270" s="37"/>
       <c r="I270" s="20"/>
     </row>
     <row r="271">
-      <c r="A271" s="33"/>
+      <c r="A271" s="37"/>
       <c r="I271" s="20"/>
     </row>
     <row r="272">
-      <c r="A272" s="33"/>
+      <c r="A272" s="37"/>
       <c r="I272" s="20"/>
     </row>
     <row r="273">
-      <c r="A273" s="33"/>
+      <c r="A273" s="37"/>
       <c r="I273" s="20"/>
     </row>
     <row r="274">
-      <c r="A274" s="33"/>
+      <c r="A274" s="37"/>
       <c r="I274" s="20"/>
     </row>
     <row r="275">
-      <c r="A275" s="33"/>
+      <c r="A275" s="37"/>
       <c r="I275" s="20"/>
     </row>
     <row r="276">
-      <c r="A276" s="33"/>
+      <c r="A276" s="37"/>
       <c r="I276" s="20"/>
     </row>
     <row r="277">
-      <c r="A277" s="33"/>
+      <c r="A277" s="37"/>
       <c r="I277" s="20"/>
     </row>
     <row r="278">
-      <c r="A278" s="33"/>
+      <c r="A278" s="37"/>
       <c r="I278" s="20"/>
     </row>
     <row r="279">
-      <c r="A279" s="33"/>
+      <c r="A279" s="37"/>
       <c r="I279" s="20"/>
     </row>
     <row r="280">
-      <c r="A280" s="33"/>
+      <c r="A280" s="37"/>
       <c r="I280" s="20"/>
     </row>
     <row r="281">
-      <c r="A281" s="33"/>
+      <c r="A281" s="37"/>
       <c r="I281" s="20"/>
     </row>
     <row r="282">
-      <c r="A282" s="33"/>
+      <c r="A282" s="37"/>
       <c r="I282" s="20"/>
     </row>
     <row r="283">
-      <c r="A283" s="33"/>
+      <c r="A283" s="37"/>
       <c r="I283" s="20"/>
     </row>
     <row r="284">
-      <c r="A284" s="33"/>
+      <c r="A284" s="37"/>
       <c r="I284" s="20"/>
     </row>
     <row r="285">
-      <c r="A285" s="33"/>
+      <c r="A285" s="37"/>
       <c r="I285" s="20"/>
     </row>
     <row r="286">
-      <c r="A286" s="33"/>
+      <c r="A286" s="37"/>
       <c r="I286" s="20"/>
     </row>
     <row r="287">
-      <c r="A287" s="33"/>
+      <c r="A287" s="37"/>
       <c r="I287" s="20"/>
     </row>
     <row r="288">
-      <c r="A288" s="33"/>
+      <c r="A288" s="37"/>
       <c r="I288" s="20"/>
     </row>
     <row r="289">
-      <c r="A289" s="33"/>
+      <c r="A289" s="37"/>
       <c r="I289" s="20"/>
     </row>
     <row r="290">
-      <c r="A290" s="33"/>
+      <c r="A290" s="37"/>
       <c r="I290" s="20"/>
     </row>
     <row r="291">
-      <c r="A291" s="33"/>
+      <c r="A291" s="37"/>
       <c r="I291" s="20"/>
     </row>
     <row r="292">
-      <c r="A292" s="33"/>
+      <c r="A292" s="37"/>
       <c r="I292" s="20"/>
     </row>
     <row r="293">
-      <c r="A293" s="33"/>
+      <c r="A293" s="37"/>
       <c r="I293" s="20"/>
     </row>
     <row r="294">
-      <c r="A294" s="33"/>
+      <c r="A294" s="37"/>
       <c r="I294" s="20"/>
     </row>
     <row r="295">
-      <c r="A295" s="33"/>
+      <c r="A295" s="37"/>
       <c r="I295" s="20"/>
     </row>
     <row r="296">
-      <c r="A296" s="33"/>
+      <c r="A296" s="37"/>
       <c r="I296" s="20"/>
     </row>
     <row r="297">
-      <c r="A297" s="33"/>
+      <c r="A297" s="37"/>
       <c r="I297" s="20"/>
     </row>
     <row r="298">
-      <c r="A298" s="33"/>
+      <c r="A298" s="37"/>
       <c r="I298" s="20"/>
     </row>
     <row r="299">
-      <c r="A299" s="33"/>
+      <c r="A299" s="37"/>
       <c r="I299" s="20"/>
     </row>
     <row r="300">
-      <c r="A300" s="33"/>
+      <c r="A300" s="37"/>
       <c r="I300" s="20"/>
     </row>
     <row r="301">
-      <c r="A301" s="33"/>
+      <c r="A301" s="37"/>
       <c r="I301" s="20"/>
     </row>
     <row r="302">
-      <c r="A302" s="33"/>
+      <c r="A302" s="37"/>
       <c r="I302" s="20"/>
     </row>
     <row r="303">
-      <c r="A303" s="33"/>
+      <c r="A303" s="37"/>
       <c r="I303" s="20"/>
     </row>
     <row r="304">
-      <c r="A304" s="33"/>
+      <c r="A304" s="37"/>
       <c r="I304" s="20"/>
     </row>
     <row r="305">
-      <c r="A305" s="33"/>
+      <c r="A305" s="37"/>
       <c r="I305" s="20"/>
     </row>
     <row r="306">
-      <c r="A306" s="33"/>
+      <c r="A306" s="37"/>
       <c r="I306" s="20"/>
     </row>
     <row r="307">
-      <c r="A307" s="33"/>
+      <c r="A307" s="37"/>
       <c r="I307" s="20"/>
     </row>
     <row r="308">
-      <c r="A308" s="33"/>
+      <c r="A308" s="37"/>
       <c r="I308" s="20"/>
     </row>
     <row r="309">
-      <c r="A309" s="33"/>
+      <c r="A309" s="37"/>
       <c r="I309" s="20"/>
     </row>
     <row r="310">
-      <c r="A310" s="33"/>
+      <c r="A310" s="37"/>
       <c r="I310" s="20"/>
     </row>
     <row r="311">
-      <c r="A311" s="33"/>
+      <c r="A311" s="37"/>
       <c r="I311" s="20"/>
     </row>
     <row r="312">
-      <c r="A312" s="33"/>
+      <c r="A312" s="37"/>
       <c r="I312" s="20"/>
     </row>
     <row r="313">
-      <c r="A313" s="33"/>
+      <c r="A313" s="37"/>
       <c r="I313" s="20"/>
     </row>
     <row r="314">
-      <c r="A314" s="33"/>
+      <c r="A314" s="37"/>
       <c r="I314" s="20"/>
     </row>
     <row r="315">
-      <c r="A315" s="33"/>
+      <c r="A315" s="37"/>
       <c r="I315" s="20"/>
     </row>
     <row r="316">
-      <c r="A316" s="33"/>
+      <c r="A316" s="37"/>
       <c r="I316" s="20"/>
     </row>
     <row r="317">
-      <c r="A317" s="33"/>
+      <c r="A317" s="37"/>
       <c r="I317" s="20"/>
     </row>
     <row r="318">
-      <c r="A318" s="33"/>
+      <c r="A318" s="37"/>
       <c r="I318" s="20"/>
     </row>
     <row r="319">
-      <c r="A319" s="33"/>
+      <c r="A319" s="37"/>
       <c r="I319" s="20"/>
     </row>
     <row r="320">
-      <c r="A320" s="33"/>
+      <c r="A320" s="37"/>
       <c r="I320" s="20"/>
     </row>
     <row r="321">
-      <c r="A321" s="33"/>
+      <c r="A321" s="37"/>
       <c r="I321" s="20"/>
     </row>
     <row r="322">
-      <c r="A322" s="33"/>
+      <c r="A322" s="37"/>
       <c r="I322" s="20"/>
     </row>
     <row r="323">
-      <c r="A323" s="33"/>
+      <c r="A323" s="37"/>
       <c r="I323" s="20"/>
     </row>
     <row r="324">
-      <c r="A324" s="33"/>
+      <c r="A324" s="37"/>
       <c r="I324" s="20"/>
     </row>
     <row r="325">
-      <c r="A325" s="33"/>
+      <c r="A325" s="37"/>
       <c r="I325" s="20"/>
     </row>
     <row r="326">
-      <c r="A326" s="33"/>
+      <c r="A326" s="37"/>
       <c r="I326" s="20"/>
     </row>
     <row r="327">
-      <c r="A327" s="33"/>
+      <c r="A327" s="37"/>
       <c r="I327" s="20"/>
     </row>
     <row r="328">
-      <c r="A328" s="33"/>
+      <c r="A328" s="37"/>
       <c r="I328" s="20"/>
     </row>
     <row r="329">
-      <c r="A329" s="33"/>
+      <c r="A329" s="37"/>
       <c r="I329" s="20"/>
     </row>
     <row r="330">
-      <c r="A330" s="33"/>
+      <c r="A330" s="37"/>
       <c r="I330" s="20"/>
     </row>
     <row r="331">
-      <c r="A331" s="33"/>
+      <c r="A331" s="37"/>
       <c r="I331" s="20"/>
     </row>
     <row r="332">
-      <c r="A332" s="33"/>
+      <c r="A332" s="37"/>
       <c r="I332" s="20"/>
     </row>
     <row r="333">
-      <c r="A333" s="33"/>
+      <c r="A333" s="37"/>
       <c r="I333" s="20"/>
     </row>
     <row r="334">
-      <c r="A334" s="33"/>
+      <c r="A334" s="37"/>
       <c r="I334" s="20"/>
     </row>
     <row r="335">
-      <c r="A335" s="33"/>
+      <c r="A335" s="37"/>
       <c r="I335" s="20"/>
     </row>
     <row r="336">
-      <c r="A336" s="33"/>
+      <c r="A336" s="37"/>
       <c r="I336" s="20"/>
     </row>
     <row r="337">
-      <c r="A337" s="33"/>
+      <c r="A337" s="37"/>
       <c r="I337" s="20"/>
     </row>
     <row r="338">
-      <c r="A338" s="33"/>
+      <c r="A338" s="37"/>
       <c r="I338" s="20"/>
     </row>
     <row r="339">
-      <c r="A339" s="33"/>
+      <c r="A339" s="37"/>
       <c r="I339" s="20"/>
     </row>
     <row r="340">
-      <c r="A340" s="33"/>
+      <c r="A340" s="37"/>
       <c r="I340" s="20"/>
     </row>
     <row r="341">
-      <c r="A341" s="33"/>
+      <c r="A341" s="37"/>
       <c r="I341" s="20"/>
     </row>
     <row r="342">
-      <c r="A342" s="33"/>
+      <c r="A342" s="37"/>
       <c r="I342" s="20"/>
     </row>
     <row r="343">
-      <c r="A343" s="33"/>
+      <c r="A343" s="37"/>
       <c r="I343" s="20"/>
     </row>
     <row r="344">
-      <c r="A344" s="33"/>
+      <c r="A344" s="37"/>
       <c r="I344" s="20"/>
     </row>
     <row r="345">
-      <c r="A345" s="33"/>
+      <c r="A345" s="37"/>
       <c r="I345" s="20"/>
     </row>
     <row r="346">
-      <c r="A346" s="33"/>
+      <c r="A346" s="37"/>
       <c r="I346" s="20"/>
     </row>
     <row r="347">
-      <c r="A347" s="33"/>
+      <c r="A347" s="37"/>
       <c r="I347" s="20"/>
     </row>
     <row r="348">
-      <c r="A348" s="33"/>
+      <c r="A348" s="37"/>
       <c r="I348" s="20"/>
     </row>
     <row r="349">
-      <c r="A349" s="33"/>
+      <c r="A349" s="37"/>
       <c r="I349" s="20"/>
     </row>
     <row r="350">
-      <c r="A350" s="33"/>
+      <c r="A350" s="37"/>
       <c r="I350" s="20"/>
     </row>
     <row r="351">
-      <c r="A351" s="33"/>
+      <c r="A351" s="37"/>
       <c r="I351" s="20"/>
     </row>
     <row r="352">
-      <c r="A352" s="33"/>
+      <c r="A352" s="37"/>
       <c r="I352" s="20"/>
     </row>
     <row r="353">
-      <c r="A353" s="33"/>
+      <c r="A353" s="37"/>
       <c r="I353" s="20"/>
     </row>
     <row r="354">
-      <c r="A354" s="33"/>
+      <c r="A354" s="37"/>
       <c r="I354" s="20"/>
     </row>
     <row r="355">
-      <c r="A355" s="33"/>
+      <c r="A355" s="37"/>
       <c r="I355" s="20"/>
     </row>
     <row r="356">
-      <c r="A356" s="33"/>
+      <c r="A356" s="37"/>
       <c r="I356" s="20"/>
     </row>
     <row r="357">
-      <c r="A357" s="33"/>
+      <c r="A357" s="37"/>
       <c r="I357" s="20"/>
     </row>
     <row r="358">
-      <c r="A358" s="33"/>
+      <c r="A358" s="37"/>
       <c r="I358" s="20"/>
     </row>
     <row r="359">
-      <c r="A359" s="33"/>
+      <c r="A359" s="37"/>
       <c r="I359" s="20"/>
     </row>
     <row r="360">
-      <c r="A360" s="33"/>
+      <c r="A360" s="37"/>
       <c r="I360" s="20"/>
     </row>
     <row r="361">
-      <c r="A361" s="33"/>
+      <c r="A361" s="37"/>
       <c r="I361" s="20"/>
     </row>
     <row r="362">
-      <c r="A362" s="33"/>
+      <c r="A362" s="37"/>
       <c r="I362" s="20"/>
     </row>
     <row r="363">
-      <c r="A363" s="33"/>
+      <c r="A363" s="37"/>
       <c r="I363" s="20"/>
     </row>
     <row r="364">
-      <c r="A364" s="33"/>
+      <c r="A364" s="37"/>
       <c r="I364" s="20"/>
     </row>
     <row r="365">
-      <c r="A365" s="33"/>
+      <c r="A365" s="37"/>
       <c r="I365" s="20"/>
     </row>
     <row r="366">
-      <c r="A366" s="33"/>
+      <c r="A366" s="37"/>
       <c r="I366" s="20"/>
     </row>
     <row r="367">
-      <c r="A367" s="33"/>
+      <c r="A367" s="37"/>
       <c r="I367" s="20"/>
     </row>
     <row r="368">
-      <c r="A368" s="33"/>
+      <c r="A368" s="37"/>
       <c r="I368" s="20"/>
     </row>
     <row r="369">
-      <c r="A369" s="33"/>
+      <c r="A369" s="37"/>
       <c r="I369" s="20"/>
     </row>
     <row r="370">
-      <c r="A370" s="33"/>
+      <c r="A370" s="37"/>
       <c r="I370" s="20"/>
     </row>
     <row r="371">
-      <c r="A371" s="33"/>
+      <c r="A371" s="37"/>
       <c r="I371" s="20"/>
     </row>
     <row r="372">
-      <c r="A372" s="33"/>
+      <c r="A372" s="37"/>
       <c r="I372" s="20"/>
     </row>
     <row r="373">
-      <c r="A373" s="33"/>
+      <c r="A373" s="37"/>
       <c r="I373" s="20"/>
     </row>
     <row r="374">
-      <c r="A374" s="33"/>
+      <c r="A374" s="37"/>
       <c r="I374" s="20"/>
     </row>
     <row r="375">
-      <c r="A375" s="33"/>
+      <c r="A375" s="37"/>
       <c r="I375" s="20"/>
     </row>
     <row r="376">
-      <c r="A376" s="33"/>
+      <c r="A376" s="37"/>
       <c r="I376" s="20"/>
     </row>
     <row r="377">
-      <c r="A377" s="33"/>
+      <c r="A377" s="37"/>
       <c r="I377" s="20"/>
     </row>
     <row r="378">
-      <c r="A378" s="33"/>
+      <c r="A378" s="37"/>
       <c r="I378" s="20"/>
     </row>
     <row r="379">
-      <c r="A379" s="33"/>
+      <c r="A379" s="37"/>
       <c r="I379" s="20"/>
     </row>
     <row r="380">
-      <c r="A380" s="33"/>
+      <c r="A380" s="37"/>
       <c r="I380" s="20"/>
     </row>
     <row r="381">
-      <c r="A381" s="33"/>
+      <c r="A381" s="37"/>
       <c r="I381" s="20"/>
     </row>
     <row r="382">
-      <c r="A382" s="33"/>
+      <c r="A382" s="37"/>
       <c r="I382" s="20"/>
     </row>
     <row r="383">
-      <c r="A383" s="33"/>
+      <c r="A383" s="37"/>
       <c r="I383" s="20"/>
     </row>
     <row r="384">
-      <c r="A384" s="33"/>
+      <c r="A384" s="37"/>
       <c r="I384" s="20"/>
     </row>
     <row r="385">
-      <c r="A385" s="33"/>
+      <c r="A385" s="37"/>
       <c r="I385" s="20"/>
     </row>
     <row r="386">
-      <c r="A386" s="33"/>
+      <c r="A386" s="37"/>
       <c r="I386" s="20"/>
     </row>
     <row r="387">
-      <c r="A387" s="33"/>
+      <c r="A387" s="37"/>
       <c r="I387" s="20"/>
     </row>
     <row r="388">
-      <c r="A388" s="33"/>
+      <c r="A388" s="37"/>
       <c r="I388" s="20"/>
     </row>
     <row r="389">
-      <c r="A389" s="33"/>
+      <c r="A389" s="37"/>
       <c r="I389" s="20"/>
     </row>
     <row r="390">
-      <c r="A390" s="33"/>
+      <c r="A390" s="37"/>
       <c r="I390" s="20"/>
     </row>
     <row r="391">
-      <c r="A391" s="33"/>
+      <c r="A391" s="37"/>
       <c r="I391" s="20"/>
     </row>
     <row r="392">
-      <c r="A392" s="33"/>
+      <c r="A392" s="37"/>
       <c r="I392" s="20"/>
     </row>
     <row r="393">
-      <c r="A393" s="33"/>
+      <c r="A393" s="37"/>
       <c r="I393" s="20"/>
     </row>
     <row r="394">
-      <c r="A394" s="33"/>
+      <c r="A394" s="37"/>
       <c r="I394" s="20"/>
     </row>
     <row r="395">
-      <c r="A395" s="33"/>
+      <c r="A395" s="37"/>
       <c r="I395" s="20"/>
     </row>
     <row r="396">
-      <c r="A396" s="33"/>
+      <c r="A396" s="37"/>
       <c r="I396" s="20"/>
     </row>
     <row r="397">
-      <c r="A397" s="33"/>
+      <c r="A397" s="37"/>
       <c r="I397" s="20"/>
     </row>
     <row r="398">
-      <c r="A398" s="33"/>
+      <c r="A398" s="37"/>
       <c r="I398" s="20"/>
     </row>
     <row r="399">
-      <c r="A399" s="33"/>
+      <c r="A399" s="37"/>
       <c r="I399" s="20"/>
     </row>
     <row r="400">
-      <c r="A400" s="33"/>
+      <c r="A400" s="37"/>
       <c r="I400" s="20"/>
     </row>
     <row r="401">
-      <c r="A401" s="33"/>
+      <c r="A401" s="37"/>
       <c r="I401" s="20"/>
     </row>
     <row r="402">
-      <c r="A402" s="33"/>
+      <c r="A402" s="37"/>
       <c r="I402" s="20"/>
     </row>
     <row r="403">
-      <c r="A403" s="33"/>
+      <c r="A403" s="37"/>
       <c r="I403" s="20"/>
     </row>
     <row r="404">
-      <c r="A404" s="33"/>
+      <c r="A404" s="37"/>
       <c r="I404" s="20"/>
     </row>
     <row r="405">
-      <c r="A405" s="33"/>
+      <c r="A405" s="37"/>
       <c r="I405" s="20"/>
     </row>
     <row r="406">
-      <c r="A406" s="33"/>
+      <c r="A406" s="37"/>
       <c r="I406" s="20"/>
     </row>
     <row r="407">
-      <c r="A407" s="33"/>
+      <c r="A407" s="37"/>
       <c r="I407" s="20"/>
     </row>
     <row r="408">
-      <c r="A408" s="33"/>
+      <c r="A408" s="37"/>
       <c r="I408" s="20"/>
     </row>
     <row r="409">
-      <c r="A409" s="33"/>
+      <c r="A409" s="37"/>
       <c r="I409" s="20"/>
     </row>
     <row r="410">
-      <c r="A410" s="33"/>
+      <c r="A410" s="37"/>
       <c r="I410" s="20"/>
     </row>
     <row r="411">
-      <c r="A411" s="33"/>
+      <c r="A411" s="37"/>
       <c r="I411" s="20"/>
     </row>
     <row r="412">
-      <c r="A412" s="33"/>
+      <c r="A412" s="37"/>
       <c r="I412" s="20"/>
     </row>
     <row r="413">
-      <c r="A413" s="33"/>
+      <c r="A413" s="37"/>
       <c r="I413" s="20"/>
     </row>
     <row r="414">
-      <c r="A414" s="33"/>
+      <c r="A414" s="37"/>
       <c r="I414" s="20"/>
     </row>
     <row r="415">
-      <c r="A415" s="33"/>
+      <c r="A415" s="37"/>
       <c r="I415" s="20"/>
     </row>
     <row r="416">
-      <c r="A416" s="33"/>
+      <c r="A416" s="37"/>
       <c r="I416" s="20"/>
     </row>
     <row r="417">
-      <c r="A417" s="33"/>
+      <c r="A417" s="37"/>
       <c r="I417" s="20"/>
     </row>
     <row r="418">
-      <c r="A418" s="33"/>
+      <c r="A418" s="37"/>
       <c r="I418" s="20"/>
     </row>
     <row r="419">
-      <c r="A419" s="33"/>
+      <c r="A419" s="37"/>
       <c r="I419" s="20"/>
     </row>
     <row r="420">
-      <c r="A420" s="33"/>
+      <c r="A420" s="37"/>
       <c r="I420" s="20"/>
     </row>
     <row r="421">
-      <c r="A421" s="33"/>
+      <c r="A421" s="37"/>
       <c r="I421" s="20"/>
     </row>
     <row r="422">
-      <c r="A422" s="33"/>
+      <c r="A422" s="37"/>
       <c r="I422" s="20"/>
     </row>
     <row r="423">
-      <c r="A423" s="33"/>
+      <c r="A423" s="37"/>
       <c r="I423" s="20"/>
     </row>
     <row r="424">
-      <c r="A424" s="33"/>
+      <c r="A424" s="37"/>
       <c r="I424" s="20"/>
     </row>
     <row r="425">
-      <c r="A425" s="33"/>
+      <c r="A425" s="37"/>
       <c r="I425" s="20"/>
     </row>
     <row r="426">
-      <c r="A426" s="33"/>
+      <c r="A426" s="37"/>
       <c r="I426" s="20"/>
     </row>
     <row r="427">
-      <c r="A427" s="33"/>
+      <c r="A427" s="37"/>
       <c r="I427" s="20"/>
     </row>
     <row r="428">
-      <c r="A428" s="33"/>
+      <c r="A428" s="37"/>
       <c r="I428" s="20"/>
     </row>
     <row r="429">
-      <c r="A429" s="33"/>
+      <c r="A429" s="37"/>
       <c r="I429" s="20"/>
     </row>
     <row r="430">
-      <c r="A430" s="33"/>
+      <c r="A430" s="37"/>
       <c r="I430" s="20"/>
     </row>
     <row r="431">
-      <c r="A431" s="33"/>
+      <c r="A431" s="37"/>
       <c r="I431" s="20"/>
     </row>
     <row r="432">
-      <c r="A432" s="33"/>
+      <c r="A432" s="37"/>
       <c r="I432" s="20"/>
     </row>
     <row r="433">
-      <c r="A433" s="33"/>
+      <c r="A433" s="37"/>
       <c r="I433" s="20"/>
     </row>
     <row r="434">
-      <c r="A434" s="33"/>
+      <c r="A434" s="37"/>
       <c r="I434" s="20"/>
     </row>
     <row r="435">
-      <c r="A435" s="33"/>
+      <c r="A435" s="37"/>
       <c r="I435" s="20"/>
     </row>
     <row r="436">
-      <c r="A436" s="33"/>
+      <c r="A436" s="37"/>
       <c r="I436" s="20"/>
     </row>
     <row r="437">
-      <c r="A437" s="33"/>
+      <c r="A437" s="37"/>
       <c r="I437" s="20"/>
     </row>
     <row r="438">
-      <c r="A438" s="33"/>
+      <c r="A438" s="37"/>
       <c r="I438" s="20"/>
     </row>
     <row r="439">
-      <c r="A439" s="33"/>
+      <c r="A439" s="37"/>
       <c r="I439" s="20"/>
     </row>
     <row r="440">
-      <c r="A440" s="33"/>
+      <c r="A440" s="37"/>
       <c r="I440" s="20"/>
     </row>
     <row r="441">
-      <c r="A441" s="33"/>
+      <c r="A441" s="37"/>
       <c r="I441" s="20"/>
     </row>
     <row r="442">
-      <c r="A442" s="33"/>
+      <c r="A442" s="37"/>
       <c r="I442" s="20"/>
     </row>
     <row r="443">
-      <c r="A443" s="33"/>
+      <c r="A443" s="37"/>
       <c r="I443" s="20"/>
     </row>
     <row r="444">
-      <c r="A444" s="33"/>
+      <c r="A444" s="37"/>
       <c r="I444" s="20"/>
     </row>
     <row r="445">
-      <c r="A445" s="33"/>
+      <c r="A445" s="37"/>
       <c r="I445" s="20"/>
     </row>
     <row r="446">
-      <c r="A446" s="33"/>
+      <c r="A446" s="37"/>
       <c r="I446" s="20"/>
     </row>
     <row r="447">
-      <c r="A447" s="33"/>
+      <c r="A447" s="37"/>
       <c r="I447" s="20"/>
     </row>
     <row r="448">
-      <c r="A448" s="33"/>
+      <c r="A448" s="37"/>
       <c r="I448" s="20"/>
     </row>
     <row r="449">
-      <c r="A449" s="33"/>
+      <c r="A449" s="37"/>
       <c r="I449" s="20"/>
     </row>
     <row r="450">
-      <c r="A450" s="33"/>
+      <c r="A450" s="37"/>
       <c r="I450" s="20"/>
     </row>
     <row r="451">
-      <c r="A451" s="33"/>
+      <c r="A451" s="37"/>
       <c r="I451" s="20"/>
     </row>
     <row r="452">
-      <c r="A452" s="33"/>
+      <c r="A452" s="37"/>
       <c r="I452" s="20"/>
     </row>
     <row r="453">
-      <c r="A453" s="33"/>
+      <c r="A453" s="37"/>
       <c r="I453" s="20"/>
     </row>
     <row r="454">
-      <c r="A454" s="33"/>
+      <c r="A454" s="37"/>
       <c r="I454" s="20"/>
     </row>
     <row r="455">
-      <c r="A455" s="33"/>
+      <c r="A455" s="37"/>
       <c r="I455" s="20"/>
     </row>
     <row r="456">
-      <c r="A456" s="33"/>
+      <c r="A456" s="37"/>
       <c r="I456" s="20"/>
     </row>
     <row r="457">
-      <c r="A457" s="33"/>
+      <c r="A457" s="37"/>
       <c r="I457" s="20"/>
     </row>
     <row r="458">
-      <c r="A458" s="33"/>
+      <c r="A458" s="37"/>
       <c r="I458" s="20"/>
     </row>
     <row r="459">
-      <c r="A459" s="33"/>
+      <c r="A459" s="37"/>
       <c r="I459" s="20"/>
     </row>
     <row r="460">
-      <c r="A460" s="33"/>
+      <c r="A460" s="37"/>
       <c r="I460" s="20"/>
     </row>
     <row r="461">
-      <c r="A461" s="33"/>
+      <c r="A461" s="37"/>
       <c r="I461" s="20"/>
     </row>
     <row r="462">
-      <c r="A462" s="33"/>
+      <c r="A462" s="37"/>
       <c r="I462" s="20"/>
     </row>
     <row r="463">
-      <c r="A463" s="33"/>
+      <c r="A463" s="37"/>
       <c r="I463" s="20"/>
     </row>
     <row r="464">
-      <c r="A464" s="33"/>
+      <c r="A464" s="37"/>
       <c r="I464" s="20"/>
     </row>
     <row r="465">
-      <c r="A465" s="33"/>
+      <c r="A465" s="37"/>
       <c r="I465" s="20"/>
     </row>
     <row r="466">
-      <c r="A466" s="33"/>
+      <c r="A466" s="37"/>
       <c r="I466" s="20"/>
     </row>
     <row r="467">
-      <c r="A467" s="33"/>
+      <c r="A467" s="37"/>
       <c r="I467" s="20"/>
     </row>
     <row r="468">
-      <c r="A468" s="33"/>
+      <c r="A468" s="37"/>
       <c r="I468" s="20"/>
     </row>
     <row r="469">
-      <c r="A469" s="33"/>
+      <c r="A469" s="37"/>
       <c r="I469" s="20"/>
     </row>
     <row r="470">
-      <c r="A470" s="33"/>
+      <c r="A470" s="37"/>
       <c r="I470" s="20"/>
     </row>
     <row r="471">
-      <c r="A471" s="33"/>
+      <c r="A471" s="37"/>
       <c r="I471" s="20"/>
     </row>
     <row r="472">
-      <c r="A472" s="33"/>
+      <c r="A472" s="37"/>
       <c r="I472" s="20"/>
     </row>
     <row r="473">
-      <c r="A473" s="33"/>
+      <c r="A473" s="37"/>
       <c r="I473" s="20"/>
     </row>
     <row r="474">
-      <c r="A474" s="33"/>
+      <c r="A474" s="37"/>
       <c r="I474" s="20"/>
     </row>
     <row r="475">
-      <c r="A475" s="33"/>
+      <c r="A475" s="37"/>
       <c r="I475" s="20"/>
     </row>
     <row r="476">
-      <c r="A476" s="33"/>
+      <c r="A476" s="37"/>
       <c r="I476" s="20"/>
     </row>
     <row r="477">
-      <c r="A477" s="33"/>
+      <c r="A477" s="37"/>
       <c r="I477" s="20"/>
     </row>
     <row r="478">
-      <c r="A478" s="33"/>
+      <c r="A478" s="37"/>
       <c r="I478" s="20"/>
     </row>
     <row r="479">
-      <c r="A479" s="33"/>
+      <c r="A479" s="37"/>
       <c r="I479" s="20"/>
     </row>
     <row r="480">
-      <c r="A480" s="33"/>
+      <c r="A480" s="37"/>
       <c r="I480" s="20"/>
     </row>
     <row r="481">
-      <c r="A481" s="33"/>
+      <c r="A481" s="37"/>
       <c r="I481" s="20"/>
     </row>
     <row r="482">
-      <c r="A482" s="33"/>
+      <c r="A482" s="37"/>
       <c r="I482" s="20"/>
     </row>
     <row r="483">
-      <c r="A483" s="33"/>
+      <c r="A483" s="37"/>
       <c r="I483" s="20"/>
     </row>
     <row r="484">
-      <c r="A484" s="33"/>
+      <c r="A484" s="37"/>
       <c r="I484" s="20"/>
     </row>
     <row r="485">
-      <c r="A485" s="33"/>
+      <c r="A485" s="37"/>
       <c r="I485" s="20"/>
     </row>
     <row r="486">
-      <c r="A486" s="33"/>
+      <c r="A486" s="37"/>
       <c r="I486" s="20"/>
     </row>
     <row r="487">
-      <c r="A487" s="33"/>
+      <c r="A487" s="37"/>
       <c r="I487" s="20"/>
     </row>
     <row r="488">
-      <c r="A488" s="33"/>
+      <c r="A488" s="37"/>
       <c r="I488" s="20"/>
     </row>
     <row r="489">
-      <c r="A489" s="33"/>
+      <c r="A489" s="37"/>
       <c r="I489" s="20"/>
     </row>
     <row r="490">
-      <c r="A490" s="33"/>
+      <c r="A490" s="37"/>
       <c r="I490" s="20"/>
     </row>
     <row r="491">
-      <c r="A491" s="33"/>
+      <c r="A491" s="37"/>
       <c r="I491" s="20"/>
     </row>
     <row r="492">
-      <c r="A492" s="33"/>
+      <c r="A492" s="37"/>
       <c r="I492" s="20"/>
     </row>
     <row r="493">
-      <c r="A493" s="33"/>
+      <c r="A493" s="37"/>
       <c r="I493" s="20"/>
     </row>
     <row r="494">
-      <c r="A494" s="33"/>
+      <c r="A494" s="37"/>
       <c r="I494" s="20"/>
     </row>
     <row r="495">
-      <c r="A495" s="33"/>
+      <c r="A495" s="37"/>
       <c r="I495" s="20"/>
     </row>
     <row r="496">
-      <c r="A496" s="33"/>
+      <c r="A496" s="37"/>
       <c r="I496" s="20"/>
     </row>
     <row r="497">
-      <c r="A497" s="33"/>
+      <c r="A497" s="37"/>
       <c r="I497" s="20"/>
     </row>
     <row r="498">
-      <c r="A498" s="33"/>
+      <c r="A498" s="37"/>
       <c r="I498" s="20"/>
     </row>
     <row r="499">
-      <c r="A499" s="33"/>
+      <c r="A499" s="37"/>
       <c r="I499" s="20"/>
     </row>
     <row r="500">
-      <c r="A500" s="33"/>
+      <c r="A500" s="37"/>
       <c r="I500" s="20"/>
     </row>
     <row r="501">
-      <c r="A501" s="33"/>
+      <c r="A501" s="37"/>
       <c r="I501" s="20"/>
     </row>
     <row r="502">
-      <c r="A502" s="33"/>
+      <c r="A502" s="37"/>
       <c r="I502" s="20"/>
     </row>
     <row r="503">
-      <c r="A503" s="33"/>
+      <c r="A503" s="37"/>
       <c r="I503" s="20"/>
     </row>
     <row r="504">
-      <c r="A504" s="33"/>
+      <c r="A504" s="37"/>
       <c r="I504" s="20"/>
     </row>
     <row r="505">
-      <c r="A505" s="33"/>
+      <c r="A505" s="37"/>
       <c r="I505" s="20"/>
     </row>
     <row r="506">
-      <c r="A506" s="33"/>
+      <c r="A506" s="37"/>
       <c r="I506" s="20"/>
     </row>
     <row r="507">
-      <c r="A507" s="33"/>
+      <c r="A507" s="37"/>
       <c r="I507" s="20"/>
     </row>
     <row r="508">
-      <c r="A508" s="33"/>
+      <c r="A508" s="37"/>
       <c r="I508" s="20"/>
     </row>
     <row r="509">
-      <c r="A509" s="33"/>
+      <c r="A509" s="37"/>
       <c r="I509" s="20"/>
     </row>
     <row r="510">
-      <c r="A510" s="33"/>
+      <c r="A510" s="37"/>
       <c r="I510" s="20"/>
     </row>
     <row r="511">
-      <c r="A511" s="33"/>
+      <c r="A511" s="37"/>
       <c r="I511" s="20"/>
     </row>
     <row r="512">
-      <c r="A512" s="33"/>
+      <c r="A512" s="37"/>
       <c r="I512" s="20"/>
     </row>
     <row r="513">
-      <c r="A513" s="33"/>
+      <c r="A513" s="37"/>
       <c r="I513" s="20"/>
     </row>
     <row r="514">
-      <c r="A514" s="33"/>
+      <c r="A514" s="37"/>
       <c r="I514" s="20"/>
     </row>
     <row r="515">
-      <c r="A515" s="33"/>
+      <c r="A515" s="37"/>
       <c r="I515" s="20"/>
     </row>
     <row r="516">
-      <c r="A516" s="33"/>
+      <c r="A516" s="37"/>
       <c r="I516" s="20"/>
     </row>
     <row r="517">
-      <c r="A517" s="33"/>
+      <c r="A517" s="37"/>
       <c r="I517" s="20"/>
     </row>
     <row r="518">
-      <c r="A518" s="33"/>
+      <c r="A518" s="37"/>
       <c r="I518" s="20"/>
     </row>
     <row r="519">
-      <c r="A519" s="33"/>
+      <c r="A519" s="37"/>
       <c r="I519" s="20"/>
     </row>
     <row r="520">
-      <c r="A520" s="33"/>
+      <c r="A520" s="37"/>
       <c r="I520" s="20"/>
     </row>
     <row r="521">
-      <c r="A521" s="33"/>
+      <c r="A521" s="37"/>
       <c r="I521" s="20"/>
     </row>
     <row r="522">
-      <c r="A522" s="33"/>
+      <c r="A522" s="37"/>
       <c r="I522" s="20"/>
     </row>
     <row r="523">
-      <c r="A523" s="33"/>
+      <c r="A523" s="37"/>
       <c r="I523" s="20"/>
     </row>
     <row r="524">
-      <c r="A524" s="33"/>
+      <c r="A524" s="37"/>
       <c r="I524" s="20"/>
     </row>
     <row r="525">
-      <c r="A525" s="33"/>
+      <c r="A525" s="37"/>
       <c r="I525" s="20"/>
     </row>
     <row r="526">
-      <c r="A526" s="33"/>
+      <c r="A526" s="37"/>
       <c r="I526" s="20"/>
     </row>
     <row r="527">
-      <c r="A527" s="33"/>
+      <c r="A527" s="37"/>
       <c r="I527" s="20"/>
     </row>
     <row r="528">
-      <c r="A528" s="33"/>
+      <c r="A528" s="37"/>
       <c r="I528" s="20"/>
     </row>
     <row r="529">
-      <c r="A529" s="33"/>
+      <c r="A529" s="37"/>
       <c r="I529" s="20"/>
     </row>
     <row r="530">
-      <c r="A530" s="33"/>
+      <c r="A530" s="37"/>
       <c r="I530" s="20"/>
     </row>
     <row r="531">
-      <c r="A531" s="33"/>
+      <c r="A531" s="37"/>
       <c r="I531" s="20"/>
     </row>
     <row r="532">
-      <c r="A532" s="33"/>
+      <c r="A532" s="37"/>
       <c r="I532" s="20"/>
     </row>
     <row r="533">
-      <c r="A533" s="33"/>
+      <c r="A533" s="37"/>
       <c r="I533" s="20"/>
     </row>
     <row r="534">
-      <c r="A534" s="33"/>
+      <c r="A534" s="37"/>
       <c r="I534" s="20"/>
     </row>
     <row r="535">
-      <c r="A535" s="33"/>
+      <c r="A535" s="37"/>
       <c r="I535" s="20"/>
     </row>
     <row r="536">
-      <c r="A536" s="33"/>
+      <c r="A536" s="37"/>
       <c r="I536" s="20"/>
     </row>
     <row r="537">
-      <c r="A537" s="33"/>
+      <c r="A537" s="37"/>
       <c r="I537" s="20"/>
     </row>
     <row r="538">
-      <c r="A538" s="33"/>
+      <c r="A538" s="37"/>
       <c r="I538" s="20"/>
     </row>
     <row r="539">
-      <c r="A539" s="33"/>
+      <c r="A539" s="37"/>
       <c r="I539" s="20"/>
     </row>
     <row r="540">
-      <c r="A540" s="33"/>
+      <c r="A540" s="37"/>
       <c r="I540" s="20"/>
     </row>
     <row r="541">
-      <c r="A541" s="33"/>
+      <c r="A541" s="37"/>
       <c r="I541" s="20"/>
     </row>
     <row r="542">
-      <c r="A542" s="33"/>
+      <c r="A542" s="37"/>
       <c r="I542" s="20"/>
     </row>
     <row r="543">
-      <c r="A543" s="33"/>
+      <c r="A543" s="37"/>
       <c r="I543" s="20"/>
     </row>
     <row r="544">
-      <c r="A544" s="33"/>
+      <c r="A544" s="37"/>
       <c r="I544" s="20"/>
     </row>
     <row r="545">
-      <c r="A545" s="33"/>
+      <c r="A545" s="37"/>
       <c r="I545" s="20"/>
     </row>
     <row r="546">
-      <c r="A546" s="33"/>
+      <c r="A546" s="37"/>
       <c r="I546" s="20"/>
     </row>
     <row r="547">
-      <c r="A547" s="33"/>
+      <c r="A547" s="37"/>
       <c r="I547" s="20"/>
     </row>
     <row r="548">
-      <c r="A548" s="33"/>
+      <c r="A548" s="37"/>
       <c r="I548" s="20"/>
     </row>
     <row r="549">
-      <c r="A549" s="33"/>
+      <c r="A549" s="37"/>
       <c r="I549" s="20"/>
     </row>
     <row r="550">
-      <c r="A550" s="33"/>
+      <c r="A550" s="37"/>
       <c r="I550" s="20"/>
     </row>
     <row r="551">
-      <c r="A551" s="33"/>
+      <c r="A551" s="37"/>
       <c r="I551" s="20"/>
     </row>
     <row r="552">
-      <c r="A552" s="33"/>
+      <c r="A552" s="37"/>
       <c r="I552" s="20"/>
     </row>
     <row r="553">
-      <c r="A553" s="33"/>
+      <c r="A553" s="37"/>
       <c r="I553" s="20"/>
     </row>
     <row r="554">
-      <c r="A554" s="33"/>
+      <c r="A554" s="37"/>
       <c r="I554" s="20"/>
     </row>
     <row r="555">
-      <c r="A555" s="33"/>
+      <c r="A555" s="37"/>
       <c r="I555" s="20"/>
     </row>
     <row r="556">
-      <c r="A556" s="33"/>
+      <c r="A556" s="37"/>
       <c r="I556" s="20"/>
     </row>
     <row r="557">
-      <c r="A557" s="33"/>
+      <c r="A557" s="37"/>
       <c r="I557" s="20"/>
     </row>
     <row r="558">
-      <c r="A558" s="33"/>
+      <c r="A558" s="37"/>
       <c r="I558" s="20"/>
     </row>
     <row r="559">
-      <c r="A559" s="33"/>
+      <c r="A559" s="37"/>
       <c r="I559" s="20"/>
     </row>
     <row r="560">
-      <c r="A560" s="33"/>
+      <c r="A560" s="37"/>
       <c r="I560" s="20"/>
     </row>
     <row r="561">
-      <c r="A561" s="33"/>
+      <c r="A561" s="37"/>
       <c r="I561" s="20"/>
     </row>
     <row r="562">
-      <c r="A562" s="33"/>
+      <c r="A562" s="37"/>
       <c r="I562" s="20"/>
     </row>
     <row r="563">
-      <c r="A563" s="33"/>
+      <c r="A563" s="37"/>
       <c r="I563" s="20"/>
     </row>
     <row r="564">
-      <c r="A564" s="33"/>
+      <c r="A564" s="37"/>
       <c r="I564" s="20"/>
     </row>
     <row r="565">
-      <c r="A565" s="33"/>
+      <c r="A565" s="37"/>
       <c r="I565" s="20"/>
     </row>
     <row r="566">
-      <c r="A566" s="33"/>
+      <c r="A566" s="37"/>
       <c r="I566" s="20"/>
     </row>
     <row r="567">
-      <c r="A567" s="33"/>
+      <c r="A567" s="37"/>
       <c r="I567" s="20"/>
     </row>
     <row r="568">
-      <c r="A568" s="33"/>
+      <c r="A568" s="37"/>
       <c r="I568" s="20"/>
     </row>
     <row r="569">
-      <c r="A569" s="33"/>
+      <c r="A569" s="37"/>
       <c r="I569" s="20"/>
     </row>
     <row r="570">
-      <c r="A570" s="33"/>
+      <c r="A570" s="37"/>
       <c r="I570" s="20"/>
     </row>
     <row r="571">
-      <c r="A571" s="33"/>
+      <c r="A571" s="37"/>
       <c r="I571" s="20"/>
     </row>
     <row r="572">
-      <c r="A572" s="33"/>
+      <c r="A572" s="37"/>
       <c r="I572" s="20"/>
     </row>
     <row r="573">
-      <c r="A573" s="33"/>
+      <c r="A573" s="37"/>
       <c r="I573" s="20"/>
     </row>
     <row r="574">
-      <c r="A574" s="33"/>
+      <c r="A574" s="37"/>
       <c r="I574" s="20"/>
     </row>
     <row r="575">
-      <c r="A575" s="33"/>
+      <c r="A575" s="37"/>
       <c r="I575" s="20"/>
     </row>
     <row r="576">
-      <c r="A576" s="33"/>
+      <c r="A576" s="37"/>
       <c r="I576" s="20"/>
     </row>
     <row r="577">
-      <c r="A577" s="33"/>
+      <c r="A577" s="37"/>
       <c r="I577" s="20"/>
     </row>
     <row r="578">
-      <c r="A578" s="33"/>
+      <c r="A578" s="37"/>
       <c r="I578" s="20"/>
     </row>
     <row r="579">
-      <c r="A579" s="33"/>
+      <c r="A579" s="37"/>
       <c r="I579" s="20"/>
     </row>
     <row r="580">
-      <c r="A580" s="33"/>
+      <c r="A580" s="37"/>
       <c r="I580" s="20"/>
     </row>
     <row r="581">
-      <c r="A581" s="33"/>
+      <c r="A581" s="37"/>
       <c r="I581" s="20"/>
     </row>
     <row r="582">
-      <c r="A582" s="33"/>
+      <c r="A582" s="37"/>
       <c r="I582" s="20"/>
     </row>
     <row r="583">
-      <c r="A583" s="33"/>
+      <c r="A583" s="37"/>
       <c r="I583" s="20"/>
     </row>
     <row r="584">
-      <c r="A584" s="33"/>
+      <c r="A584" s="37"/>
       <c r="I584" s="20"/>
     </row>
     <row r="585">
-      <c r="A585" s="33"/>
+      <c r="A585" s="37"/>
       <c r="I585" s="20"/>
     </row>
     <row r="586">
-      <c r="A586" s="33"/>
+      <c r="A586" s="37"/>
       <c r="I586" s="20"/>
     </row>
     <row r="587">
-      <c r="A587" s="33"/>
+      <c r="A587" s="37"/>
       <c r="I587" s="20"/>
     </row>
     <row r="588">
-      <c r="A588" s="33"/>
+      <c r="A588" s="37"/>
       <c r="I588" s="20"/>
     </row>
     <row r="589">
-      <c r="A589" s="33"/>
+      <c r="A589" s="37"/>
       <c r="I589" s="20"/>
     </row>
     <row r="590">
-      <c r="A590" s="33"/>
+      <c r="A590" s="37"/>
       <c r="I590" s="20"/>
     </row>
     <row r="591">
-      <c r="A591" s="33"/>
+      <c r="A591" s="37"/>
       <c r="I591" s="20"/>
     </row>
     <row r="592">
-      <c r="A592" s="33"/>
+      <c r="A592" s="37"/>
       <c r="I592" s="20"/>
     </row>
     <row r="593">
-      <c r="A593" s="33"/>
+      <c r="A593" s="37"/>
       <c r="I593" s="20"/>
     </row>
     <row r="594">
-      <c r="A594" s="33"/>
+      <c r="A594" s="37"/>
       <c r="I594" s="20"/>
     </row>
     <row r="595">
-      <c r="A595" s="33"/>
+      <c r="A595" s="37"/>
       <c r="I595" s="20"/>
     </row>
     <row r="596">
-      <c r="A596" s="33"/>
+      <c r="A596" s="37"/>
       <c r="I596" s="20"/>
     </row>
     <row r="597">
-      <c r="A597" s="33"/>
+      <c r="A597" s="37"/>
       <c r="I597" s="20"/>
     </row>
     <row r="598">
-      <c r="A598" s="33"/>
+      <c r="A598" s="37"/>
       <c r="I598" s="20"/>
     </row>
     <row r="599">
-      <c r="A599" s="33"/>
+      <c r="A599" s="37"/>
       <c r="I599" s="20"/>
     </row>
     <row r="600">
-      <c r="A600" s="33"/>
+      <c r="A600" s="37"/>
       <c r="I600" s="20"/>
     </row>
     <row r="601">
-      <c r="A601" s="33"/>
+      <c r="A601" s="37"/>
       <c r="I601" s="20"/>
     </row>
     <row r="602">
-      <c r="A602" s="33"/>
+      <c r="A602" s="37"/>
       <c r="I602" s="20"/>
     </row>
     <row r="603">
-      <c r="A603" s="33"/>
+      <c r="A603" s="37"/>
       <c r="I603" s="20"/>
     </row>
     <row r="604">
-      <c r="A604" s="33"/>
+      <c r="A604" s="37"/>
       <c r="I604" s="20"/>
     </row>
     <row r="605">
-      <c r="A605" s="33"/>
+      <c r="A605" s="37"/>
       <c r="I605" s="20"/>
     </row>
     <row r="606">
-      <c r="A606" s="33"/>
+      <c r="A606" s="37"/>
       <c r="I606" s="20"/>
     </row>
     <row r="607">
-      <c r="A607" s="33"/>
+      <c r="A607" s="37"/>
       <c r="I607" s="20"/>
     </row>
     <row r="608">
-      <c r="A608" s="33"/>
+      <c r="A608" s="37"/>
       <c r="I608" s="20"/>
     </row>
     <row r="609">
-      <c r="A609" s="33"/>
+      <c r="A609" s="37"/>
       <c r="I609" s="20"/>
     </row>
     <row r="610">
-      <c r="A610" s="33"/>
+      <c r="A610" s="37"/>
       <c r="I610" s="20"/>
     </row>
     <row r="611">
-      <c r="A611" s="33"/>
+      <c r="A611" s="37"/>
       <c r="I611" s="20"/>
     </row>
     <row r="612">
-      <c r="A612" s="33"/>
+      <c r="A612" s="37"/>
       <c r="I612" s="20"/>
     </row>
     <row r="613">
-      <c r="A613" s="33"/>
+      <c r="A613" s="37"/>
       <c r="I613" s="20"/>
     </row>
     <row r="614">
-      <c r="A614" s="33"/>
+      <c r="A614" s="37"/>
       <c r="I614" s="20"/>
     </row>
     <row r="615">
-      <c r="A615" s="33"/>
+      <c r="A615" s="37"/>
       <c r="I615" s="20"/>
     </row>
     <row r="616">
-      <c r="A616" s="33"/>
+      <c r="A616" s="37"/>
       <c r="I616" s="20"/>
     </row>
     <row r="617">
-      <c r="A617" s="33"/>
+      <c r="A617" s="37"/>
       <c r="I617" s="20"/>
     </row>
     <row r="618">
-      <c r="A618" s="33"/>
+      <c r="A618" s="37"/>
       <c r="I618" s="20"/>
     </row>
     <row r="619">
-      <c r="A619" s="33"/>
+      <c r="A619" s="37"/>
       <c r="I619" s="20"/>
     </row>
     <row r="620">
-      <c r="A620" s="33"/>
+      <c r="A620" s="37"/>
       <c r="I620" s="20"/>
     </row>
     <row r="621">
-      <c r="A621" s="33"/>
+      <c r="A621" s="37"/>
       <c r="I621" s="20"/>
     </row>
     <row r="622">
-      <c r="A622" s="33"/>
+      <c r="A622" s="37"/>
       <c r="I622" s="20"/>
     </row>
     <row r="623">
-      <c r="A623" s="33"/>
+      <c r="A623" s="37"/>
       <c r="I623" s="20"/>
     </row>
     <row r="624">
-      <c r="A624" s="33"/>
+      <c r="A624" s="37"/>
       <c r="I624" s="20"/>
     </row>
     <row r="625">
-      <c r="A625" s="33"/>
+      <c r="A625" s="37"/>
       <c r="I625" s="20"/>
     </row>
     <row r="626">
-      <c r="A626" s="33"/>
+      <c r="A626" s="37"/>
       <c r="I626" s="20"/>
     </row>
     <row r="627">
-      <c r="A627" s="33"/>
+      <c r="A627" s="37"/>
       <c r="I627" s="20"/>
     </row>
     <row r="628">
-      <c r="A628" s="33"/>
+      <c r="A628" s="37"/>
       <c r="I628" s="20"/>
     </row>
     <row r="629">
-      <c r="A629" s="33"/>
+      <c r="A629" s="37"/>
       <c r="I629" s="20"/>
     </row>
     <row r="630">
-      <c r="A630" s="33"/>
+      <c r="A630" s="37"/>
       <c r="I630" s="20"/>
     </row>
     <row r="631">
-      <c r="A631" s="33"/>
+      <c r="A631" s="37"/>
       <c r="I631" s="20"/>
     </row>
     <row r="632">
-      <c r="A632" s="33"/>
+      <c r="A632" s="37"/>
       <c r="I632" s="20"/>
     </row>
     <row r="633">
-      <c r="A633" s="33"/>
+      <c r="A633" s="37"/>
       <c r="I633" s="20"/>
     </row>
     <row r="634">
-      <c r="A634" s="33"/>
+      <c r="A634" s="37"/>
       <c r="I634" s="20"/>
     </row>
     <row r="635">
-      <c r="A635" s="33"/>
+      <c r="A635" s="37"/>
       <c r="I635" s="20"/>
     </row>
     <row r="636">
-      <c r="A636" s="33"/>
+      <c r="A636" s="37"/>
       <c r="I636" s="20"/>
     </row>
     <row r="637">
-      <c r="A637" s="33"/>
+      <c r="A637" s="37"/>
       <c r="I637" s="20"/>
     </row>
     <row r="638">
-      <c r="A638" s="33"/>
+      <c r="A638" s="37"/>
       <c r="I638" s="20"/>
     </row>
     <row r="639">
-      <c r="A639" s="33"/>
+      <c r="A639" s="37"/>
       <c r="I639" s="20"/>
     </row>
     <row r="640">
-      <c r="A640" s="33"/>
+      <c r="A640" s="37"/>
       <c r="I640" s="20"/>
     </row>
     <row r="641">
-      <c r="A641" s="33"/>
+      <c r="A641" s="37"/>
       <c r="I641" s="20"/>
     </row>
     <row r="642">
-      <c r="A642" s="33"/>
+      <c r="A642" s="37"/>
       <c r="I642" s="20"/>
     </row>
     <row r="643">
-      <c r="A643" s="33"/>
+      <c r="A643" s="37"/>
       <c r="I643" s="20"/>
     </row>
     <row r="644">
-      <c r="A644" s="33"/>
+      <c r="A644" s="37"/>
       <c r="I644" s="20"/>
     </row>
     <row r="645">
-      <c r="A645" s="33"/>
+      <c r="A645" s="37"/>
       <c r="I645" s="20"/>
     </row>
     <row r="646">
-      <c r="A646" s="33"/>
+      <c r="A646" s="37"/>
       <c r="I646" s="20"/>
     </row>
     <row r="647">
-      <c r="A647" s="33"/>
+      <c r="A647" s="37"/>
       <c r="I647" s="20"/>
     </row>
     <row r="648">
-      <c r="A648" s="33"/>
+      <c r="A648" s="37"/>
       <c r="I648" s="20"/>
     </row>
     <row r="649">
-      <c r="A649" s="33"/>
+      <c r="A649" s="37"/>
       <c r="I649" s="20"/>
     </row>
     <row r="650">
-      <c r="A650" s="33"/>
+      <c r="A650" s="37"/>
       <c r="I650" s="20"/>
     </row>
     <row r="651">
-      <c r="A651" s="33"/>
+      <c r="A651" s="37"/>
       <c r="I651" s="20"/>
     </row>
     <row r="652">
-      <c r="A652" s="33"/>
+      <c r="A652" s="37"/>
       <c r="I652" s="20"/>
     </row>
     <row r="653">
-      <c r="A653" s="33"/>
+      <c r="A653" s="37"/>
       <c r="I653" s="20"/>
     </row>
     <row r="654">
-      <c r="A654" s="33"/>
+      <c r="A654" s="37"/>
       <c r="I654" s="20"/>
     </row>
     <row r="655">
-      <c r="A655" s="33"/>
+      <c r="A655" s="37"/>
       <c r="I655" s="20"/>
     </row>
     <row r="656">
-      <c r="A656" s="33"/>
+      <c r="A656" s="37"/>
       <c r="I656" s="20"/>
     </row>
     <row r="657">
-      <c r="A657" s="33"/>
+      <c r="A657" s="37"/>
       <c r="I657" s="20"/>
     </row>
     <row r="658">
-      <c r="A658" s="33"/>
+      <c r="A658" s="37"/>
       <c r="I658" s="20"/>
     </row>
     <row r="659">
-      <c r="A659" s="33"/>
+      <c r="A659" s="37"/>
       <c r="I659" s="20"/>
     </row>
     <row r="660">
-      <c r="A660" s="33"/>
+      <c r="A660" s="37"/>
       <c r="I660" s="20"/>
     </row>
     <row r="661">
-      <c r="A661" s="33"/>
+      <c r="A661" s="37"/>
       <c r="I661" s="20"/>
     </row>
     <row r="662">
-      <c r="A662" s="33"/>
+      <c r="A662" s="37"/>
       <c r="I662" s="20"/>
     </row>
     <row r="663">
-      <c r="A663" s="33"/>
+      <c r="A663" s="37"/>
       <c r="I663" s="20"/>
     </row>
     <row r="664">
-      <c r="A664" s="33"/>
+      <c r="A664" s="37"/>
       <c r="I664" s="20"/>
     </row>
     <row r="665">
-      <c r="A665" s="33"/>
+      <c r="A665" s="37"/>
       <c r="I665" s="20"/>
     </row>
     <row r="666">
-      <c r="A666" s="33"/>
+      <c r="A666" s="37"/>
       <c r="I666" s="20"/>
     </row>
     <row r="667">
-      <c r="A667" s="33"/>
+      <c r="A667" s="37"/>
       <c r="I667" s="20"/>
     </row>
     <row r="668">
-      <c r="A668" s="33"/>
+      <c r="A668" s="37"/>
       <c r="I668" s="20"/>
     </row>
     <row r="669">
-      <c r="A669" s="33"/>
+      <c r="A669" s="37"/>
       <c r="I669" s="20"/>
     </row>
     <row r="670">
-      <c r="A670" s="33"/>
+      <c r="A670" s="37"/>
       <c r="I670" s="20"/>
     </row>
     <row r="671">
-      <c r="A671" s="33"/>
+      <c r="A671" s="37"/>
       <c r="I671" s="20"/>
     </row>
     <row r="672">
-      <c r="A672" s="33"/>
+      <c r="A672" s="37"/>
       <c r="I672" s="20"/>
     </row>
     <row r="673">
-      <c r="A673" s="33"/>
+      <c r="A673" s="37"/>
       <c r="I673" s="20"/>
     </row>
     <row r="674">
-      <c r="A674" s="33"/>
+      <c r="A674" s="37"/>
       <c r="I674" s="20"/>
     </row>
     <row r="675">
-      <c r="A675" s="33"/>
+      <c r="A675" s="37"/>
       <c r="I675" s="20"/>
     </row>
     <row r="676">
-      <c r="A676" s="33"/>
+      <c r="A676" s="37"/>
       <c r="I676" s="20"/>
     </row>
     <row r="677">
-      <c r="A677" s="33"/>
+      <c r="A677" s="37"/>
       <c r="I677" s="20"/>
     </row>
     <row r="678">
-      <c r="A678" s="33"/>
+      <c r="A678" s="37"/>
       <c r="I678" s="20"/>
     </row>
     <row r="679">
-      <c r="A679" s="33"/>
+      <c r="A679" s="37"/>
       <c r="I679" s="20"/>
     </row>
     <row r="680">
-      <c r="A680" s="33"/>
+      <c r="A680" s="37"/>
       <c r="I680" s="20"/>
     </row>
     <row r="681">
-      <c r="A681" s="33"/>
+      <c r="A681" s="37"/>
       <c r="I681" s="20"/>
     </row>
     <row r="682">
-      <c r="A682" s="33"/>
+      <c r="A682" s="37"/>
       <c r="I682" s="20"/>
     </row>
     <row r="683">
-      <c r="A683" s="33"/>
+      <c r="A683" s="37"/>
       <c r="I683" s="20"/>
     </row>
     <row r="684">
-      <c r="A684" s="33"/>
+      <c r="A684" s="37"/>
       <c r="I684" s="20"/>
     </row>
     <row r="685">
-      <c r="A685" s="33"/>
+      <c r="A685" s="37"/>
       <c r="I685" s="20"/>
     </row>
     <row r="686">
-      <c r="A686" s="33"/>
+      <c r="A686" s="37"/>
       <c r="I686" s="20"/>
     </row>
     <row r="687">
-      <c r="A687" s="33"/>
+      <c r="A687" s="37"/>
       <c r="I687" s="20"/>
     </row>
     <row r="688">
-      <c r="A688" s="33"/>
+      <c r="A688" s="37"/>
       <c r="I688" s="20"/>
     </row>
     <row r="689">
-      <c r="A689" s="33"/>
+      <c r="A689" s="37"/>
       <c r="I689" s="20"/>
     </row>
     <row r="690">
-      <c r="A690" s="33"/>
+      <c r="A690" s="37"/>
       <c r="I690" s="20"/>
     </row>
     <row r="691">
-      <c r="A691" s="33"/>
+      <c r="A691" s="37"/>
       <c r="I691" s="20"/>
     </row>
     <row r="692">
-      <c r="A692" s="33"/>
+      <c r="A692" s="37"/>
       <c r="I692" s="20"/>
     </row>
     <row r="693">
-      <c r="A693" s="33"/>
+      <c r="A693" s="37"/>
       <c r="I693" s="20"/>
     </row>
     <row r="694">
-      <c r="A694" s="33"/>
+      <c r="A694" s="37"/>
       <c r="I694" s="20"/>
     </row>
     <row r="695">
-      <c r="A695" s="33"/>
+      <c r="A695" s="37"/>
       <c r="I695" s="20"/>
     </row>
     <row r="696">
-      <c r="A696" s="33"/>
+      <c r="A696" s="37"/>
       <c r="I696" s="20"/>
     </row>
     <row r="697">
-      <c r="A697" s="33"/>
+      <c r="A697" s="37"/>
       <c r="I697" s="20"/>
     </row>
     <row r="698">
-      <c r="A698" s="33"/>
+      <c r="A698" s="37"/>
       <c r="I698" s="20"/>
     </row>
     <row r="699">
-      <c r="A699" s="33"/>
+      <c r="A699" s="37"/>
       <c r="I699" s="20"/>
     </row>
     <row r="700">
-      <c r="A700" s="33"/>
+      <c r="A700" s="37"/>
       <c r="I700" s="20"/>
     </row>
     <row r="701">
-      <c r="A701" s="33"/>
+      <c r="A701" s="37"/>
       <c r="I701" s="20"/>
     </row>
     <row r="702">
-      <c r="A702" s="33"/>
+      <c r="A702" s="37"/>
       <c r="I702" s="20"/>
     </row>
     <row r="703">
-      <c r="A703" s="33"/>
+      <c r="A703" s="37"/>
       <c r="I703" s="20"/>
     </row>
     <row r="704">
-      <c r="A704" s="33"/>
+      <c r="A704" s="37"/>
       <c r="I704" s="20"/>
     </row>
     <row r="705">
-      <c r="A705" s="33"/>
+      <c r="A705" s="37"/>
       <c r="I705" s="20"/>
     </row>
     <row r="706">
-      <c r="A706" s="33"/>
+      <c r="A706" s="37"/>
       <c r="I706" s="20"/>
     </row>
     <row r="707">
-      <c r="A707" s="33"/>
+      <c r="A707" s="37"/>
       <c r="I707" s="20"/>
     </row>
     <row r="708">
-      <c r="A708" s="33"/>
+      <c r="A708" s="37"/>
       <c r="I708" s="20"/>
     </row>
     <row r="709">
-      <c r="A709" s="33"/>
+      <c r="A709" s="37"/>
       <c r="I709" s="20"/>
     </row>
     <row r="710">
-      <c r="A710" s="33"/>
+      <c r="A710" s="37"/>
       <c r="I710" s="20"/>
     </row>
     <row r="711">
-      <c r="A711" s="33"/>
+      <c r="A711" s="37"/>
       <c r="I711" s="20"/>
     </row>
     <row r="712">
-      <c r="A712" s="33"/>
+      <c r="A712" s="37"/>
       <c r="I712" s="20"/>
     </row>
     <row r="713">
-      <c r="A713" s="33"/>
+      <c r="A713" s="37"/>
       <c r="I713" s="20"/>
     </row>
     <row r="714">
-      <c r="A714" s="33"/>
+      <c r="A714" s="37"/>
       <c r="I714" s="20"/>
     </row>
     <row r="715">
-      <c r="A715" s="33"/>
+      <c r="A715" s="37"/>
       <c r="I715" s="20"/>
     </row>
     <row r="716">
-      <c r="A716" s="33"/>
+      <c r="A716" s="37"/>
       <c r="I716" s="20"/>
     </row>
     <row r="717">
-      <c r="A717" s="33"/>
+      <c r="A717" s="37"/>
       <c r="I717" s="20"/>
     </row>
     <row r="718">
-      <c r="A718" s="33"/>
+      <c r="A718" s="37"/>
       <c r="I718" s="20"/>
     </row>
     <row r="719">
-      <c r="A719" s="33"/>
+      <c r="A719" s="37"/>
       <c r="I719" s="20"/>
     </row>
     <row r="720">
-      <c r="A720" s="33"/>
+      <c r="A720" s="37"/>
       <c r="I720" s="20"/>
     </row>
     <row r="721">
-      <c r="A721" s="33"/>
+      <c r="A721" s="37"/>
       <c r="I721" s="20"/>
     </row>
     <row r="722">
-      <c r="A722" s="33"/>
+      <c r="A722" s="37"/>
       <c r="I722" s="20"/>
     </row>
     <row r="723">
-      <c r="A723" s="33"/>
+      <c r="A723" s="37"/>
       <c r="I723" s="20"/>
     </row>
     <row r="724">
-      <c r="A724" s="33"/>
+      <c r="A724" s="37"/>
       <c r="I724" s="20"/>
     </row>
     <row r="725">
-      <c r="A725" s="33"/>
+      <c r="A725" s="37"/>
       <c r="I725" s="20"/>
     </row>
     <row r="726">
-      <c r="A726" s="33"/>
+      <c r="A726" s="37"/>
       <c r="I726" s="20"/>
     </row>
     <row r="727">
-      <c r="A727" s="33"/>
+      <c r="A727" s="37"/>
       <c r="I727" s="20"/>
     </row>
     <row r="728">
-      <c r="A728" s="33"/>
+      <c r="A728" s="37"/>
       <c r="I728" s="20"/>
     </row>
     <row r="729">
-      <c r="A729" s="33"/>
+      <c r="A729" s="37"/>
       <c r="I729" s="20"/>
     </row>
     <row r="730">
-      <c r="A730" s="33"/>
+      <c r="A730" s="37"/>
       <c r="I730" s="20"/>
     </row>
     <row r="731">
-      <c r="A731" s="33"/>
+      <c r="A731" s="37"/>
       <c r="I731" s="20"/>
     </row>
     <row r="732">
-      <c r="A732" s="33"/>
+      <c r="A732" s="37"/>
       <c r="I732" s="20"/>
     </row>
     <row r="733">
-      <c r="A733" s="33"/>
+      <c r="A733" s="37"/>
       <c r="I733" s="20"/>
     </row>
     <row r="734">
-      <c r="A734" s="33"/>
+      <c r="A734" s="37"/>
       <c r="I734" s="20"/>
     </row>
     <row r="735">
-      <c r="A735" s="33"/>
+      <c r="A735" s="37"/>
       <c r="I735" s="20"/>
     </row>
     <row r="736">
-      <c r="A736" s="33"/>
+      <c r="A736" s="37"/>
       <c r="I736" s="20"/>
     </row>
     <row r="737">
-      <c r="A737" s="33"/>
+      <c r="A737" s="37"/>
       <c r="I737" s="20"/>
     </row>
     <row r="738">
-      <c r="A738" s="33"/>
+      <c r="A738" s="37"/>
       <c r="I738" s="20"/>
     </row>
     <row r="739">
-      <c r="A739" s="33"/>
+      <c r="A739" s="37"/>
       <c r="I739" s="20"/>
     </row>
     <row r="740">
-      <c r="A740" s="33"/>
+      <c r="A740" s="37"/>
       <c r="I740" s="20"/>
     </row>
     <row r="741">
-      <c r="A741" s="33"/>
+      <c r="A741" s="37"/>
       <c r="I741" s="20"/>
     </row>
     <row r="742">
-      <c r="A742" s="33"/>
+      <c r="A742" s="37"/>
       <c r="I742" s="20"/>
     </row>
     <row r="743">
-      <c r="A743" s="33"/>
+      <c r="A743" s="37"/>
       <c r="I743" s="20"/>
     </row>
     <row r="744">
-      <c r="A744" s="33"/>
+      <c r="A744" s="37"/>
       <c r="I744" s="20"/>
     </row>
     <row r="745">
-      <c r="A745" s="33"/>
+      <c r="A745" s="37"/>
       <c r="I745" s="20"/>
     </row>
     <row r="746">
-      <c r="A746" s="33"/>
+      <c r="A746" s="37"/>
       <c r="I746" s="20"/>
     </row>
     <row r="747">
-      <c r="A747" s="33"/>
+      <c r="A747" s="37"/>
       <c r="I747" s="20"/>
     </row>
     <row r="748">
-      <c r="A748" s="33"/>
+      <c r="A748" s="37"/>
       <c r="I748" s="20"/>
     </row>
     <row r="749">
-      <c r="A749" s="33"/>
+      <c r="A749" s="37"/>
       <c r="I749" s="20"/>
     </row>
     <row r="750">
-      <c r="A750" s="33"/>
+      <c r="A750" s="37"/>
       <c r="I750" s="20"/>
     </row>
     <row r="751">
-      <c r="A751" s="33"/>
+      <c r="A751" s="37"/>
       <c r="I751" s="20"/>
     </row>
     <row r="752">
-      <c r="A752" s="33"/>
+      <c r="A752" s="37"/>
       <c r="I752" s="20"/>
     </row>
     <row r="753">
-      <c r="A753" s="33"/>
+      <c r="A753" s="37"/>
       <c r="I753" s="20"/>
     </row>
     <row r="754">
-      <c r="A754" s="33"/>
+      <c r="A754" s="37"/>
       <c r="I754" s="20"/>
     </row>
     <row r="755">
-      <c r="A755" s="33"/>
+      <c r="A755" s="37"/>
       <c r="I755" s="20"/>
     </row>
     <row r="756">
-      <c r="A756" s="33"/>
+      <c r="A756" s="37"/>
       <c r="I756" s="20"/>
     </row>
     <row r="757">
-      <c r="A757" s="33"/>
+      <c r="A757" s="37"/>
       <c r="I757" s="20"/>
     </row>
     <row r="758">
-      <c r="A758" s="33"/>
+      <c r="A758" s="37"/>
       <c r="I758" s="20"/>
     </row>
     <row r="759">
-      <c r="A759" s="33"/>
+      <c r="A759" s="37"/>
       <c r="I759" s="20"/>
     </row>
     <row r="760">
-      <c r="A760" s="33"/>
+      <c r="A760" s="37"/>
       <c r="I760" s="20"/>
     </row>
     <row r="761">
-      <c r="A761" s="33"/>
+      <c r="A761" s="37"/>
       <c r="I761" s="20"/>
     </row>
     <row r="762">
-      <c r="A762" s="33"/>
+      <c r="A762" s="37"/>
       <c r="I762" s="20"/>
     </row>
     <row r="763">
-      <c r="A763" s="33"/>
+      <c r="A763" s="37"/>
       <c r="I763" s="20"/>
     </row>
     <row r="764">
-      <c r="A764" s="33"/>
+      <c r="A764" s="37"/>
       <c r="I764" s="20"/>
     </row>
     <row r="765">
-      <c r="A765" s="33"/>
+      <c r="A765" s="37"/>
       <c r="I765" s="20"/>
     </row>
     <row r="766">
-      <c r="A766" s="33"/>
+      <c r="A766" s="37"/>
       <c r="I766" s="20"/>
     </row>
     <row r="767">
-      <c r="A767" s="33"/>
+      <c r="A767" s="37"/>
       <c r="I767" s="20"/>
     </row>
     <row r="768">
-      <c r="A768" s="33"/>
+      <c r="A768" s="37"/>
       <c r="I768" s="20"/>
     </row>
     <row r="769">
-      <c r="A769" s="33"/>
+      <c r="A769" s="37"/>
       <c r="I769" s="20"/>
     </row>
     <row r="770">
-      <c r="A770" s="33"/>
+      <c r="A770" s="37"/>
       <c r="I770" s="20"/>
     </row>
     <row r="771">
-      <c r="A771" s="33"/>
+      <c r="A771" s="37"/>
       <c r="I771" s="20"/>
     </row>
     <row r="772">
-      <c r="A772" s="33"/>
+      <c r="A772" s="37"/>
       <c r="I772" s="20"/>
     </row>
     <row r="773">
-      <c r="A773" s="33"/>
+      <c r="A773" s="37"/>
       <c r="I773" s="20"/>
     </row>
     <row r="774">
-      <c r="A774" s="33"/>
+      <c r="A774" s="37"/>
       <c r="I774" s="20"/>
     </row>
     <row r="775">
-      <c r="A775" s="33"/>
+      <c r="A775" s="37"/>
       <c r="I775" s="20"/>
     </row>
     <row r="776">
-      <c r="A776" s="33"/>
+      <c r="A776" s="37"/>
       <c r="I776" s="20"/>
     </row>
     <row r="777">
-      <c r="A777" s="33"/>
+      <c r="A777" s="37"/>
       <c r="I777" s="20"/>
     </row>
     <row r="778">
-      <c r="A778" s="33"/>
+      <c r="A778" s="37"/>
       <c r="I778" s="20"/>
     </row>
     <row r="779">
-      <c r="A779" s="33"/>
+      <c r="A779" s="37"/>
       <c r="I779" s="20"/>
     </row>
     <row r="780">
-      <c r="A780" s="33"/>
+      <c r="A780" s="37"/>
       <c r="I780" s="20"/>
     </row>
     <row r="781">
-      <c r="A781" s="33"/>
+      <c r="A781" s="37"/>
       <c r="I781" s="20"/>
     </row>
     <row r="782">
-      <c r="A782" s="33"/>
+      <c r="A782" s="37"/>
       <c r="I782" s="20"/>
     </row>
     <row r="783">
-      <c r="A783" s="33"/>
+      <c r="A783" s="37"/>
       <c r="I783" s="20"/>
     </row>
     <row r="784">
-      <c r="A784" s="33"/>
+      <c r="A784" s="37"/>
       <c r="I784" s="20"/>
     </row>
     <row r="785">
-      <c r="A785" s="33"/>
+      <c r="A785" s="37"/>
       <c r="I785" s="20"/>
     </row>
     <row r="786">
-      <c r="A786" s="33"/>
+      <c r="A786" s="37"/>
       <c r="I786" s="20"/>
     </row>
     <row r="787">
-      <c r="A787" s="33"/>
+      <c r="A787" s="37"/>
       <c r="I787" s="20"/>
     </row>
     <row r="788">
-      <c r="A788" s="33"/>
+      <c r="A788" s="37"/>
       <c r="I788" s="20"/>
     </row>
     <row r="789">
-      <c r="A789" s="33"/>
+      <c r="A789" s="37"/>
       <c r="I789" s="20"/>
     </row>
     <row r="790">
-      <c r="A790" s="33"/>
+      <c r="A790" s="37"/>
       <c r="I790" s="20"/>
     </row>
     <row r="791">
-      <c r="A791" s="33"/>
+      <c r="A791" s="37"/>
       <c r="I791" s="20"/>
     </row>
     <row r="792">
-      <c r="A792" s="33"/>
+      <c r="A792" s="37"/>
       <c r="I792" s="20"/>
     </row>
     <row r="793">
-      <c r="A793" s="33"/>
+      <c r="A793" s="37"/>
       <c r="I793" s="20"/>
     </row>
     <row r="794">
-      <c r="A794" s="33"/>
+      <c r="A794" s="37"/>
       <c r="I794" s="20"/>
     </row>
     <row r="795">
-      <c r="A795" s="33"/>
+      <c r="A795" s="37"/>
       <c r="I795" s="20"/>
     </row>
     <row r="796">
-      <c r="A796" s="33"/>
+      <c r="A796" s="37"/>
       <c r="I796" s="20"/>
     </row>
     <row r="797">
-      <c r="A797" s="33"/>
+      <c r="A797" s="37"/>
       <c r="I797" s="20"/>
     </row>
     <row r="798">
-      <c r="A798" s="33"/>
+      <c r="A798" s="37"/>
       <c r="I798" s="20"/>
     </row>
     <row r="799">
-      <c r="A799" s="33"/>
+      <c r="A799" s="37"/>
       <c r="I799" s="20"/>
     </row>
     <row r="800">
-      <c r="A800" s="33"/>
+      <c r="A800" s="37"/>
       <c r="I800" s="20"/>
     </row>
     <row r="801">
-      <c r="A801" s="33"/>
+      <c r="A801" s="37"/>
       <c r="I801" s="20"/>
     </row>
     <row r="802">
-      <c r="A802" s="33"/>
+      <c r="A802" s="37"/>
       <c r="I802" s="20"/>
     </row>
     <row r="803">
-      <c r="A803" s="33"/>
+      <c r="A803" s="37"/>
       <c r="I803" s="20"/>
     </row>
     <row r="804">
-      <c r="A804" s="33"/>
+      <c r="A804" s="37"/>
       <c r="I804" s="20"/>
     </row>
     <row r="805">
-      <c r="A805" s="33"/>
+      <c r="A805" s="37"/>
       <c r="I805" s="20"/>
     </row>
     <row r="806">
-      <c r="A806" s="33"/>
+      <c r="A806" s="37"/>
       <c r="I806" s="20"/>
     </row>
     <row r="807">
-      <c r="A807" s="33"/>
+      <c r="A807" s="37"/>
       <c r="I807" s="20"/>
     </row>
     <row r="808">
-      <c r="A808" s="33"/>
+      <c r="A808" s="37"/>
       <c r="I808" s="20"/>
     </row>
     <row r="809">
-      <c r="A809" s="33"/>
+      <c r="A809" s="37"/>
       <c r="I809" s="20"/>
     </row>
     <row r="810">
-      <c r="A810" s="33"/>
+      <c r="A810" s="37"/>
       <c r="I810" s="20"/>
     </row>
     <row r="811">
-      <c r="A811" s="33"/>
+      <c r="A811" s="37"/>
       <c r="I811" s="20"/>
     </row>
     <row r="812">
-      <c r="A812" s="33"/>
+      <c r="A812" s="37"/>
       <c r="I812" s="20"/>
     </row>
     <row r="813">
-      <c r="A813" s="33"/>
+      <c r="A813" s="37"/>
       <c r="I813" s="20"/>
     </row>
     <row r="814">
-      <c r="A814" s="33"/>
+      <c r="A814" s="37"/>
       <c r="I814" s="20"/>
     </row>
     <row r="815">
-      <c r="A815" s="33"/>
+      <c r="A815" s="37"/>
       <c r="I815" s="20"/>
     </row>
     <row r="816">
-      <c r="A816" s="33"/>
+      <c r="A816" s="37"/>
       <c r="I816" s="20"/>
     </row>
     <row r="817">
-      <c r="A817" s="33"/>
+      <c r="A817" s="37"/>
       <c r="I817" s="20"/>
     </row>
     <row r="818">
-      <c r="A818" s="33"/>
+      <c r="A818" s="37"/>
       <c r="I818" s="20"/>
     </row>
     <row r="819">
-      <c r="A819" s="33"/>
+      <c r="A819" s="37"/>
       <c r="I819" s="20"/>
     </row>
     <row r="820">
-      <c r="A820" s="33"/>
+      <c r="A820" s="37"/>
       <c r="I820" s="20"/>
     </row>
     <row r="821">
-      <c r="A821" s="33"/>
+      <c r="A821" s="37"/>
       <c r="I821" s="20"/>
     </row>
     <row r="822">
-      <c r="A822" s="33"/>
+      <c r="A822" s="37"/>
       <c r="I822" s="20"/>
     </row>
     <row r="823">
-      <c r="A823" s="33"/>
+      <c r="A823" s="37"/>
       <c r="I823" s="20"/>
     </row>
     <row r="824">
-      <c r="A824" s="33"/>
+      <c r="A824" s="37"/>
       <c r="I824" s="20"/>
     </row>
     <row r="825">
-      <c r="A825" s="33"/>
+      <c r="A825" s="37"/>
       <c r="I825" s="20"/>
     </row>
     <row r="826">
-      <c r="A826" s="33"/>
+      <c r="A826" s="37"/>
       <c r="I826" s="20"/>
     </row>
     <row r="827">
-      <c r="A827" s="33"/>
+      <c r="A827" s="37"/>
       <c r="I827" s="20"/>
     </row>
     <row r="828">
-      <c r="A828" s="33"/>
+      <c r="A828" s="37"/>
       <c r="I828" s="20"/>
     </row>
     <row r="829">
-      <c r="A829" s="33"/>
+      <c r="A829" s="37"/>
       <c r="I829" s="20"/>
     </row>
     <row r="830">
-      <c r="A830" s="33"/>
+      <c r="A830" s="37"/>
       <c r="I830" s="20"/>
     </row>
     <row r="831">
-      <c r="A831" s="33"/>
+      <c r="A831" s="37"/>
       <c r="I831" s="20"/>
     </row>
     <row r="832">
-      <c r="A832" s="33"/>
+      <c r="A832" s="37"/>
       <c r="I832" s="20"/>
     </row>
     <row r="833">
-      <c r="A833" s="33"/>
+      <c r="A833" s="37"/>
       <c r="I833" s="20"/>
     </row>
     <row r="834">
-      <c r="A834" s="33"/>
+      <c r="A834" s="37"/>
       <c r="I834" s="20"/>
     </row>
     <row r="835">
-      <c r="A835" s="33"/>
+      <c r="A835" s="37"/>
       <c r="I835" s="20"/>
     </row>
     <row r="836">
-      <c r="A836" s="33"/>
+      <c r="A836" s="37"/>
       <c r="I836" s="20"/>
     </row>
     <row r="837">
-      <c r="A837" s="33"/>
+      <c r="A837" s="37"/>
       <c r="I837" s="20"/>
     </row>
     <row r="838">
-      <c r="A838" s="33"/>
+      <c r="A838" s="37"/>
       <c r="I838" s="20"/>
     </row>
     <row r="839">
-      <c r="A839" s="33"/>
+      <c r="A839" s="37"/>
       <c r="I839" s="20"/>
     </row>
     <row r="840">
-      <c r="A840" s="33"/>
+      <c r="A840" s="37"/>
       <c r="I840" s="20"/>
     </row>
     <row r="841">
-      <c r="A841" s="33"/>
+      <c r="A841" s="37"/>
       <c r="I841" s="20"/>
     </row>
     <row r="842">
-      <c r="A842" s="33"/>
+      <c r="A842" s="37"/>
       <c r="I842" s="20"/>
     </row>
     <row r="843">
-      <c r="A843" s="33"/>
+      <c r="A843" s="37"/>
       <c r="I843" s="20"/>
     </row>
     <row r="844">
-      <c r="A844" s="33"/>
+      <c r="A844" s="37"/>
       <c r="I844" s="20"/>
     </row>
     <row r="845">
-      <c r="A845" s="33"/>
+      <c r="A845" s="37"/>
       <c r="I845" s="20"/>
     </row>
     <row r="846">
-      <c r="A846" s="33"/>
+      <c r="A846" s="37"/>
       <c r="I846" s="20"/>
     </row>
     <row r="847">
-      <c r="A847" s="33"/>
+      <c r="A847" s="37"/>
       <c r="I847" s="20"/>
     </row>
     <row r="848">
-      <c r="A848" s="33"/>
+      <c r="A848" s="37"/>
       <c r="I848" s="20"/>
     </row>
     <row r="849">
-      <c r="A849" s="33"/>
+      <c r="A849" s="37"/>
       <c r="I849" s="20"/>
     </row>
     <row r="850">
-      <c r="A850" s="33"/>
+      <c r="A850" s="37"/>
       <c r="I850" s="20"/>
     </row>
     <row r="851">
-      <c r="A851" s="33"/>
+      <c r="A851" s="37"/>
       <c r="I851" s="20"/>
     </row>
     <row r="852">
-      <c r="A852" s="33"/>
+      <c r="A852" s="37"/>
       <c r="I852" s="20"/>
     </row>
     <row r="853">
-      <c r="A853" s="33"/>
+      <c r="A853" s="37"/>
       <c r="I853" s="20"/>
     </row>
     <row r="854">
-      <c r="A854" s="33"/>
+      <c r="A854" s="37"/>
       <c r="I854" s="20"/>
     </row>
     <row r="855">
-      <c r="A855" s="33"/>
+      <c r="A855" s="37"/>
       <c r="I855" s="20"/>
     </row>
     <row r="856">
-      <c r="A856" s="33"/>
+      <c r="A856" s="37"/>
       <c r="I856" s="20"/>
     </row>
     <row r="857">
-      <c r="A857" s="33"/>
+      <c r="A857" s="37"/>
       <c r="I857" s="20"/>
     </row>
     <row r="858">
-      <c r="A858" s="33"/>
+      <c r="A858" s="37"/>
       <c r="I858" s="20"/>
     </row>
     <row r="859">
-      <c r="A859" s="33"/>
+      <c r="A859" s="37"/>
       <c r="I859" s="20"/>
     </row>
     <row r="860">
-      <c r="A860" s="33"/>
+      <c r="A860" s="37"/>
       <c r="I860" s="20"/>
     </row>
     <row r="861">
-      <c r="A861" s="33"/>
+      <c r="A861" s="37"/>
       <c r="I861" s="20"/>
     </row>
     <row r="862">
-      <c r="A862" s="33"/>
+      <c r="A862" s="37"/>
       <c r="I862" s="20"/>
     </row>
     <row r="863">
-      <c r="A863" s="33"/>
+      <c r="A863" s="37"/>
       <c r="I863" s="20"/>
     </row>
     <row r="864">
-      <c r="A864" s="33"/>
+      <c r="A864" s="37"/>
       <c r="I864" s="20"/>
     </row>
     <row r="865">
-      <c r="A865" s="33"/>
+      <c r="A865" s="37"/>
       <c r="I865" s="20"/>
     </row>
     <row r="866">
-      <c r="A866" s="33"/>
+      <c r="A866" s="37"/>
       <c r="I866" s="20"/>
     </row>
     <row r="867">
-      <c r="A867" s="33"/>
+      <c r="A867" s="37"/>
       <c r="I867" s="20"/>
     </row>
     <row r="868">
-      <c r="A868" s="33"/>
+      <c r="A868" s="37"/>
       <c r="I868" s="20"/>
     </row>
     <row r="869">
-      <c r="A869" s="33"/>
+      <c r="A869" s="37"/>
       <c r="I869" s="20"/>
     </row>
     <row r="870">
-      <c r="A870" s="33"/>
+      <c r="A870" s="37"/>
       <c r="I870" s="20"/>
     </row>
     <row r="871">
-      <c r="A871" s="33"/>
+      <c r="A871" s="37"/>
       <c r="I871" s="20"/>
     </row>
     <row r="872">
-      <c r="A872" s="33"/>
+      <c r="A872" s="37"/>
       <c r="I872" s="20"/>
     </row>
     <row r="873">
-      <c r="A873" s="33"/>
+      <c r="A873" s="37"/>
       <c r="I873" s="20"/>
     </row>
     <row r="874">
-      <c r="A874" s="33"/>
+      <c r="A874" s="37"/>
       <c r="I874" s="20"/>
     </row>
     <row r="875">
-      <c r="A875" s="33"/>
+      <c r="A875" s="37"/>
       <c r="I875" s="20"/>
     </row>
     <row r="876">
-      <c r="A876" s="33"/>
+      <c r="A876" s="37"/>
       <c r="I876" s="20"/>
     </row>
     <row r="877">
-      <c r="A877" s="33"/>
+      <c r="A877" s="37"/>
       <c r="I877" s="20"/>
     </row>
     <row r="878">
-      <c r="A878" s="33"/>
+      <c r="A878" s="37"/>
       <c r="I878" s="20"/>
     </row>
     <row r="879">
-      <c r="A879" s="33"/>
+      <c r="A879" s="37"/>
       <c r="I879" s="20"/>
     </row>
     <row r="880">
-      <c r="A880" s="33"/>
+      <c r="A880" s="37"/>
       <c r="I880" s="20"/>
     </row>
     <row r="881">
-      <c r="A881" s="33"/>
+      <c r="A881" s="37"/>
       <c r="I881" s="20"/>
     </row>
     <row r="882">
-      <c r="A882" s="33"/>
+      <c r="A882" s="37"/>
       <c r="I882" s="20"/>
     </row>
     <row r="883">
-      <c r="A883" s="33"/>
+      <c r="A883" s="37"/>
       <c r="I883" s="20"/>
     </row>
     <row r="884">
-      <c r="A884" s="33"/>
+      <c r="A884" s="37"/>
       <c r="I884" s="20"/>
     </row>
     <row r="885">
-      <c r="A885" s="33"/>
+      <c r="A885" s="37"/>
       <c r="I885" s="20"/>
     </row>
     <row r="886">
-      <c r="A886" s="33"/>
+      <c r="A886" s="37"/>
       <c r="I886" s="20"/>
     </row>
     <row r="887">
-      <c r="A887" s="33"/>
+      <c r="A887" s="37"/>
       <c r="I887" s="20"/>
     </row>
     <row r="888">
-      <c r="A888" s="33"/>
+      <c r="A888" s="37"/>
       <c r="I888" s="20"/>
     </row>
     <row r="889">
-      <c r="A889" s="33"/>
+      <c r="A889" s="37"/>
       <c r="I889" s="20"/>
     </row>
     <row r="890">
-      <c r="A890" s="33"/>
+      <c r="A890" s="37"/>
       <c r="I890" s="20"/>
     </row>
     <row r="891">
-      <c r="A891" s="33"/>
+      <c r="A891" s="37"/>
       <c r="I891" s="20"/>
     </row>
     <row r="892">
-      <c r="A892" s="33"/>
+      <c r="A892" s="37"/>
       <c r="I892" s="20"/>
     </row>
     <row r="893">
-      <c r="A893" s="33"/>
+      <c r="A893" s="37"/>
       <c r="I893" s="20"/>
     </row>
     <row r="894">
-      <c r="A894" s="33"/>
+      <c r="A894" s="37"/>
       <c r="I894" s="20"/>
     </row>
     <row r="895">
-      <c r="A895" s="33"/>
+      <c r="A895" s="37"/>
       <c r="I895" s="20"/>
     </row>
     <row r="896">
-      <c r="A896" s="33"/>
+      <c r="A896" s="37"/>
       <c r="I896" s="20"/>
     </row>
     <row r="897">
-      <c r="A897" s="33"/>
+      <c r="A897" s="37"/>
       <c r="I897" s="20"/>
     </row>
     <row r="898">
-      <c r="A898" s="33"/>
+      <c r="A898" s="37"/>
       <c r="I898" s="20"/>
     </row>
     <row r="899">
-      <c r="A899" s="33"/>
+      <c r="A899" s="37"/>
       <c r="I899" s="20"/>
     </row>
     <row r="900">
-      <c r="A900" s="33"/>
+      <c r="A900" s="37"/>
       <c r="I900" s="20"/>
     </row>
     <row r="901">
-      <c r="A901" s="33"/>
+      <c r="A901" s="37"/>
       <c r="I901" s="20"/>
     </row>
     <row r="902">
-      <c r="A902" s="33"/>
+      <c r="A902" s="37"/>
       <c r="I902" s="20"/>
     </row>
     <row r="903">
-      <c r="A903" s="33"/>
+      <c r="A903" s="37"/>
       <c r="I903" s="20"/>
     </row>
     <row r="904">
-      <c r="A904" s="33"/>
+      <c r="A904" s="37"/>
       <c r="I904" s="20"/>
     </row>
     <row r="905">
-      <c r="A905" s="33"/>
+      <c r="A905" s="37"/>
       <c r="I905" s="20"/>
     </row>
     <row r="906">
-      <c r="A906" s="33"/>
+      <c r="A906" s="37"/>
       <c r="I906" s="20"/>
     </row>
     <row r="907">
-      <c r="A907" s="33"/>
+      <c r="A907" s="37"/>
       <c r="I907" s="20"/>
     </row>
     <row r="908">
-      <c r="A908" s="33"/>
+      <c r="A908" s="37"/>
       <c r="I908" s="20"/>
     </row>
     <row r="909">
-      <c r="A909" s="33"/>
+      <c r="A909" s="37"/>
       <c r="I909" s="20"/>
     </row>
     <row r="910">
-      <c r="A910" s="33"/>
+      <c r="A910" s="37"/>
       <c r="I910" s="20"/>
     </row>
     <row r="911">
-      <c r="A911" s="33"/>
+      <c r="A911" s="37"/>
       <c r="I911" s="20"/>
     </row>
     <row r="912">
-      <c r="A912" s="33"/>
+      <c r="A912" s="37"/>
       <c r="I912" s="20"/>
     </row>
     <row r="913">
-      <c r="A913" s="33"/>
+      <c r="A913" s="37"/>
       <c r="I913" s="20"/>
     </row>
     <row r="914">
-      <c r="A914" s="33"/>
+      <c r="A914" s="37"/>
       <c r="I914" s="20"/>
     </row>
     <row r="915">
-      <c r="A915" s="33"/>
+      <c r="A915" s="37"/>
       <c r="I915" s="20"/>
     </row>
     <row r="916">
-      <c r="A916" s="33"/>
+      <c r="A916" s="37"/>
       <c r="I916" s="20"/>
     </row>
     <row r="917">
-      <c r="A917" s="33"/>
+      <c r="A917" s="37"/>
       <c r="I917" s="20"/>
     </row>
     <row r="918">
-      <c r="A918" s="33"/>
+      <c r="A918" s="37"/>
       <c r="I918" s="20"/>
     </row>
     <row r="919">
-      <c r="A919" s="33"/>
+      <c r="A919" s="37"/>
       <c r="I919" s="20"/>
     </row>
     <row r="920">
-      <c r="A920" s="33"/>
+      <c r="A920" s="37"/>
       <c r="I920" s="20"/>
     </row>
     <row r="921">
-      <c r="A921" s="33"/>
+      <c r="A921" s="37"/>
       <c r="I921" s="20"/>
     </row>
     <row r="922">
-      <c r="A922" s="33"/>
+      <c r="A922" s="37"/>
       <c r="I922" s="20"/>
     </row>
     <row r="923">
-      <c r="A923" s="33"/>
+      <c r="A923" s="37"/>
       <c r="I923" s="20"/>
     </row>
     <row r="924">
-      <c r="A924" s="33"/>
+      <c r="A924" s="37"/>
       <c r="I924" s="20"/>
     </row>
     <row r="925">
-      <c r="A925" s="33"/>
+      <c r="A925" s="37"/>
       <c r="I925" s="20"/>
     </row>
     <row r="926">
-      <c r="A926" s="33"/>
+      <c r="A926" s="37"/>
       <c r="I926" s="20"/>
     </row>
     <row r="927">
-      <c r="A927" s="33"/>
+      <c r="A927" s="37"/>
       <c r="I927" s="20"/>
     </row>
     <row r="928">
-      <c r="A928" s="33"/>
+      <c r="A928" s="37"/>
       <c r="I928" s="20"/>
     </row>
     <row r="929">
-      <c r="A929" s="33"/>
+      <c r="A929" s="37"/>
       <c r="I929" s="20"/>
     </row>
     <row r="930">
-      <c r="A930" s="33"/>
+      <c r="A930" s="37"/>
       <c r="I930" s="20"/>
     </row>
     <row r="931">
-      <c r="A931" s="33"/>
+      <c r="A931" s="37"/>
       <c r="I931" s="20"/>
     </row>
     <row r="932">
-      <c r="A932" s="33"/>
+      <c r="A932" s="37"/>
       <c r="I932" s="20"/>
     </row>
     <row r="933">
-      <c r="A933" s="33"/>
+      <c r="A933" s="37"/>
       <c r="I933" s="20"/>
     </row>
     <row r="934">
-      <c r="A934" s="33"/>
+      <c r="A934" s="37"/>
       <c r="I934" s="20"/>
     </row>
     <row r="935">
-      <c r="A935" s="33"/>
+      <c r="A935" s="37"/>
       <c r="I935" s="20"/>
     </row>
     <row r="936">
-      <c r="A936" s="33"/>
+      <c r="A936" s="37"/>
       <c r="I936" s="20"/>
     </row>
     <row r="937">
-      <c r="A937" s="33"/>
+      <c r="A937" s="37"/>
       <c r="I937" s="20"/>
     </row>
     <row r="938">
-      <c r="A938" s="33"/>
+      <c r="A938" s="37"/>
       <c r="I938" s="20"/>
     </row>
     <row r="939">
-      <c r="A939" s="33"/>
+      <c r="A939" s="37"/>
       <c r="I939" s="20"/>
     </row>
     <row r="940">
-      <c r="A940" s="33"/>
+      <c r="A940" s="37"/>
       <c r="I940" s="20"/>
     </row>
     <row r="941">
-      <c r="A941" s="33"/>
+      <c r="A941" s="37"/>
       <c r="I941" s="20"/>
     </row>
     <row r="942">
-      <c r="A942" s="33"/>
+      <c r="A942" s="37"/>
       <c r="I942" s="20"/>
     </row>
     <row r="943">
-      <c r="A943" s="33"/>
+      <c r="A943" s="37"/>
       <c r="I943" s="20"/>
     </row>
     <row r="944">
-      <c r="A944" s="33"/>
+      <c r="A944" s="37"/>
       <c r="I944" s="20"/>
     </row>
     <row r="945">
-      <c r="A945" s="33"/>
+      <c r="A945" s="37"/>
       <c r="I945" s="20"/>
     </row>
     <row r="946">
-      <c r="A946" s="33"/>
+      <c r="A946" s="37"/>
       <c r="I946" s="20"/>
     </row>
     <row r="947">
-      <c r="A947" s="33"/>
+      <c r="A947" s="37"/>
       <c r="I947" s="20"/>
     </row>
     <row r="948">
-      <c r="A948" s="33"/>
+      <c r="A948" s="37"/>
       <c r="I948" s="20"/>
     </row>
     <row r="949">
-      <c r="A949" s="33"/>
+      <c r="A949" s="37"/>
       <c r="I949" s="20"/>
     </row>
     <row r="950">
-      <c r="A950" s="33"/>
+      <c r="A950" s="37"/>
       <c r="I950" s="20"/>
     </row>
     <row r="951">
-      <c r="A951" s="33"/>
+      <c r="A951" s="37"/>
       <c r="I951" s="20"/>
     </row>
     <row r="952">
-      <c r="A952" s="33"/>
+      <c r="A952" s="37"/>
       <c r="I952" s="20"/>
     </row>
     <row r="953">
-      <c r="A953" s="33"/>
+      <c r="A953" s="37"/>
       <c r="I953" s="20"/>
     </row>
     <row r="954">
-      <c r="A954" s="33"/>
+      <c r="A954" s="37"/>
       <c r="I954" s="20"/>
     </row>
     <row r="955">
-      <c r="A955" s="33"/>
+      <c r="A955" s="37"/>
       <c r="I955" s="20"/>
     </row>
     <row r="956">
-      <c r="A956" s="33"/>
+      <c r="A956" s="37"/>
       <c r="I956" s="20"/>
     </row>
     <row r="957">
-      <c r="A957" s="33"/>
+      <c r="A957" s="37"/>
       <c r="I957" s="20"/>
     </row>
     <row r="958">
-      <c r="A958" s="33"/>
+      <c r="A958" s="37"/>
       <c r="I958" s="20"/>
     </row>
     <row r="959">
-      <c r="A959" s="33"/>
+      <c r="A959" s="37"/>
       <c r="I959" s="20"/>
     </row>
     <row r="960">
-      <c r="A960" s="33"/>
+      <c r="A960" s="37"/>
       <c r="I960" s="20"/>
     </row>
     <row r="961">
-      <c r="A961" s="33"/>
+      <c r="A961" s="37"/>
       <c r="I961" s="20"/>
     </row>
     <row r="962">
-      <c r="A962" s="33"/>
+      <c r="A962" s="37"/>
       <c r="I962" s="20"/>
     </row>
     <row r="963">
-      <c r="A963" s="33"/>
+      <c r="A963" s="37"/>
       <c r="I963" s="20"/>
     </row>
     <row r="964">
-      <c r="A964" s="33"/>
+      <c r="A964" s="37"/>
       <c r="I964" s="20"/>
     </row>
     <row r="965">
-      <c r="A965" s="33"/>
+      <c r="A965" s="37"/>
       <c r="I965" s="20"/>
     </row>
     <row r="966">
-      <c r="A966" s="33"/>
+      <c r="A966" s="37"/>
       <c r="I966" s="20"/>
     </row>
     <row r="967">
-      <c r="A967" s="33"/>
+      <c r="A967" s="37"/>
       <c r="I967" s="20"/>
     </row>
     <row r="968">
-      <c r="A968" s="33"/>
+      <c r="A968" s="37"/>
       <c r="I968" s="20"/>
     </row>
     <row r="969">
-      <c r="A969" s="33"/>
+      <c r="A969" s="37"/>
       <c r="I969" s="20"/>
     </row>
     <row r="970">
-      <c r="A970" s="33"/>
+      <c r="A970" s="37"/>
       <c r="I970" s="20"/>
     </row>
     <row r="971">
-      <c r="A971" s="33"/>
+      <c r="A971" s="37"/>
       <c r="I971" s="20"/>
     </row>
     <row r="972">
-      <c r="A972" s="33"/>
+      <c r="A972" s="37"/>
       <c r="I972" s="20"/>
     </row>
     <row r="973">
-      <c r="A973" s="33"/>
+      <c r="A973" s="37"/>
       <c r="I973" s="20"/>
     </row>
     <row r="974">
-      <c r="A974" s="33"/>
+      <c r="A974" s="37"/>
       <c r="I974" s="20"/>
     </row>
     <row r="975">
-      <c r="A975" s="33"/>
+      <c r="A975" s="37"/>
       <c r="I975" s="20"/>
     </row>
     <row r="976">
-      <c r="A976" s="33"/>
+      <c r="A976" s="37"/>
       <c r="I976" s="20"/>
     </row>
     <row r="977">
-      <c r="A977" s="33"/>
+      <c r="A977" s="37"/>
       <c r="I977" s="20"/>
     </row>
     <row r="978">
-      <c r="A978" s="33"/>
+      <c r="A978" s="37"/>
       <c r="I978" s="20"/>
     </row>
     <row r="979">
-      <c r="A979" s="33"/>
+      <c r="A979" s="37"/>
       <c r="I979" s="20"/>
     </row>
     <row r="980">
-      <c r="A980" s="33"/>
+      <c r="A980" s="37"/>
       <c r="I980" s="20"/>
     </row>
     <row r="981">
-      <c r="A981" s="33"/>
+      <c r="A981" s="37"/>
       <c r="I981" s="20"/>
     </row>
     <row r="982">
-      <c r="A982" s="33"/>
+      <c r="A982" s="37"/>
       <c r="I982" s="20"/>
     </row>
     <row r="983">
-      <c r="A983" s="33"/>
+      <c r="A983" s="37"/>
       <c r="I983" s="20"/>
     </row>
     <row r="984">
-      <c r="A984" s="33"/>
+      <c r="A984" s="37"/>
       <c r="I984" s="20"/>
     </row>
     <row r="985">
-      <c r="A985" s="33"/>
+      <c r="A985" s="37"/>
       <c r="I985" s="20"/>
     </row>
     <row r="986">
-      <c r="A986" s="33"/>
+      <c r="A986" s="37"/>
       <c r="I986" s="20"/>
     </row>
     <row r="987">
-      <c r="A987" s="33"/>
+      <c r="A987" s="37"/>
       <c r="I987" s="20"/>
     </row>
     <row r="988">
-      <c r="A988" s="33"/>
+      <c r="A988" s="37"/>
       <c r="I988" s="20"/>
     </row>
     <row r="989">
-      <c r="A989" s="33"/>
+      <c r="A989" s="37"/>
       <c r="I989" s="20"/>
     </row>
     <row r="990">
-      <c r="A990" s="33"/>
+      <c r="A990" s="37"/>
       <c r="I990" s="20"/>
     </row>
     <row r="991">
-      <c r="A991" s="33"/>
+      <c r="A991" s="37"/>
       <c r="I991" s="20"/>
     </row>
     <row r="992">
-      <c r="A992" s="33"/>
+      <c r="A992" s="37"/>
       <c r="I992" s="20"/>
     </row>
     <row r="993">
-      <c r="A993" s="33"/>
+      <c r="A993" s="37"/>
       <c r="I993" s="20"/>
     </row>
     <row r="994">
-      <c r="A994" s="33"/>
+      <c r="A994" s="37"/>
       <c r="I994" s="20"/>
     </row>
     <row r="995">
-      <c r="A995" s="33"/>
+      <c r="A995" s="37"/>
       <c r="I995" s="20"/>
     </row>
     <row r="996">
-      <c r="A996" s="33"/>
+      <c r="A996" s="37"/>
       <c r="I996" s="20"/>
     </row>
     <row r="997">
-      <c r="A997" s="33"/>
+      <c r="A997" s="37"/>
       <c r="I997" s="20"/>
     </row>
     <row r="998">
-      <c r="A998" s="33"/>
+      <c r="A998" s="37"/>
       <c r="I998" s="20"/>
     </row>
     <row r="999">
-      <c r="A999" s="33"/>
+      <c r="A999" s="37"/>
       <c r="I999" s="20"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="33"/>
+      <c r="A1000" s="37"/>
       <c r="I1000" s="20"/>
     </row>
   </sheetData>

--- a/src/data/AFCARS.xlsx
+++ b/src/data/AFCARS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="67">
   <si>
     <t>State</t>
   </si>
@@ -221,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -255,10 +255,16 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,6 +287,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -362,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -458,9 +470,27 @@
     <xf borderId="5" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="6" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="6" fillId="5" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -8259,22 +8289,22 @@
         <v>2025.0</v>
       </c>
       <c r="C210" s="22">
-        <v>2460.0</v>
+        <v>2516.0</v>
       </c>
       <c r="D210" s="23">
+        <v>977.0</v>
+      </c>
+      <c r="E210" s="24">
         <v>771.0</v>
       </c>
-      <c r="E210" s="24">
-        <v>1199.0</v>
-      </c>
       <c r="F210" s="23">
-        <v>297.0</v>
+        <v>239.0</v>
       </c>
       <c r="G210" s="23">
-        <v>196.0</v>
+        <v>179.0</v>
       </c>
       <c r="H210" s="25">
-        <v>0.559</v>
+        <v>0.57</v>
       </c>
       <c r="I210" s="26" t="s">
         <v>13</v>
@@ -8284,7 +8314,7 @@
       </c>
       <c r="K210" s="12">
         <f t="shared" si="1"/>
-        <v>0.3707317073</v>
+        <v>0.3624801272</v>
       </c>
       <c r="L210" s="27"/>
     </row>
@@ -8296,22 +8326,22 @@
         <v>2025.0</v>
       </c>
       <c r="C211" s="28">
-        <v>5616.0</v>
+        <v>5734.0</v>
       </c>
       <c r="D211" s="29">
-        <v>3189.0</v>
+        <v>3600.0</v>
       </c>
       <c r="E211" s="30">
-        <v>866.0</v>
+        <v>893.0</v>
       </c>
       <c r="F211" s="30">
-        <v>398.0</v>
+        <v>375.0</v>
       </c>
       <c r="G211" s="30">
-        <v>720.0</v>
+        <v>768.0</v>
       </c>
       <c r="H211" s="31">
-        <v>0.361</v>
+        <v>0.375</v>
       </c>
       <c r="I211" s="26">
         <v>11.0</v>
@@ -8321,7 +8351,7 @@
       </c>
       <c r="K211" s="12">
         <f t="shared" si="1"/>
-        <v>0.4802350427</v>
+        <v>0.4703522846</v>
       </c>
       <c r="L211" s="27"/>
     </row>
@@ -8333,22 +8363,22 @@
         <v>2025.0</v>
       </c>
       <c r="C212" s="28">
-        <v>3264.0</v>
+        <v>3278.0</v>
       </c>
       <c r="D212" s="29">
-        <v>1011.0</v>
+        <v>1460.0</v>
       </c>
       <c r="E212" s="29">
-        <v>1028.0</v>
+        <v>777.0</v>
       </c>
       <c r="F212" s="30">
-        <v>96.0</v>
+        <v>78.0</v>
       </c>
       <c r="G212" s="30">
-        <v>511.0</v>
+        <v>561.0</v>
       </c>
       <c r="H212" s="31">
-        <v>0.415</v>
+        <v>0.42</v>
       </c>
       <c r="I212" s="26">
         <v>648.0</v>
@@ -8358,7 +8388,7 @@
       </c>
       <c r="K212" s="12">
         <f t="shared" si="1"/>
-        <v>0.4957107843</v>
+        <v>0.4935936547</v>
       </c>
       <c r="L212" s="27"/>
     </row>
@@ -8370,16 +8400,16 @@
         <v>2025.0</v>
       </c>
       <c r="C213" s="28">
-        <v>8306.0</v>
+        <v>8369.0</v>
       </c>
       <c r="D213" s="29">
-        <v>1929.0</v>
+        <v>1970.0</v>
       </c>
       <c r="E213" s="29">
-        <v>3232.0</v>
+        <v>2155.0</v>
       </c>
       <c r="F213" s="29">
-        <v>1073.0</v>
+        <v>1002.0</v>
       </c>
       <c r="G213" s="29">
         <v>1440.0</v>
@@ -8395,7 +8425,7 @@
       </c>
       <c r="K213" s="12">
         <f t="shared" si="1"/>
-        <v>0.2309174091</v>
+        <v>0.2291791134</v>
       </c>
       <c r="L213" s="27"/>
     </row>
@@ -8407,22 +8437,22 @@
         <v>2025.0</v>
       </c>
       <c r="C214" s="28">
-        <v>36212.0</v>
+        <v>37499.0</v>
       </c>
       <c r="D214" s="29">
-        <v>16560.0</v>
+        <v>19552.0</v>
       </c>
       <c r="E214" s="29">
-        <v>14495.0</v>
+        <v>11580.0</v>
       </c>
       <c r="F214" s="29">
-        <v>4916.0</v>
+        <v>4636.0</v>
       </c>
       <c r="G214" s="29">
-        <v>5352.0</v>
+        <v>5234.0</v>
       </c>
       <c r="H214" s="31">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="I214" s="32">
         <v>23372.0</v>
@@ -8432,7 +8462,7 @@
       </c>
       <c r="K214" s="12">
         <f t="shared" si="1"/>
-        <v>0.8545509776</v>
+        <v>0.8252220059</v>
       </c>
       <c r="L214" s="27"/>
     </row>
@@ -8444,22 +8474,22 @@
         <v>2025.0</v>
       </c>
       <c r="C215" s="28">
-        <v>4194.0</v>
+        <v>4373.0</v>
       </c>
       <c r="D215" s="29">
-        <v>1394.0</v>
+        <v>1906.0</v>
       </c>
       <c r="E215" s="29">
-        <v>1772.0</v>
-      </c>
-      <c r="F215" s="30" t="s">
-        <v>66</v>
+        <v>1397.0</v>
+      </c>
+      <c r="F215" s="30">
+        <v>6.0</v>
       </c>
       <c r="G215" s="30">
-        <v>451.0</v>
+        <v>436.0</v>
       </c>
       <c r="H215" s="31">
-        <v>0.443</v>
+        <v>0.458</v>
       </c>
       <c r="I215" s="26">
         <v>613.0</v>
@@ -8469,7 +8499,7 @@
       </c>
       <c r="K215" s="12">
         <f t="shared" si="1"/>
-        <v>0.5195517406</v>
+        <v>0.4982849303</v>
       </c>
       <c r="L215" s="27"/>
     </row>
@@ -8481,20 +8511,22 @@
         <v>2025.0</v>
       </c>
       <c r="C216" s="28">
-        <v>3440.0</v>
+        <v>3639.0</v>
       </c>
       <c r="D216" s="30">
-        <v>755.0</v>
+        <v>1425.0</v>
       </c>
       <c r="E216" s="29">
-        <v>1517.0</v>
-      </c>
-      <c r="F216" s="33"/>
+        <v>1269.0</v>
+      </c>
+      <c r="F216" s="33">
+        <v>16.0</v>
+      </c>
       <c r="G216" s="30">
         <v>133.0</v>
       </c>
       <c r="H216" s="31">
-        <v>0.196</v>
+        <v>0.406</v>
       </c>
       <c r="I216" s="26">
         <v>151.0</v>
@@ -8504,7 +8536,7 @@
       </c>
       <c r="K216" s="12">
         <f t="shared" si="1"/>
-        <v>0.6075581395</v>
+        <v>0.5743336081</v>
       </c>
       <c r="L216" s="27"/>
     </row>
@@ -8516,20 +8548,20 @@
         <v>2025.0</v>
       </c>
       <c r="C217" s="34">
-        <v>523.0</v>
+        <v>533.0</v>
       </c>
       <c r="D217" s="30">
-        <v>267.0</v>
+        <v>285.0</v>
       </c>
       <c r="E217" s="30">
         <v>103.0</v>
       </c>
-      <c r="F217" s="33"/>
+      <c r="F217" s="35"/>
       <c r="G217" s="30">
         <v>60.0</v>
       </c>
       <c r="H217" s="31">
-        <v>0.357</v>
+        <v>0.367</v>
       </c>
       <c r="I217" s="26">
         <v>49.0</v>
@@ -8539,7 +8571,7 @@
       </c>
       <c r="K217" s="12">
         <f t="shared" si="1"/>
-        <v>0.6615678776</v>
+        <v>0.6491557223</v>
       </c>
       <c r="L217" s="27"/>
     </row>
@@ -8551,22 +8583,22 @@
         <v>2025.0</v>
       </c>
       <c r="C218" s="34">
-        <v>469.0</v>
+        <v>470.0</v>
       </c>
       <c r="D218" s="30">
-        <v>244.0</v>
+        <v>291.0</v>
       </c>
       <c r="E218" s="30">
+        <v>67.0</v>
+      </c>
+      <c r="F218" s="30">
         <v>95.0</v>
       </c>
-      <c r="F218" s="30">
-        <v>101.0</v>
-      </c>
       <c r="G218" s="30">
-        <v>80.0</v>
+        <v>79.0</v>
       </c>
       <c r="H218" s="31">
-        <v>0.293</v>
+        <v>0.283</v>
       </c>
       <c r="I218" s="26" t="s">
         <v>32</v>
@@ -8576,7 +8608,7 @@
       </c>
       <c r="K218" s="12">
         <f t="shared" si="1"/>
-        <v>0.763326226</v>
+        <v>0.7617021277</v>
       </c>
       <c r="L218" s="27"/>
     </row>
@@ -8588,22 +8620,22 @@
         <v>2025.0</v>
       </c>
       <c r="C219" s="28">
-        <v>15346.0</v>
+        <v>15594.0</v>
       </c>
       <c r="D219" s="29">
-        <v>4603.0</v>
+        <v>6783.0</v>
       </c>
       <c r="E219" s="29">
-        <v>7187.0</v>
+        <v>5148.0</v>
       </c>
       <c r="F219" s="29">
-        <v>1539.0</v>
+        <v>816.0</v>
       </c>
       <c r="G219" s="29">
         <v>3591.0</v>
       </c>
       <c r="H219" s="31">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="I219" s="26" t="s">
         <v>13</v>
@@ -8613,7 +8645,7 @@
       </c>
       <c r="K219" s="12">
         <f t="shared" si="1"/>
-        <v>0.436530692</v>
+        <v>0.4295883032</v>
       </c>
       <c r="L219" s="27"/>
     </row>
@@ -8625,22 +8657,22 @@
         <v>2025.0</v>
       </c>
       <c r="C220" s="28">
-        <v>10877.0</v>
+        <v>10989.0</v>
       </c>
       <c r="D220" s="29">
-        <v>6449.0</v>
+        <v>6751.0</v>
       </c>
       <c r="E220" s="29">
-        <v>2376.0</v>
+        <v>2065.0</v>
       </c>
       <c r="F220" s="30">
-        <v>891.0</v>
+        <v>833.0</v>
       </c>
       <c r="G220" s="29">
-        <v>1051.0</v>
+        <v>1093.0</v>
       </c>
       <c r="H220" s="31">
-        <v>0.458</v>
+        <v>0.446</v>
       </c>
       <c r="I220" s="32">
         <v>4402.0</v>
@@ -8650,7 +8682,7 @@
       </c>
       <c r="K220" s="12">
         <f t="shared" si="1"/>
-        <v>0.413257332</v>
+        <v>0.409045409</v>
       </c>
       <c r="L220" s="27"/>
     </row>
@@ -8662,22 +8694,22 @@
         <v>2025.0</v>
       </c>
       <c r="C221" s="34">
-        <v>913.0</v>
+        <v>922.0</v>
       </c>
       <c r="D221" s="30">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
       <c r="E221" s="30">
-        <v>307.0</v>
+        <v>269.0</v>
       </c>
       <c r="F221" s="30">
-        <v>178.0</v>
+        <v>169.0</v>
       </c>
       <c r="G221" s="30">
         <v>122.0</v>
       </c>
       <c r="H221" s="31">
-        <v>0.57</v>
+        <v>0.571</v>
       </c>
       <c r="I221" s="26">
         <v>83.0</v>
@@ -8687,7 +8719,7 @@
       </c>
       <c r="K221" s="12">
         <f t="shared" si="1"/>
-        <v>0.7688937568</v>
+        <v>0.7613882863</v>
       </c>
       <c r="L221" s="27"/>
     </row>
@@ -8699,19 +8731,19 @@
         <v>2025.0</v>
       </c>
       <c r="C222" s="28">
-        <v>3365.0</v>
+        <v>3410.0</v>
       </c>
       <c r="D222" s="30">
-        <v>824.0</v>
+        <v>1228.0</v>
       </c>
       <c r="E222" s="29">
-        <v>1770.0</v>
+        <v>1395.0</v>
       </c>
       <c r="F222" s="30">
-        <v>600.0</v>
+        <v>529.0</v>
       </c>
       <c r="G222" s="30">
-        <v>806.0</v>
+        <v>802.0</v>
       </c>
       <c r="H222" s="31">
         <v>0.477</v>
@@ -8724,7 +8756,7 @@
       </c>
       <c r="K222" s="12">
         <f t="shared" si="1"/>
-        <v>0.5797919762</v>
+        <v>0.5721407625</v>
       </c>
       <c r="L222" s="27"/>
     </row>
@@ -8736,22 +8768,22 @@
         <v>2025.0</v>
       </c>
       <c r="C223" s="28">
-        <v>1258.0</v>
+        <v>1269.0</v>
       </c>
       <c r="D223" s="30">
-        <v>534.0</v>
+        <v>640.0</v>
       </c>
       <c r="E223" s="30">
-        <v>361.0</v>
+        <v>244.0</v>
       </c>
       <c r="F223" s="30">
-        <v>104.0</v>
+        <v>101.0</v>
       </c>
       <c r="G223" s="30">
         <v>237.0</v>
       </c>
       <c r="H223" s="31">
-        <v>0.598</v>
+        <v>0.599</v>
       </c>
       <c r="I223" s="26">
         <v>215.0</v>
@@ -8761,7 +8793,7 @@
       </c>
       <c r="K223" s="12">
         <f t="shared" si="1"/>
-        <v>0.9515103339</v>
+        <v>0.9432624113</v>
       </c>
       <c r="L223" s="27"/>
     </row>
@@ -8773,22 +8805,22 @@
         <v>2025.0</v>
       </c>
       <c r="C224" s="28">
-        <v>16610.0</v>
+        <v>16806.0</v>
       </c>
       <c r="D224" s="29">
-        <v>4398.0</v>
+        <v>6755.0</v>
       </c>
       <c r="E224" s="29">
-        <v>9483.0</v>
+        <v>7391.0</v>
       </c>
       <c r="F224" s="29">
-        <v>2454.0</v>
+        <v>2286.0</v>
       </c>
       <c r="G224" s="29">
-        <v>2549.0</v>
+        <v>2538.0</v>
       </c>
       <c r="H224" s="31">
-        <v>0.395</v>
+        <v>0.424</v>
       </c>
       <c r="I224" s="26" t="s">
         <v>13</v>
@@ -8798,7 +8830,7 @@
       </c>
       <c r="K224" s="12">
         <f t="shared" si="1"/>
-        <v>0.4082480433</v>
+        <v>0.4034868499</v>
       </c>
       <c r="L224" s="27"/>
     </row>
@@ -8810,22 +8842,22 @@
         <v>2025.0</v>
       </c>
       <c r="C225" s="28">
-        <v>11843.0</v>
+        <v>11849.0</v>
       </c>
       <c r="D225" s="29">
-        <v>2529.0</v>
+        <v>3372.0</v>
       </c>
       <c r="E225" s="29">
-        <v>6552.0</v>
+        <v>5122.0</v>
       </c>
       <c r="F225" s="29">
-        <v>1007.0</v>
+        <v>945.0</v>
       </c>
       <c r="G225" s="29">
         <v>1729.0</v>
       </c>
       <c r="H225" s="31">
-        <v>0.584</v>
+        <v>0.586</v>
       </c>
       <c r="I225" s="32">
         <v>7292.0</v>
@@ -8835,7 +8867,7 @@
       </c>
       <c r="K225" s="12">
         <f t="shared" si="1"/>
-        <v>0.3239888542</v>
+        <v>0.3238247953</v>
       </c>
       <c r="L225" s="27"/>
     </row>
@@ -8847,22 +8879,22 @@
         <v>2025.0</v>
       </c>
       <c r="C226" s="28">
-        <v>7022.0</v>
+        <v>6083.0</v>
       </c>
       <c r="D226" s="30">
-        <v>685.0</v>
+        <v>2653.0</v>
       </c>
       <c r="E226" s="29">
-        <v>2894.0</v>
+        <v>2072.0</v>
       </c>
       <c r="F226" s="29">
-        <v>1926.0</v>
+        <v>1518.0</v>
       </c>
       <c r="G226" s="30">
-        <v>421.0</v>
+        <v>679.0</v>
       </c>
       <c r="H226" s="31">
-        <v>0.495</v>
+        <v>0.51</v>
       </c>
       <c r="I226" s="26">
         <v>101.0</v>
@@ -8872,7 +8904,7 @@
       </c>
       <c r="K226" s="12">
         <f t="shared" si="1"/>
-        <v>0.273853603</v>
+        <v>0.3161269111</v>
       </c>
       <c r="L226" s="27"/>
     </row>
@@ -8884,22 +8916,22 @@
         <v>2025.0</v>
       </c>
       <c r="C227" s="28">
-        <v>8569.0</v>
+        <v>8571.0</v>
       </c>
       <c r="D227" s="29">
-        <v>2519.0</v>
+        <v>4853.0</v>
       </c>
       <c r="E227" s="29">
-        <v>1683.0</v>
+        <v>1308.0</v>
       </c>
       <c r="F227" s="29">
-        <v>1697.0</v>
+        <v>1305.0</v>
       </c>
       <c r="G227" s="29">
-        <v>1125.0</v>
+        <v>1350.0</v>
       </c>
       <c r="H227" s="31">
-        <v>0.41</v>
+        <v>0.411</v>
       </c>
       <c r="I227" s="26">
         <v>960.0</v>
@@ -8909,7 +8941,7 @@
       </c>
       <c r="K227" s="12">
         <f t="shared" si="1"/>
-        <v>0.5270159879</v>
+        <v>0.5268930113</v>
       </c>
       <c r="L227" s="27"/>
     </row>
@@ -8921,22 +8953,22 @@
         <v>2025.0</v>
       </c>
       <c r="C228" s="28">
-        <v>4619.0</v>
+        <v>4636.0</v>
       </c>
       <c r="D228" s="29">
-        <v>1532.0</v>
+        <v>2114.0</v>
       </c>
       <c r="E228" s="29">
-        <v>1960.0</v>
+        <v>1648.0</v>
       </c>
       <c r="F228" s="30">
-        <v>496.0</v>
+        <v>413.0</v>
       </c>
       <c r="G228" s="30">
         <v>651.0</v>
       </c>
       <c r="H228" s="31">
-        <v>0.506</v>
+        <v>0.514</v>
       </c>
       <c r="I228" s="32">
         <v>2000.0</v>
@@ -8946,7 +8978,7 @@
       </c>
       <c r="K228" s="12">
         <f t="shared" si="1"/>
-        <v>0.4576748214</v>
+        <v>0.4559965487</v>
       </c>
       <c r="L228" s="27"/>
     </row>
@@ -8958,22 +8990,22 @@
         <v>2025.0</v>
       </c>
       <c r="C229" s="28">
-        <v>8323.0</v>
+        <v>8338.0</v>
       </c>
       <c r="D229" s="29">
-        <v>2062.0</v>
+        <v>4276.0</v>
       </c>
       <c r="E229" s="29">
-        <v>2491.0</v>
+        <v>115.0</v>
       </c>
       <c r="F229" s="29">
-        <v>1309.0</v>
+        <v>1196.0</v>
       </c>
       <c r="G229" s="30">
         <v>758.0</v>
       </c>
       <c r="H229" s="31">
-        <v>0.556</v>
+        <v>0.554</v>
       </c>
       <c r="I229" s="32">
         <v>2941.0</v>
@@ -8983,7 +9015,7 @@
       </c>
       <c r="K229" s="12">
         <f t="shared" si="1"/>
-        <v>0.3639312748</v>
+        <v>0.3632765651</v>
       </c>
       <c r="L229" s="27"/>
     </row>
@@ -8995,22 +9027,22 @@
         <v>2025.0</v>
       </c>
       <c r="C230" s="28">
-        <v>3703.0</v>
+        <v>3718.0</v>
       </c>
       <c r="D230" s="30">
-        <v>489.0</v>
+        <v>1294.0</v>
       </c>
       <c r="E230" s="29">
         <v>1124.0</v>
       </c>
       <c r="F230" s="30">
-        <v>133.0</v>
+        <v>126.0</v>
       </c>
       <c r="G230" s="30">
         <v>265.0</v>
       </c>
       <c r="H230" s="31">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="I230" s="26">
         <v>485.0</v>
@@ -9020,7 +9052,7 @@
       </c>
       <c r="K230" s="12">
         <f t="shared" si="1"/>
-        <v>0.6130164731</v>
+        <v>0.6105433029</v>
       </c>
       <c r="L230" s="27"/>
     </row>
@@ -9032,22 +9064,22 @@
         <v>2025.0</v>
       </c>
       <c r="C231" s="28">
-        <v>2133.0</v>
+        <v>2137.0</v>
       </c>
       <c r="D231" s="30">
-        <v>881.0</v>
+        <v>1196.0</v>
       </c>
       <c r="E231" s="30">
-        <v>815.0</v>
+        <v>565.0</v>
       </c>
       <c r="F231" s="30">
-        <v>565.0</v>
+        <v>377.0</v>
       </c>
       <c r="G231" s="30">
-        <v>426.0</v>
+        <v>446.0</v>
       </c>
       <c r="H231" s="31">
-        <v>0.462</v>
+        <v>0.459</v>
       </c>
       <c r="I231" s="26" t="s">
         <v>13</v>
@@ -9057,7 +9089,7 @@
       </c>
       <c r="K231" s="12">
         <f t="shared" si="1"/>
-        <v>0.7299578059</v>
+        <v>0.7285914834</v>
       </c>
       <c r="L231" s="27"/>
     </row>
@@ -9069,22 +9101,22 @@
         <v>2025.0</v>
       </c>
       <c r="C232" s="28">
-        <v>9558.0</v>
+        <v>9605.0</v>
       </c>
       <c r="D232" s="29">
-        <v>2374.0</v>
+        <v>2470.0</v>
       </c>
       <c r="E232" s="29">
-        <v>4777.0</v>
+        <v>4709.0</v>
       </c>
       <c r="F232" s="29">
-        <v>2234.0</v>
+        <v>1582.0</v>
       </c>
       <c r="G232" s="29">
-        <v>1254.0</v>
+        <v>1232.0</v>
       </c>
       <c r="H232" s="31">
-        <v>0.429</v>
+        <v>0.436</v>
       </c>
       <c r="I232" s="32">
         <v>1290.0</v>
@@ -9094,7 +9126,7 @@
       </c>
       <c r="K232" s="12">
         <f t="shared" si="1"/>
-        <v>0.3889935133</v>
+        <v>0.3870900573</v>
       </c>
       <c r="L232" s="27"/>
     </row>
@@ -9106,22 +9138,22 @@
         <v>2025.0</v>
       </c>
       <c r="C233" s="28">
-        <v>5434.0</v>
+        <v>5591.0</v>
       </c>
       <c r="D233" s="29">
-        <v>1144.0</v>
+        <v>1460.0</v>
       </c>
       <c r="E233" s="29">
-        <v>2471.0</v>
+        <v>1926.0</v>
       </c>
       <c r="F233" s="29">
-        <v>1048.0</v>
+        <v>774.0</v>
       </c>
       <c r="G233" s="30">
-        <v>597.0</v>
+        <v>586.0</v>
       </c>
       <c r="H233" s="31">
-        <v>0.546</v>
+        <v>0.543</v>
       </c>
       <c r="I233" s="26">
         <v>64.0</v>
@@ -9131,7 +9163,7 @@
       </c>
       <c r="K233" s="12">
         <f t="shared" si="1"/>
-        <v>0.5863084284</v>
+        <v>0.5698443928</v>
       </c>
       <c r="L233" s="27"/>
     </row>
@@ -9143,19 +9175,19 @@
         <v>2025.0</v>
       </c>
       <c r="C234" s="28">
-        <v>11727.0</v>
+        <v>12774.0</v>
       </c>
       <c r="D234" s="29">
-        <v>1624.0</v>
+        <v>2755.0</v>
       </c>
       <c r="E234" s="29">
-        <v>5956.0</v>
+        <v>5233.0</v>
       </c>
       <c r="F234" s="30">
-        <v>417.0</v>
+        <v>369.0</v>
       </c>
       <c r="G234" s="29">
-        <v>1058.0</v>
+        <v>1061.0</v>
       </c>
       <c r="H234" s="31">
         <v>0.569</v>
@@ -9168,7 +9200,7 @@
       </c>
       <c r="K234" s="12">
         <f t="shared" si="1"/>
-        <v>0.4303743498</v>
+        <v>0.3950994207</v>
       </c>
       <c r="L234" s="27"/>
     </row>
@@ -9180,22 +9212,22 @@
         <v>2025.0</v>
       </c>
       <c r="C235" s="28">
-        <v>3787.0</v>
+        <v>3832.0</v>
       </c>
       <c r="D235" s="29">
-        <v>1294.0</v>
+        <v>1478.0</v>
       </c>
       <c r="E235" s="29">
-        <v>1479.0</v>
+        <v>1462.0</v>
       </c>
       <c r="F235" s="30">
-        <v>562.0</v>
+        <v>477.0</v>
       </c>
       <c r="G235" s="30">
         <v>583.0</v>
       </c>
       <c r="H235" s="31">
-        <v>0.479</v>
+        <v>0.483</v>
       </c>
       <c r="I235" s="26" t="s">
         <v>32</v>
@@ -9205,7 +9237,7 @@
       </c>
       <c r="K235" s="12">
         <f t="shared" si="1"/>
-        <v>0.4486400845</v>
+        <v>0.4433716075</v>
       </c>
       <c r="L235" s="27"/>
     </row>
@@ -9217,22 +9249,22 @@
         <v>2025.0</v>
       </c>
       <c r="C236" s="28">
-        <v>1965.0</v>
+        <v>2028.0</v>
       </c>
       <c r="D236" s="30">
-        <v>584.0</v>
+        <v>1332.0</v>
       </c>
       <c r="E236" s="30">
-        <v>837.0</v>
+        <v>120.0</v>
       </c>
       <c r="F236" s="30">
-        <v>216.0</v>
+        <v>196.0</v>
       </c>
       <c r="G236" s="30">
-        <v>212.0</v>
+        <v>207.0</v>
       </c>
       <c r="H236" s="31">
-        <v>0.588</v>
+        <v>0.578</v>
       </c>
       <c r="I236" s="26">
         <v>225.0</v>
@@ -9242,7 +9274,7 @@
       </c>
       <c r="K236" s="12">
         <f t="shared" si="1"/>
-        <v>0.5363867684</v>
+        <v>0.5197238659</v>
       </c>
       <c r="L236" s="27"/>
     </row>
@@ -9254,22 +9286,22 @@
         <v>2025.0</v>
       </c>
       <c r="C237" s="28">
-        <v>11056.0</v>
+        <v>11559.0</v>
       </c>
       <c r="D237" s="29">
-        <v>3966.0</v>
+        <v>5954.0</v>
       </c>
       <c r="E237" s="29">
-        <v>3316.0</v>
+        <v>2731.0</v>
       </c>
       <c r="F237" s="29">
-        <v>1113.0</v>
+        <v>1131.0</v>
       </c>
       <c r="G237" s="29">
         <v>1063.0</v>
       </c>
       <c r="H237" s="31">
-        <v>0.212</v>
+        <v>0.252</v>
       </c>
       <c r="I237" s="26">
         <v>196.0</v>
@@ -9279,7 +9311,7 @@
       </c>
       <c r="K237" s="12">
         <f t="shared" si="1"/>
-        <v>0.5264109986</v>
+        <v>0.5035037633</v>
       </c>
       <c r="L237" s="27"/>
     </row>
@@ -9291,22 +9323,22 @@
         <v>2025.0</v>
       </c>
       <c r="C238" s="28">
-        <v>1102.0</v>
+        <v>1157.0</v>
       </c>
       <c r="D238" s="30">
-        <v>506.0</v>
+        <v>621.0</v>
       </c>
       <c r="E238" s="30">
-        <v>357.0</v>
+        <v>263.0</v>
       </c>
       <c r="F238" s="30">
-        <v>186.0</v>
+        <v>173.0</v>
       </c>
       <c r="G238" s="30">
-        <v>264.0</v>
+        <v>255.0</v>
       </c>
       <c r="H238" s="31">
-        <v>0.414</v>
+        <v>0.412</v>
       </c>
       <c r="I238" s="26">
         <v>77.0</v>
@@ -9316,7 +9348,7 @@
       </c>
       <c r="K238" s="12">
         <f t="shared" si="1"/>
-        <v>0.6569872958</v>
+        <v>0.6257562662</v>
       </c>
       <c r="L238" s="27"/>
     </row>
@@ -9328,22 +9360,22 @@
         <v>2025.0</v>
       </c>
       <c r="C239" s="28">
-        <v>3599.0</v>
+        <v>3604.0</v>
       </c>
       <c r="D239" s="29">
-        <v>1253.0</v>
+        <v>1685.0</v>
       </c>
       <c r="E239" s="29">
-        <v>1587.0</v>
+        <v>1066.0</v>
       </c>
       <c r="F239" s="30">
-        <v>521.0</v>
+        <v>261.0</v>
       </c>
       <c r="G239" s="30">
         <v>476.0</v>
       </c>
       <c r="H239" s="31">
-        <v>0.537</v>
+        <v>0.542</v>
       </c>
       <c r="I239" s="26">
         <v>384.0</v>
@@ -9353,7 +9385,7 @@
       </c>
       <c r="K239" s="12">
         <f t="shared" si="1"/>
-        <v>0.6890803001</v>
+        <v>0.6881243063</v>
       </c>
       <c r="L239" s="27"/>
     </row>
@@ -9368,19 +9400,19 @@
         <v>1062.0</v>
       </c>
       <c r="D240" s="30">
-        <v>348.0</v>
+        <v>496.0</v>
       </c>
       <c r="E240" s="30">
-        <v>376.0</v>
+        <v>223.0</v>
       </c>
       <c r="F240" s="30">
-        <v>30.0</v>
+        <v>26.0</v>
       </c>
       <c r="G240" s="30">
         <v>186.0</v>
       </c>
       <c r="H240" s="31">
-        <v>0.532</v>
+        <v>0.533</v>
       </c>
       <c r="I240" s="26">
         <v>91.0</v>
@@ -9402,22 +9434,22 @@
         <v>2025.0</v>
       </c>
       <c r="C241" s="28">
-        <v>2846.0</v>
+        <v>2866.0</v>
       </c>
       <c r="D241" s="29">
-        <v>1063.0</v>
+        <v>1467.0</v>
       </c>
       <c r="E241" s="29">
-        <v>1387.0</v>
+        <v>1134.0</v>
       </c>
       <c r="F241" s="30">
-        <v>381.0</v>
+        <v>313.0</v>
       </c>
       <c r="G241" s="30">
         <v>327.0</v>
       </c>
       <c r="H241" s="31">
-        <v>0.498</v>
+        <v>0.501</v>
       </c>
       <c r="I241" s="26">
         <v>569.0</v>
@@ -9427,7 +9459,7 @@
       </c>
       <c r="K241" s="12">
         <f t="shared" si="1"/>
-        <v>0.722417428</v>
+        <v>0.717376134</v>
       </c>
       <c r="L241" s="27"/>
     </row>
@@ -9439,22 +9471,22 @@
         <v>2025.0</v>
       </c>
       <c r="C242" s="28">
-        <v>2282.0</v>
+        <v>2365.0</v>
       </c>
       <c r="D242" s="30">
-        <v>713.0</v>
+        <v>955.0</v>
       </c>
       <c r="E242" s="30">
-        <v>940.0</v>
+        <v>820.0</v>
       </c>
       <c r="F242" s="30">
-        <v>418.0</v>
+        <v>336.0</v>
       </c>
       <c r="G242" s="30">
-        <v>175.0</v>
+        <v>171.0</v>
       </c>
       <c r="H242" s="31">
-        <v>0.6</v>
+        <v>0.577</v>
       </c>
       <c r="I242" s="26">
         <v>147.0</v>
@@ -9464,7 +9496,7 @@
       </c>
       <c r="K242" s="12">
         <f t="shared" si="1"/>
-        <v>0.4640666082</v>
+        <v>0.4477801268</v>
       </c>
       <c r="L242" s="27"/>
     </row>
@@ -9476,22 +9508,22 @@
         <v>2025.0</v>
       </c>
       <c r="C243" s="28">
-        <v>4048.0</v>
+        <v>4142.0</v>
       </c>
       <c r="D243" s="29">
-        <v>1008.0</v>
+        <v>1733.0</v>
       </c>
       <c r="E243" s="29">
-        <v>1729.0</v>
+        <v>1664.0</v>
       </c>
       <c r="F243" s="30">
-        <v>428.0</v>
+        <v>327.0</v>
       </c>
       <c r="G243" s="30">
-        <v>577.0</v>
+        <v>601.0</v>
       </c>
       <c r="H243" s="31">
-        <v>0.58</v>
+        <v>0.589</v>
       </c>
       <c r="I243" s="26">
         <v>895.0</v>
@@ -9501,7 +9533,7 @@
       </c>
       <c r="K243" s="12">
         <f t="shared" si="1"/>
-        <v>0.2986660079</v>
+        <v>0.2918879768</v>
       </c>
       <c r="L243" s="27"/>
     </row>
@@ -9513,22 +9545,22 @@
         <v>2025.0</v>
       </c>
       <c r="C244" s="28">
-        <v>14455.0</v>
+        <v>14488.0</v>
       </c>
       <c r="D244" s="29">
-        <v>2219.0</v>
+        <v>5919.0</v>
       </c>
       <c r="E244" s="29">
-        <v>4936.0</v>
+        <v>4454.0</v>
       </c>
       <c r="F244" s="29">
-        <v>1512.0</v>
+        <v>1354.0</v>
       </c>
       <c r="G244" s="29">
         <v>1392.0</v>
       </c>
       <c r="H244" s="31">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="I244" s="26" t="s">
         <v>13</v>
@@ -9538,7 +9570,7 @@
       </c>
       <c r="K244" s="12">
         <f t="shared" si="1"/>
-        <v>0.6873746109</v>
+        <v>0.6858089453</v>
       </c>
       <c r="L244" s="27"/>
     </row>
@@ -9550,22 +9582,22 @@
         <v>2025.0</v>
       </c>
       <c r="C245" s="28">
-        <v>15268.0</v>
+        <v>15278.0</v>
       </c>
       <c r="D245" s="29">
-        <v>2451.0</v>
+        <v>7589.0</v>
       </c>
       <c r="E245" s="29">
-        <v>4622.0</v>
+        <v>3522.0</v>
       </c>
       <c r="F245" s="29">
-        <v>3803.0</v>
+        <v>3651.0</v>
       </c>
       <c r="G245" s="29">
         <v>1439.0</v>
       </c>
       <c r="H245" s="31">
-        <v>0.418</v>
+        <v>0.421</v>
       </c>
       <c r="I245" s="26">
         <v>55.0</v>
@@ -9575,7 +9607,7 @@
       </c>
       <c r="K245" s="12">
         <f t="shared" si="1"/>
-        <v>0.4569033272</v>
+        <v>0.4566042676</v>
       </c>
       <c r="L245" s="27"/>
     </row>
@@ -9587,22 +9619,22 @@
         <v>2025.0</v>
       </c>
       <c r="C246" s="28">
-        <v>6171.0</v>
+        <v>6198.0</v>
       </c>
       <c r="D246" s="29">
-        <v>2075.0</v>
+        <v>3036.0</v>
       </c>
       <c r="E246" s="29">
-        <v>2892.0</v>
+        <v>1961.0</v>
       </c>
       <c r="F246" s="29">
-        <v>1245.0</v>
+        <v>1223.0</v>
       </c>
       <c r="G246" s="29">
-        <v>1103.0</v>
+        <v>1199.0</v>
       </c>
       <c r="H246" s="31">
-        <v>0.477</v>
+        <v>0.479</v>
       </c>
       <c r="I246" s="26">
         <v>447.0</v>
@@ -9612,7 +9644,7 @@
       </c>
       <c r="K246" s="12">
         <f t="shared" si="1"/>
-        <v>0.6190244693</v>
+        <v>0.6163278477</v>
       </c>
       <c r="L246" s="27"/>
     </row>
@@ -9624,16 +9656,16 @@
         <v>2025.0</v>
       </c>
       <c r="C247" s="28">
-        <v>4526.0</v>
+        <v>4619.0</v>
       </c>
       <c r="D247" s="30">
-        <v>829.0</v>
+        <v>1870.0</v>
       </c>
       <c r="E247" s="29">
-        <v>1888.0</v>
+        <v>1666.0</v>
       </c>
       <c r="F247" s="30">
-        <v>346.0</v>
+        <v>130.0</v>
       </c>
       <c r="G247" s="30">
         <v>362.0</v>
@@ -9649,7 +9681,7 @@
       </c>
       <c r="K247" s="12">
         <f t="shared" si="1"/>
-        <v>0.6330092797</v>
+        <v>0.6202641264</v>
       </c>
       <c r="L247" s="27"/>
     </row>
@@ -9661,22 +9693,22 @@
         <v>2025.0</v>
       </c>
       <c r="C248" s="28">
-        <v>10865.0</v>
+        <v>11258.0</v>
       </c>
       <c r="D248" s="29">
-        <v>3611.0</v>
+        <v>4844.0</v>
       </c>
       <c r="E248" s="29">
-        <v>4091.0</v>
+        <v>2841.0</v>
       </c>
       <c r="F248" s="29">
-        <v>1031.0</v>
+        <v>1194.0</v>
       </c>
       <c r="G248" s="29">
-        <v>1709.0</v>
+        <v>1692.0</v>
       </c>
       <c r="H248" s="31">
-        <v>0.452</v>
+        <v>0.465</v>
       </c>
       <c r="I248" s="26">
         <v>34.0</v>
@@ -9686,7 +9718,7 @@
       </c>
       <c r="K248" s="12">
         <f t="shared" si="1"/>
-        <v>0.8269673263</v>
+        <v>0.7980991295</v>
       </c>
       <c r="L248" s="27"/>
     </row>
@@ -9698,19 +9730,25 @@
         <v>2025.0</v>
       </c>
       <c r="C249" s="28">
-        <v>2432.0</v>
-      </c>
-      <c r="D249" s="33"/>
-      <c r="E249" s="33"/>
+        <v>2716.0</v>
+      </c>
+      <c r="D249" s="35"/>
+      <c r="E249" s="33">
+        <v>281.0</v>
+      </c>
       <c r="F249" s="30">
-        <v>19.0</v>
-      </c>
-      <c r="G249" s="33"/>
-      <c r="H249" s="33"/>
+        <v>15.0</v>
+      </c>
+      <c r="G249" s="33">
+        <v>45.0</v>
+      </c>
+      <c r="H249" s="36">
+        <v>0.442</v>
+      </c>
       <c r="I249" s="32">
         <v>2285.0</v>
       </c>
-      <c r="J249" s="33"/>
+      <c r="J249" s="35"/>
       <c r="K249" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -9725,22 +9763,22 @@
         <v>2025.0</v>
       </c>
       <c r="C250" s="28">
-        <v>1574.0</v>
+        <v>1595.0</v>
       </c>
       <c r="D250" s="30">
-        <v>122.0</v>
+        <v>407.0</v>
       </c>
       <c r="E250" s="30">
-        <v>633.0</v>
+        <v>459.0</v>
       </c>
       <c r="F250" s="30">
-        <v>64.0</v>
+        <v>43.0</v>
       </c>
       <c r="G250" s="30">
         <v>107.0</v>
       </c>
       <c r="H250" s="31">
-        <v>0.492</v>
+        <v>0.493</v>
       </c>
       <c r="I250" s="26" t="s">
         <v>13</v>
@@ -9750,7 +9788,7 @@
       </c>
       <c r="K250" s="12">
         <f t="shared" si="1"/>
-        <v>0.4358322745</v>
+        <v>0.4300940439</v>
       </c>
       <c r="L250" s="27"/>
     </row>
@@ -9762,19 +9800,19 @@
         <v>2025.0</v>
       </c>
       <c r="C251" s="28">
-        <v>3322.0</v>
+        <v>3330.0</v>
       </c>
       <c r="D251" s="30">
-        <v>915.0</v>
+        <v>1759.0</v>
       </c>
       <c r="E251" s="30">
-        <v>998.0</v>
+        <v>907.0</v>
       </c>
       <c r="F251" s="30">
         <v>567.0</v>
       </c>
       <c r="G251" s="30">
-        <v>522.0</v>
+        <v>521.0</v>
       </c>
       <c r="H251" s="31">
         <v>0.482</v>
@@ -9787,7 +9825,7 @@
       </c>
       <c r="K251" s="12">
         <f t="shared" si="1"/>
-        <v>0.6475015051</v>
+        <v>0.6459459459</v>
       </c>
       <c r="L251" s="27"/>
     </row>
@@ -9799,22 +9837,22 @@
         <v>2025.0</v>
       </c>
       <c r="C252" s="28">
-        <v>1698.0</v>
+        <v>1708.0</v>
       </c>
       <c r="D252" s="30">
-        <v>672.0</v>
+        <v>838.0</v>
       </c>
       <c r="E252" s="30">
-        <v>597.0</v>
+        <v>541.0</v>
       </c>
       <c r="F252" s="30">
-        <v>545.0</v>
+        <v>541.0</v>
       </c>
       <c r="G252" s="30">
         <v>265.0</v>
       </c>
       <c r="H252" s="31">
-        <v>0.399</v>
+        <v>0.398</v>
       </c>
       <c r="I252" s="26" t="s">
         <v>13</v>
@@ -9824,7 +9862,7 @@
       </c>
       <c r="K252" s="12">
         <f t="shared" si="1"/>
-        <v>0.4740871614</v>
+        <v>0.4713114754</v>
       </c>
       <c r="L252" s="27"/>
     </row>
@@ -9836,22 +9874,22 @@
         <v>2025.0</v>
       </c>
       <c r="C253" s="28">
-        <v>8990.0</v>
+        <v>9021.0</v>
       </c>
       <c r="D253" s="30">
-        <v>563.0</v>
+        <v>1134.0</v>
       </c>
       <c r="E253" s="30">
-        <v>937.0</v>
+        <v>437.0</v>
       </c>
       <c r="F253" s="29">
-        <v>1116.0</v>
+        <v>726.0</v>
       </c>
       <c r="G253" s="29">
         <v>1147.0</v>
       </c>
       <c r="H253" s="31">
-        <v>0.413</v>
+        <v>0.412</v>
       </c>
       <c r="I253" s="26" t="s">
         <v>13</v>
@@ -9861,7 +9899,7 @@
       </c>
       <c r="K253" s="12">
         <f t="shared" si="1"/>
-        <v>0.5383759733</v>
+        <v>0.536525884</v>
       </c>
       <c r="L253" s="27"/>
     </row>
@@ -9873,22 +9911,22 @@
         <v>2025.0</v>
       </c>
       <c r="C254" s="28">
-        <v>17520.0</v>
+        <v>17645.0</v>
       </c>
       <c r="D254" s="29">
-        <v>3112.0</v>
+        <v>7810.0</v>
       </c>
       <c r="E254" s="29">
-        <v>6998.0</v>
+        <v>5432.0</v>
       </c>
       <c r="F254" s="29">
-        <v>5146.0</v>
+        <v>3706.0</v>
       </c>
       <c r="G254" s="29">
-        <v>2581.0</v>
+        <v>3429.0</v>
       </c>
       <c r="H254" s="31">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="I254" s="32">
         <v>15156.0</v>
@@ -9898,7 +9936,7 @@
       </c>
       <c r="K254" s="12">
         <f t="shared" si="1"/>
-        <v>0.3944634703</v>
+        <v>0.3916690281</v>
       </c>
       <c r="L254" s="27"/>
     </row>
@@ -9910,22 +9948,20 @@
         <v>2025.0</v>
       </c>
       <c r="C255" s="28">
-        <v>1593.0</v>
+        <v>1619.0</v>
       </c>
       <c r="D255" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="E255" s="30">
-        <v>585.0</v>
-      </c>
+      <c r="E255" s="30"/>
       <c r="F255" s="30">
-        <v>216.0</v>
+        <v>200.0</v>
       </c>
       <c r="G255" s="30">
-        <v>276.0</v>
+        <v>274.0</v>
       </c>
       <c r="H255" s="31">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="I255" s="32">
         <v>1266.0</v>
@@ -9935,7 +9971,7 @@
       </c>
       <c r="K255" s="12">
         <f t="shared" si="1"/>
-        <v>0.5875706215</v>
+        <v>0.578134651</v>
       </c>
       <c r="L255" s="27"/>
     </row>
@@ -9947,22 +9983,22 @@
         <v>2025.0</v>
       </c>
       <c r="C256" s="28">
-        <v>5576.0</v>
+        <v>5625.0</v>
       </c>
       <c r="D256" s="29">
-        <v>1089.0</v>
+        <v>2797.0</v>
       </c>
       <c r="E256" s="29">
-        <v>1064.0</v>
+        <v>687.0</v>
       </c>
       <c r="F256" s="29">
-        <v>1208.0</v>
+        <v>1001.0</v>
       </c>
       <c r="G256" s="30">
-        <v>620.0</v>
+        <v>606.0</v>
       </c>
       <c r="H256" s="31">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="I256" s="26" t="s">
         <v>13</v>
@@ -9972,7 +10008,7 @@
       </c>
       <c r="K256" s="12">
         <f t="shared" si="1"/>
-        <v>0.8081061693</v>
+        <v>0.8010666667</v>
       </c>
       <c r="L256" s="27"/>
     </row>
@@ -9984,22 +10020,22 @@
         <v>2025.0</v>
       </c>
       <c r="C257" s="34">
-        <v>828.0</v>
+        <v>839.0</v>
       </c>
       <c r="D257" s="30">
-        <v>257.0</v>
+        <v>89.0</v>
       </c>
       <c r="E257" s="30">
-        <v>362.0</v>
+        <v>368.0</v>
       </c>
       <c r="F257" s="30">
-        <v>173.0</v>
+        <v>172.0</v>
       </c>
       <c r="G257" s="30">
         <v>184.0</v>
       </c>
       <c r="H257" s="31">
-        <v>0.411</v>
+        <v>0.413</v>
       </c>
       <c r="I257" s="26" t="s">
         <v>13</v>
@@ -10009,7 +10045,7 @@
       </c>
       <c r="K257" s="12">
         <f t="shared" si="1"/>
-        <v>0.9601449275</v>
+        <v>0.947556615</v>
       </c>
       <c r="L257" s="27"/>
     </row>
@@ -10020,22 +10056,22 @@
       <c r="B258" s="3">
         <v>2025.0</v>
       </c>
-      <c r="C258" s="28">
+      <c r="C258" s="37">
         <v>5480.0</v>
       </c>
-      <c r="D258" s="29">
+      <c r="D258" s="38">
         <v>1649.0</v>
       </c>
-      <c r="E258" s="29">
+      <c r="E258" s="38">
         <v>2600.0</v>
       </c>
-      <c r="F258" s="30" t="s">
+      <c r="F258" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="G258" s="30">
+      <c r="G258" s="39">
         <v>497.0</v>
       </c>
-      <c r="H258" s="31">
+      <c r="H258" s="40">
         <v>0.594</v>
       </c>
       <c r="I258" s="26">
@@ -10058,22 +10094,22 @@
         <v>2025.0</v>
       </c>
       <c r="C259" s="28">
-        <v>5687.0</v>
+        <v>5746.0</v>
       </c>
       <c r="D259" s="29">
-        <v>1749.0</v>
+        <v>2575.0</v>
       </c>
       <c r="E259" s="29">
-        <v>2408.0</v>
+        <v>2280.0</v>
       </c>
       <c r="F259" s="30">
-        <v>655.0</v>
+        <v>457.0</v>
       </c>
       <c r="G259" s="30">
-        <v>563.0</v>
+        <v>578.0</v>
       </c>
       <c r="H259" s="31">
-        <v>0.505</v>
+        <v>0.512</v>
       </c>
       <c r="I259" s="26" t="s">
         <v>13</v>
@@ -10083,7 +10119,7 @@
       </c>
       <c r="K259" s="12">
         <f t="shared" si="1"/>
-        <v>0.5039563918</v>
+        <v>0.4987817612</v>
       </c>
       <c r="L259" s="27"/>
     </row>
@@ -10095,22 +10131,22 @@
         <v>2025.0</v>
       </c>
       <c r="C260" s="28">
-        <v>6616.0</v>
+        <v>6907.0</v>
       </c>
       <c r="D260" s="30">
-        <v>51.0</v>
+        <v>1773.0</v>
       </c>
       <c r="E260" s="29">
-        <v>3038.0</v>
+        <v>3111.0</v>
       </c>
       <c r="F260" s="29">
-        <v>1303.0</v>
+        <v>1038.0</v>
       </c>
       <c r="G260" s="29">
-        <v>1037.0</v>
+        <v>1044.0</v>
       </c>
       <c r="H260" s="31">
-        <v>0.516</v>
+        <v>0.511</v>
       </c>
       <c r="I260" s="26" t="s">
         <v>32</v>
@@ -10120,7 +10156,7 @@
       </c>
       <c r="K260" s="12">
         <f t="shared" si="1"/>
-        <v>0.4738512696</v>
+        <v>0.4538873606</v>
       </c>
       <c r="L260" s="27"/>
     </row>
@@ -10132,22 +10168,22 @@
         <v>2025.0</v>
       </c>
       <c r="C261" s="34">
-        <v>688.0</v>
+        <v>737.0</v>
       </c>
       <c r="D261" s="30">
-        <v>162.0</v>
+        <v>172.0</v>
       </c>
       <c r="E261" s="30">
-        <v>159.0</v>
-      </c>
-      <c r="F261" s="33"/>
+        <v>133.0</v>
+      </c>
+      <c r="F261" s="35"/>
       <c r="G261" s="30">
-        <v>60.0</v>
+        <v>71.0</v>
       </c>
       <c r="H261" s="31">
-        <v>0.704</v>
-      </c>
-      <c r="I261" s="35" t="s">
+        <v>0.771</v>
+      </c>
+      <c r="I261" s="41" t="s">
         <v>13</v>
       </c>
       <c r="J261" s="30">
@@ -10155,2964 +10191,2964 @@
       </c>
       <c r="K261" s="12">
         <f t="shared" si="1"/>
-        <v>0.7296511628</v>
-      </c>
-      <c r="L261" s="36"/>
+        <v>0.6811397558</v>
+      </c>
+      <c r="L261" s="42"/>
     </row>
     <row r="262">
-      <c r="A262" s="37"/>
+      <c r="A262" s="43"/>
       <c r="I262" s="20"/>
     </row>
     <row r="263">
-      <c r="A263" s="37"/>
+      <c r="A263" s="43"/>
       <c r="I263" s="20"/>
     </row>
     <row r="264">
-      <c r="A264" s="37"/>
+      <c r="A264" s="43"/>
       <c r="I264" s="20"/>
     </row>
     <row r="265">
-      <c r="A265" s="37"/>
+      <c r="A265" s="43"/>
       <c r="I265" s="20"/>
     </row>
     <row r="266">
-      <c r="A266" s="37"/>
+      <c r="A266" s="43"/>
       <c r="I266" s="20"/>
     </row>
     <row r="267">
-      <c r="A267" s="37"/>
+      <c r="A267" s="43"/>
       <c r="I267" s="20"/>
     </row>
     <row r="268">
-      <c r="A268" s="37"/>
+      <c r="A268" s="43"/>
       <c r="I268" s="20"/>
     </row>
     <row r="269">
-      <c r="A269" s="37"/>
+      <c r="A269" s="43"/>
       <c r="I269" s="20"/>
     </row>
     <row r="270">
-      <c r="A270" s="37"/>
+      <c r="A270" s="43"/>
       <c r="I270" s="20"/>
     </row>
     <row r="271">
-      <c r="A271" s="37"/>
+      <c r="A271" s="43"/>
       <c r="I271" s="20"/>
     </row>
     <row r="272">
-      <c r="A272" s="37"/>
+      <c r="A272" s="43"/>
       <c r="I272" s="20"/>
     </row>
     <row r="273">
-      <c r="A273" s="37"/>
+      <c r="A273" s="43"/>
       <c r="I273" s="20"/>
     </row>
     <row r="274">
-      <c r="A274" s="37"/>
+      <c r="A274" s="43"/>
       <c r="I274" s="20"/>
     </row>
     <row r="275">
-      <c r="A275" s="37"/>
+      <c r="A275" s="43"/>
       <c r="I275" s="20"/>
     </row>
     <row r="276">
-      <c r="A276" s="37"/>
+      <c r="A276" s="43"/>
       <c r="I276" s="20"/>
     </row>
     <row r="277">
-      <c r="A277" s="37"/>
+      <c r="A277" s="43"/>
       <c r="I277" s="20"/>
     </row>
     <row r="278">
-      <c r="A278" s="37"/>
+      <c r="A278" s="43"/>
       <c r="I278" s="20"/>
     </row>
     <row r="279">
-      <c r="A279" s="37"/>
+      <c r="A279" s="43"/>
       <c r="I279" s="20"/>
     </row>
     <row r="280">
-      <c r="A280" s="37"/>
+      <c r="A280" s="43"/>
       <c r="I280" s="20"/>
     </row>
     <row r="281">
-      <c r="A281" s="37"/>
+      <c r="A281" s="43"/>
       <c r="I281" s="20"/>
     </row>
     <row r="282">
-      <c r="A282" s="37"/>
+      <c r="A282" s="43"/>
       <c r="I282" s="20"/>
     </row>
     <row r="283">
-      <c r="A283" s="37"/>
+      <c r="A283" s="43"/>
       <c r="I283" s="20"/>
     </row>
     <row r="284">
-      <c r="A284" s="37"/>
+      <c r="A284" s="43"/>
       <c r="I284" s="20"/>
     </row>
     <row r="285">
-      <c r="A285" s="37"/>
+      <c r="A285" s="43"/>
       <c r="I285" s="20"/>
     </row>
     <row r="286">
-      <c r="A286" s="37"/>
+      <c r="A286" s="43"/>
       <c r="I286" s="20"/>
     </row>
     <row r="287">
-      <c r="A287" s="37"/>
+      <c r="A287" s="43"/>
       <c r="I287" s="20"/>
     </row>
     <row r="288">
-      <c r="A288" s="37"/>
+      <c r="A288" s="43"/>
       <c r="I288" s="20"/>
     </row>
     <row r="289">
-      <c r="A289" s="37"/>
+      <c r="A289" s="43"/>
       <c r="I289" s="20"/>
     </row>
     <row r="290">
-      <c r="A290" s="37"/>
+      <c r="A290" s="43"/>
       <c r="I290" s="20"/>
     </row>
     <row r="291">
-      <c r="A291" s="37"/>
+      <c r="A291" s="43"/>
       <c r="I291" s="20"/>
     </row>
     <row r="292">
-      <c r="A292" s="37"/>
+      <c r="A292" s="43"/>
       <c r="I292" s="20"/>
     </row>
     <row r="293">
-      <c r="A293" s="37"/>
+      <c r="A293" s="43"/>
       <c r="I293" s="20"/>
     </row>
     <row r="294">
-      <c r="A294" s="37"/>
+      <c r="A294" s="43"/>
       <c r="I294" s="20"/>
     </row>
     <row r="295">
-      <c r="A295" s="37"/>
+      <c r="A295" s="43"/>
       <c r="I295" s="20"/>
     </row>
     <row r="296">
-      <c r="A296" s="37"/>
+      <c r="A296" s="43"/>
       <c r="I296" s="20"/>
     </row>
     <row r="297">
-      <c r="A297" s="37"/>
+      <c r="A297" s="43"/>
       <c r="I297" s="20"/>
     </row>
     <row r="298">
-      <c r="A298" s="37"/>
+      <c r="A298" s="43"/>
       <c r="I298" s="20"/>
     </row>
     <row r="299">
-      <c r="A299" s="37"/>
+      <c r="A299" s="43"/>
       <c r="I299" s="20"/>
     </row>
     <row r="300">
-      <c r="A300" s="37"/>
+      <c r="A300" s="43"/>
       <c r="I300" s="20"/>
     </row>
     <row r="301">
-      <c r="A301" s="37"/>
+      <c r="A301" s="43"/>
       <c r="I301" s="20"/>
     </row>
     <row r="302">
-      <c r="A302" s="37"/>
+      <c r="A302" s="43"/>
       <c r="I302" s="20"/>
     </row>
     <row r="303">
-      <c r="A303" s="37"/>
+      <c r="A303" s="43"/>
       <c r="I303" s="20"/>
     </row>
     <row r="304">
-      <c r="A304" s="37"/>
+      <c r="A304" s="43"/>
       <c r="I304" s="20"/>
     </row>
     <row r="305">
-      <c r="A305" s="37"/>
+      <c r="A305" s="43"/>
       <c r="I305" s="20"/>
     </row>
     <row r="306">
-      <c r="A306" s="37"/>
+      <c r="A306" s="43"/>
       <c r="I306" s="20"/>
     </row>
     <row r="307">
-      <c r="A307" s="37"/>
+      <c r="A307" s="43"/>
       <c r="I307" s="20"/>
     </row>
     <row r="308">
-      <c r="A308" s="37"/>
+      <c r="A308" s="43"/>
       <c r="I308" s="20"/>
     </row>
     <row r="309">
-      <c r="A309" s="37"/>
+      <c r="A309" s="43"/>
       <c r="I309" s="20"/>
     </row>
     <row r="310">
-      <c r="A310" s="37"/>
+      <c r="A310" s="43"/>
       <c r="I310" s="20"/>
     </row>
     <row r="311">
-      <c r="A311" s="37"/>
+      <c r="A311" s="43"/>
       <c r="I311" s="20"/>
     </row>
     <row r="312">
-      <c r="A312" s="37"/>
+      <c r="A312" s="43"/>
       <c r="I312" s="20"/>
     </row>
     <row r="313">
-      <c r="A313" s="37"/>
+      <c r="A313" s="43"/>
       <c r="I313" s="20"/>
     </row>
     <row r="314">
-      <c r="A314" s="37"/>
+      <c r="A314" s="43"/>
       <c r="I314" s="20"/>
     </row>
     <row r="315">
-      <c r="A315" s="37"/>
+      <c r="A315" s="43"/>
       <c r="I315" s="20"/>
     </row>
     <row r="316">
-      <c r="A316" s="37"/>
+      <c r="A316" s="43"/>
       <c r="I316" s="20"/>
     </row>
     <row r="317">
-      <c r="A317" s="37"/>
+      <c r="A317" s="43"/>
       <c r="I317" s="20"/>
     </row>
     <row r="318">
-      <c r="A318" s="37"/>
+      <c r="A318" s="43"/>
       <c r="I318" s="20"/>
     </row>
     <row r="319">
-      <c r="A319" s="37"/>
+      <c r="A319" s="43"/>
       <c r="I319" s="20"/>
     </row>
     <row r="320">
-      <c r="A320" s="37"/>
+      <c r="A320" s="43"/>
       <c r="I320" s="20"/>
     </row>
     <row r="321">
-      <c r="A321" s="37"/>
+      <c r="A321" s="43"/>
       <c r="I321" s="20"/>
     </row>
     <row r="322">
-      <c r="A322" s="37"/>
+      <c r="A322" s="43"/>
       <c r="I322" s="20"/>
     </row>
     <row r="323">
-      <c r="A323" s="37"/>
+      <c r="A323" s="43"/>
       <c r="I323" s="20"/>
     </row>
     <row r="324">
-      <c r="A324" s="37"/>
+      <c r="A324" s="43"/>
       <c r="I324" s="20"/>
     </row>
     <row r="325">
-      <c r="A325" s="37"/>
+      <c r="A325" s="43"/>
       <c r="I325" s="20"/>
     </row>
     <row r="326">
-      <c r="A326" s="37"/>
+      <c r="A326" s="43"/>
       <c r="I326" s="20"/>
     </row>
     <row r="327">
-      <c r="A327" s="37"/>
+      <c r="A327" s="43"/>
       <c r="I327" s="20"/>
     </row>
     <row r="328">
-      <c r="A328" s="37"/>
+      <c r="A328" s="43"/>
       <c r="I328" s="20"/>
     </row>
     <row r="329">
-      <c r="A329" s="37"/>
+      <c r="A329" s="43"/>
       <c r="I329" s="20"/>
     </row>
     <row r="330">
-      <c r="A330" s="37"/>
+      <c r="A330" s="43"/>
       <c r="I330" s="20"/>
     </row>
     <row r="331">
-      <c r="A331" s="37"/>
+      <c r="A331" s="43"/>
       <c r="I331" s="20"/>
     </row>
     <row r="332">
-      <c r="A332" s="37"/>
+      <c r="A332" s="43"/>
       <c r="I332" s="20"/>
     </row>
     <row r="333">
-      <c r="A333" s="37"/>
+      <c r="A333" s="43"/>
       <c r="I333" s="20"/>
     </row>
     <row r="334">
-      <c r="A334" s="37"/>
+      <c r="A334" s="43"/>
       <c r="I334" s="20"/>
     </row>
     <row r="335">
-      <c r="A335" s="37"/>
+      <c r="A335" s="43"/>
       <c r="I335" s="20"/>
     </row>
     <row r="336">
-      <c r="A336" s="37"/>
+      <c r="A336" s="43"/>
       <c r="I336" s="20"/>
     </row>
     <row r="337">
-      <c r="A337" s="37"/>
+      <c r="A337" s="43"/>
       <c r="I337" s="20"/>
     </row>
     <row r="338">
-      <c r="A338" s="37"/>
+      <c r="A338" s="43"/>
       <c r="I338" s="20"/>
     </row>
     <row r="339">
-      <c r="A339" s="37"/>
+      <c r="A339" s="43"/>
       <c r="I339" s="20"/>
     </row>
     <row r="340">
-      <c r="A340" s="37"/>
+      <c r="A340" s="43"/>
       <c r="I340" s="20"/>
     </row>
     <row r="341">
-      <c r="A341" s="37"/>
+      <c r="A341" s="43"/>
       <c r="I341" s="20"/>
     </row>
     <row r="342">
-      <c r="A342" s="37"/>
+      <c r="A342" s="43"/>
       <c r="I342" s="20"/>
     </row>
     <row r="343">
-      <c r="A343" s="37"/>
+      <c r="A343" s="43"/>
       <c r="I343" s="20"/>
     </row>
     <row r="344">
-      <c r="A344" s="37"/>
+      <c r="A344" s="43"/>
       <c r="I344" s="20"/>
     </row>
     <row r="345">
-      <c r="A345" s="37"/>
+      <c r="A345" s="43"/>
       <c r="I345" s="20"/>
     </row>
     <row r="346">
-      <c r="A346" s="37"/>
+      <c r="A346" s="43"/>
       <c r="I346" s="20"/>
     </row>
     <row r="347">
-      <c r="A347" s="37"/>
+      <c r="A347" s="43"/>
       <c r="I347" s="20"/>
     </row>
     <row r="348">
-      <c r="A348" s="37"/>
+      <c r="A348" s="43"/>
       <c r="I348" s="20"/>
     </row>
     <row r="349">
-      <c r="A349" s="37"/>
+      <c r="A349" s="43"/>
       <c r="I349" s="20"/>
     </row>
     <row r="350">
-      <c r="A350" s="37"/>
+      <c r="A350" s="43"/>
       <c r="I350" s="20"/>
     </row>
     <row r="351">
-      <c r="A351" s="37"/>
+      <c r="A351" s="43"/>
       <c r="I351" s="20"/>
     </row>
     <row r="352">
-      <c r="A352" s="37"/>
+      <c r="A352" s="43"/>
       <c r="I352" s="20"/>
     </row>
     <row r="353">
-      <c r="A353" s="37"/>
+      <c r="A353" s="43"/>
       <c r="I353" s="20"/>
     </row>
     <row r="354">
-      <c r="A354" s="37"/>
+      <c r="A354" s="43"/>
       <c r="I354" s="20"/>
     </row>
     <row r="355">
-      <c r="A355" s="37"/>
+      <c r="A355" s="43"/>
       <c r="I355" s="20"/>
     </row>
     <row r="356">
-      <c r="A356" s="37"/>
+      <c r="A356" s="43"/>
       <c r="I356" s="20"/>
     </row>
     <row r="357">
-      <c r="A357" s="37"/>
+      <c r="A357" s="43"/>
       <c r="I357" s="20"/>
     </row>
     <row r="358">
-      <c r="A358" s="37"/>
+      <c r="A358" s="43"/>
       <c r="I358" s="20"/>
     </row>
     <row r="359">
-      <c r="A359" s="37"/>
+      <c r="A359" s="43"/>
       <c r="I359" s="20"/>
     </row>
     <row r="360">
-      <c r="A360" s="37"/>
+      <c r="A360" s="43"/>
       <c r="I360" s="20"/>
     </row>
     <row r="361">
-      <c r="A361" s="37"/>
+      <c r="A361" s="43"/>
       <c r="I361" s="20"/>
     </row>
     <row r="362">
-      <c r="A362" s="37"/>
+      <c r="A362" s="43"/>
       <c r="I362" s="20"/>
     </row>
     <row r="363">
-      <c r="A363" s="37"/>
+      <c r="A363" s="43"/>
       <c r="I363" s="20"/>
     </row>
     <row r="364">
-      <c r="A364" s="37"/>
+      <c r="A364" s="43"/>
       <c r="I364" s="20"/>
     </row>
     <row r="365">
-      <c r="A365" s="37"/>
+      <c r="A365" s="43"/>
       <c r="I365" s="20"/>
     </row>
     <row r="366">
-      <c r="A366" s="37"/>
+      <c r="A366" s="43"/>
       <c r="I366" s="20"/>
     </row>
     <row r="367">
-      <c r="A367" s="37"/>
+      <c r="A367" s="43"/>
       <c r="I367" s="20"/>
     </row>
     <row r="368">
-      <c r="A368" s="37"/>
+      <c r="A368" s="43"/>
       <c r="I368" s="20"/>
     </row>
     <row r="369">
-      <c r="A369" s="37"/>
+      <c r="A369" s="43"/>
       <c r="I369" s="20"/>
     </row>
     <row r="370">
-      <c r="A370" s="37"/>
+      <c r="A370" s="43"/>
       <c r="I370" s="20"/>
     </row>
     <row r="371">
-      <c r="A371" s="37"/>
+      <c r="A371" s="43"/>
       <c r="I371" s="20"/>
     </row>
     <row r="372">
-      <c r="A372" s="37"/>
+      <c r="A372" s="43"/>
       <c r="I372" s="20"/>
     </row>
     <row r="373">
-      <c r="A373" s="37"/>
+      <c r="A373" s="43"/>
       <c r="I373" s="20"/>
     </row>
     <row r="374">
-      <c r="A374" s="37"/>
+      <c r="A374" s="43"/>
       <c r="I374" s="20"/>
     </row>
     <row r="375">
-      <c r="A375" s="37"/>
+      <c r="A375" s="43"/>
       <c r="I375" s="20"/>
     </row>
     <row r="376">
-      <c r="A376" s="37"/>
+      <c r="A376" s="43"/>
       <c r="I376" s="20"/>
     </row>
     <row r="377">
-      <c r="A377" s="37"/>
+      <c r="A377" s="43"/>
       <c r="I377" s="20"/>
     </row>
     <row r="378">
-      <c r="A378" s="37"/>
+      <c r="A378" s="43"/>
       <c r="I378" s="20"/>
     </row>
     <row r="379">
-      <c r="A379" s="37"/>
+      <c r="A379" s="43"/>
       <c r="I379" s="20"/>
     </row>
     <row r="380">
-      <c r="A380" s="37"/>
+      <c r="A380" s="43"/>
       <c r="I380" s="20"/>
     </row>
     <row r="381">
-      <c r="A381" s="37"/>
+      <c r="A381" s="43"/>
       <c r="I381" s="20"/>
     </row>
     <row r="382">
-      <c r="A382" s="37"/>
+      <c r="A382" s="43"/>
       <c r="I382" s="20"/>
     </row>
     <row r="383">
-      <c r="A383" s="37"/>
+      <c r="A383" s="43"/>
       <c r="I383" s="20"/>
     </row>
     <row r="384">
-      <c r="A384" s="37"/>
+      <c r="A384" s="43"/>
       <c r="I384" s="20"/>
     </row>
     <row r="385">
-      <c r="A385" s="37"/>
+      <c r="A385" s="43"/>
       <c r="I385" s="20"/>
     </row>
     <row r="386">
-      <c r="A386" s="37"/>
+      <c r="A386" s="43"/>
       <c r="I386" s="20"/>
     </row>
     <row r="387">
-      <c r="A387" s="37"/>
+      <c r="A387" s="43"/>
       <c r="I387" s="20"/>
     </row>
     <row r="388">
-      <c r="A388" s="37"/>
+      <c r="A388" s="43"/>
       <c r="I388" s="20"/>
     </row>
     <row r="389">
-      <c r="A389" s="37"/>
+      <c r="A389" s="43"/>
       <c r="I389" s="20"/>
     </row>
     <row r="390">
-      <c r="A390" s="37"/>
+      <c r="A390" s="43"/>
       <c r="I390" s="20"/>
     </row>
     <row r="391">
-      <c r="A391" s="37"/>
+      <c r="A391" s="43"/>
       <c r="I391" s="20"/>
     </row>
     <row r="392">
-      <c r="A392" s="37"/>
+      <c r="A392" s="43"/>
       <c r="I392" s="20"/>
     </row>
     <row r="393">
-      <c r="A393" s="37"/>
+      <c r="A393" s="43"/>
       <c r="I393" s="20"/>
     </row>
     <row r="394">
-      <c r="A394" s="37"/>
+      <c r="A394" s="43"/>
       <c r="I394" s="20"/>
     </row>
     <row r="395">
-      <c r="A395" s="37"/>
+      <c r="A395" s="43"/>
       <c r="I395" s="20"/>
     </row>
     <row r="396">
-      <c r="A396" s="37"/>
+      <c r="A396" s="43"/>
       <c r="I396" s="20"/>
     </row>
     <row r="397">
-      <c r="A397" s="37"/>
+      <c r="A397" s="43"/>
       <c r="I397" s="20"/>
     </row>
     <row r="398">
-      <c r="A398" s="37"/>
+      <c r="A398" s="43"/>
       <c r="I398" s="20"/>
     </row>
     <row r="399">
-      <c r="A399" s="37"/>
+      <c r="A399" s="43"/>
       <c r="I399" s="20"/>
     </row>
     <row r="400">
-      <c r="A400" s="37"/>
+      <c r="A400" s="43"/>
       <c r="I400" s="20"/>
     </row>
     <row r="401">
-      <c r="A401" s="37"/>
+      <c r="A401" s="43"/>
       <c r="I401" s="20"/>
     </row>
     <row r="402">
-      <c r="A402" s="37"/>
+      <c r="A402" s="43"/>
       <c r="I402" s="20"/>
     </row>
     <row r="403">
-      <c r="A403" s="37"/>
+      <c r="A403" s="43"/>
       <c r="I403" s="20"/>
     </row>
     <row r="404">
-      <c r="A404" s="37"/>
+      <c r="A404" s="43"/>
       <c r="I404" s="20"/>
     </row>
     <row r="405">
-      <c r="A405" s="37"/>
+      <c r="A405" s="43"/>
       <c r="I405" s="20"/>
     </row>
     <row r="406">
-      <c r="A406" s="37"/>
+      <c r="A406" s="43"/>
       <c r="I406" s="20"/>
     </row>
     <row r="407">
-      <c r="A407" s="37"/>
+      <c r="A407" s="43"/>
       <c r="I407" s="20"/>
     </row>
     <row r="408">
-      <c r="A408" s="37"/>
+      <c r="A408" s="43"/>
       <c r="I408" s="20"/>
     </row>
     <row r="409">
-      <c r="A409" s="37"/>
+      <c r="A409" s="43"/>
       <c r="I409" s="20"/>
     </row>
     <row r="410">
-      <c r="A410" s="37"/>
+      <c r="A410" s="43"/>
       <c r="I410" s="20"/>
     </row>
     <row r="411">
-      <c r="A411" s="37"/>
+      <c r="A411" s="43"/>
       <c r="I411" s="20"/>
     </row>
     <row r="412">
-      <c r="A412" s="37"/>
+      <c r="A412" s="43"/>
       <c r="I412" s="20"/>
     </row>
     <row r="413">
-      <c r="A413" s="37"/>
+      <c r="A413" s="43"/>
       <c r="I413" s="20"/>
     </row>
     <row r="414">
-      <c r="A414" s="37"/>
+      <c r="A414" s="43"/>
       <c r="I414" s="20"/>
     </row>
     <row r="415">
-      <c r="A415" s="37"/>
+      <c r="A415" s="43"/>
       <c r="I415" s="20"/>
     </row>
     <row r="416">
-      <c r="A416" s="37"/>
+      <c r="A416" s="43"/>
       <c r="I416" s="20"/>
     </row>
     <row r="417">
-      <c r="A417" s="37"/>
+      <c r="A417" s="43"/>
       <c r="I417" s="20"/>
     </row>
     <row r="418">
-      <c r="A418" s="37"/>
+      <c r="A418" s="43"/>
       <c r="I418" s="20"/>
     </row>
     <row r="419">
-      <c r="A419" s="37"/>
+      <c r="A419" s="43"/>
       <c r="I419" s="20"/>
     </row>
     <row r="420">
-      <c r="A420" s="37"/>
+      <c r="A420" s="43"/>
       <c r="I420" s="20"/>
     </row>
     <row r="421">
-      <c r="A421" s="37"/>
+      <c r="A421" s="43"/>
       <c r="I421" s="20"/>
     </row>
     <row r="422">
-      <c r="A422" s="37"/>
+      <c r="A422" s="43"/>
       <c r="I422" s="20"/>
     </row>
     <row r="423">
-      <c r="A423" s="37"/>
+      <c r="A423" s="43"/>
       <c r="I423" s="20"/>
     </row>
     <row r="424">
-      <c r="A424" s="37"/>
+      <c r="A424" s="43"/>
       <c r="I424" s="20"/>
     </row>
     <row r="425">
-      <c r="A425" s="37"/>
+      <c r="A425" s="43"/>
       <c r="I425" s="20"/>
     </row>
     <row r="426">
-      <c r="A426" s="37"/>
+      <c r="A426" s="43"/>
       <c r="I426" s="20"/>
     </row>
     <row r="427">
-      <c r="A427" s="37"/>
+      <c r="A427" s="43"/>
       <c r="I427" s="20"/>
     </row>
     <row r="428">
-      <c r="A428" s="37"/>
+      <c r="A428" s="43"/>
       <c r="I428" s="20"/>
     </row>
     <row r="429">
-      <c r="A429" s="37"/>
+      <c r="A429" s="43"/>
       <c r="I429" s="20"/>
     </row>
     <row r="430">
-      <c r="A430" s="37"/>
+      <c r="A430" s="43"/>
       <c r="I430" s="20"/>
     </row>
     <row r="431">
-      <c r="A431" s="37"/>
+      <c r="A431" s="43"/>
       <c r="I431" s="20"/>
     </row>
     <row r="432">
-      <c r="A432" s="37"/>
+      <c r="A432" s="43"/>
       <c r="I432" s="20"/>
     </row>
     <row r="433">
-      <c r="A433" s="37"/>
+      <c r="A433" s="43"/>
       <c r="I433" s="20"/>
     </row>
     <row r="434">
-      <c r="A434" s="37"/>
+      <c r="A434" s="43"/>
       <c r="I434" s="20"/>
     </row>
     <row r="435">
-      <c r="A435" s="37"/>
+      <c r="A435" s="43"/>
       <c r="I435" s="20"/>
     </row>
     <row r="436">
-      <c r="A436" s="37"/>
+      <c r="A436" s="43"/>
       <c r="I436" s="20"/>
     </row>
     <row r="437">
-      <c r="A437" s="37"/>
+      <c r="A437" s="43"/>
       <c r="I437" s="20"/>
     </row>
     <row r="438">
-      <c r="A438" s="37"/>
+      <c r="A438" s="43"/>
       <c r="I438" s="20"/>
     </row>
     <row r="439">
-      <c r="A439" s="37"/>
+      <c r="A439" s="43"/>
       <c r="I439" s="20"/>
     </row>
     <row r="440">
-      <c r="A440" s="37"/>
+      <c r="A440" s="43"/>
       <c r="I440" s="20"/>
     </row>
     <row r="441">
-      <c r="A441" s="37"/>
+      <c r="A441" s="43"/>
       <c r="I441" s="20"/>
     </row>
     <row r="442">
-      <c r="A442" s="37"/>
+      <c r="A442" s="43"/>
       <c r="I442" s="20"/>
     </row>
     <row r="443">
-      <c r="A443" s="37"/>
+      <c r="A443" s="43"/>
       <c r="I443" s="20"/>
     </row>
     <row r="444">
-      <c r="A444" s="37"/>
+      <c r="A444" s="43"/>
       <c r="I444" s="20"/>
     </row>
     <row r="445">
-      <c r="A445" s="37"/>
+      <c r="A445" s="43"/>
       <c r="I445" s="20"/>
     </row>
     <row r="446">
-      <c r="A446" s="37"/>
+      <c r="A446" s="43"/>
       <c r="I446" s="20"/>
     </row>
     <row r="447">
-      <c r="A447" s="37"/>
+      <c r="A447" s="43"/>
       <c r="I447" s="20"/>
     </row>
     <row r="448">
-      <c r="A448" s="37"/>
+      <c r="A448" s="43"/>
       <c r="I448" s="20"/>
     </row>
     <row r="449">
-      <c r="A449" s="37"/>
+      <c r="A449" s="43"/>
       <c r="I449" s="20"/>
     </row>
     <row r="450">
-      <c r="A450" s="37"/>
+      <c r="A450" s="43"/>
       <c r="I450" s="20"/>
     </row>
     <row r="451">
-      <c r="A451" s="37"/>
+      <c r="A451" s="43"/>
       <c r="I451" s="20"/>
     </row>
     <row r="452">
-      <c r="A452" s="37"/>
+      <c r="A452" s="43"/>
       <c r="I452" s="20"/>
     </row>
     <row r="453">
-      <c r="A453" s="37"/>
+      <c r="A453" s="43"/>
       <c r="I453" s="20"/>
     </row>
     <row r="454">
-      <c r="A454" s="37"/>
+      <c r="A454" s="43"/>
       <c r="I454" s="20"/>
     </row>
     <row r="455">
-      <c r="A455" s="37"/>
+      <c r="A455" s="43"/>
       <c r="I455" s="20"/>
     </row>
     <row r="456">
-      <c r="A456" s="37"/>
+      <c r="A456" s="43"/>
       <c r="I456" s="20"/>
     </row>
     <row r="457">
-      <c r="A457" s="37"/>
+      <c r="A457" s="43"/>
       <c r="I457" s="20"/>
     </row>
     <row r="458">
-      <c r="A458" s="37"/>
+      <c r="A458" s="43"/>
       <c r="I458" s="20"/>
     </row>
     <row r="459">
-      <c r="A459" s="37"/>
+      <c r="A459" s="43"/>
       <c r="I459" s="20"/>
     </row>
     <row r="460">
-      <c r="A460" s="37"/>
+      <c r="A460" s="43"/>
       <c r="I460" s="20"/>
     </row>
     <row r="461">
-      <c r="A461" s="37"/>
+      <c r="A461" s="43"/>
       <c r="I461" s="20"/>
     </row>
     <row r="462">
-      <c r="A462" s="37"/>
+      <c r="A462" s="43"/>
       <c r="I462" s="20"/>
     </row>
     <row r="463">
-      <c r="A463" s="37"/>
+      <c r="A463" s="43"/>
       <c r="I463" s="20"/>
     </row>
     <row r="464">
-      <c r="A464" s="37"/>
+      <c r="A464" s="43"/>
       <c r="I464" s="20"/>
     </row>
     <row r="465">
-      <c r="A465" s="37"/>
+      <c r="A465" s="43"/>
       <c r="I465" s="20"/>
     </row>
     <row r="466">
-      <c r="A466" s="37"/>
+      <c r="A466" s="43"/>
       <c r="I466" s="20"/>
     </row>
     <row r="467">
-      <c r="A467" s="37"/>
+      <c r="A467" s="43"/>
       <c r="I467" s="20"/>
     </row>
     <row r="468">
-      <c r="A468" s="37"/>
+      <c r="A468" s="43"/>
       <c r="I468" s="20"/>
     </row>
     <row r="469">
-      <c r="A469" s="37"/>
+      <c r="A469" s="43"/>
       <c r="I469" s="20"/>
     </row>
     <row r="470">
-      <c r="A470" s="37"/>
+      <c r="A470" s="43"/>
       <c r="I470" s="20"/>
     </row>
     <row r="471">
-      <c r="A471" s="37"/>
+      <c r="A471" s="43"/>
       <c r="I471" s="20"/>
     </row>
     <row r="472">
-      <c r="A472" s="37"/>
+      <c r="A472" s="43"/>
       <c r="I472" s="20"/>
     </row>
     <row r="473">
-      <c r="A473" s="37"/>
+      <c r="A473" s="43"/>
       <c r="I473" s="20"/>
     </row>
     <row r="474">
-      <c r="A474" s="37"/>
+      <c r="A474" s="43"/>
       <c r="I474" s="20"/>
     </row>
     <row r="475">
-      <c r="A475" s="37"/>
+      <c r="A475" s="43"/>
       <c r="I475" s="20"/>
     </row>
     <row r="476">
-      <c r="A476" s="37"/>
+      <c r="A476" s="43"/>
       <c r="I476" s="20"/>
     </row>
     <row r="477">
-      <c r="A477" s="37"/>
+      <c r="A477" s="43"/>
       <c r="I477" s="20"/>
     </row>
     <row r="478">
-      <c r="A478" s="37"/>
+      <c r="A478" s="43"/>
       <c r="I478" s="20"/>
     </row>
     <row r="479">
-      <c r="A479" s="37"/>
+      <c r="A479" s="43"/>
       <c r="I479" s="20"/>
     </row>
     <row r="480">
-      <c r="A480" s="37"/>
+      <c r="A480" s="43"/>
       <c r="I480" s="20"/>
     </row>
     <row r="481">
-      <c r="A481" s="37"/>
+      <c r="A481" s="43"/>
       <c r="I481" s="20"/>
     </row>
     <row r="482">
-      <c r="A482" s="37"/>
+      <c r="A482" s="43"/>
       <c r="I482" s="20"/>
     </row>
     <row r="483">
-      <c r="A483" s="37"/>
+      <c r="A483" s="43"/>
       <c r="I483" s="20"/>
     </row>
     <row r="484">
-      <c r="A484" s="37"/>
+      <c r="A484" s="43"/>
       <c r="I484" s="20"/>
     </row>
     <row r="485">
-      <c r="A485" s="37"/>
+      <c r="A485" s="43"/>
       <c r="I485" s="20"/>
     </row>
     <row r="486">
-      <c r="A486" s="37"/>
+      <c r="A486" s="43"/>
       <c r="I486" s="20"/>
     </row>
     <row r="487">
-      <c r="A487" s="37"/>
+      <c r="A487" s="43"/>
       <c r="I487" s="20"/>
     </row>
     <row r="488">
-      <c r="A488" s="37"/>
+      <c r="A488" s="43"/>
       <c r="I488" s="20"/>
     </row>
     <row r="489">
-      <c r="A489" s="37"/>
+      <c r="A489" s="43"/>
       <c r="I489" s="20"/>
     </row>
     <row r="490">
-      <c r="A490" s="37"/>
+      <c r="A490" s="43"/>
       <c r="I490" s="20"/>
     </row>
     <row r="491">
-      <c r="A491" s="37"/>
+      <c r="A491" s="43"/>
       <c r="I491" s="20"/>
     </row>
     <row r="492">
-      <c r="A492" s="37"/>
+      <c r="A492" s="43"/>
       <c r="I492" s="20"/>
     </row>
     <row r="493">
-      <c r="A493" s="37"/>
+      <c r="A493" s="43"/>
       <c r="I493" s="20"/>
     </row>
     <row r="494">
-      <c r="A494" s="37"/>
+      <c r="A494" s="43"/>
       <c r="I494" s="20"/>
     </row>
     <row r="495">
-      <c r="A495" s="37"/>
+      <c r="A495" s="43"/>
       <c r="I495" s="20"/>
     </row>
     <row r="496">
-      <c r="A496" s="37"/>
+      <c r="A496" s="43"/>
       <c r="I496" s="20"/>
     </row>
     <row r="497">
-      <c r="A497" s="37"/>
+      <c r="A497" s="43"/>
       <c r="I497" s="20"/>
     </row>
     <row r="498">
-      <c r="A498" s="37"/>
+      <c r="A498" s="43"/>
       <c r="I498" s="20"/>
     </row>
     <row r="499">
-      <c r="A499" s="37"/>
+      <c r="A499" s="43"/>
       <c r="I499" s="20"/>
     </row>
     <row r="500">
-      <c r="A500" s="37"/>
+      <c r="A500" s="43"/>
       <c r="I500" s="20"/>
     </row>
     <row r="501">
-      <c r="A501" s="37"/>
+      <c r="A501" s="43"/>
       <c r="I501" s="20"/>
     </row>
     <row r="502">
-      <c r="A502" s="37"/>
+      <c r="A502" s="43"/>
       <c r="I502" s="20"/>
     </row>
     <row r="503">
-      <c r="A503" s="37"/>
+      <c r="A503" s="43"/>
       <c r="I503" s="20"/>
     </row>
     <row r="504">
-      <c r="A504" s="37"/>
+      <c r="A504" s="43"/>
       <c r="I504" s="20"/>
     </row>
     <row r="505">
-      <c r="A505" s="37"/>
+      <c r="A505" s="43"/>
       <c r="I505" s="20"/>
     </row>
     <row r="506">
-      <c r="A506" s="37"/>
+      <c r="A506" s="43"/>
       <c r="I506" s="20"/>
     </row>
     <row r="507">
-      <c r="A507" s="37"/>
+      <c r="A507" s="43"/>
       <c r="I507" s="20"/>
     </row>
     <row r="508">
-      <c r="A508" s="37"/>
+      <c r="A508" s="43"/>
       <c r="I508" s="20"/>
     </row>
     <row r="509">
-      <c r="A509" s="37"/>
+      <c r="A509" s="43"/>
       <c r="I509" s="20"/>
     </row>
     <row r="510">
-      <c r="A510" s="37"/>
+      <c r="A510" s="43"/>
       <c r="I510" s="20"/>
     </row>
     <row r="511">
-      <c r="A511" s="37"/>
+      <c r="A511" s="43"/>
       <c r="I511" s="20"/>
     </row>
     <row r="512">
-      <c r="A512" s="37"/>
+      <c r="A512" s="43"/>
       <c r="I512" s="20"/>
     </row>
     <row r="513">
-      <c r="A513" s="37"/>
+      <c r="A513" s="43"/>
       <c r="I513" s="20"/>
     </row>
     <row r="514">
-      <c r="A514" s="37"/>
+      <c r="A514" s="43"/>
       <c r="I514" s="20"/>
     </row>
     <row r="515">
-      <c r="A515" s="37"/>
+      <c r="A515" s="43"/>
       <c r="I515" s="20"/>
     </row>
     <row r="516">
-      <c r="A516" s="37"/>
+      <c r="A516" s="43"/>
       <c r="I516" s="20"/>
     </row>
     <row r="517">
-      <c r="A517" s="37"/>
+      <c r="A517" s="43"/>
       <c r="I517" s="20"/>
     </row>
     <row r="518">
-      <c r="A518" s="37"/>
+      <c r="A518" s="43"/>
       <c r="I518" s="20"/>
     </row>
     <row r="519">
-      <c r="A519" s="37"/>
+      <c r="A519" s="43"/>
       <c r="I519" s="20"/>
     </row>
     <row r="520">
-      <c r="A520" s="37"/>
+      <c r="A520" s="43"/>
       <c r="I520" s="20"/>
     </row>
     <row r="521">
-      <c r="A521" s="37"/>
+      <c r="A521" s="43"/>
       <c r="I521" s="20"/>
     </row>
     <row r="522">
-      <c r="A522" s="37"/>
+      <c r="A522" s="43"/>
       <c r="I522" s="20"/>
     </row>
     <row r="523">
-      <c r="A523" s="37"/>
+      <c r="A523" s="43"/>
       <c r="I523" s="20"/>
     </row>
     <row r="524">
-      <c r="A524" s="37"/>
+      <c r="A524" s="43"/>
       <c r="I524" s="20"/>
     </row>
     <row r="525">
-      <c r="A525" s="37"/>
+      <c r="A525" s="43"/>
       <c r="I525" s="20"/>
     </row>
     <row r="526">
-      <c r="A526" s="37"/>
+      <c r="A526" s="43"/>
       <c r="I526" s="20"/>
     </row>
     <row r="527">
-      <c r="A527" s="37"/>
+      <c r="A527" s="43"/>
       <c r="I527" s="20"/>
     </row>
     <row r="528">
-      <c r="A528" s="37"/>
+      <c r="A528" s="43"/>
       <c r="I528" s="20"/>
     </row>
     <row r="529">
-      <c r="A529" s="37"/>
+      <c r="A529" s="43"/>
       <c r="I529" s="20"/>
     </row>
     <row r="530">
-      <c r="A530" s="37"/>
+      <c r="A530" s="43"/>
       <c r="I530" s="20"/>
     </row>
     <row r="531">
-      <c r="A531" s="37"/>
+      <c r="A531" s="43"/>
       <c r="I531" s="20"/>
     </row>
     <row r="532">
-      <c r="A532" s="37"/>
+      <c r="A532" s="43"/>
       <c r="I532" s="20"/>
     </row>
     <row r="533">
-      <c r="A533" s="37"/>
+      <c r="A533" s="43"/>
       <c r="I533" s="20"/>
     </row>
     <row r="534">
-      <c r="A534" s="37"/>
+      <c r="A534" s="43"/>
       <c r="I534" s="20"/>
     </row>
     <row r="535">
-      <c r="A535" s="37"/>
+      <c r="A535" s="43"/>
       <c r="I535" s="20"/>
     </row>
     <row r="536">
-      <c r="A536" s="37"/>
+      <c r="A536" s="43"/>
       <c r="I536" s="20"/>
     </row>
     <row r="537">
-      <c r="A537" s="37"/>
+      <c r="A537" s="43"/>
       <c r="I537" s="20"/>
     </row>
     <row r="538">
-      <c r="A538" s="37"/>
+      <c r="A538" s="43"/>
       <c r="I538" s="20"/>
     </row>
     <row r="539">
-      <c r="A539" s="37"/>
+      <c r="A539" s="43"/>
       <c r="I539" s="20"/>
     </row>
     <row r="540">
-      <c r="A540" s="37"/>
+      <c r="A540" s="43"/>
       <c r="I540" s="20"/>
     </row>
     <row r="541">
-      <c r="A541" s="37"/>
+      <c r="A541" s="43"/>
       <c r="I541" s="20"/>
     </row>
     <row r="542">
-      <c r="A542" s="37"/>
+      <c r="A542" s="43"/>
       <c r="I542" s="20"/>
     </row>
     <row r="543">
-      <c r="A543" s="37"/>
+      <c r="A543" s="43"/>
       <c r="I543" s="20"/>
     </row>
     <row r="544">
-      <c r="A544" s="37"/>
+      <c r="A544" s="43"/>
       <c r="I544" s="20"/>
     </row>
     <row r="545">
-      <c r="A545" s="37"/>
+      <c r="A545" s="43"/>
       <c r="I545" s="20"/>
     </row>
     <row r="546">
-      <c r="A546" s="37"/>
+      <c r="A546" s="43"/>
       <c r="I546" s="20"/>
     </row>
     <row r="547">
-      <c r="A547" s="37"/>
+      <c r="A547" s="43"/>
       <c r="I547" s="20"/>
     </row>
     <row r="548">
-      <c r="A548" s="37"/>
+      <c r="A548" s="43"/>
       <c r="I548" s="20"/>
     </row>
     <row r="549">
-      <c r="A549" s="37"/>
+      <c r="A549" s="43"/>
       <c r="I549" s="20"/>
     </row>
     <row r="550">
-      <c r="A550" s="37"/>
+      <c r="A550" s="43"/>
       <c r="I550" s="20"/>
     </row>
     <row r="551">
-      <c r="A551" s="37"/>
+      <c r="A551" s="43"/>
       <c r="I551" s="20"/>
     </row>
     <row r="552">
-      <c r="A552" s="37"/>
+      <c r="A552" s="43"/>
       <c r="I552" s="20"/>
     </row>
     <row r="553">
-      <c r="A553" s="37"/>
+      <c r="A553" s="43"/>
       <c r="I553" s="20"/>
     </row>
     <row r="554">
-      <c r="A554" s="37"/>
+      <c r="A554" s="43"/>
       <c r="I554" s="20"/>
     </row>
     <row r="555">
-      <c r="A555" s="37"/>
+      <c r="A555" s="43"/>
       <c r="I555" s="20"/>
     </row>
     <row r="556">
-      <c r="A556" s="37"/>
+      <c r="A556" s="43"/>
       <c r="I556" s="20"/>
     </row>
     <row r="557">
-      <c r="A557" s="37"/>
+      <c r="A557" s="43"/>
       <c r="I557" s="20"/>
     </row>
     <row r="558">
-      <c r="A558" s="37"/>
+      <c r="A558" s="43"/>
       <c r="I558" s="20"/>
     </row>
     <row r="559">
-      <c r="A559" s="37"/>
+      <c r="A559" s="43"/>
       <c r="I559" s="20"/>
     </row>
     <row r="560">
-      <c r="A560" s="37"/>
+      <c r="A560" s="43"/>
       <c r="I560" s="20"/>
     </row>
     <row r="561">
-      <c r="A561" s="37"/>
+      <c r="A561" s="43"/>
       <c r="I561" s="20"/>
     </row>
     <row r="562">
-      <c r="A562" s="37"/>
+      <c r="A562" s="43"/>
       <c r="I562" s="20"/>
     </row>
     <row r="563">
-      <c r="A563" s="37"/>
+      <c r="A563" s="43"/>
       <c r="I563" s="20"/>
     </row>
     <row r="564">
-      <c r="A564" s="37"/>
+      <c r="A564" s="43"/>
       <c r="I564" s="20"/>
     </row>
     <row r="565">
-      <c r="A565" s="37"/>
+      <c r="A565" s="43"/>
       <c r="I565" s="20"/>
     </row>
     <row r="566">
-      <c r="A566" s="37"/>
+      <c r="A566" s="43"/>
       <c r="I566" s="20"/>
     </row>
     <row r="567">
-      <c r="A567" s="37"/>
+      <c r="A567" s="43"/>
       <c r="I567" s="20"/>
     </row>
     <row r="568">
-      <c r="A568" s="37"/>
+      <c r="A568" s="43"/>
       <c r="I568" s="20"/>
     </row>
     <row r="569">
-      <c r="A569" s="37"/>
+      <c r="A569" s="43"/>
       <c r="I569" s="20"/>
     </row>
     <row r="570">
-      <c r="A570" s="37"/>
+      <c r="A570" s="43"/>
       <c r="I570" s="20"/>
     </row>
     <row r="571">
-      <c r="A571" s="37"/>
+      <c r="A571" s="43"/>
       <c r="I571" s="20"/>
     </row>
     <row r="572">
-      <c r="A572" s="37"/>
+      <c r="A572" s="43"/>
       <c r="I572" s="20"/>
     </row>
     <row r="573">
-      <c r="A573" s="37"/>
+      <c r="A573" s="43"/>
       <c r="I573" s="20"/>
     </row>
     <row r="574">
-      <c r="A574" s="37"/>
+      <c r="A574" s="43"/>
       <c r="I574" s="20"/>
     </row>
     <row r="575">
-      <c r="A575" s="37"/>
+      <c r="A575" s="43"/>
       <c r="I575" s="20"/>
     </row>
     <row r="576">
-      <c r="A576" s="37"/>
+      <c r="A576" s="43"/>
       <c r="I576" s="20"/>
     </row>
     <row r="577">
-      <c r="A577" s="37"/>
+      <c r="A577" s="43"/>
       <c r="I577" s="20"/>
     </row>
     <row r="578">
-      <c r="A578" s="37"/>
+      <c r="A578" s="43"/>
       <c r="I578" s="20"/>
     </row>
     <row r="579">
-      <c r="A579" s="37"/>
+      <c r="A579" s="43"/>
       <c r="I579" s="20"/>
     </row>
     <row r="580">
-      <c r="A580" s="37"/>
+      <c r="A580" s="43"/>
       <c r="I580" s="20"/>
     </row>
     <row r="581">
-      <c r="A581" s="37"/>
+      <c r="A581" s="43"/>
       <c r="I581" s="20"/>
     </row>
     <row r="582">
-      <c r="A582" s="37"/>
+      <c r="A582" s="43"/>
       <c r="I582" s="20"/>
     </row>
     <row r="583">
-      <c r="A583" s="37"/>
+      <c r="A583" s="43"/>
       <c r="I583" s="20"/>
     </row>
     <row r="584">
-      <c r="A584" s="37"/>
+      <c r="A584" s="43"/>
       <c r="I584" s="20"/>
     </row>
     <row r="585">
-      <c r="A585" s="37"/>
+      <c r="A585" s="43"/>
       <c r="I585" s="20"/>
     </row>
     <row r="586">
-      <c r="A586" s="37"/>
+      <c r="A586" s="43"/>
       <c r="I586" s="20"/>
     </row>
     <row r="587">
-      <c r="A587" s="37"/>
+      <c r="A587" s="43"/>
       <c r="I587" s="20"/>
     </row>
     <row r="588">
-      <c r="A588" s="37"/>
+      <c r="A588" s="43"/>
       <c r="I588" s="20"/>
     </row>
     <row r="589">
-      <c r="A589" s="37"/>
+      <c r="A589" s="43"/>
       <c r="I589" s="20"/>
     </row>
     <row r="590">
-      <c r="A590" s="37"/>
+      <c r="A590" s="43"/>
       <c r="I590" s="20"/>
     </row>
     <row r="591">
-      <c r="A591" s="37"/>
+      <c r="A591" s="43"/>
       <c r="I591" s="20"/>
     </row>
     <row r="592">
-      <c r="A592" s="37"/>
+      <c r="A592" s="43"/>
       <c r="I592" s="20"/>
     </row>
     <row r="593">
-      <c r="A593" s="37"/>
+      <c r="A593" s="43"/>
       <c r="I593" s="20"/>
     </row>
     <row r="594">
-      <c r="A594" s="37"/>
+      <c r="A594" s="43"/>
       <c r="I594" s="20"/>
     </row>
     <row r="595">
-      <c r="A595" s="37"/>
+      <c r="A595" s="43"/>
       <c r="I595" s="20"/>
     </row>
     <row r="596">
-      <c r="A596" s="37"/>
+      <c r="A596" s="43"/>
       <c r="I596" s="20"/>
     </row>
     <row r="597">
-      <c r="A597" s="37"/>
+      <c r="A597" s="43"/>
       <c r="I597" s="20"/>
     </row>
     <row r="598">
-      <c r="A598" s="37"/>
+      <c r="A598" s="43"/>
       <c r="I598" s="20"/>
     </row>
     <row r="599">
-      <c r="A599" s="37"/>
+      <c r="A599" s="43"/>
       <c r="I599" s="20"/>
     </row>
     <row r="600">
-      <c r="A600" s="37"/>
+      <c r="A600" s="43"/>
       <c r="I600" s="20"/>
     </row>
     <row r="601">
-      <c r="A601" s="37"/>
+      <c r="A601" s="43"/>
       <c r="I601" s="20"/>
     </row>
     <row r="602">
-      <c r="A602" s="37"/>
+      <c r="A602" s="43"/>
       <c r="I602" s="20"/>
     </row>
     <row r="603">
-      <c r="A603" s="37"/>
+      <c r="A603" s="43"/>
       <c r="I603" s="20"/>
     </row>
     <row r="604">
-      <c r="A604" s="37"/>
+      <c r="A604" s="43"/>
       <c r="I604" s="20"/>
     </row>
     <row r="605">
-      <c r="A605" s="37"/>
+      <c r="A605" s="43"/>
       <c r="I605" s="20"/>
     </row>
     <row r="606">
-      <c r="A606" s="37"/>
+      <c r="A606" s="43"/>
       <c r="I606" s="20"/>
     </row>
     <row r="607">
-      <c r="A607" s="37"/>
+      <c r="A607" s="43"/>
       <c r="I607" s="20"/>
     </row>
     <row r="608">
-      <c r="A608" s="37"/>
+      <c r="A608" s="43"/>
       <c r="I608" s="20"/>
     </row>
     <row r="609">
-      <c r="A609" s="37"/>
+      <c r="A609" s="43"/>
       <c r="I609" s="20"/>
     </row>
     <row r="610">
-      <c r="A610" s="37"/>
+      <c r="A610" s="43"/>
       <c r="I610" s="20"/>
     </row>
     <row r="611">
-      <c r="A611" s="37"/>
+      <c r="A611" s="43"/>
       <c r="I611" s="20"/>
     </row>
     <row r="612">
-      <c r="A612" s="37"/>
+      <c r="A612" s="43"/>
       <c r="I612" s="20"/>
     </row>
     <row r="613">
-      <c r="A613" s="37"/>
+      <c r="A613" s="43"/>
       <c r="I613" s="20"/>
     </row>
     <row r="614">
-      <c r="A614" s="37"/>
+      <c r="A614" s="43"/>
       <c r="I614" s="20"/>
     </row>
     <row r="615">
-      <c r="A615" s="37"/>
+      <c r="A615" s="43"/>
       <c r="I615" s="20"/>
     </row>
     <row r="616">
-      <c r="A616" s="37"/>
+      <c r="A616" s="43"/>
       <c r="I616" s="20"/>
     </row>
     <row r="617">
-      <c r="A617" s="37"/>
+      <c r="A617" s="43"/>
       <c r="I617" s="20"/>
     </row>
     <row r="618">
-      <c r="A618" s="37"/>
+      <c r="A618" s="43"/>
       <c r="I618" s="20"/>
     </row>
     <row r="619">
-      <c r="A619" s="37"/>
+      <c r="A619" s="43"/>
       <c r="I619" s="20"/>
     </row>
     <row r="620">
-      <c r="A620" s="37"/>
+      <c r="A620" s="43"/>
       <c r="I620" s="20"/>
     </row>
     <row r="621">
-      <c r="A621" s="37"/>
+      <c r="A621" s="43"/>
       <c r="I621" s="20"/>
     </row>
     <row r="622">
-      <c r="A622" s="37"/>
+      <c r="A622" s="43"/>
       <c r="I622" s="20"/>
     </row>
     <row r="623">
-      <c r="A623" s="37"/>
+      <c r="A623" s="43"/>
       <c r="I623" s="20"/>
     </row>
     <row r="624">
-      <c r="A624" s="37"/>
+      <c r="A624" s="43"/>
       <c r="I624" s="20"/>
     </row>
     <row r="625">
-      <c r="A625" s="37"/>
+      <c r="A625" s="43"/>
       <c r="I625" s="20"/>
     </row>
     <row r="626">
-      <c r="A626" s="37"/>
+      <c r="A626" s="43"/>
       <c r="I626" s="20"/>
     </row>
     <row r="627">
-      <c r="A627" s="37"/>
+      <c r="A627" s="43"/>
       <c r="I627" s="20"/>
     </row>
     <row r="628">
-      <c r="A628" s="37"/>
+      <c r="A628" s="43"/>
       <c r="I628" s="20"/>
     </row>
     <row r="629">
-      <c r="A629" s="37"/>
+      <c r="A629" s="43"/>
       <c r="I629" s="20"/>
     </row>
     <row r="630">
-      <c r="A630" s="37"/>
+      <c r="A630" s="43"/>
       <c r="I630" s="20"/>
     </row>
     <row r="631">
-      <c r="A631" s="37"/>
+      <c r="A631" s="43"/>
       <c r="I631" s="20"/>
     </row>
     <row r="632">
-      <c r="A632" s="37"/>
+      <c r="A632" s="43"/>
       <c r="I632" s="20"/>
     </row>
     <row r="633">
-      <c r="A633" s="37"/>
+      <c r="A633" s="43"/>
       <c r="I633" s="20"/>
     </row>
     <row r="634">
-      <c r="A634" s="37"/>
+      <c r="A634" s="43"/>
       <c r="I634" s="20"/>
     </row>
     <row r="635">
-      <c r="A635" s="37"/>
+      <c r="A635" s="43"/>
       <c r="I635" s="20"/>
     </row>
     <row r="636">
-      <c r="A636" s="37"/>
+      <c r="A636" s="43"/>
       <c r="I636" s="20"/>
     </row>
     <row r="637">
-      <c r="A637" s="37"/>
+      <c r="A637" s="43"/>
       <c r="I637" s="20"/>
     </row>
     <row r="638">
-      <c r="A638" s="37"/>
+      <c r="A638" s="43"/>
       <c r="I638" s="20"/>
     </row>
     <row r="639">
-      <c r="A639" s="37"/>
+      <c r="A639" s="43"/>
       <c r="I639" s="20"/>
     </row>
     <row r="640">
-      <c r="A640" s="37"/>
+      <c r="A640" s="43"/>
       <c r="I640" s="20"/>
     </row>
     <row r="641">
-      <c r="A641" s="37"/>
+      <c r="A641" s="43"/>
       <c r="I641" s="20"/>
     </row>
     <row r="642">
-      <c r="A642" s="37"/>
+      <c r="A642" s="43"/>
       <c r="I642" s="20"/>
     </row>
     <row r="643">
-      <c r="A643" s="37"/>
+      <c r="A643" s="43"/>
       <c r="I643" s="20"/>
     </row>
     <row r="644">
-      <c r="A644" s="37"/>
+      <c r="A644" s="43"/>
       <c r="I644" s="20"/>
     </row>
     <row r="645">
-      <c r="A645" s="37"/>
+      <c r="A645" s="43"/>
       <c r="I645" s="20"/>
     </row>
     <row r="646">
-      <c r="A646" s="37"/>
+      <c r="A646" s="43"/>
       <c r="I646" s="20"/>
     </row>
     <row r="647">
-      <c r="A647" s="37"/>
+      <c r="A647" s="43"/>
       <c r="I647" s="20"/>
     </row>
     <row r="648">
-      <c r="A648" s="37"/>
+      <c r="A648" s="43"/>
       <c r="I648" s="20"/>
     </row>
     <row r="649">
-      <c r="A649" s="37"/>
+      <c r="A649" s="43"/>
       <c r="I649" s="20"/>
     </row>
     <row r="650">
-      <c r="A650" s="37"/>
+      <c r="A650" s="43"/>
       <c r="I650" s="20"/>
     </row>
     <row r="651">
-      <c r="A651" s="37"/>
+      <c r="A651" s="43"/>
       <c r="I651" s="20"/>
     </row>
     <row r="652">
-      <c r="A652" s="37"/>
+      <c r="A652" s="43"/>
       <c r="I652" s="20"/>
     </row>
     <row r="653">
-      <c r="A653" s="37"/>
+      <c r="A653" s="43"/>
       <c r="I653" s="20"/>
     </row>
     <row r="654">
-      <c r="A654" s="37"/>
+      <c r="A654" s="43"/>
       <c r="I654" s="20"/>
     </row>
     <row r="655">
-      <c r="A655" s="37"/>
+      <c r="A655" s="43"/>
       <c r="I655" s="20"/>
     </row>
     <row r="656">
-      <c r="A656" s="37"/>
+      <c r="A656" s="43"/>
       <c r="I656" s="20"/>
     </row>
     <row r="657">
-      <c r="A657" s="37"/>
+      <c r="A657" s="43"/>
       <c r="I657" s="20"/>
     </row>
     <row r="658">
-      <c r="A658" s="37"/>
+      <c r="A658" s="43"/>
       <c r="I658" s="20"/>
     </row>
     <row r="659">
-      <c r="A659" s="37"/>
+      <c r="A659" s="43"/>
       <c r="I659" s="20"/>
     </row>
     <row r="660">
-      <c r="A660" s="37"/>
+      <c r="A660" s="43"/>
       <c r="I660" s="20"/>
     </row>
     <row r="661">
-      <c r="A661" s="37"/>
+      <c r="A661" s="43"/>
       <c r="I661" s="20"/>
     </row>
     <row r="662">
-      <c r="A662" s="37"/>
+      <c r="A662" s="43"/>
       <c r="I662" s="20"/>
     </row>
     <row r="663">
-      <c r="A663" s="37"/>
+      <c r="A663" s="43"/>
       <c r="I663" s="20"/>
     </row>
     <row r="664">
-      <c r="A664" s="37"/>
+      <c r="A664" s="43"/>
       <c r="I664" s="20"/>
     </row>
     <row r="665">
-      <c r="A665" s="37"/>
+      <c r="A665" s="43"/>
       <c r="I665" s="20"/>
     </row>
     <row r="666">
-      <c r="A666" s="37"/>
+      <c r="A666" s="43"/>
       <c r="I666" s="20"/>
     </row>
     <row r="667">
-      <c r="A667" s="37"/>
+      <c r="A667" s="43"/>
       <c r="I667" s="20"/>
     </row>
     <row r="668">
-      <c r="A668" s="37"/>
+      <c r="A668" s="43"/>
       <c r="I668" s="20"/>
     </row>
     <row r="669">
-      <c r="A669" s="37"/>
+      <c r="A669" s="43"/>
       <c r="I669" s="20"/>
     </row>
     <row r="670">
-      <c r="A670" s="37"/>
+      <c r="A670" s="43"/>
       <c r="I670" s="20"/>
     </row>
     <row r="671">
-      <c r="A671" s="37"/>
+      <c r="A671" s="43"/>
       <c r="I671" s="20"/>
     </row>
     <row r="672">
-      <c r="A672" s="37"/>
+      <c r="A672" s="43"/>
       <c r="I672" s="20"/>
     </row>
     <row r="673">
-      <c r="A673" s="37"/>
+      <c r="A673" s="43"/>
       <c r="I673" s="20"/>
     </row>
     <row r="674">
-      <c r="A674" s="37"/>
+      <c r="A674" s="43"/>
       <c r="I674" s="20"/>
     </row>
     <row r="675">
-      <c r="A675" s="37"/>
+      <c r="A675" s="43"/>
       <c r="I675" s="20"/>
     </row>
     <row r="676">
-      <c r="A676" s="37"/>
+      <c r="A676" s="43"/>
       <c r="I676" s="20"/>
     </row>
     <row r="677">
-      <c r="A677" s="37"/>
+      <c r="A677" s="43"/>
       <c r="I677" s="20"/>
     </row>
     <row r="678">
-      <c r="A678" s="37"/>
+      <c r="A678" s="43"/>
       <c r="I678" s="20"/>
     </row>
     <row r="679">
-      <c r="A679" s="37"/>
+      <c r="A679" s="43"/>
       <c r="I679" s="20"/>
     </row>
     <row r="680">
-      <c r="A680" s="37"/>
+      <c r="A680" s="43"/>
       <c r="I680" s="20"/>
     </row>
     <row r="681">
-      <c r="A681" s="37"/>
+      <c r="A681" s="43"/>
       <c r="I681" s="20"/>
     </row>
     <row r="682">
-      <c r="A682" s="37"/>
+      <c r="A682" s="43"/>
       <c r="I682" s="20"/>
     </row>
     <row r="683">
-      <c r="A683" s="37"/>
+      <c r="A683" s="43"/>
       <c r="I683" s="20"/>
     </row>
     <row r="684">
-      <c r="A684" s="37"/>
+      <c r="A684" s="43"/>
       <c r="I684" s="20"/>
     </row>
     <row r="685">
-      <c r="A685" s="37"/>
+      <c r="A685" s="43"/>
       <c r="I685" s="20"/>
     </row>
     <row r="686">
-      <c r="A686" s="37"/>
+      <c r="A686" s="43"/>
       <c r="I686" s="20"/>
     </row>
     <row r="687">
-      <c r="A687" s="37"/>
+      <c r="A687" s="43"/>
       <c r="I687" s="20"/>
     </row>
     <row r="688">
-      <c r="A688" s="37"/>
+      <c r="A688" s="43"/>
       <c r="I688" s="20"/>
     </row>
     <row r="689">
-      <c r="A689" s="37"/>
+      <c r="A689" s="43"/>
       <c r="I689" s="20"/>
     </row>
     <row r="690">
-      <c r="A690" s="37"/>
+      <c r="A690" s="43"/>
       <c r="I690" s="20"/>
     </row>
     <row r="691">
-      <c r="A691" s="37"/>
+      <c r="A691" s="43"/>
       <c r="I691" s="20"/>
     </row>
     <row r="692">
-      <c r="A692" s="37"/>
+      <c r="A692" s="43"/>
       <c r="I692" s="20"/>
     </row>
     <row r="693">
-      <c r="A693" s="37"/>
+      <c r="A693" s="43"/>
       <c r="I693" s="20"/>
     </row>
     <row r="694">
-      <c r="A694" s="37"/>
+      <c r="A694" s="43"/>
       <c r="I694" s="20"/>
     </row>
     <row r="695">
-      <c r="A695" s="37"/>
+      <c r="A695" s="43"/>
       <c r="I695" s="20"/>
     </row>
     <row r="696">
-      <c r="A696" s="37"/>
+      <c r="A696" s="43"/>
       <c r="I696" s="20"/>
     </row>
     <row r="697">
-      <c r="A697" s="37"/>
+      <c r="A697" s="43"/>
       <c r="I697" s="20"/>
     </row>
     <row r="698">
-      <c r="A698" s="37"/>
+      <c r="A698" s="43"/>
       <c r="I698" s="20"/>
     </row>
     <row r="699">
-      <c r="A699" s="37"/>
+      <c r="A699" s="43"/>
       <c r="I699" s="20"/>
     </row>
     <row r="700">
-      <c r="A700" s="37"/>
+      <c r="A700" s="43"/>
       <c r="I700" s="20"/>
     </row>
     <row r="701">
-      <c r="A701" s="37"/>
+      <c r="A701" s="43"/>
       <c r="I701" s="20"/>
     </row>
     <row r="702">
-      <c r="A702" s="37"/>
+      <c r="A702" s="43"/>
       <c r="I702" s="20"/>
     </row>
     <row r="703">
-      <c r="A703" s="37"/>
+      <c r="A703" s="43"/>
       <c r="I703" s="20"/>
     </row>
     <row r="704">
-      <c r="A704" s="37"/>
+      <c r="A704" s="43"/>
       <c r="I704" s="20"/>
     </row>
     <row r="705">
-      <c r="A705" s="37"/>
+      <c r="A705" s="43"/>
       <c r="I705" s="20"/>
     </row>
     <row r="706">
-      <c r="A706" s="37"/>
+      <c r="A706" s="43"/>
       <c r="I706" s="20"/>
     </row>
     <row r="707">
-      <c r="A707" s="37"/>
+      <c r="A707" s="43"/>
       <c r="I707" s="20"/>
     </row>
     <row r="708">
-      <c r="A708" s="37"/>
+      <c r="A708" s="43"/>
       <c r="I708" s="20"/>
     </row>
     <row r="709">
-      <c r="A709" s="37"/>
+      <c r="A709" s="43"/>
       <c r="I709" s="20"/>
     </row>
     <row r="710">
-      <c r="A710" s="37"/>
+      <c r="A710" s="43"/>
       <c r="I710" s="20"/>
     </row>
     <row r="711">
-      <c r="A711" s="37"/>
+      <c r="A711" s="43"/>
       <c r="I711" s="20"/>
     </row>
     <row r="712">
-      <c r="A712" s="37"/>
+      <c r="A712" s="43"/>
       <c r="I712" s="20"/>
     </row>
     <row r="713">
-      <c r="A713" s="37"/>
+      <c r="A713" s="43"/>
       <c r="I713" s="20"/>
     </row>
     <row r="714">
-      <c r="A714" s="37"/>
+      <c r="A714" s="43"/>
       <c r="I714" s="20"/>
     </row>
     <row r="715">
-      <c r="A715" s="37"/>
+      <c r="A715" s="43"/>
       <c r="I715" s="20"/>
     </row>
     <row r="716">
-      <c r="A716" s="37"/>
+      <c r="A716" s="43"/>
       <c r="I716" s="20"/>
     </row>
     <row r="717">
-      <c r="A717" s="37"/>
+      <c r="A717" s="43"/>
       <c r="I717" s="20"/>
     </row>
     <row r="718">
-      <c r="A718" s="37"/>
+      <c r="A718" s="43"/>
       <c r="I718" s="20"/>
     </row>
     <row r="719">
-      <c r="A719" s="37"/>
+      <c r="A719" s="43"/>
       <c r="I719" s="20"/>
     </row>
     <row r="720">
-      <c r="A720" s="37"/>
+      <c r="A720" s="43"/>
       <c r="I720" s="20"/>
     </row>
     <row r="721">
-      <c r="A721" s="37"/>
+      <c r="A721" s="43"/>
       <c r="I721" s="20"/>
     </row>
     <row r="722">
-      <c r="A722" s="37"/>
+      <c r="A722" s="43"/>
       <c r="I722" s="20"/>
     </row>
     <row r="723">
-      <c r="A723" s="37"/>
+      <c r="A723" s="43"/>
       <c r="I723" s="20"/>
     </row>
     <row r="724">
-      <c r="A724" s="37"/>
+      <c r="A724" s="43"/>
       <c r="I724" s="20"/>
     </row>
     <row r="725">
-      <c r="A725" s="37"/>
+      <c r="A725" s="43"/>
       <c r="I725" s="20"/>
     </row>
     <row r="726">
-      <c r="A726" s="37"/>
+      <c r="A726" s="43"/>
       <c r="I726" s="20"/>
     </row>
     <row r="727">
-      <c r="A727" s="37"/>
+      <c r="A727" s="43"/>
       <c r="I727" s="20"/>
     </row>
     <row r="728">
-      <c r="A728" s="37"/>
+      <c r="A728" s="43"/>
       <c r="I728" s="20"/>
     </row>
     <row r="729">
-      <c r="A729" s="37"/>
+      <c r="A729" s="43"/>
       <c r="I729" s="20"/>
     </row>
     <row r="730">
-      <c r="A730" s="37"/>
+      <c r="A730" s="43"/>
       <c r="I730" s="20"/>
     </row>
     <row r="731">
-      <c r="A731" s="37"/>
+      <c r="A731" s="43"/>
       <c r="I731" s="20"/>
     </row>
     <row r="732">
-      <c r="A732" s="37"/>
+      <c r="A732" s="43"/>
       <c r="I732" s="20"/>
     </row>
     <row r="733">
-      <c r="A733" s="37"/>
+      <c r="A733" s="43"/>
       <c r="I733" s="20"/>
     </row>
     <row r="734">
-      <c r="A734" s="37"/>
+      <c r="A734" s="43"/>
       <c r="I734" s="20"/>
     </row>
     <row r="735">
-      <c r="A735" s="37"/>
+      <c r="A735" s="43"/>
       <c r="I735" s="20"/>
     </row>
     <row r="736">
-      <c r="A736" s="37"/>
+      <c r="A736" s="43"/>
       <c r="I736" s="20"/>
     </row>
     <row r="737">
-      <c r="A737" s="37"/>
+      <c r="A737" s="43"/>
       <c r="I737" s="20"/>
     </row>
     <row r="738">
-      <c r="A738" s="37"/>
+      <c r="A738" s="43"/>
       <c r="I738" s="20"/>
     </row>
     <row r="739">
-      <c r="A739" s="37"/>
+      <c r="A739" s="43"/>
       <c r="I739" s="20"/>
     </row>
     <row r="740">
-      <c r="A740" s="37"/>
+      <c r="A740" s="43"/>
       <c r="I740" s="20"/>
     </row>
     <row r="741">
-      <c r="A741" s="37"/>
+      <c r="A741" s="43"/>
       <c r="I741" s="20"/>
     </row>
     <row r="742">
-      <c r="A742" s="37"/>
+      <c r="A742" s="43"/>
       <c r="I742" s="20"/>
     </row>
     <row r="743">
-      <c r="A743" s="37"/>
+      <c r="A743" s="43"/>
       <c r="I743" s="20"/>
     </row>
     <row r="744">
-      <c r="A744" s="37"/>
+      <c r="A744" s="43"/>
       <c r="I744" s="20"/>
     </row>
     <row r="745">
-      <c r="A745" s="37"/>
+      <c r="A745" s="43"/>
       <c r="I745" s="20"/>
     </row>
     <row r="746">
-      <c r="A746" s="37"/>
+      <c r="A746" s="43"/>
       <c r="I746" s="20"/>
     </row>
     <row r="747">
-      <c r="A747" s="37"/>
+      <c r="A747" s="43"/>
       <c r="I747" s="20"/>
     </row>
     <row r="748">
-      <c r="A748" s="37"/>
+      <c r="A748" s="43"/>
       <c r="I748" s="20"/>
     </row>
     <row r="749">
-      <c r="A749" s="37"/>
+      <c r="A749" s="43"/>
       <c r="I749" s="20"/>
     </row>
     <row r="750">
-      <c r="A750" s="37"/>
+      <c r="A750" s="43"/>
       <c r="I750" s="20"/>
     </row>
     <row r="751">
-      <c r="A751" s="37"/>
+      <c r="A751" s="43"/>
       <c r="I751" s="20"/>
     </row>
     <row r="752">
-      <c r="A752" s="37"/>
+      <c r="A752" s="43"/>
       <c r="I752" s="20"/>
     </row>
     <row r="753">
-      <c r="A753" s="37"/>
+      <c r="A753" s="43"/>
       <c r="I753" s="20"/>
     </row>
     <row r="754">
-      <c r="A754" s="37"/>
+      <c r="A754" s="43"/>
       <c r="I754" s="20"/>
     </row>
     <row r="755">
-      <c r="A755" s="37"/>
+      <c r="A755" s="43"/>
       <c r="I755" s="20"/>
     </row>
     <row r="756">
-      <c r="A756" s="37"/>
+      <c r="A756" s="43"/>
       <c r="I756" s="20"/>
     </row>
     <row r="757">
-      <c r="A757" s="37"/>
+      <c r="A757" s="43"/>
       <c r="I757" s="20"/>
     </row>
     <row r="758">
-      <c r="A758" s="37"/>
+      <c r="A758" s="43"/>
       <c r="I758" s="20"/>
     </row>
     <row r="759">
-      <c r="A759" s="37"/>
+      <c r="A759" s="43"/>
       <c r="I759" s="20"/>
     </row>
     <row r="760">
-      <c r="A760" s="37"/>
+      <c r="A760" s="43"/>
       <c r="I760" s="20"/>
     </row>
     <row r="761">
-      <c r="A761" s="37"/>
+      <c r="A761" s="43"/>
       <c r="I761" s="20"/>
     </row>
     <row r="762">
-      <c r="A762" s="37"/>
+      <c r="A762" s="43"/>
       <c r="I762" s="20"/>
     </row>
     <row r="763">
-      <c r="A763" s="37"/>
+      <c r="A763" s="43"/>
       <c r="I763" s="20"/>
     </row>
     <row r="764">
-      <c r="A764" s="37"/>
+      <c r="A764" s="43"/>
       <c r="I764" s="20"/>
     </row>
     <row r="765">
-      <c r="A765" s="37"/>
+      <c r="A765" s="43"/>
       <c r="I765" s="20"/>
     </row>
     <row r="766">
-      <c r="A766" s="37"/>
+      <c r="A766" s="43"/>
       <c r="I766" s="20"/>
     </row>
     <row r="767">
-      <c r="A767" s="37"/>
+      <c r="A767" s="43"/>
       <c r="I767" s="20"/>
     </row>
     <row r="768">
-      <c r="A768" s="37"/>
+      <c r="A768" s="43"/>
       <c r="I768" s="20"/>
     </row>
     <row r="769">
-      <c r="A769" s="37"/>
+      <c r="A769" s="43"/>
       <c r="I769" s="20"/>
     </row>
     <row r="770">
-      <c r="A770" s="37"/>
+      <c r="A770" s="43"/>
       <c r="I770" s="20"/>
     </row>
     <row r="771">
-      <c r="A771" s="37"/>
+      <c r="A771" s="43"/>
       <c r="I771" s="20"/>
     </row>
     <row r="772">
-      <c r="A772" s="37"/>
+      <c r="A772" s="43"/>
       <c r="I772" s="20"/>
     </row>
     <row r="773">
-      <c r="A773" s="37"/>
+      <c r="A773" s="43"/>
       <c r="I773" s="20"/>
     </row>
     <row r="774">
-      <c r="A774" s="37"/>
+      <c r="A774" s="43"/>
       <c r="I774" s="20"/>
     </row>
     <row r="775">
-      <c r="A775" s="37"/>
+      <c r="A775" s="43"/>
       <c r="I775" s="20"/>
     </row>
     <row r="776">
-      <c r="A776" s="37"/>
+      <c r="A776" s="43"/>
       <c r="I776" s="20"/>
     </row>
     <row r="777">
-      <c r="A777" s="37"/>
+      <c r="A777" s="43"/>
       <c r="I777" s="20"/>
     </row>
     <row r="778">
-      <c r="A778" s="37"/>
+      <c r="A778" s="43"/>
       <c r="I778" s="20"/>
     </row>
     <row r="779">
-      <c r="A779" s="37"/>
+      <c r="A779" s="43"/>
       <c r="I779" s="20"/>
     </row>
     <row r="780">
-      <c r="A780" s="37"/>
+      <c r="A780" s="43"/>
       <c r="I780" s="20"/>
     </row>
     <row r="781">
-      <c r="A781" s="37"/>
+      <c r="A781" s="43"/>
       <c r="I781" s="20"/>
     </row>
     <row r="782">
-      <c r="A782" s="37"/>
+      <c r="A782" s="43"/>
       <c r="I782" s="20"/>
     </row>
     <row r="783">
-      <c r="A783" s="37"/>
+      <c r="A783" s="43"/>
       <c r="I783" s="20"/>
     </row>
     <row r="784">
-      <c r="A784" s="37"/>
+      <c r="A784" s="43"/>
       <c r="I784" s="20"/>
     </row>
     <row r="785">
-      <c r="A785" s="37"/>
+      <c r="A785" s="43"/>
       <c r="I785" s="20"/>
     </row>
     <row r="786">
-      <c r="A786" s="37"/>
+      <c r="A786" s="43"/>
       <c r="I786" s="20"/>
     </row>
     <row r="787">
-      <c r="A787" s="37"/>
+      <c r="A787" s="43"/>
       <c r="I787" s="20"/>
     </row>
     <row r="788">
-      <c r="A788" s="37"/>
+      <c r="A788" s="43"/>
       <c r="I788" s="20"/>
     </row>
     <row r="789">
-      <c r="A789" s="37"/>
+      <c r="A789" s="43"/>
       <c r="I789" s="20"/>
     </row>
     <row r="790">
-      <c r="A790" s="37"/>
+      <c r="A790" s="43"/>
       <c r="I790" s="20"/>
     </row>
     <row r="791">
-      <c r="A791" s="37"/>
+      <c r="A791" s="43"/>
       <c r="I791" s="20"/>
     </row>
     <row r="792">
-      <c r="A792" s="37"/>
+      <c r="A792" s="43"/>
       <c r="I792" s="20"/>
     </row>
     <row r="793">
-      <c r="A793" s="37"/>
+      <c r="A793" s="43"/>
       <c r="I793" s="20"/>
     </row>
     <row r="794">
-      <c r="A794" s="37"/>
+      <c r="A794" s="43"/>
       <c r="I794" s="20"/>
     </row>
     <row r="795">
-      <c r="A795" s="37"/>
+      <c r="A795" s="43"/>
       <c r="I795" s="20"/>
     </row>
     <row r="796">
-      <c r="A796" s="37"/>
+      <c r="A796" s="43"/>
       <c r="I796" s="20"/>
     </row>
     <row r="797">
-      <c r="A797" s="37"/>
+      <c r="A797" s="43"/>
       <c r="I797" s="20"/>
     </row>
     <row r="798">
-      <c r="A798" s="37"/>
+      <c r="A798" s="43"/>
       <c r="I798" s="20"/>
     </row>
     <row r="799">
-      <c r="A799" s="37"/>
+      <c r="A799" s="43"/>
       <c r="I799" s="20"/>
     </row>
     <row r="800">
-      <c r="A800" s="37"/>
+      <c r="A800" s="43"/>
       <c r="I800" s="20"/>
     </row>
     <row r="801">
-      <c r="A801" s="37"/>
+      <c r="A801" s="43"/>
       <c r="I801" s="20"/>
     </row>
     <row r="802">
-      <c r="A802" s="37"/>
+      <c r="A802" s="43"/>
       <c r="I802" s="20"/>
     </row>
     <row r="803">
-      <c r="A803" s="37"/>
+      <c r="A803" s="43"/>
       <c r="I803" s="20"/>
     </row>
     <row r="804">
-      <c r="A804" s="37"/>
+      <c r="A804" s="43"/>
       <c r="I804" s="20"/>
     </row>
     <row r="805">
-      <c r="A805" s="37"/>
+      <c r="A805" s="43"/>
       <c r="I805" s="20"/>
     </row>
     <row r="806">
-      <c r="A806" s="37"/>
+      <c r="A806" s="43"/>
       <c r="I806" s="20"/>
     </row>
     <row r="807">
-      <c r="A807" s="37"/>
+      <c r="A807" s="43"/>
       <c r="I807" s="20"/>
     </row>
     <row r="808">
-      <c r="A808" s="37"/>
+      <c r="A808" s="43"/>
       <c r="I808" s="20"/>
     </row>
     <row r="809">
-      <c r="A809" s="37"/>
+      <c r="A809" s="43"/>
       <c r="I809" s="20"/>
     </row>
     <row r="810">
-      <c r="A810" s="37"/>
+      <c r="A810" s="43"/>
       <c r="I810" s="20"/>
     </row>
     <row r="811">
-      <c r="A811" s="37"/>
+      <c r="A811" s="43"/>
       <c r="I811" s="20"/>
     </row>
     <row r="812">
-      <c r="A812" s="37"/>
+      <c r="A812" s="43"/>
       <c r="I812" s="20"/>
     </row>
     <row r="813">
-      <c r="A813" s="37"/>
+      <c r="A813" s="43"/>
       <c r="I813" s="20"/>
     </row>
     <row r="814">
-      <c r="A814" s="37"/>
+      <c r="A814" s="43"/>
       <c r="I814" s="20"/>
     </row>
     <row r="815">
-      <c r="A815" s="37"/>
+      <c r="A815" s="43"/>
       <c r="I815" s="20"/>
     </row>
     <row r="816">
-      <c r="A816" s="37"/>
+      <c r="A816" s="43"/>
       <c r="I816" s="20"/>
     </row>
     <row r="817">
-      <c r="A817" s="37"/>
+      <c r="A817" s="43"/>
       <c r="I817" s="20"/>
     </row>
     <row r="818">
-      <c r="A818" s="37"/>
+      <c r="A818" s="43"/>
       <c r="I818" s="20"/>
     </row>
     <row r="819">
-      <c r="A819" s="37"/>
+      <c r="A819" s="43"/>
       <c r="I819" s="20"/>
     </row>
     <row r="820">
-      <c r="A820" s="37"/>
+      <c r="A820" s="43"/>
       <c r="I820" s="20"/>
     </row>
     <row r="821">
-      <c r="A821" s="37"/>
+      <c r="A821" s="43"/>
       <c r="I821" s="20"/>
     </row>
     <row r="822">
-      <c r="A822" s="37"/>
+      <c r="A822" s="43"/>
       <c r="I822" s="20"/>
     </row>
     <row r="823">
-      <c r="A823" s="37"/>
+      <c r="A823" s="43"/>
       <c r="I823" s="20"/>
     </row>
     <row r="824">
-      <c r="A824" s="37"/>
+      <c r="A824" s="43"/>
       <c r="I824" s="20"/>
     </row>
     <row r="825">
-      <c r="A825" s="37"/>
+      <c r="A825" s="43"/>
       <c r="I825" s="20"/>
     </row>
     <row r="826">
-      <c r="A826" s="37"/>
+      <c r="A826" s="43"/>
       <c r="I826" s="20"/>
     </row>
     <row r="827">
-      <c r="A827" s="37"/>
+      <c r="A827" s="43"/>
       <c r="I827" s="20"/>
     </row>
     <row r="828">
-      <c r="A828" s="37"/>
+      <c r="A828" s="43"/>
       <c r="I828" s="20"/>
     </row>
     <row r="829">
-      <c r="A829" s="37"/>
+      <c r="A829" s="43"/>
       <c r="I829" s="20"/>
     </row>
     <row r="830">
-      <c r="A830" s="37"/>
+      <c r="A830" s="43"/>
       <c r="I830" s="20"/>
     </row>
     <row r="831">
-      <c r="A831" s="37"/>
+      <c r="A831" s="43"/>
       <c r="I831" s="20"/>
     </row>
     <row r="832">
-      <c r="A832" s="37"/>
+      <c r="A832" s="43"/>
       <c r="I832" s="20"/>
     </row>
     <row r="833">
-      <c r="A833" s="37"/>
+      <c r="A833" s="43"/>
       <c r="I833" s="20"/>
     </row>
     <row r="834">
-      <c r="A834" s="37"/>
+      <c r="A834" s="43"/>
       <c r="I834" s="20"/>
     </row>
     <row r="835">
-      <c r="A835" s="37"/>
+      <c r="A835" s="43"/>
       <c r="I835" s="20"/>
     </row>
     <row r="836">
-      <c r="A836" s="37"/>
+      <c r="A836" s="43"/>
       <c r="I836" s="20"/>
     </row>
     <row r="837">
-      <c r="A837" s="37"/>
+      <c r="A837" s="43"/>
       <c r="I837" s="20"/>
     </row>
     <row r="838">
-      <c r="A838" s="37"/>
+      <c r="A838" s="43"/>
       <c r="I838" s="20"/>
     </row>
     <row r="839">
-      <c r="A839" s="37"/>
+      <c r="A839" s="43"/>
       <c r="I839" s="20"/>
     </row>
     <row r="840">
-      <c r="A840" s="37"/>
+      <c r="A840" s="43"/>
       <c r="I840" s="20"/>
     </row>
     <row r="841">
-      <c r="A841" s="37"/>
+      <c r="A841" s="43"/>
       <c r="I841" s="20"/>
     </row>
     <row r="842">
-      <c r="A842" s="37"/>
+      <c r="A842" s="43"/>
       <c r="I842" s="20"/>
     </row>
     <row r="843">
-      <c r="A843" s="37"/>
+      <c r="A843" s="43"/>
       <c r="I843" s="20"/>
     </row>
     <row r="844">
-      <c r="A844" s="37"/>
+      <c r="A844" s="43"/>
       <c r="I844" s="20"/>
     </row>
     <row r="845">
-      <c r="A845" s="37"/>
+      <c r="A845" s="43"/>
       <c r="I845" s="20"/>
     </row>
     <row r="846">
-      <c r="A846" s="37"/>
+      <c r="A846" s="43"/>
       <c r="I846" s="20"/>
     </row>
     <row r="847">
-      <c r="A847" s="37"/>
+      <c r="A847" s="43"/>
       <c r="I847" s="20"/>
     </row>
     <row r="848">
-      <c r="A848" s="37"/>
+      <c r="A848" s="43"/>
       <c r="I848" s="20"/>
     </row>
     <row r="849">
-      <c r="A849" s="37"/>
+      <c r="A849" s="43"/>
       <c r="I849" s="20"/>
     </row>
     <row r="850">
-      <c r="A850" s="37"/>
+      <c r="A850" s="43"/>
       <c r="I850" s="20"/>
     </row>
     <row r="851">
-      <c r="A851" s="37"/>
+      <c r="A851" s="43"/>
       <c r="I851" s="20"/>
     </row>
     <row r="852">
-      <c r="A852" s="37"/>
+      <c r="A852" s="43"/>
       <c r="I852" s="20"/>
     </row>
     <row r="853">
-      <c r="A853" s="37"/>
+      <c r="A853" s="43"/>
       <c r="I853" s="20"/>
     </row>
     <row r="854">
-      <c r="A854" s="37"/>
+      <c r="A854" s="43"/>
       <c r="I854" s="20"/>
     </row>
     <row r="855">
-      <c r="A855" s="37"/>
+      <c r="A855" s="43"/>
       <c r="I855" s="20"/>
     </row>
     <row r="856">
-      <c r="A856" s="37"/>
+      <c r="A856" s="43"/>
       <c r="I856" s="20"/>
     </row>
     <row r="857">
-      <c r="A857" s="37"/>
+      <c r="A857" s="43"/>
       <c r="I857" s="20"/>
     </row>
     <row r="858">
-      <c r="A858" s="37"/>
+      <c r="A858" s="43"/>
       <c r="I858" s="20"/>
     </row>
     <row r="859">
-      <c r="A859" s="37"/>
+      <c r="A859" s="43"/>
       <c r="I859" s="20"/>
     </row>
     <row r="860">
-      <c r="A860" s="37"/>
+      <c r="A860" s="43"/>
       <c r="I860" s="20"/>
     </row>
     <row r="861">
-      <c r="A861" s="37"/>
+      <c r="A861" s="43"/>
       <c r="I861" s="20"/>
     </row>
     <row r="862">
-      <c r="A862" s="37"/>
+      <c r="A862" s="43"/>
       <c r="I862" s="20"/>
     </row>
     <row r="863">
-      <c r="A863" s="37"/>
+      <c r="A863" s="43"/>
       <c r="I863" s="20"/>
     </row>
     <row r="864">
-      <c r="A864" s="37"/>
+      <c r="A864" s="43"/>
       <c r="I864" s="20"/>
     </row>
     <row r="865">
-      <c r="A865" s="37"/>
+      <c r="A865" s="43"/>
       <c r="I865" s="20"/>
     </row>
     <row r="866">
-      <c r="A866" s="37"/>
+      <c r="A866" s="43"/>
       <c r="I866" s="20"/>
     </row>
     <row r="867">
-      <c r="A867" s="37"/>
+      <c r="A867" s="43"/>
       <c r="I867" s="20"/>
     </row>
     <row r="868">
-      <c r="A868" s="37"/>
+      <c r="A868" s="43"/>
       <c r="I868" s="20"/>
     </row>
     <row r="869">
-      <c r="A869" s="37"/>
+      <c r="A869" s="43"/>
       <c r="I869" s="20"/>
     </row>
     <row r="870">
-      <c r="A870" s="37"/>
+      <c r="A870" s="43"/>
       <c r="I870" s="20"/>
     </row>
     <row r="871">
-      <c r="A871" s="37"/>
+      <c r="A871" s="43"/>
       <c r="I871" s="20"/>
     </row>
     <row r="872">
-      <c r="A872" s="37"/>
+      <c r="A872" s="43"/>
       <c r="I872" s="20"/>
     </row>
     <row r="873">
-      <c r="A873" s="37"/>
+      <c r="A873" s="43"/>
       <c r="I873" s="20"/>
     </row>
     <row r="874">
-      <c r="A874" s="37"/>
+      <c r="A874" s="43"/>
       <c r="I874" s="20"/>
     </row>
     <row r="875">
-      <c r="A875" s="37"/>
+      <c r="A875" s="43"/>
       <c r="I875" s="20"/>
     </row>
     <row r="876">
-      <c r="A876" s="37"/>
+      <c r="A876" s="43"/>
       <c r="I876" s="20"/>
     </row>
     <row r="877">
-      <c r="A877" s="37"/>
+      <c r="A877" s="43"/>
       <c r="I877" s="20"/>
     </row>
     <row r="878">
-      <c r="A878" s="37"/>
+      <c r="A878" s="43"/>
       <c r="I878" s="20"/>
     </row>
     <row r="879">
-      <c r="A879" s="37"/>
+      <c r="A879" s="43"/>
       <c r="I879" s="20"/>
     </row>
     <row r="880">
-      <c r="A880" s="37"/>
+      <c r="A880" s="43"/>
       <c r="I880" s="20"/>
     </row>
     <row r="881">
-      <c r="A881" s="37"/>
+      <c r="A881" s="43"/>
       <c r="I881" s="20"/>
     </row>
     <row r="882">
-      <c r="A882" s="37"/>
+      <c r="A882" s="43"/>
       <c r="I882" s="20"/>
     </row>
     <row r="883">
-      <c r="A883" s="37"/>
+      <c r="A883" s="43"/>
       <c r="I883" s="20"/>
     </row>
     <row r="884">
-      <c r="A884" s="37"/>
+      <c r="A884" s="43"/>
       <c r="I884" s="20"/>
     </row>
     <row r="885">
-      <c r="A885" s="37"/>
+      <c r="A885" s="43"/>
       <c r="I885" s="20"/>
     </row>
     <row r="886">
-      <c r="A886" s="37"/>
+      <c r="A886" s="43"/>
       <c r="I886" s="20"/>
     </row>
     <row r="887">
-      <c r="A887" s="37"/>
+      <c r="A887" s="43"/>
       <c r="I887" s="20"/>
     </row>
     <row r="888">
-      <c r="A888" s="37"/>
+      <c r="A888" s="43"/>
       <c r="I888" s="20"/>
     </row>
     <row r="889">
-      <c r="A889" s="37"/>
+      <c r="A889" s="43"/>
       <c r="I889" s="20"/>
     </row>
     <row r="890">
-      <c r="A890" s="37"/>
+      <c r="A890" s="43"/>
       <c r="I890" s="20"/>
     </row>
     <row r="891">
-      <c r="A891" s="37"/>
+      <c r="A891" s="43"/>
       <c r="I891" s="20"/>
     </row>
     <row r="892">
-      <c r="A892" s="37"/>
+      <c r="A892" s="43"/>
       <c r="I892" s="20"/>
     </row>
     <row r="893">
-      <c r="A893" s="37"/>
+      <c r="A893" s="43"/>
       <c r="I893" s="20"/>
     </row>
     <row r="894">
-      <c r="A894" s="37"/>
+      <c r="A894" s="43"/>
       <c r="I894" s="20"/>
     </row>
     <row r="895">
-      <c r="A895" s="37"/>
+      <c r="A895" s="43"/>
       <c r="I895" s="20"/>
     </row>
     <row r="896">
-      <c r="A896" s="37"/>
+      <c r="A896" s="43"/>
       <c r="I896" s="20"/>
     </row>
     <row r="897">
-      <c r="A897" s="37"/>
+      <c r="A897" s="43"/>
       <c r="I897" s="20"/>
     </row>
     <row r="898">
-      <c r="A898" s="37"/>
+      <c r="A898" s="43"/>
       <c r="I898" s="20"/>
     </row>
     <row r="899">
-      <c r="A899" s="37"/>
+      <c r="A899" s="43"/>
       <c r="I899" s="20"/>
     </row>
     <row r="900">
-      <c r="A900" s="37"/>
+      <c r="A900" s="43"/>
       <c r="I900" s="20"/>
     </row>
     <row r="901">
-      <c r="A901" s="37"/>
+      <c r="A901" s="43"/>
       <c r="I901" s="20"/>
     </row>
     <row r="902">
-      <c r="A902" s="37"/>
+      <c r="A902" s="43"/>
       <c r="I902" s="20"/>
     </row>
     <row r="903">
-      <c r="A903" s="37"/>
+      <c r="A903" s="43"/>
       <c r="I903" s="20"/>
     </row>
     <row r="904">
-      <c r="A904" s="37"/>
+      <c r="A904" s="43"/>
       <c r="I904" s="20"/>
     </row>
     <row r="905">
-      <c r="A905" s="37"/>
+      <c r="A905" s="43"/>
       <c r="I905" s="20"/>
     </row>
     <row r="906">
-      <c r="A906" s="37"/>
+      <c r="A906" s="43"/>
       <c r="I906" s="20"/>
     </row>
     <row r="907">
-      <c r="A907" s="37"/>
+      <c r="A907" s="43"/>
       <c r="I907" s="20"/>
     </row>
     <row r="908">
-      <c r="A908" s="37"/>
+      <c r="A908" s="43"/>
       <c r="I908" s="20"/>
     </row>
     <row r="909">
-      <c r="A909" s="37"/>
+      <c r="A909" s="43"/>
       <c r="I909" s="20"/>
     </row>
     <row r="910">
-      <c r="A910" s="37"/>
+      <c r="A910" s="43"/>
       <c r="I910" s="20"/>
     </row>
     <row r="911">
-      <c r="A911" s="37"/>
+      <c r="A911" s="43"/>
       <c r="I911" s="20"/>
     </row>
     <row r="912">
-      <c r="A912" s="37"/>
+      <c r="A912" s="43"/>
       <c r="I912" s="20"/>
     </row>
     <row r="913">
-      <c r="A913" s="37"/>
+      <c r="A913" s="43"/>
       <c r="I913" s="20"/>
     </row>
     <row r="914">
-      <c r="A914" s="37"/>
+      <c r="A914" s="43"/>
       <c r="I914" s="20"/>
     </row>
     <row r="915">
-      <c r="A915" s="37"/>
+      <c r="A915" s="43"/>
       <c r="I915" s="20"/>
     </row>
     <row r="916">
-      <c r="A916" s="37"/>
+      <c r="A916" s="43"/>
       <c r="I916" s="20"/>
     </row>
     <row r="917">
-      <c r="A917" s="37"/>
+      <c r="A917" s="43"/>
       <c r="I917" s="20"/>
     </row>
     <row r="918">
-      <c r="A918" s="37"/>
+      <c r="A918" s="43"/>
       <c r="I918" s="20"/>
     </row>
     <row r="919">
-      <c r="A919" s="37"/>
+      <c r="A919" s="43"/>
       <c r="I919" s="20"/>
     </row>
     <row r="920">
-      <c r="A920" s="37"/>
+      <c r="A920" s="43"/>
       <c r="I920" s="20"/>
     </row>
     <row r="921">
-      <c r="A921" s="37"/>
+      <c r="A921" s="43"/>
       <c r="I921" s="20"/>
     </row>
     <row r="922">
-      <c r="A922" s="37"/>
+      <c r="A922" s="43"/>
       <c r="I922" s="20"/>
     </row>
     <row r="923">
-      <c r="A923" s="37"/>
+      <c r="A923" s="43"/>
       <c r="I923" s="20"/>
     </row>
     <row r="924">
-      <c r="A924" s="37"/>
+      <c r="A924" s="43"/>
       <c r="I924" s="20"/>
     </row>
     <row r="925">
-      <c r="A925" s="37"/>
+      <c r="A925" s="43"/>
       <c r="I925" s="20"/>
     </row>
     <row r="926">
-      <c r="A926" s="37"/>
+      <c r="A926" s="43"/>
       <c r="I926" s="20"/>
     </row>
     <row r="927">
-      <c r="A927" s="37"/>
+      <c r="A927" s="43"/>
       <c r="I927" s="20"/>
     </row>
     <row r="928">
-      <c r="A928" s="37"/>
+      <c r="A928" s="43"/>
       <c r="I928" s="20"/>
     </row>
     <row r="929">
-      <c r="A929" s="37"/>
+      <c r="A929" s="43"/>
       <c r="I929" s="20"/>
     </row>
     <row r="930">
-      <c r="A930" s="37"/>
+      <c r="A930" s="43"/>
       <c r="I930" s="20"/>
     </row>
     <row r="931">
-      <c r="A931" s="37"/>
+      <c r="A931" s="43"/>
       <c r="I931" s="20"/>
     </row>
     <row r="932">
-      <c r="A932" s="37"/>
+      <c r="A932" s="43"/>
       <c r="I932" s="20"/>
     </row>
     <row r="933">
-      <c r="A933" s="37"/>
+      <c r="A933" s="43"/>
       <c r="I933" s="20"/>
     </row>
     <row r="934">
-      <c r="A934" s="37"/>
+      <c r="A934" s="43"/>
       <c r="I934" s="20"/>
     </row>
     <row r="935">
-      <c r="A935" s="37"/>
+      <c r="A935" s="43"/>
       <c r="I935" s="20"/>
     </row>
     <row r="936">
-      <c r="A936" s="37"/>
+      <c r="A936" s="43"/>
       <c r="I936" s="20"/>
     </row>
     <row r="937">
-      <c r="A937" s="37"/>
+      <c r="A937" s="43"/>
       <c r="I937" s="20"/>
     </row>
     <row r="938">
-      <c r="A938" s="37"/>
+      <c r="A938" s="43"/>
       <c r="I938" s="20"/>
     </row>
     <row r="939">
-      <c r="A939" s="37"/>
+      <c r="A939" s="43"/>
       <c r="I939" s="20"/>
     </row>
     <row r="940">
-      <c r="A940" s="37"/>
+      <c r="A940" s="43"/>
       <c r="I940" s="20"/>
     </row>
     <row r="941">
-      <c r="A941" s="37"/>
+      <c r="A941" s="43"/>
       <c r="I941" s="20"/>
     </row>
     <row r="942">
-      <c r="A942" s="37"/>
+      <c r="A942" s="43"/>
       <c r="I942" s="20"/>
     </row>
     <row r="943">
-      <c r="A943" s="37"/>
+      <c r="A943" s="43"/>
       <c r="I943" s="20"/>
     </row>
     <row r="944">
-      <c r="A944" s="37"/>
+      <c r="A944" s="43"/>
       <c r="I944" s="20"/>
     </row>
     <row r="945">
-      <c r="A945" s="37"/>
+      <c r="A945" s="43"/>
       <c r="I945" s="20"/>
     </row>
     <row r="946">
-      <c r="A946" s="37"/>
+      <c r="A946" s="43"/>
       <c r="I946" s="20"/>
     </row>
     <row r="947">
-      <c r="A947" s="37"/>
+      <c r="A947" s="43"/>
       <c r="I947" s="20"/>
     </row>
     <row r="948">
-      <c r="A948" s="37"/>
+      <c r="A948" s="43"/>
       <c r="I948" s="20"/>
     </row>
     <row r="949">
-      <c r="A949" s="37"/>
+      <c r="A949" s="43"/>
       <c r="I949" s="20"/>
     </row>
     <row r="950">
-      <c r="A950" s="37"/>
+      <c r="A950" s="43"/>
       <c r="I950" s="20"/>
     </row>
     <row r="951">
-      <c r="A951" s="37"/>
+      <c r="A951" s="43"/>
       <c r="I951" s="20"/>
     </row>
     <row r="952">
-      <c r="A952" s="37"/>
+      <c r="A952" s="43"/>
       <c r="I952" s="20"/>
     </row>
     <row r="953">
-      <c r="A953" s="37"/>
+      <c r="A953" s="43"/>
       <c r="I953" s="20"/>
     </row>
     <row r="954">
-      <c r="A954" s="37"/>
+      <c r="A954" s="43"/>
       <c r="I954" s="20"/>
     </row>
     <row r="955">
-      <c r="A955" s="37"/>
+      <c r="A955" s="43"/>
       <c r="I955" s="20"/>
     </row>
     <row r="956">
-      <c r="A956" s="37"/>
+      <c r="A956" s="43"/>
       <c r="I956" s="20"/>
     </row>
     <row r="957">
-      <c r="A957" s="37"/>
+      <c r="A957" s="43"/>
       <c r="I957" s="20"/>
     </row>
     <row r="958">
-      <c r="A958" s="37"/>
+      <c r="A958" s="43"/>
       <c r="I958" s="20"/>
     </row>
     <row r="959">
-      <c r="A959" s="37"/>
+      <c r="A959" s="43"/>
       <c r="I959" s="20"/>
     </row>
     <row r="960">
-      <c r="A960" s="37"/>
+      <c r="A960" s="43"/>
       <c r="I960" s="20"/>
     </row>
     <row r="961">
-      <c r="A961" s="37"/>
+      <c r="A961" s="43"/>
       <c r="I961" s="20"/>
     </row>
     <row r="962">
-      <c r="A962" s="37"/>
+      <c r="A962" s="43"/>
       <c r="I962" s="20"/>
     </row>
     <row r="963">
-      <c r="A963" s="37"/>
+      <c r="A963" s="43"/>
       <c r="I963" s="20"/>
     </row>
     <row r="964">
-      <c r="A964" s="37"/>
+      <c r="A964" s="43"/>
       <c r="I964" s="20"/>
     </row>
     <row r="965">
-      <c r="A965" s="37"/>
+      <c r="A965" s="43"/>
       <c r="I965" s="20"/>
     </row>
     <row r="966">
-      <c r="A966" s="37"/>
+      <c r="A966" s="43"/>
       <c r="I966" s="20"/>
     </row>
     <row r="967">
-      <c r="A967" s="37"/>
+      <c r="A967" s="43"/>
       <c r="I967" s="20"/>
     </row>
     <row r="968">
-      <c r="A968" s="37"/>
+      <c r="A968" s="43"/>
       <c r="I968" s="20"/>
     </row>
     <row r="969">
-      <c r="A969" s="37"/>
+      <c r="A969" s="43"/>
       <c r="I969" s="20"/>
     </row>
     <row r="970">
-      <c r="A970" s="37"/>
+      <c r="A970" s="43"/>
       <c r="I970" s="20"/>
     </row>
     <row r="971">
-      <c r="A971" s="37"/>
+      <c r="A971" s="43"/>
       <c r="I971" s="20"/>
     </row>
     <row r="972">
-      <c r="A972" s="37"/>
+      <c r="A972" s="43"/>
       <c r="I972" s="20"/>
     </row>
     <row r="973">
-      <c r="A973" s="37"/>
+      <c r="A973" s="43"/>
       <c r="I973" s="20"/>
     </row>
     <row r="974">
-      <c r="A974" s="37"/>
+      <c r="A974" s="43"/>
       <c r="I974" s="20"/>
     </row>
     <row r="975">
-      <c r="A975" s="37"/>
+      <c r="A975" s="43"/>
       <c r="I975" s="20"/>
     </row>
     <row r="976">
-      <c r="A976" s="37"/>
+      <c r="A976" s="43"/>
       <c r="I976" s="20"/>
     </row>
     <row r="977">
-      <c r="A977" s="37"/>
+      <c r="A977" s="43"/>
       <c r="I977" s="20"/>
     </row>
     <row r="978">
-      <c r="A978" s="37"/>
+      <c r="A978" s="43"/>
       <c r="I978" s="20"/>
     </row>
     <row r="979">
-      <c r="A979" s="37"/>
+      <c r="A979" s="43"/>
       <c r="I979" s="20"/>
     </row>
     <row r="980">
-      <c r="A980" s="37"/>
+      <c r="A980" s="43"/>
       <c r="I980" s="20"/>
     </row>
     <row r="981">
-      <c r="A981" s="37"/>
+      <c r="A981" s="43"/>
       <c r="I981" s="20"/>
     </row>
     <row r="982">
-      <c r="A982" s="37"/>
+      <c r="A982" s="43"/>
       <c r="I982" s="20"/>
     </row>
     <row r="983">
-      <c r="A983" s="37"/>
+      <c r="A983" s="43"/>
       <c r="I983" s="20"/>
     </row>
     <row r="984">
-      <c r="A984" s="37"/>
+      <c r="A984" s="43"/>
       <c r="I984" s="20"/>
     </row>
     <row r="985">
-      <c r="A985" s="37"/>
+      <c r="A985" s="43"/>
       <c r="I985" s="20"/>
     </row>
     <row r="986">
-      <c r="A986" s="37"/>
+      <c r="A986" s="43"/>
       <c r="I986" s="20"/>
     </row>
     <row r="987">
-      <c r="A987" s="37"/>
+      <c r="A987" s="43"/>
       <c r="I987" s="20"/>
     </row>
     <row r="988">
-      <c r="A988" s="37"/>
+      <c r="A988" s="43"/>
       <c r="I988" s="20"/>
     </row>
     <row r="989">
-      <c r="A989" s="37"/>
+      <c r="A989" s="43"/>
       <c r="I989" s="20"/>
     </row>
     <row r="990">
-      <c r="A990" s="37"/>
+      <c r="A990" s="43"/>
       <c r="I990" s="20"/>
     </row>
     <row r="991">
-      <c r="A991" s="37"/>
+      <c r="A991" s="43"/>
       <c r="I991" s="20"/>
     </row>
     <row r="992">
-      <c r="A992" s="37"/>
+      <c r="A992" s="43"/>
       <c r="I992" s="20"/>
     </row>
     <row r="993">
-      <c r="A993" s="37"/>
+      <c r="A993" s="43"/>
       <c r="I993" s="20"/>
     </row>
     <row r="994">
-      <c r="A994" s="37"/>
+      <c r="A994" s="43"/>
       <c r="I994" s="20"/>
     </row>
     <row r="995">
-      <c r="A995" s="37"/>
+      <c r="A995" s="43"/>
       <c r="I995" s="20"/>
     </row>
     <row r="996">
-      <c r="A996" s="37"/>
+      <c r="A996" s="43"/>
       <c r="I996" s="20"/>
     </row>
     <row r="997">
-      <c r="A997" s="37"/>
+      <c r="A997" s="43"/>
       <c r="I997" s="20"/>
     </row>
     <row r="998">
-      <c r="A998" s="37"/>
+      <c r="A998" s="43"/>
       <c r="I998" s="20"/>
     </row>
     <row r="999">
-      <c r="A999" s="37"/>
+      <c r="A999" s="43"/>
       <c r="I999" s="20"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="37"/>
+      <c r="A1000" s="43"/>
       <c r="I1000" s="20"/>
     </row>
   </sheetData>

--- a/src/data/AFCARS.xlsx
+++ b/src/data/AFCARS.xlsx
@@ -387,16 +387,16 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -411,7 +411,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -420,7 +420,7 @@
     <xf borderId="2" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -429,7 +429,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -483,13 +483,13 @@
     <xf borderId="6" fillId="5" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="5" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="5" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -498,7 +498,7 @@
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
